--- a/Legge di Hooke.xlsx
+++ b/Legge di Hooke.xlsx
@@ -843,9 +843,6 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="3">
@@ -866,9 +863,6 @@
       <c r="F2" s="4">
         <v>1.26</v>
       </c>
-      <c r="G2" s="4">
-        <v>1.e-002</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="3">
@@ -886,7 +880,9 @@
       <c r="E3" s="4">
         <v>1.4142135619999999e-002</v>
       </c>
-      <c r="F3" s="6"/>
+      <c r="F3" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="G3" s="6"/>
     </row>
     <row r="4">
@@ -905,7 +901,9 @@
       <c r="E4" s="4">
         <v>1.4142135619999999e-002</v>
       </c>
-      <c r="F4" s="6"/>
+      <c r="F4" s="4">
+        <v>1.e-002</v>
+      </c>
       <c r="G4" s="6"/>
     </row>
     <row r="5">

--- a/Legge di Hooke.xlsx
+++ b/Legge di Hooke.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Misure statiche 1" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,7 +16,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Molle in serie'!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Molle in serie'!$A$1:$G$1</definedName>
   </definedNames>
   <calcPr/>
   <extLst>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>m[g]</t>
   </si>
@@ -86,6 +85,15 @@
   </si>
   <si>
     <t>Dev.std.med</t>
+  </si>
+  <si>
+    <t>m[kg]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">l [m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Err.l [m]</t>
   </si>
   <si>
     <t xml:space="preserve">Velocity (m/s) Run #6</t>
@@ -249,7 +257,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -292,6 +300,7 @@
     <xf fontId="0" fillId="4" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="4" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="1" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -1051,7 +1060,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" ht="39.75">
+    <row r="1" ht="25.5">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1079,7 +1088,7 @@
         <v>1.23</v>
       </c>
       <c r="C2" s="4">
-        <f t="shared" ref="C2:C6" si="0">$E$2-B2</f>
+        <f>$E$2-B2</f>
         <v>3.0000000000000027e-002</v>
       </c>
       <c r="D2" s="4">
@@ -1100,7 +1109,7 @@
         <v>1.1899999999999999</v>
       </c>
       <c r="C3" s="4">
-        <f t="shared" si="0"/>
+        <f>$E$2-B3</f>
         <v>7.0000000000000062e-002</v>
       </c>
       <c r="D3" s="4">
@@ -1117,7 +1126,7 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="C4" s="4">
-        <f t="shared" si="0"/>
+        <f>$E$2-B4</f>
         <v>0.10000000000000009</v>
       </c>
       <c r="D4" s="4">
@@ -1134,7 +1143,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C5" s="4">
-        <f t="shared" si="0"/>
+        <f>$E$2-B5</f>
         <v>0.13000000000000012</v>
       </c>
       <c r="D5" s="4">
@@ -1151,7 +1160,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="C6" s="4">
-        <f t="shared" si="0"/>
+        <f>$E$2-B6</f>
         <v>0.15999999999999992</v>
       </c>
       <c r="D6" s="4">
@@ -1220,11 +1229,11 @@
         <v>1.1100000000000001</v>
       </c>
       <c r="C2" s="6">
-        <f t="shared" ref="C2:C6" si="1">$E$2-B2</f>
+        <f t="shared" ref="C2:C6" si="0">$E$2-B2</f>
         <v>5.9999999999999831e-002</v>
       </c>
       <c r="D2" s="6">
-        <f t="shared" ref="D2:D6" si="2">0.01*SQRT(2)</f>
+        <f t="shared" ref="D2:D6" si="1">0.01*SQRT(2)</f>
         <v>1.4142135623730952e-002</v>
       </c>
       <c r="E2" s="4">
@@ -1239,11 +1248,11 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="C3" s="6">
+        <f t="shared" si="0"/>
+        <v>7.9999999999999849e-002</v>
+      </c>
+      <c r="D3" s="6">
         <f t="shared" si="1"/>
-        <v>7.9999999999999849e-002</v>
-      </c>
-      <c r="D3" s="6">
-        <f t="shared" si="2"/>
         <v>1.4142135623730952e-002</v>
       </c>
       <c r="E3" s="6"/>
@@ -1256,11 +1265,11 @@
         <v>1.0600000000000001</v>
       </c>
       <c r="C4" s="6">
+        <f t="shared" si="0"/>
+        <v>0.10999999999999988</v>
+      </c>
+      <c r="D4" s="6">
         <f t="shared" si="1"/>
-        <v>0.10999999999999988</v>
-      </c>
-      <c r="D4" s="6">
-        <f t="shared" si="2"/>
         <v>1.4142135623730952e-002</v>
       </c>
       <c r="E4" s="6"/>
@@ -1273,11 +1282,11 @@
         <v>1.01</v>
       </c>
       <c r="C5" s="6">
+        <f t="shared" si="0"/>
+        <v>0.15999999999999992</v>
+      </c>
+      <c r="D5" s="6">
         <f t="shared" si="1"/>
-        <v>0.15999999999999992</v>
-      </c>
-      <c r="D5" s="6">
-        <f t="shared" si="2"/>
         <v>1.4142135623730952e-002</v>
       </c>
       <c r="E5" s="6"/>
@@ -1290,11 +1299,11 @@
         <v>0.94999999999999996</v>
       </c>
       <c r="C6" s="6">
+        <f t="shared" si="0"/>
+        <v>0.21999999999999997</v>
+      </c>
+      <c r="D6" s="6">
         <f t="shared" si="1"/>
-        <v>0.21999999999999997</v>
-      </c>
-      <c r="D6" s="6">
-        <f t="shared" si="2"/>
         <v>1.4142135623730952e-002</v>
       </c>
       <c r="E6" s="6"/>
@@ -1396,7 +1405,7 @@
         <v>3.4269706290817735e-004</v>
       </c>
       <c r="K2">
-        <f t="shared" ref="K2:K7" si="3">I2^2</f>
+        <f t="shared" ref="K2:K7" si="2">I2^2</f>
         <v>6.7075485130871235e-002</v>
       </c>
       <c r="L2" s="15" t="s">
@@ -1438,7 +1447,7 @@
         <v>3.8366081728098282e-004</v>
       </c>
       <c r="K3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.18601499145723874</v>
       </c>
       <c r="L3" s="15" t="s">
@@ -1480,7 +1489,7 @@
         <v>6.3645316027282251e-004</v>
       </c>
       <c r="K4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.31113123214987526</v>
       </c>
       <c r="L4" s="15" t="s">
@@ -1522,7 +1531,7 @@
         <v>4.4533067242994513e-004</v>
       </c>
       <c r="K5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.42731711305976344</v>
       </c>
       <c r="L5" s="15" t="s">
@@ -1564,7 +1573,7 @@
         <v>3.0745106222261452e-004</v>
       </c>
       <c r="K6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.56043505251155346</v>
       </c>
       <c r="L6" s="15" t="s">
@@ -1588,15 +1597,15 @@
         <v>11.264399999999998</v>
       </c>
       <c r="E7" s="18">
-        <f t="shared" ref="E7:G7" si="4">AVERAGE(E2:E6)</f>
+        <f t="shared" ref="E7:G7" si="3">AVERAGE(E2:E6)</f>
         <v>9.6117999999999988</v>
       </c>
       <c r="F7" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>8.3930000000000007</v>
       </c>
       <c r="G7" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>7.6345999999999989</v>
       </c>
       <c r="H7">
@@ -1612,7 +1621,7 @@
         <v>1.6455760778816024e-003</v>
       </c>
       <c r="K7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.67730949012262742</v>
       </c>
       <c r="L7" s="15" t="s">
@@ -1665,15 +1674,15 @@
         <v>2.3042569301186932e-002</v>
       </c>
       <c r="E9" s="21">
-        <f t="shared" ref="E9:G9" si="5">E8/SQRT(5)</f>
+        <f t="shared" ref="E9:G9" si="4">E8/SQRT(5)</f>
         <v>1.0016985574512895e-002</v>
       </c>
       <c r="F9" s="21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>4.6043457732887032e-003</v>
       </c>
       <c r="G9" s="21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1.8548854412065423e-002</v>
       </c>
     </row>
@@ -1692,37 +1701,44 @@
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
   <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col bestFit="1" min="1" max="1" width="5.203125"/>
+    <col bestFit="1" min="2" max="2" width="8.29296875"/>
+    <col bestFit="1" min="3" max="3" width="4.29296875"/>
+    <col bestFit="1" min="4" max="4" width="9.375"/>
+    <col bestFit="1" min="5" max="5" width="13.703125"/>
+  </cols>
   <sheetData>
     <row r="1" ht="39.75">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="8" t="s">
+      <c r="A1" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="C1" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="22" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4">
-        <v>70</v>
+      <c r="A2" s="3">
+        <v>7.0000000000000007e-002</v>
       </c>
       <c r="B2" s="4">
         <v>0.98999999999999999</v>
       </c>
       <c r="C2" s="6">
-        <f t="shared" ref="C2:C6" si="6">$E$2-B2</f>
+        <f t="shared" ref="C2:C6" si="5">$E$2-B2</f>
         <v>9.000000000000008e-002</v>
       </c>
       <c r="D2" s="6">
-        <f t="shared" ref="D2:D6" si="7">0.01*SQRT(2)</f>
+        <f t="shared" ref="D2:D6" si="6">0.01*SQRT(2)</f>
         <v>1.4142135623730952e-002</v>
       </c>
       <c r="E2" s="4">
@@ -1730,67 +1746,67 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4">
-        <v>100</v>
+      <c r="A3" s="3">
+        <v>0.10000000000000001</v>
       </c>
       <c r="B3" s="4">
         <v>0.93999999999999995</v>
       </c>
       <c r="C3" s="6">
+        <f t="shared" si="5"/>
+        <v>0.14000000000000012</v>
+      </c>
+      <c r="D3" s="6">
         <f t="shared" si="6"/>
-        <v>0.14000000000000012</v>
-      </c>
-      <c r="D3" s="6">
-        <f t="shared" si="7"/>
         <v>1.4142135623730952e-002</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4">
-        <v>120</v>
+      <c r="A4" s="3">
+        <v>0.12</v>
       </c>
       <c r="B4" s="4">
         <v>0.91000000000000003</v>
       </c>
       <c r="C4" s="6">
+        <f t="shared" si="5"/>
+        <v>0.17000000000000004</v>
+      </c>
+      <c r="D4" s="6">
         <f t="shared" si="6"/>
-        <v>0.17000000000000004</v>
-      </c>
-      <c r="D4" s="6">
-        <f t="shared" si="7"/>
         <v>1.4142135623730952e-002</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4">
-        <v>150</v>
+      <c r="A5" s="3">
+        <v>0.14999999999999999</v>
       </c>
       <c r="B5" s="4">
         <v>0.87</v>
       </c>
       <c r="C5" s="6">
+        <f t="shared" si="5"/>
+        <v>0.21000000000000008</v>
+      </c>
+      <c r="D5" s="6">
         <f t="shared" si="6"/>
-        <v>0.21000000000000008</v>
-      </c>
-      <c r="D5" s="6">
-        <f t="shared" si="7"/>
         <v>1.4142135623730952e-002</v>
       </c>
       <c r="E5" s="6"/>
     </row>
     <row r="6">
-      <c r="A6" s="4">
-        <v>200</v>
-      </c>
-      <c r="B6" s="4">
+      <c r="A6" s="3">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="B6" s="7">
         <v>0.80000000000000004</v>
       </c>
       <c r="C6" s="6">
+        <f t="shared" si="5"/>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="D6" s="6">
         <f t="shared" si="6"/>
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="D6" s="6">
-        <f t="shared" si="7"/>
         <v>1.4142135623730952e-002</v>
       </c>
       <c r="E6" s="6"/>
@@ -1804,7 +1820,7 @@
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
-      <c r="G8" s="22"/>
+      <c r="G8" s="23"/>
     </row>
     <row r="9">
       <c r="D9" s="6"/>
@@ -1817,13 +1833,6 @@
       <c r="F10" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="m[g]"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
@@ -1835,39 +1844,43 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="16.265625"/>
+    <col bestFit="1" customWidth="1" min="1" max="1" width="5.203125"/>
+    <col bestFit="1" min="2" max="2" width="8.29296875"/>
+    <col bestFit="1" min="3" max="3" width="4.29296875"/>
+    <col bestFit="1" min="4" max="4" width="10.29296875"/>
+    <col bestFit="1" min="5" max="5" width="13.703125"/>
   </cols>
   <sheetData>
     <row r="1" ht="26.25">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
+      <c r="A1" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>10</v>
+      <c r="C1" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4">
-        <v>100</v>
+      <c r="A2" s="3">
+        <v>0.10000000000000001</v>
       </c>
       <c r="B2" s="4">
         <v>1.25</v>
       </c>
       <c r="C2" s="6">
-        <f t="shared" ref="C2:C7" si="8">$E$2-B2</f>
+        <f t="shared" ref="C2:C7" si="7">$E$2-B2</f>
         <v>2.0000000000000018e-002</v>
       </c>
       <c r="D2" s="6">
-        <f t="shared" ref="D2:D7" si="9">0.01*SQRT(2)</f>
+        <f t="shared" ref="D2:D7" si="8">0.01*SQRT(2)</f>
         <v>1.4142135623730952e-002</v>
       </c>
       <c r="E2" s="4">
@@ -1875,86 +1888,86 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4">
-        <v>200</v>
+      <c r="A3" s="3">
+        <v>0.20000000000000001</v>
       </c>
       <c r="B3" s="4">
         <v>1.23</v>
       </c>
       <c r="C3" s="6">
+        <f t="shared" si="7"/>
+        <v>4.0000000000000036e-002</v>
+      </c>
+      <c r="D3" s="6">
         <f t="shared" si="8"/>
-        <v>4.0000000000000036e-002</v>
-      </c>
-      <c r="D3" s="6">
-        <f t="shared" si="9"/>
         <v>1.4142135623730952e-002</v>
       </c>
       <c r="E3" s="6"/>
     </row>
     <row r="4">
-      <c r="A4" s="4">
-        <v>500</v>
+      <c r="A4" s="3">
+        <v>0.5</v>
       </c>
       <c r="B4" s="4">
         <v>1.1799999999999999</v>
       </c>
       <c r="C4" s="6">
+        <f t="shared" si="7"/>
+        <v>9.000000000000008e-002</v>
+      </c>
+      <c r="D4" s="6">
         <f t="shared" si="8"/>
-        <v>9.000000000000008e-002</v>
-      </c>
-      <c r="D4" s="6">
-        <f t="shared" si="9"/>
         <v>1.4142135623730952e-002</v>
       </c>
       <c r="E4" s="6"/>
     </row>
     <row r="5">
-      <c r="A5" s="4">
-        <v>700</v>
+      <c r="A5" s="3">
+        <v>0.69999999999999996</v>
       </c>
       <c r="B5" s="4">
         <v>1.1499999999999999</v>
       </c>
       <c r="C5" s="6">
+        <f t="shared" si="7"/>
+        <v>0.12000000000000011</v>
+      </c>
+      <c r="D5" s="6">
         <f t="shared" si="8"/>
-        <v>0.12000000000000011</v>
-      </c>
-      <c r="D5" s="6">
-        <f t="shared" si="9"/>
         <v>1.4142135623730952e-002</v>
       </c>
       <c r="E5" s="6"/>
     </row>
     <row r="6">
-      <c r="A6" s="4">
-        <v>900</v>
+      <c r="A6" s="3">
+        <v>0.90000000000000002</v>
       </c>
       <c r="B6" s="4">
         <v>1.1200000000000001</v>
       </c>
       <c r="C6" s="6">
+        <f t="shared" si="7"/>
+        <v>0.14999999999999991</v>
+      </c>
+      <c r="D6" s="6">
         <f t="shared" si="8"/>
-        <v>0.14999999999999991</v>
-      </c>
-      <c r="D6" s="6">
-        <f t="shared" si="9"/>
         <v>1.4142135623730952e-002</v>
       </c>
       <c r="E6" s="6"/>
     </row>
     <row r="7">
-      <c r="A7" s="4">
-        <v>1000</v>
-      </c>
-      <c r="B7" s="4">
+      <c r="A7" s="3">
+        <v>1</v>
+      </c>
+      <c r="B7" s="7">
         <v>1.1000000000000001</v>
       </c>
       <c r="C7" s="6">
+        <f t="shared" si="7"/>
+        <v>0.16999999999999993</v>
+      </c>
+      <c r="D7" s="6">
         <f t="shared" si="8"/>
-        <v>0.16999999999999993</v>
-      </c>
-      <c r="D7" s="6">
-        <f t="shared" si="9"/>
         <v>1.4142135623730952e-002</v>
       </c>
       <c r="E7" s="6"/>
@@ -1978,22 +1991,22 @@
   <sheetData>
     <row r="1" ht="38.25">
       <c r="A1" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G1" s="4">
         <v>1.1299999999999999</v>
@@ -2005,7 +2018,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C2">
-        <f t="shared" ref="C2:C9" si="10">B2-$G$1</f>
+        <f t="shared" ref="C2:C9" si="9">B2-$G$1</f>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D2" s="4">
@@ -2026,7 +2039,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D3" s="4">
@@ -2047,7 +2060,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D4" s="4">
@@ -2068,7 +2081,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D5" s="4">
@@ -2089,7 +2102,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D6" s="4">
@@ -2110,7 +2123,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D7" s="4">
@@ -2131,7 +2144,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D8" s="4">
@@ -2152,7 +2165,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D9" s="4">
@@ -2173,7 +2186,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C10">
-        <f t="shared" ref="C10:C73" si="11">B10-$G$1</f>
+        <f t="shared" ref="C10:C73" si="10">B10-$G$1</f>
         <v>0</v>
       </c>
       <c r="D10" s="4">
@@ -2194,7 +2207,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="D11" s="4">
@@ -2215,7 +2228,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="D12" s="4">
@@ -2236,7 +2249,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="D13" s="4">
@@ -2257,7 +2270,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="D14" s="4">
@@ -2278,7 +2291,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D15" s="4">
@@ -2299,7 +2312,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D16" s="4">
@@ -2320,7 +2333,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D17" s="4">
@@ -2341,7 +2354,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C18">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D18" s="4">
@@ -2362,7 +2375,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D19" s="4">
@@ -2383,7 +2396,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C20">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D20" s="4">
@@ -2404,7 +2417,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C21">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D21" s="4">
@@ -2425,7 +2438,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D22" s="4">
@@ -2446,7 +2459,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C23">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D23" s="4">
@@ -2467,7 +2480,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D24" s="4">
@@ -2488,7 +2501,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D25" s="4">
@@ -2509,7 +2522,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C26">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="D26" s="4">
@@ -2530,7 +2543,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C27">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="D27" s="4">
@@ -2551,7 +2564,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C28">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="D28" s="4">
@@ -2560,7 +2573,7 @@
       <c r="E28" s="4">
         <v>-7.0000000000000007e-002</v>
       </c>
-      <c r="F28" s="23">
+      <c r="F28" s="24">
         <v>4.2000000000000002e-004</v>
       </c>
     </row>
@@ -2572,7 +2585,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C29">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="D29" s="4">
@@ -2593,7 +2606,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C30">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="D30" s="4">
@@ -2614,7 +2627,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C31">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="D31" s="4">
@@ -2635,7 +2648,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="D32" s="4">
@@ -2656,7 +2669,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C33">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D33" s="4">
@@ -2677,7 +2690,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C34">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D34" s="4">
@@ -2698,7 +2711,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C35">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D35" s="4">
@@ -2719,7 +2732,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D36" s="4">
@@ -2740,7 +2753,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C37">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D37" s="4">
@@ -2761,7 +2774,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C38">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D38" s="4">
@@ -2782,7 +2795,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C39">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D39" s="4">
@@ -2803,7 +2816,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C40">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D40" s="4">
@@ -2824,7 +2837,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C41">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D41" s="4">
@@ -2845,7 +2858,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C42">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D42" s="4">
@@ -2866,7 +2879,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C43">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D43" s="4">
@@ -2887,7 +2900,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C44">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D44" s="4">
@@ -2908,7 +2921,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="D45" s="4">
@@ -2929,7 +2942,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="D46" s="4">
@@ -2950,7 +2963,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C47">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="D47" s="4">
@@ -2971,7 +2984,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C48">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="D48" s="4">
@@ -2992,7 +3005,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C49">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="D49" s="4">
@@ -3013,7 +3026,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C50">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="D50" s="4">
@@ -3034,7 +3047,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C51">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="D51" s="4">
@@ -3055,7 +3068,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C52">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D52" s="4">
@@ -3076,7 +3089,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C53">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D53" s="4">
@@ -3097,7 +3110,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D54" s="4">
@@ -3118,7 +3131,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C55">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D55" s="4">
@@ -3139,7 +3152,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C56">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D56" s="4">
@@ -3160,7 +3173,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C57">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D57" s="4">
@@ -3181,7 +3194,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C58">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D58" s="4">
@@ -3202,7 +3215,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C59">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D59" s="4">
@@ -3223,7 +3236,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C60">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D60" s="4">
@@ -3244,7 +3257,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C61">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D61" s="4">
@@ -3265,7 +3278,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C62">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D62" s="4">
@@ -3286,7 +3299,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D63" s="4">
@@ -3307,7 +3320,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C64">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D64" s="4">
@@ -3328,7 +3341,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C65">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="D65" s="4">
@@ -3349,7 +3362,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C66">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="D66" s="4">
@@ -3370,7 +3383,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C67">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="D67" s="4">
@@ -3391,7 +3404,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C68">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="D68" s="4">
@@ -3412,7 +3425,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C69">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="D69" s="4">
@@ -3433,7 +3446,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C70">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="D70" s="4">
@@ -3454,7 +3467,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C71">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D71" s="4">
@@ -3475,7 +3488,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C72">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D72" s="4">
@@ -3496,7 +3509,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C73">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D73" s="4">
@@ -3517,7 +3530,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C74">
-        <f t="shared" ref="C74:C99" si="12">B74-$G$1</f>
+        <f t="shared" ref="C74:C99" si="11">B74-$G$1</f>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D74" s="4">
@@ -3538,7 +3551,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C75">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D75" s="4">
@@ -3559,7 +3572,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C76">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D76" s="4">
@@ -3580,7 +3593,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C77">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D77" s="4">
@@ -3601,7 +3614,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C78">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D78" s="4">
@@ -3622,7 +3635,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C79">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D79" s="4">
@@ -3643,7 +3656,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C80">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D80" s="4">
@@ -3664,7 +3677,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C81">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D81" s="4">
@@ -3685,7 +3698,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C82">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D82" s="4">
@@ -3706,7 +3719,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D83" s="4">
@@ -3727,7 +3740,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C84">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D84" s="4">
@@ -3748,7 +3761,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C85">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D85" s="4">
@@ -3769,7 +3782,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C86">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D86" s="4">
@@ -3790,7 +3803,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C87">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D87" s="4">
@@ -3811,7 +3824,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C88">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D88" s="4">
@@ -3832,7 +3845,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C89">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D89" s="4">
@@ -3853,7 +3866,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D90" s="4">
@@ -3874,7 +3887,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C91">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D91" s="4">
@@ -3895,7 +3908,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C92">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D92" s="4">
@@ -3916,7 +3929,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C93">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D93" s="4">
@@ -3937,7 +3950,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C94">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D94" s="4">
@@ -3958,7 +3971,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C95">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D95" s="4">
@@ -3979,7 +3992,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C96">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D96" s="4">
@@ -4000,7 +4013,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C97">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D97" s="4">
@@ -4021,7 +4034,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C98">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D98" s="4">
@@ -4042,7 +4055,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C99">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D99" s="4">
@@ -4063,7 +4076,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C100">
-        <f t="shared" ref="C100:C163" si="13">B100-$G$1</f>
+        <f t="shared" ref="C100:C163" si="12">B100-$G$1</f>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D100" s="4">
@@ -4084,7 +4097,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C101">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D101" s="4">
@@ -4105,7 +4118,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D102" s="4">
@@ -4126,7 +4139,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C103">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D103" s="4">
@@ -4147,7 +4160,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C104">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D104" s="4">
@@ -4168,7 +4181,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D105" s="4">
@@ -4189,7 +4202,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C106">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D106" s="4">
@@ -4210,7 +4223,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C107">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D107" s="4">
@@ -4231,7 +4244,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C108">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D108" s="4">
@@ -4252,7 +4265,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C109">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D109" s="4">
@@ -4273,7 +4286,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C110">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D110" s="4">
@@ -4294,7 +4307,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C111">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D111" s="4">
@@ -4315,7 +4328,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C112">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D112" s="4">
@@ -4336,7 +4349,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C113">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D113" s="4">
@@ -4357,7 +4370,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C114">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D114" s="4">
@@ -4378,7 +4391,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C115">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D115" s="4">
@@ -4399,7 +4412,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C116">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D116" s="4">
@@ -4420,7 +4433,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C117">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D117" s="4">
@@ -4441,7 +4454,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C118">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D118" s="4">
@@ -4462,7 +4475,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C119">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D119" s="4">
@@ -4483,7 +4496,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C120">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D120" s="4">
@@ -4504,7 +4517,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C121">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D121" s="4">
@@ -4525,7 +4538,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C122">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D122" s="4">
@@ -4546,7 +4559,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C123">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D123" s="4">
@@ -4567,7 +4580,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C124">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D124" s="4">
@@ -4588,7 +4601,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C125">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D125" s="4">
@@ -4609,7 +4622,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C126">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D126" s="4">
@@ -4630,7 +4643,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C127">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D127" s="4">
@@ -4651,7 +4664,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C128">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D128" s="4">
@@ -4672,7 +4685,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C129">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D129" s="4">
@@ -4693,7 +4706,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C130">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D130" s="4">
@@ -4714,7 +4727,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C131">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D131" s="4">
@@ -4735,7 +4748,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C132">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D132" s="4">
@@ -4756,7 +4769,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C133">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D133" s="4">
@@ -4777,7 +4790,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C134">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D134" s="4">
@@ -4798,7 +4811,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C135">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D135" s="4">
@@ -4819,7 +4832,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C136">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D136" s="4">
@@ -4840,7 +4853,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C137">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D137" s="4">
@@ -4861,7 +4874,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C138">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D138" s="4">
@@ -4882,7 +4895,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C139">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D139" s="4">
@@ -4903,7 +4916,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C140">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D140" s="4">
@@ -4924,7 +4937,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C141">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D141" s="4">
@@ -4945,7 +4958,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C142">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D142" s="4">
@@ -4966,7 +4979,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C143">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D143" s="4">
@@ -4987,7 +5000,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C144">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D144" s="4">
@@ -5008,7 +5021,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C145">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D145" s="4">
@@ -5029,7 +5042,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C146">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D146" s="4">
@@ -5050,7 +5063,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C147">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D147" s="4">
@@ -5071,7 +5084,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C148">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D148" s="4">
@@ -5092,7 +5105,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C149">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D149" s="4">
@@ -5113,7 +5126,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C150">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D150" s="4">
@@ -5134,7 +5147,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C151">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D151" s="4">
@@ -5155,7 +5168,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C152">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D152" s="4">
@@ -5176,7 +5189,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C153">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D153" s="4">
@@ -5197,7 +5210,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C154">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D154" s="4">
@@ -5218,7 +5231,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C155">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D155" s="4">
@@ -5239,7 +5252,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D156" s="4">
@@ -5260,7 +5273,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C157">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D157" s="4">
@@ -5281,7 +5294,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C158">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D158" s="4">
@@ -5302,7 +5315,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C159">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D159" s="4">
@@ -5323,7 +5336,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C160">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D160" s="4">
@@ -5344,7 +5357,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C161">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D161" s="4">
@@ -5365,7 +5378,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C162">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D162" s="4">
@@ -5386,7 +5399,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C163">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D163" s="4">
@@ -5407,7 +5420,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C164">
-        <f t="shared" ref="C164:C227" si="14">B164-$G$1</f>
+        <f t="shared" ref="C164:C227" si="13">B164-$G$1</f>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D164" s="4">
@@ -5428,7 +5441,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C165">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D165" s="4">
@@ -5449,7 +5462,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C166">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D166" s="4">
@@ -5470,7 +5483,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C167">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D167" s="4">
@@ -5491,7 +5504,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C168">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D168" s="4">
@@ -5512,13 +5525,13 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C169">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D169" s="4">
         <v>3.3399999999999999</v>
       </c>
-      <c r="E169" s="23">
+      <c r="E169" s="24">
         <v>4.66e-004</v>
       </c>
       <c r="F169" s="4">
@@ -5526,14 +5539,14 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="23">
+      <c r="A170" s="24">
         <v>4.66e-004</v>
       </c>
       <c r="B170" s="4">
         <v>1.1399999999999999</v>
       </c>
       <c r="C170">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D170" s="4">
@@ -5554,7 +5567,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C171">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D171" s="4">
@@ -5575,7 +5588,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C172">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D172" s="4">
@@ -5596,7 +5609,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C173">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D173" s="4">
@@ -5617,7 +5630,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C174">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D174" s="4">
@@ -5638,7 +5651,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C175">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D175" s="4">
@@ -5659,7 +5672,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C176">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D176" s="4">
@@ -5680,7 +5693,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C177">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D177" s="4">
@@ -5701,7 +5714,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C178">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D178" s="4">
@@ -5722,7 +5735,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C179">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D179" s="4">
@@ -5743,7 +5756,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C180">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D180" s="4">
@@ -5764,7 +5777,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C181">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D181" s="4">
@@ -5785,7 +5798,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C182">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D182" s="4">
@@ -5806,7 +5819,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C183">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D183" s="4">
@@ -5827,7 +5840,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C184">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D184" s="4">
@@ -5848,7 +5861,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C185">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D185" s="4">
@@ -5869,7 +5882,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C186">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D186" s="4">
@@ -5890,7 +5903,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C187">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D187" s="4">
@@ -5911,13 +5924,13 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C188">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D188" s="4">
         <v>3.7200000000000002</v>
       </c>
-      <c r="E188" s="23">
+      <c r="E188" s="24">
         <v>2.9799999999999998e-004</v>
       </c>
       <c r="F188" s="4">
@@ -5925,14 +5938,14 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="23">
+      <c r="A189" s="24">
         <v>2.9799999999999998e-004</v>
       </c>
       <c r="B189" s="4">
         <v>1.1200000000000001</v>
       </c>
       <c r="C189">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D189" s="4">
@@ -5953,7 +5966,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C190">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D190" s="4">
@@ -5974,7 +5987,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C191">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D191" s="4">
@@ -5995,7 +6008,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C192">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D192" s="4">
@@ -6016,7 +6029,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C193">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D193" s="4">
@@ -6037,7 +6050,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C194">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D194" s="4">
@@ -6058,7 +6071,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C195">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D195" s="4">
@@ -6079,7 +6092,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D196" s="4">
@@ -6100,7 +6113,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C197">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D197" s="4">
@@ -6121,7 +6134,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C198">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D198" s="4">
@@ -6142,7 +6155,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C199">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D199" s="4">
@@ -6163,7 +6176,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C200">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D200" s="4">
@@ -6184,7 +6197,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C201">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D201" s="4">
@@ -6205,7 +6218,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C202">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D202" s="4">
@@ -6226,7 +6239,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C203">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D203" s="4">
@@ -6247,7 +6260,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C204">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D204" s="4">
@@ -6268,7 +6281,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C205">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D205" s="4">
@@ -6289,7 +6302,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C206">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D206" s="4">
@@ -6310,7 +6323,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C207">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D207" s="4">
@@ -6331,7 +6344,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C208">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D208" s="4">
@@ -6352,7 +6365,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C209">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D209" s="4">
@@ -6373,7 +6386,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C210">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D210" s="4">
@@ -6394,7 +6407,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C211">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D211" s="4">
@@ -6415,7 +6428,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C212">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D212" s="4">
@@ -6436,7 +6449,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C213">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D213" s="4">
@@ -6457,7 +6470,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C214">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D214" s="4">
@@ -6478,7 +6491,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C215">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D215" s="4">
@@ -6487,7 +6500,7 @@
       <c r="E215" s="4">
         <v>-7.0000000000000007e-002</v>
       </c>
-      <c r="F215" s="23">
+      <c r="F215" s="24">
         <v>1.75e-004</v>
       </c>
     </row>
@@ -6499,7 +6512,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C216">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D216" s="4">
@@ -6520,7 +6533,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C217">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D217" s="4">
@@ -6541,7 +6554,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C218">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D218" s="4">
@@ -6562,7 +6575,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C219">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D219" s="4">
@@ -6583,7 +6596,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C220">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D220" s="4">
@@ -6604,7 +6617,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C221">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D221" s="4">
@@ -6625,7 +6638,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C222">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D222" s="4">
@@ -6646,7 +6659,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C223">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D223" s="4">
@@ -6667,7 +6680,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C224">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D224" s="4">
@@ -6688,7 +6701,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C225">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D225" s="4">
@@ -6709,7 +6722,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C226">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D226" s="4">
@@ -6730,7 +6743,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C227">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D227" s="4">
@@ -6751,7 +6764,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C228">
-        <f t="shared" ref="C228:C291" si="15">B228-$G$1</f>
+        <f t="shared" ref="C228:C291" si="14">B228-$G$1</f>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D228" s="4">
@@ -6772,7 +6785,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C229">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D229" s="4">
@@ -6793,7 +6806,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C230">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D230" s="4">
@@ -6814,7 +6827,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C231">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D231" s="4">
@@ -6835,7 +6848,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C232">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="D232" s="4">
@@ -6856,7 +6869,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C233">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="D233" s="4">
@@ -6877,7 +6890,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C234">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="D234" s="4">
@@ -6898,7 +6911,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C235">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="D235" s="4">
@@ -6919,7 +6932,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C236">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="D236" s="4">
@@ -6940,7 +6953,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C237">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="D237" s="4">
@@ -6961,7 +6974,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C238">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="D238" s="4">
@@ -6982,7 +6995,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C239">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="D239" s="4">
@@ -7003,7 +7016,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C240">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D240" s="4">
@@ -7024,7 +7037,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C241">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D241" s="4">
@@ -7045,7 +7058,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C242">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D242" s="4">
@@ -7066,7 +7079,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C243">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D243" s="4">
@@ -7087,13 +7100,13 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C244">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D244" s="4">
         <v>4.8399999999999999</v>
       </c>
-      <c r="E244" s="23">
+      <c r="E244" s="24">
         <v>-1.15e-005</v>
       </c>
       <c r="F244" s="4">
@@ -7101,14 +7114,14 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="23">
+      <c r="A245" s="24">
         <v>-1.15e-005</v>
       </c>
       <c r="B245" s="4">
         <v>1.1399999999999999</v>
       </c>
       <c r="C245">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D245" s="4">
@@ -7129,7 +7142,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C246">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D246" s="4">
@@ -7150,7 +7163,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C247">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D247" s="4">
@@ -7171,7 +7184,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C248">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D248" s="4">
@@ -7192,7 +7205,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C249">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D249" s="4">
@@ -7213,7 +7226,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C250">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D250" s="4">
@@ -7234,7 +7247,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C251">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="D251" s="4">
@@ -7255,7 +7268,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C252">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="D252" s="4">
@@ -7276,7 +7289,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C253">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="D253" s="4">
@@ -7297,7 +7310,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C254">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="D254" s="4">
@@ -7318,7 +7331,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C255">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="D255" s="4">
@@ -7339,7 +7352,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C256">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="D256" s="4">
@@ -7360,7 +7373,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C257">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="D257" s="4">
@@ -7381,7 +7394,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C258">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="D258" s="4">
@@ -7402,7 +7415,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C259">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D259" s="4">
@@ -7423,7 +7436,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C260">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D260" s="4">
@@ -7444,7 +7457,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C261">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D261" s="4">
@@ -7465,7 +7478,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C262">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D262" s="4">
@@ -7486,7 +7499,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C263">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D263" s="4">
@@ -7507,7 +7520,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C264">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D264" s="4">
@@ -7528,7 +7541,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C265">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D265" s="4">
@@ -7549,7 +7562,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C266">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D266" s="4">
@@ -7570,7 +7583,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C267">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D267" s="4">
@@ -7591,7 +7604,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C268">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D268" s="4">
@@ -7612,7 +7625,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C269">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="D269" s="4">
@@ -7633,7 +7646,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C270">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="D270" s="4">
@@ -7654,7 +7667,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C271">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="D271" s="4">
@@ -7675,7 +7688,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C272">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="D272" s="4">
@@ -7696,7 +7709,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C273">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="D273" s="4">
@@ -7717,7 +7730,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C274">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="D274" s="4">
@@ -7738,7 +7751,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C275">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="D275" s="4">
@@ -7759,7 +7772,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C276">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D276" s="4">
@@ -7780,7 +7793,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C277">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D277" s="4">
@@ -7801,7 +7814,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C278">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D278" s="4">
@@ -7822,7 +7835,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C279">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D279" s="4">
@@ -7843,7 +7856,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C280">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D280" s="4">
@@ -7864,7 +7877,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C281">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D281" s="4">
@@ -7885,7 +7898,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C282">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D282" s="4">
@@ -7906,7 +7919,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C283">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D283" s="4">
@@ -7927,7 +7940,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C284">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D284" s="4">
@@ -7948,7 +7961,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C285">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D285" s="4">
@@ -7969,7 +7982,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C286">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D286" s="4">
@@ -7990,7 +8003,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C287">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D287" s="4">
@@ -8011,7 +8024,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C288">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D288" s="4">
@@ -8032,7 +8045,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C289">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="D289" s="4">
@@ -8053,7 +8066,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C290">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="D290" s="4">
@@ -8074,7 +8087,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C291">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="D291" s="4">
@@ -8095,7 +8108,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C292">
-        <f t="shared" ref="C292:C355" si="16">B292-$G$1</f>
+        <f t="shared" ref="C292:C355" si="15">B292-$G$1</f>
         <v>0</v>
       </c>
       <c r="D292" s="4">
@@ -8116,7 +8129,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C293">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="D293" s="4">
@@ -8137,7 +8150,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C294">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="D294" s="4">
@@ -8158,7 +8171,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C295">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="D295" s="4">
@@ -8179,7 +8192,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C296">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D296" s="4">
@@ -8200,7 +8213,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C297">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D297" s="4">
@@ -8221,7 +8234,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C298">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D298" s="4">
@@ -8242,7 +8255,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C299">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D299" s="4">
@@ -8263,13 +8276,13 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C300">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D300" s="4">
         <v>5.96</v>
       </c>
-      <c r="E300" s="23">
+      <c r="E300" s="24">
         <v>2.9700000000000001e-004</v>
       </c>
       <c r="F300" s="4">
@@ -8277,14 +8290,14 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="23">
+      <c r="A301" s="24">
         <v>2.9700000000000001e-004</v>
       </c>
       <c r="B301" s="4">
         <v>1.1200000000000001</v>
       </c>
       <c r="C301">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D301" s="4">
@@ -8305,7 +8318,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C302">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D302" s="4">
@@ -8326,7 +8339,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C303">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D303" s="4">
@@ -8347,7 +8360,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C304">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D304" s="4">
@@ -8368,7 +8381,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C305">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D305" s="4">
@@ -8389,7 +8402,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C306">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D306" s="4">
@@ -8410,7 +8423,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C307">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="D307" s="4">
@@ -8431,7 +8444,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C308">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="D308" s="4">
@@ -8440,7 +8453,7 @@
       <c r="E308" s="4">
         <v>7.0000000000000007e-002</v>
       </c>
-      <c r="F308" s="23">
+      <c r="F308" s="24">
         <v>-1.45e-004</v>
       </c>
     </row>
@@ -8452,7 +8465,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C309">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="D309" s="4">
@@ -8473,7 +8486,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C310">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="D310" s="4">
@@ -8494,7 +8507,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C311">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="D311" s="4">
@@ -8515,7 +8528,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C312">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="D312" s="4">
@@ -8536,7 +8549,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C313">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="D313" s="4">
@@ -8557,7 +8570,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C314">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D314" s="4">
@@ -8578,7 +8591,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C315">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D315" s="4">
@@ -8599,7 +8612,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C316">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D316" s="4">
@@ -8620,7 +8633,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C317">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D317" s="4">
@@ -8641,7 +8654,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C318">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D318" s="4">
@@ -8662,13 +8675,13 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C319">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D319" s="4">
         <v>6.3399999999999999</v>
       </c>
-      <c r="E319" s="23">
+      <c r="E319" s="24">
         <v>7.0299999999999996e-004</v>
       </c>
       <c r="F319" s="4">
@@ -8676,14 +8689,14 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="23">
+      <c r="A320" s="24">
         <v>7.0299999999999996e-004</v>
       </c>
       <c r="B320" s="4">
         <v>1.1399999999999999</v>
       </c>
       <c r="C320">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D320" s="4">
@@ -8704,7 +8717,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C321">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D321" s="4">
@@ -8725,7 +8738,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C322">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D322" s="4">
@@ -8746,7 +8759,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C323">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D323" s="4">
@@ -8767,7 +8780,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C324">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D324" s="4">
@@ -8788,7 +8801,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C325">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D325" s="4">
@@ -8809,7 +8822,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C326">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D326" s="4">
@@ -8830,7 +8843,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C327">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="D327" s="4">
@@ -8851,7 +8864,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C328">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="D328" s="4">
@@ -8872,7 +8885,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C329">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="D329" s="4">
@@ -8893,7 +8906,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C330">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="D330" s="4">
@@ -8914,7 +8927,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C331">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="D331" s="4">
@@ -8935,7 +8948,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C332">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="D332" s="4">
@@ -8956,7 +8969,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C333">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="D333" s="4">
@@ -8977,7 +8990,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C334">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="D334" s="4">
@@ -8998,7 +9011,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C335">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D335" s="4">
@@ -9019,7 +9032,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C336">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D336" s="4">
@@ -9040,7 +9053,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C337">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D337" s="4">
@@ -9061,13 +9074,13 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C338">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D338" s="4">
         <v>6.7199999999999998</v>
       </c>
-      <c r="E338" s="23">
+      <c r="E338" s="24">
         <v>9.9500000000000001e-004</v>
       </c>
       <c r="F338" s="4">
@@ -9075,14 +9088,14 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="23">
+      <c r="A339" s="24">
         <v>9.9500000000000001e-004</v>
       </c>
       <c r="B339" s="4">
         <v>1.1200000000000001</v>
       </c>
       <c r="C339">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D339" s="4">
@@ -9103,7 +9116,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C340">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D340" s="4">
@@ -9124,7 +9137,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C341">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D341" s="4">
@@ -9145,7 +9158,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C342">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D342" s="4">
@@ -9166,7 +9179,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C343">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D343" s="4">
@@ -9187,7 +9200,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C344">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D344" s="4">
@@ -9208,7 +9221,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C345">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="D345" s="4">
@@ -9229,7 +9242,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C346">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="D346" s="4">
@@ -9250,7 +9263,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C347">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="D347" s="4">
@@ -9271,7 +9284,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C348">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="D348" s="4">
@@ -9292,7 +9305,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C349">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="D349" s="4">
@@ -9313,7 +9326,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C350">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="D350" s="4">
@@ -9334,7 +9347,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C351">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="D351" s="4">
@@ -9355,7 +9368,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C352">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D352" s="4">
@@ -9376,7 +9389,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C353">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D353" s="4">
@@ -9397,7 +9410,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C354">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D354" s="4">
@@ -9418,7 +9431,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C355">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D355" s="4">
@@ -9439,7 +9452,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C356">
-        <f t="shared" ref="C356:C396" si="17">B356-$G$1</f>
+        <f t="shared" ref="C356:C396" si="16">B356-$G$1</f>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D356" s="4">
@@ -9460,7 +9473,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C357">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D357" s="4">
@@ -9481,7 +9494,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C358">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D358" s="4">
@@ -9502,7 +9515,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C359">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D359" s="4">
@@ -9523,7 +9536,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C360">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D360" s="4">
@@ -9544,7 +9557,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C361">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D361" s="4">
@@ -9565,7 +9578,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C362">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D362" s="4">
@@ -9586,7 +9599,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C363">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D363" s="4">
@@ -9607,7 +9620,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C364">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="D364" s="4">
@@ -9628,7 +9641,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C365">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="D365" s="4">
@@ -9649,7 +9662,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C366">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="D366" s="4">
@@ -9670,7 +9683,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C367">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="D367" s="4">
@@ -9691,7 +9704,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C368">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="D368" s="4">
@@ -9712,7 +9725,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C369">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="D369" s="4">
@@ -9733,7 +9746,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C370">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="D370" s="4">
@@ -9754,7 +9767,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C371">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="D371" s="4">
@@ -9775,7 +9788,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C372">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D372" s="4">
@@ -9796,7 +9809,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C373">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D373" s="4">
@@ -9817,7 +9830,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C374">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D374" s="4">
@@ -9838,7 +9851,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C375">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D375" s="4">
@@ -9859,7 +9872,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C376">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D376" s="4">
@@ -9880,7 +9893,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C377">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D377" s="4">
@@ -9901,7 +9914,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C378">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D378" s="4">
@@ -9922,7 +9935,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C379">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D379" s="4">
@@ -9943,7 +9956,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C380">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-9.9999999999997868e-003</v>
       </c>
       <c r="D380" s="4">
@@ -9964,7 +9977,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C381">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="D381" s="4">
@@ -9985,7 +9998,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C382">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="D382" s="4">
@@ -10006,7 +10019,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C383">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="D383" s="4">
@@ -10027,7 +10040,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C384">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="D384" s="4">
@@ -10048,7 +10061,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C385">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="D385" s="4">
@@ -10069,7 +10082,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C386">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="D386" s="4">
@@ -10090,7 +10103,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C387">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="D387" s="4">
@@ -10111,7 +10124,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C388">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="D388" s="4">
@@ -10132,7 +10145,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C389">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D389" s="4">
@@ -10153,7 +10166,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C390">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D390" s="4">
@@ -10174,7 +10187,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C391">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D391" s="4">
@@ -10195,7 +10208,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C392">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D392" s="4">
@@ -10216,7 +10229,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C393">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D393" s="4">
@@ -10234,7 +10247,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C394">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D394" s="4">
@@ -10253,7 +10266,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C395">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D395" s="4">
@@ -10272,7 +10285,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C396">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1.0000000000000009e-002</v>
       </c>
       <c r="D396" s="4">

--- a/Legge di Hooke.xlsx
+++ b/Legge di Hooke.xlsx
@@ -18,9 +18,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Molle in serie'!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
-  </extLst>
 </workbook>
 </file>
 

--- a/Legge di Hooke.xlsx
+++ b/Legge di Hooke.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="448" documentId="8_{776634F0-C4C9-4588-BBA4-07B3E3D5FCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C816B5D9-DAE4-48B4-B4F2-84AF46336FBC}"/>
+  <xr:revisionPtr revIDLastSave="450" documentId="8_{776634F0-C4C9-4588-BBA4-07B3E3D5FCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77AB726E-B7F6-4945-97E0-76C0DCE162BE}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="2" activeTab="6" xr2:uid="{90936311-A4D2-4EF7-9615-E94103A7D1D9}"/>
+    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{90936311-A4D2-4EF7-9615-E94103A7D1D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Misure statiche 1" sheetId="1" r:id="rId1"/>
@@ -272,7 +272,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -307,6 +307,9 @@
     <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -322,10 +325,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -750,7 +749,7 @@
         <v>400</v>
       </c>
       <c r="B6" s="2"/>
-      <c r="C6" s="1">
+      <c r="C6" s="20">
         <v>1.1299999999999999</v>
       </c>
       <c r="D6" s="1">
@@ -1044,11 +1043,11 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="C3" s="2">
-        <f t="shared" ref="C3:C6" si="0">$E$2-B3</f>
+        <f>$E$2-B3</f>
         <v>7.9999999999999849E-2</v>
       </c>
       <c r="D3" s="2">
-        <f t="shared" ref="D3:D6" si="1">0.01*SQRT(2)</f>
+        <f t="shared" ref="D3:D6" si="0">0.01*SQRT(2)</f>
         <v>1.4142135623730952E-2</v>
       </c>
       <c r="E3" s="2"/>
@@ -1061,11 +1060,11 @@
         <v>1.06</v>
       </c>
       <c r="C4" s="2">
+        <f t="shared" ref="C3:C6" si="1">$E$2-B4</f>
+        <v>0.10999999999999988</v>
+      </c>
+      <c r="D4" s="2">
         <f t="shared" si="0"/>
-        <v>0.10999999999999988</v>
-      </c>
-      <c r="D4" s="2">
-        <f t="shared" si="1"/>
         <v>1.4142135623730952E-2</v>
       </c>
       <c r="E4" s="2"/>
@@ -1078,11 +1077,11 @@
         <v>1.01</v>
       </c>
       <c r="C5" s="2">
+        <f t="shared" si="1"/>
+        <v>0.15999999999999992</v>
+      </c>
+      <c r="D5" s="2">
         <f t="shared" si="0"/>
-        <v>0.15999999999999992</v>
-      </c>
-      <c r="D5" s="2">
-        <f t="shared" si="1"/>
         <v>1.4142135623730952E-2</v>
       </c>
       <c r="E5" s="2"/>
@@ -1095,11 +1094,11 @@
         <v>0.95</v>
       </c>
       <c r="C6" s="2">
+        <f t="shared" si="1"/>
+        <v>0.21999999999999997</v>
+      </c>
+      <c r="D6" s="2">
         <f t="shared" si="0"/>
-        <v>0.21999999999999997</v>
-      </c>
-      <c r="D6" s="2">
-        <f t="shared" si="1"/>
         <v>1.4142135623730952E-2</v>
       </c>
       <c r="E6" s="2"/>
@@ -1802,7 +1801,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C2">
-        <f>B2-$G$1</f>
+        <f t="shared" ref="C2:C65" si="0">B2-$G$1</f>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D2" s="1">
@@ -1823,7 +1822,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C3">
-        <f>B3-$G$1</f>
+        <f t="shared" si="0"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D3" s="1">
@@ -1844,7 +1843,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C4">
-        <f>B4-$G$1</f>
+        <f t="shared" si="0"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D4" s="1">
@@ -1865,7 +1864,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C5">
-        <f>B5-$G$1</f>
+        <f t="shared" si="0"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D5" s="1">
@@ -1886,7 +1885,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C6">
-        <f>B6-$G$1</f>
+        <f t="shared" si="0"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D6" s="1">
@@ -1907,7 +1906,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C7">
-        <f>B7-$G$1</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D7" s="1">
@@ -1928,7 +1927,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C8">
-        <f>B8-$G$1</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D8" s="1">
@@ -1949,7 +1948,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C9">
-        <f>B9-$G$1</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D9" s="1">
@@ -1970,7 +1969,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C10">
-        <f>B10-$G$1</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D10" s="1">
@@ -1991,7 +1990,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C11">
-        <f>B11-$G$1</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D11" s="1">
@@ -2012,7 +2011,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C12">
-        <f>B12-$G$1</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D12" s="1">
@@ -2033,7 +2032,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C13">
-        <f>B13-$G$1</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D13" s="1">
@@ -2054,7 +2053,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C14">
-        <f>B14-$G$1</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D14" s="1">
@@ -2075,7 +2074,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C15">
-        <f>B15-$G$1</f>
+        <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D15" s="1">
@@ -2096,7 +2095,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C16">
-        <f>B16-$G$1</f>
+        <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D16" s="1">
@@ -2117,7 +2116,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C17">
-        <f>B17-$G$1</f>
+        <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D17" s="1">
@@ -2138,7 +2137,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C18">
-        <f>B18-$G$1</f>
+        <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D18" s="1">
@@ -2159,7 +2158,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C19">
-        <f>B19-$G$1</f>
+        <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D19" s="1">
@@ -2180,7 +2179,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C20">
-        <f>B20-$G$1</f>
+        <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D20" s="1">
@@ -2201,7 +2200,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C21">
-        <f>B21-$G$1</f>
+        <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D21" s="1">
@@ -2222,7 +2221,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C22">
-        <f>B22-$G$1</f>
+        <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D22" s="1">
@@ -2243,7 +2242,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C23">
-        <f>B23-$G$1</f>
+        <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D23" s="1">
@@ -2264,7 +2263,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C24">
-        <f>B24-$G$1</f>
+        <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D24" s="1">
@@ -2285,7 +2284,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C25">
-        <f>B25-$G$1</f>
+        <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D25" s="1">
@@ -2306,7 +2305,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C26">
-        <f>B26-$G$1</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D26" s="1">
@@ -2327,7 +2326,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C27">
-        <f>B27-$G$1</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D27" s="1">
@@ -2348,7 +2347,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C28">
-        <f>B28-$G$1</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D28" s="1">
@@ -2369,7 +2368,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C29">
-        <f>B29-$G$1</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D29" s="1">
@@ -2390,7 +2389,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C30">
-        <f>B30-$G$1</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D30" s="1">
@@ -2411,7 +2410,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C31">
-        <f>B31-$G$1</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D31" s="1">
@@ -2432,7 +2431,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C32">
-        <f>B32-$G$1</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D32" s="1">
@@ -2453,7 +2452,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C33">
-        <f>B33-$G$1</f>
+        <f t="shared" si="0"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D33" s="1">
@@ -2474,7 +2473,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C34">
-        <f>B34-$G$1</f>
+        <f t="shared" si="0"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D34" s="1">
@@ -2495,7 +2494,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C35">
-        <f>B35-$G$1</f>
+        <f t="shared" si="0"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D35" s="1">
@@ -2516,7 +2515,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C36">
-        <f>B36-$G$1</f>
+        <f t="shared" si="0"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D36" s="1">
@@ -2537,7 +2536,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C37">
-        <f>B37-$G$1</f>
+        <f t="shared" si="0"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D37" s="1">
@@ -2558,7 +2557,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C38">
-        <f>B38-$G$1</f>
+        <f t="shared" si="0"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D38" s="1">
@@ -2579,7 +2578,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C39">
-        <f>B39-$G$1</f>
+        <f t="shared" si="0"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D39" s="1">
@@ -2600,7 +2599,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C40">
-        <f>B40-$G$1</f>
+        <f t="shared" si="0"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D40" s="1">
@@ -2621,7 +2620,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C41">
-        <f>B41-$G$1</f>
+        <f t="shared" si="0"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D41" s="1">
@@ -2642,7 +2641,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C42">
-        <f>B42-$G$1</f>
+        <f t="shared" si="0"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D42" s="1">
@@ -2663,7 +2662,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C43">
-        <f>B43-$G$1</f>
+        <f t="shared" si="0"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D43" s="1">
@@ -2684,7 +2683,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C44">
-        <f>B44-$G$1</f>
+        <f t="shared" si="0"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D44" s="1">
@@ -2705,7 +2704,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C45">
-        <f>B45-$G$1</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D45" s="1">
@@ -2726,7 +2725,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C46">
-        <f>B46-$G$1</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D46" s="1">
@@ -2747,7 +2746,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C47">
-        <f>B47-$G$1</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D47" s="1">
@@ -2768,7 +2767,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C48">
-        <f>B48-$G$1</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D48" s="1">
@@ -2789,7 +2788,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C49">
-        <f>B49-$G$1</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D49" s="1">
@@ -2810,7 +2809,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C50">
-        <f>B50-$G$1</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D50" s="1">
@@ -2831,7 +2830,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C51">
-        <f>B51-$G$1</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D51" s="1">
@@ -2852,7 +2851,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C52">
-        <f>B52-$G$1</f>
+        <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D52" s="1">
@@ -2873,7 +2872,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C53">
-        <f>B53-$G$1</f>
+        <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D53" s="1">
@@ -2894,7 +2893,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C54">
-        <f>B54-$G$1</f>
+        <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D54" s="1">
@@ -2915,7 +2914,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C55">
-        <f>B55-$G$1</f>
+        <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D55" s="1">
@@ -2936,7 +2935,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C56">
-        <f>B56-$G$1</f>
+        <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D56" s="1">
@@ -2957,7 +2956,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C57">
-        <f>B57-$G$1</f>
+        <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D57" s="1">
@@ -2978,7 +2977,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C58">
-        <f>B58-$G$1</f>
+        <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D58" s="1">
@@ -2999,7 +2998,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C59">
-        <f>B59-$G$1</f>
+        <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D59" s="1">
@@ -3020,7 +3019,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C60">
-        <f>B60-$G$1</f>
+        <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D60" s="1">
@@ -3041,7 +3040,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C61">
-        <f>B61-$G$1</f>
+        <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D61" s="1">
@@ -3062,7 +3061,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C62">
-        <f>B62-$G$1</f>
+        <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D62" s="1">
@@ -3083,7 +3082,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C63">
-        <f>B63-$G$1</f>
+        <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D63" s="1">
@@ -3104,7 +3103,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C64">
-        <f>B64-$G$1</f>
+        <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D64" s="1">
@@ -3125,7 +3124,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C65">
-        <f>B65-$G$1</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D65" s="1">
@@ -3146,7 +3145,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C66">
-        <f>B66-$G$1</f>
+        <f t="shared" ref="C66:C129" si="1">B66-$G$1</f>
         <v>0</v>
       </c>
       <c r="D66" s="1">
@@ -3167,7 +3166,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C67">
-        <f>B67-$G$1</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D67" s="1">
@@ -3188,7 +3187,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C68">
-        <f>B68-$G$1</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D68" s="1">
@@ -3209,7 +3208,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C69">
-        <f>B69-$G$1</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D69" s="1">
@@ -3230,7 +3229,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C70">
-        <f>B70-$G$1</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D70" s="1">
@@ -3251,7 +3250,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C71">
-        <f>B71-$G$1</f>
+        <f t="shared" si="1"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D71" s="1">
@@ -3272,7 +3271,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C72">
-        <f>B72-$G$1</f>
+        <f t="shared" si="1"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D72" s="1">
@@ -3293,7 +3292,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C73">
-        <f>B73-$G$1</f>
+        <f t="shared" si="1"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D73" s="1">
@@ -3314,7 +3313,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C74">
-        <f>B74-$G$1</f>
+        <f t="shared" si="1"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D74" s="1">
@@ -3335,7 +3334,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C75">
-        <f>B75-$G$1</f>
+        <f t="shared" si="1"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D75" s="1">
@@ -3356,7 +3355,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C76">
-        <f>B76-$G$1</f>
+        <f t="shared" si="1"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D76" s="1">
@@ -3377,7 +3376,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C77">
-        <f>B77-$G$1</f>
+        <f t="shared" si="1"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D77" s="1">
@@ -3398,7 +3397,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C78">
-        <f>B78-$G$1</f>
+        <f t="shared" si="1"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D78" s="1">
@@ -3419,7 +3418,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C79">
-        <f>B79-$G$1</f>
+        <f t="shared" si="1"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D79" s="1">
@@ -3440,7 +3439,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C80">
-        <f>B80-$G$1</f>
+        <f t="shared" si="1"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D80" s="1">
@@ -3461,7 +3460,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C81">
-        <f>B81-$G$1</f>
+        <f t="shared" si="1"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D81" s="1">
@@ -3482,7 +3481,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C82">
-        <f>B82-$G$1</f>
+        <f t="shared" si="1"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D82" s="1">
@@ -3503,7 +3502,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C83">
-        <f>B83-$G$1</f>
+        <f t="shared" si="1"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D83" s="1">
@@ -3524,7 +3523,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C84">
-        <f>B84-$G$1</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D84" s="1">
@@ -3545,7 +3544,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C85">
-        <f>B85-$G$1</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D85" s="1">
@@ -3566,7 +3565,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C86">
-        <f>B86-$G$1</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D86" s="1">
@@ -3587,7 +3586,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C87">
-        <f>B87-$G$1</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D87" s="1">
@@ -3608,7 +3607,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C88">
-        <f>B88-$G$1</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D88" s="1">
@@ -3629,7 +3628,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C89">
-        <f>B89-$G$1</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D89" s="1">
@@ -3650,7 +3649,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C90">
-        <f>B90-$G$1</f>
+        <f t="shared" si="1"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D90" s="1">
@@ -3671,7 +3670,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C91">
-        <f>B91-$G$1</f>
+        <f t="shared" si="1"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D91" s="1">
@@ -3692,7 +3691,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C92">
-        <f>B92-$G$1</f>
+        <f t="shared" si="1"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D92" s="1">
@@ -3713,7 +3712,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C93">
-        <f>B93-$G$1</f>
+        <f t="shared" si="1"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D93" s="1">
@@ -3734,7 +3733,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C94">
-        <f>B94-$G$1</f>
+        <f t="shared" si="1"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D94" s="1">
@@ -3755,7 +3754,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C95">
-        <f>B95-$G$1</f>
+        <f t="shared" si="1"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D95" s="1">
@@ -3776,7 +3775,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C96">
-        <f>B96-$G$1</f>
+        <f t="shared" si="1"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D96" s="1">
@@ -3797,7 +3796,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C97">
-        <f>B97-$G$1</f>
+        <f t="shared" si="1"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D97" s="1">
@@ -3818,7 +3817,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C98">
-        <f>B98-$G$1</f>
+        <f t="shared" si="1"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D98" s="1">
@@ -3839,7 +3838,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C99">
-        <f>B99-$G$1</f>
+        <f t="shared" si="1"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D99" s="1">
@@ -3860,7 +3859,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C100">
-        <f>B100-$G$1</f>
+        <f t="shared" si="1"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D100" s="1">
@@ -3881,7 +3880,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C101">
-        <f>B101-$G$1</f>
+        <f t="shared" si="1"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D101" s="1">
@@ -3902,7 +3901,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C102">
-        <f>B102-$G$1</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D102" s="1">
@@ -3923,7 +3922,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C103">
-        <f>B103-$G$1</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D103" s="1">
@@ -3944,7 +3943,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C104">
-        <f>B104-$G$1</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D104" s="1">
@@ -3965,7 +3964,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C105">
-        <f>B105-$G$1</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D105" s="1">
@@ -3986,7 +3985,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C106">
-        <f>B106-$G$1</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D106" s="1">
@@ -4007,7 +4006,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C107">
-        <f>B107-$G$1</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D107" s="1">
@@ -4028,7 +4027,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C108">
-        <f>B108-$G$1</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D108" s="1">
@@ -4049,7 +4048,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C109">
-        <f>B109-$G$1</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D109" s="1">
@@ -4070,7 +4069,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C110">
-        <f>B110-$G$1</f>
+        <f t="shared" si="1"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D110" s="1">
@@ -4091,7 +4090,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C111">
-        <f>B111-$G$1</f>
+        <f t="shared" si="1"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D111" s="1">
@@ -4112,7 +4111,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C112">
-        <f>B112-$G$1</f>
+        <f t="shared" si="1"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D112" s="1">
@@ -4133,7 +4132,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C113">
-        <f>B113-$G$1</f>
+        <f t="shared" si="1"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D113" s="1">
@@ -4154,7 +4153,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C114">
-        <f>B114-$G$1</f>
+        <f t="shared" si="1"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D114" s="1">
@@ -4175,7 +4174,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C115">
-        <f>B115-$G$1</f>
+        <f t="shared" si="1"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D115" s="1">
@@ -4196,7 +4195,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C116">
-        <f>B116-$G$1</f>
+        <f t="shared" si="1"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D116" s="1">
@@ -4217,7 +4216,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C117">
-        <f>B117-$G$1</f>
+        <f t="shared" si="1"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D117" s="1">
@@ -4238,7 +4237,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C118">
-        <f>B118-$G$1</f>
+        <f t="shared" si="1"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D118" s="1">
@@ -4259,7 +4258,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C119">
-        <f>B119-$G$1</f>
+        <f t="shared" si="1"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D119" s="1">
@@ -4280,7 +4279,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C120">
-        <f>B120-$G$1</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D120" s="1">
@@ -4301,7 +4300,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C121">
-        <f>B121-$G$1</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D121" s="1">
@@ -4322,7 +4321,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C122">
-        <f>B122-$G$1</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D122" s="1">
@@ -4343,7 +4342,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C123">
-        <f>B123-$G$1</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D123" s="1">
@@ -4364,7 +4363,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C124">
-        <f>B124-$G$1</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D124" s="1">
@@ -4385,7 +4384,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C125">
-        <f>B125-$G$1</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D125" s="1">
@@ -4406,7 +4405,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C126">
-        <f>B126-$G$1</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D126" s="1">
@@ -4427,7 +4426,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C127">
-        <f>B127-$G$1</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D127" s="1">
@@ -4448,7 +4447,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C128">
-        <f>B128-$G$1</f>
+        <f t="shared" si="1"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D128" s="1">
@@ -4469,7 +4468,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C129">
-        <f>B129-$G$1</f>
+        <f t="shared" si="1"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D129" s="1">
@@ -4490,7 +4489,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C130">
-        <f>B130-$G$1</f>
+        <f t="shared" ref="C130:C193" si="2">B130-$G$1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D130" s="1">
@@ -4511,7 +4510,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C131">
-        <f>B131-$G$1</f>
+        <f t="shared" si="2"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D131" s="1">
@@ -4532,7 +4531,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C132">
-        <f>B132-$G$1</f>
+        <f t="shared" si="2"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D132" s="1">
@@ -4553,7 +4552,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C133">
-        <f>B133-$G$1</f>
+        <f t="shared" si="2"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D133" s="1">
@@ -4574,7 +4573,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C134">
-        <f>B134-$G$1</f>
+        <f t="shared" si="2"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D134" s="1">
@@ -4595,7 +4594,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C135">
-        <f>B135-$G$1</f>
+        <f t="shared" si="2"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D135" s="1">
@@ -4616,7 +4615,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C136">
-        <f>B136-$G$1</f>
+        <f t="shared" si="2"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D136" s="1">
@@ -4637,7 +4636,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C137">
-        <f>B137-$G$1</f>
+        <f t="shared" si="2"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D137" s="1">
@@ -4658,7 +4657,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C138">
-        <f>B138-$G$1</f>
+        <f t="shared" si="2"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D138" s="1">
@@ -4679,7 +4678,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C139">
-        <f>B139-$G$1</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D139" s="1">
@@ -4700,7 +4699,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C140">
-        <f>B140-$G$1</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D140" s="1">
@@ -4721,7 +4720,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C141">
-        <f>B141-$G$1</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D141" s="1">
@@ -4742,7 +4741,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C142">
-        <f>B142-$G$1</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D142" s="1">
@@ -4763,7 +4762,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C143">
-        <f>B143-$G$1</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D143" s="1">
@@ -4784,7 +4783,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C144">
-        <f>B144-$G$1</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D144" s="1">
@@ -4805,7 +4804,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C145">
-        <f>B145-$G$1</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D145" s="1">
@@ -4826,7 +4825,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C146">
-        <f>B146-$G$1</f>
+        <f t="shared" si="2"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D146" s="1">
@@ -4847,7 +4846,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C147">
-        <f>B147-$G$1</f>
+        <f t="shared" si="2"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D147" s="1">
@@ -4868,7 +4867,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C148">
-        <f>B148-$G$1</f>
+        <f t="shared" si="2"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D148" s="1">
@@ -4889,7 +4888,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C149">
-        <f>B149-$G$1</f>
+        <f t="shared" si="2"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D149" s="1">
@@ -4910,7 +4909,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C150">
-        <f>B150-$G$1</f>
+        <f t="shared" si="2"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D150" s="1">
@@ -4931,7 +4930,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C151">
-        <f>B151-$G$1</f>
+        <f t="shared" si="2"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D151" s="1">
@@ -4952,7 +4951,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C152">
-        <f>B152-$G$1</f>
+        <f t="shared" si="2"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D152" s="1">
@@ -4973,7 +4972,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C153">
-        <f>B153-$G$1</f>
+        <f t="shared" si="2"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D153" s="1">
@@ -4994,7 +4993,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C154">
-        <f>B154-$G$1</f>
+        <f t="shared" si="2"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D154" s="1">
@@ -5015,7 +5014,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C155">
-        <f>B155-$G$1</f>
+        <f t="shared" si="2"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D155" s="1">
@@ -5036,7 +5035,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C156">
-        <f>B156-$G$1</f>
+        <f t="shared" si="2"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D156" s="1">
@@ -5057,7 +5056,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C157">
-        <f>B157-$G$1</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D157" s="1">
@@ -5078,7 +5077,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C158">
-        <f>B158-$G$1</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D158" s="1">
@@ -5099,7 +5098,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C159">
-        <f>B159-$G$1</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D159" s="1">
@@ -5120,7 +5119,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C160">
-        <f>B160-$G$1</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D160" s="1">
@@ -5141,7 +5140,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C161">
-        <f>B161-$G$1</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D161" s="1">
@@ -5162,7 +5161,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C162">
-        <f>B162-$G$1</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D162" s="1">
@@ -5183,7 +5182,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C163">
-        <f>B163-$G$1</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D163" s="1">
@@ -5204,7 +5203,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C164">
-        <f>B164-$G$1</f>
+        <f t="shared" si="2"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D164" s="1">
@@ -5225,7 +5224,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C165">
-        <f>B165-$G$1</f>
+        <f t="shared" si="2"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D165" s="1">
@@ -5246,7 +5245,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C166">
-        <f>B166-$G$1</f>
+        <f t="shared" si="2"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D166" s="1">
@@ -5267,7 +5266,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C167">
-        <f>B167-$G$1</f>
+        <f t="shared" si="2"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D167" s="1">
@@ -5288,7 +5287,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C168">
-        <f>B168-$G$1</f>
+        <f t="shared" si="2"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D168" s="1">
@@ -5309,7 +5308,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C169">
-        <f>B169-$G$1</f>
+        <f t="shared" si="2"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D169" s="1">
@@ -5330,7 +5329,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C170">
-        <f>B170-$G$1</f>
+        <f t="shared" si="2"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D170" s="1">
@@ -5351,7 +5350,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C171">
-        <f>B171-$G$1</f>
+        <f t="shared" si="2"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D171" s="1">
@@ -5372,7 +5371,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C172">
-        <f>B172-$G$1</f>
+        <f t="shared" si="2"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D172" s="1">
@@ -5393,7 +5392,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C173">
-        <f>B173-$G$1</f>
+        <f t="shared" si="2"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D173" s="1">
@@ -5414,7 +5413,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C174">
-        <f>B174-$G$1</f>
+        <f t="shared" si="2"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D174" s="1">
@@ -5435,7 +5434,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C175">
-        <f>B175-$G$1</f>
+        <f t="shared" si="2"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D175" s="1">
@@ -5456,7 +5455,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C176">
-        <f>B176-$G$1</f>
+        <f t="shared" si="2"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D176" s="1">
@@ -5477,7 +5476,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C177">
-        <f>B177-$G$1</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D177" s="1">
@@ -5498,7 +5497,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C178">
-        <f>B178-$G$1</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D178" s="1">
@@ -5519,7 +5518,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C179">
-        <f>B179-$G$1</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D179" s="1">
@@ -5540,7 +5539,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C180">
-        <f>B180-$G$1</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D180" s="1">
@@ -5561,7 +5560,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C181">
-        <f>B181-$G$1</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D181" s="1">
@@ -5582,7 +5581,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C182">
-        <f>B182-$G$1</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D182" s="1">
@@ -5603,7 +5602,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C183">
-        <f>B183-$G$1</f>
+        <f t="shared" si="2"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D183" s="1">
@@ -5624,7 +5623,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C184">
-        <f>B184-$G$1</f>
+        <f t="shared" si="2"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D184" s="1">
@@ -5645,7 +5644,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C185">
-        <f>B185-$G$1</f>
+        <f t="shared" si="2"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D185" s="1">
@@ -5666,7 +5665,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C186">
-        <f>B186-$G$1</f>
+        <f t="shared" si="2"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D186" s="1">
@@ -5687,7 +5686,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C187">
-        <f>B187-$G$1</f>
+        <f t="shared" si="2"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D187" s="1">
@@ -5708,7 +5707,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C188">
-        <f>B188-$G$1</f>
+        <f t="shared" si="2"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D188" s="1">
@@ -5729,7 +5728,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C189">
-        <f>B189-$G$1</f>
+        <f t="shared" si="2"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D189" s="1">
@@ -5750,7 +5749,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C190">
-        <f>B190-$G$1</f>
+        <f t="shared" si="2"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D190" s="1">
@@ -5771,7 +5770,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C191">
-        <f>B191-$G$1</f>
+        <f t="shared" si="2"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D191" s="1">
@@ -5792,7 +5791,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C192">
-        <f>B192-$G$1</f>
+        <f t="shared" si="2"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D192" s="1">
@@ -5813,7 +5812,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C193">
-        <f>B193-$G$1</f>
+        <f t="shared" si="2"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D193" s="1">
@@ -5834,7 +5833,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C194">
-        <f>B194-$G$1</f>
+        <f t="shared" ref="C194:C257" si="3">B194-$G$1</f>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D194" s="1">
@@ -5855,7 +5854,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C195">
-        <f>B195-$G$1</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D195" s="1">
@@ -5876,7 +5875,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C196">
-        <f>B196-$G$1</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D196" s="1">
@@ -5897,7 +5896,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C197">
-        <f>B197-$G$1</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D197" s="1">
@@ -5918,7 +5917,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C198">
-        <f>B198-$G$1</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D198" s="1">
@@ -5939,7 +5938,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C199">
-        <f>B199-$G$1</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D199" s="1">
@@ -5960,7 +5959,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C200">
-        <f>B200-$G$1</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D200" s="1">
@@ -5981,7 +5980,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C201">
-        <f>B201-$G$1</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D201" s="1">
@@ -6002,7 +6001,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C202">
-        <f>B202-$G$1</f>
+        <f t="shared" si="3"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D202" s="1">
@@ -6023,7 +6022,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C203">
-        <f>B203-$G$1</f>
+        <f t="shared" si="3"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D203" s="1">
@@ -6044,7 +6043,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C204">
-        <f>B204-$G$1</f>
+        <f t="shared" si="3"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D204" s="1">
@@ -6065,7 +6064,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C205">
-        <f>B205-$G$1</f>
+        <f t="shared" si="3"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D205" s="1">
@@ -6086,7 +6085,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C206">
-        <f>B206-$G$1</f>
+        <f t="shared" si="3"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D206" s="1">
@@ -6107,7 +6106,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C207">
-        <f>B207-$G$1</f>
+        <f t="shared" si="3"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D207" s="1">
@@ -6128,7 +6127,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C208">
-        <f>B208-$G$1</f>
+        <f t="shared" si="3"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D208" s="1">
@@ -6149,7 +6148,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C209">
-        <f>B209-$G$1</f>
+        <f t="shared" si="3"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D209" s="1">
@@ -6170,7 +6169,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C210">
-        <f>B210-$G$1</f>
+        <f t="shared" si="3"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D210" s="1">
@@ -6191,7 +6190,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C211">
-        <f>B211-$G$1</f>
+        <f t="shared" si="3"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D211" s="1">
@@ -6212,7 +6211,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C212">
-        <f>B212-$G$1</f>
+        <f t="shared" si="3"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D212" s="1">
@@ -6233,7 +6232,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C213">
-        <f>B213-$G$1</f>
+        <f t="shared" si="3"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D213" s="1">
@@ -6254,7 +6253,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C214">
-        <f>B214-$G$1</f>
+        <f t="shared" si="3"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D214" s="1">
@@ -6275,7 +6274,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C215">
-        <f>B215-$G$1</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D215" s="1">
@@ -6296,7 +6295,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C216">
-        <f>B216-$G$1</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D216" s="1">
@@ -6317,7 +6316,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C217">
-        <f>B217-$G$1</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D217" s="1">
@@ -6338,7 +6337,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C218">
-        <f>B218-$G$1</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D218" s="1">
@@ -6359,7 +6358,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C219">
-        <f>B219-$G$1</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D219" s="1">
@@ -6380,7 +6379,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C220">
-        <f>B220-$G$1</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D220" s="1">
@@ -6401,7 +6400,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C221">
-        <f>B221-$G$1</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D221" s="1">
@@ -6422,7 +6421,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C222">
-        <f>B222-$G$1</f>
+        <f t="shared" si="3"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D222" s="1">
@@ -6443,7 +6442,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C223">
-        <f>B223-$G$1</f>
+        <f t="shared" si="3"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D223" s="1">
@@ -6464,7 +6463,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C224">
-        <f>B224-$G$1</f>
+        <f t="shared" si="3"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D224" s="1">
@@ -6485,7 +6484,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C225">
-        <f>B225-$G$1</f>
+        <f t="shared" si="3"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D225" s="1">
@@ -6506,7 +6505,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C226">
-        <f>B226-$G$1</f>
+        <f t="shared" si="3"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D226" s="1">
@@ -6527,7 +6526,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C227">
-        <f>B227-$G$1</f>
+        <f t="shared" si="3"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D227" s="1">
@@ -6548,7 +6547,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C228">
-        <f>B228-$G$1</f>
+        <f t="shared" si="3"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D228" s="1">
@@ -6569,7 +6568,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C229">
-        <f>B229-$G$1</f>
+        <f t="shared" si="3"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D229" s="1">
@@ -6590,7 +6589,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C230">
-        <f>B230-$G$1</f>
+        <f t="shared" si="3"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D230" s="1">
@@ -6611,7 +6610,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C231">
-        <f>B231-$G$1</f>
+        <f t="shared" si="3"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D231" s="1">
@@ -6632,7 +6631,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C232">
-        <f>B232-$G$1</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D232" s="1">
@@ -6653,7 +6652,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C233">
-        <f>B233-$G$1</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D233" s="1">
@@ -6674,7 +6673,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C234">
-        <f>B234-$G$1</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D234" s="1">
@@ -6695,7 +6694,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C235">
-        <f>B235-$G$1</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D235" s="1">
@@ -6716,7 +6715,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C236">
-        <f>B236-$G$1</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D236" s="1">
@@ -6737,7 +6736,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C237">
-        <f>B237-$G$1</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D237" s="1">
@@ -6758,7 +6757,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C238">
-        <f>B238-$G$1</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D238" s="1">
@@ -6779,7 +6778,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C239">
-        <f>B239-$G$1</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D239" s="1">
@@ -6800,7 +6799,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C240">
-        <f>B240-$G$1</f>
+        <f t="shared" si="3"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D240" s="1">
@@ -6821,7 +6820,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C241">
-        <f>B241-$G$1</f>
+        <f t="shared" si="3"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D241" s="1">
@@ -6842,7 +6841,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C242">
-        <f>B242-$G$1</f>
+        <f t="shared" si="3"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D242" s="1">
@@ -6863,7 +6862,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C243">
-        <f>B243-$G$1</f>
+        <f t="shared" si="3"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D243" s="1">
@@ -6884,7 +6883,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C244">
-        <f>B244-$G$1</f>
+        <f t="shared" si="3"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D244" s="1">
@@ -6905,7 +6904,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C245">
-        <f>B245-$G$1</f>
+        <f t="shared" si="3"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D245" s="1">
@@ -6926,7 +6925,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C246">
-        <f>B246-$G$1</f>
+        <f t="shared" si="3"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D246" s="1">
@@ -6947,7 +6946,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C247">
-        <f>B247-$G$1</f>
+        <f t="shared" si="3"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D247" s="1">
@@ -6968,7 +6967,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C248">
-        <f>B248-$G$1</f>
+        <f t="shared" si="3"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D248" s="1">
@@ -6989,7 +6988,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C249">
-        <f>B249-$G$1</f>
+        <f t="shared" si="3"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D249" s="1">
@@ -7010,7 +7009,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C250">
-        <f>B250-$G$1</f>
+        <f t="shared" si="3"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D250" s="1">
@@ -7031,7 +7030,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C251">
-        <f>B251-$G$1</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D251" s="1">
@@ -7052,7 +7051,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C252">
-        <f>B252-$G$1</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D252" s="1">
@@ -7073,7 +7072,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C253">
-        <f>B253-$G$1</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D253" s="1">
@@ -7094,7 +7093,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C254">
-        <f>B254-$G$1</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D254" s="1">
@@ -7115,7 +7114,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C255">
-        <f>B255-$G$1</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D255" s="1">
@@ -7136,7 +7135,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C256">
-        <f>B256-$G$1</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D256" s="1">
@@ -7157,7 +7156,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C257">
-        <f>B257-$G$1</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D257" s="1">
@@ -7178,7 +7177,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C258">
-        <f>B258-$G$1</f>
+        <f t="shared" ref="C258:C321" si="4">B258-$G$1</f>
         <v>0</v>
       </c>
       <c r="D258" s="1">
@@ -7199,7 +7198,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C259">
-        <f>B259-$G$1</f>
+        <f t="shared" si="4"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D259" s="1">
@@ -7220,7 +7219,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C260">
-        <f>B260-$G$1</f>
+        <f t="shared" si="4"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D260" s="1">
@@ -7241,7 +7240,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C261">
-        <f>B261-$G$1</f>
+        <f t="shared" si="4"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D261" s="1">
@@ -7262,7 +7261,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C262">
-        <f>B262-$G$1</f>
+        <f t="shared" si="4"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D262" s="1">
@@ -7283,7 +7282,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C263">
-        <f>B263-$G$1</f>
+        <f t="shared" si="4"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D263" s="1">
@@ -7304,7 +7303,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C264">
-        <f>B264-$G$1</f>
+        <f t="shared" si="4"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D264" s="1">
@@ -7325,7 +7324,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C265">
-        <f>B265-$G$1</f>
+        <f t="shared" si="4"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D265" s="1">
@@ -7346,7 +7345,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C266">
-        <f>B266-$G$1</f>
+        <f t="shared" si="4"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D266" s="1">
@@ -7367,7 +7366,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C267">
-        <f>B267-$G$1</f>
+        <f t="shared" si="4"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D267" s="1">
@@ -7388,7 +7387,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C268">
-        <f>B268-$G$1</f>
+        <f t="shared" si="4"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D268" s="1">
@@ -7409,7 +7408,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C269">
-        <f>B269-$G$1</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D269" s="1">
@@ -7430,7 +7429,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C270">
-        <f>B270-$G$1</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D270" s="1">
@@ -7451,7 +7450,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C271">
-        <f>B271-$G$1</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D271" s="1">
@@ -7472,7 +7471,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C272">
-        <f>B272-$G$1</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D272" s="1">
@@ -7493,7 +7492,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C273">
-        <f>B273-$G$1</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D273" s="1">
@@ -7514,7 +7513,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C274">
-        <f>B274-$G$1</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D274" s="1">
@@ -7535,7 +7534,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C275">
-        <f>B275-$G$1</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D275" s="1">
@@ -7556,7 +7555,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C276">
-        <f>B276-$G$1</f>
+        <f t="shared" si="4"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D276" s="1">
@@ -7577,7 +7576,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C277">
-        <f>B277-$G$1</f>
+        <f t="shared" si="4"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D277" s="1">
@@ -7598,7 +7597,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C278">
-        <f>B278-$G$1</f>
+        <f t="shared" si="4"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D278" s="1">
@@ -7619,7 +7618,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C279">
-        <f>B279-$G$1</f>
+        <f t="shared" si="4"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D279" s="1">
@@ -7640,7 +7639,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C280">
-        <f>B280-$G$1</f>
+        <f t="shared" si="4"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D280" s="1">
@@ -7661,7 +7660,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C281">
-        <f>B281-$G$1</f>
+        <f t="shared" si="4"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D281" s="1">
@@ -7682,7 +7681,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C282">
-        <f>B282-$G$1</f>
+        <f t="shared" si="4"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D282" s="1">
@@ -7703,7 +7702,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C283">
-        <f>B283-$G$1</f>
+        <f t="shared" si="4"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D283" s="1">
@@ -7724,7 +7723,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C284">
-        <f>B284-$G$1</f>
+        <f t="shared" si="4"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D284" s="1">
@@ -7745,7 +7744,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C285">
-        <f>B285-$G$1</f>
+        <f t="shared" si="4"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D285" s="1">
@@ -7766,7 +7765,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C286">
-        <f>B286-$G$1</f>
+        <f t="shared" si="4"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D286" s="1">
@@ -7787,7 +7786,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C287">
-        <f>B287-$G$1</f>
+        <f t="shared" si="4"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D287" s="1">
@@ -7808,7 +7807,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C288">
-        <f>B288-$G$1</f>
+        <f t="shared" si="4"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D288" s="1">
@@ -7829,7 +7828,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C289">
-        <f>B289-$G$1</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D289" s="1">
@@ -7850,7 +7849,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C290">
-        <f>B290-$G$1</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D290" s="1">
@@ -7871,7 +7870,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C291">
-        <f>B291-$G$1</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D291" s="1">
@@ -7892,7 +7891,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C292">
-        <f>B292-$G$1</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D292" s="1">
@@ -7913,7 +7912,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C293">
-        <f>B293-$G$1</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D293" s="1">
@@ -7934,7 +7933,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C294">
-        <f>B294-$G$1</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D294" s="1">
@@ -7955,7 +7954,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C295">
-        <f>B295-$G$1</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D295" s="1">
@@ -7976,7 +7975,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C296">
-        <f>B296-$G$1</f>
+        <f t="shared" si="4"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D296" s="1">
@@ -7997,7 +7996,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C297">
-        <f>B297-$G$1</f>
+        <f t="shared" si="4"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D297" s="1">
@@ -8018,7 +8017,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C298">
-        <f>B298-$G$1</f>
+        <f t="shared" si="4"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D298" s="1">
@@ -8039,7 +8038,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C299">
-        <f>B299-$G$1</f>
+        <f t="shared" si="4"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D299" s="1">
@@ -8060,7 +8059,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C300">
-        <f>B300-$G$1</f>
+        <f t="shared" si="4"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D300" s="1">
@@ -8081,7 +8080,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C301">
-        <f>B301-$G$1</f>
+        <f t="shared" si="4"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D301" s="1">
@@ -8102,7 +8101,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C302">
-        <f>B302-$G$1</f>
+        <f t="shared" si="4"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D302" s="1">
@@ -8123,7 +8122,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C303">
-        <f>B303-$G$1</f>
+        <f t="shared" si="4"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D303" s="1">
@@ -8144,7 +8143,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C304">
-        <f>B304-$G$1</f>
+        <f t="shared" si="4"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D304" s="1">
@@ -8165,7 +8164,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C305">
-        <f>B305-$G$1</f>
+        <f t="shared" si="4"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D305" s="1">
@@ -8186,7 +8185,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C306">
-        <f>B306-$G$1</f>
+        <f t="shared" si="4"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D306" s="1">
@@ -8207,7 +8206,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C307">
-        <f>B307-$G$1</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D307" s="1">
@@ -8228,7 +8227,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C308">
-        <f>B308-$G$1</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D308" s="1">
@@ -8249,7 +8248,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C309">
-        <f>B309-$G$1</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D309" s="1">
@@ -8270,7 +8269,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C310">
-        <f>B310-$G$1</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D310" s="1">
@@ -8291,7 +8290,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C311">
-        <f>B311-$G$1</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D311" s="1">
@@ -8312,7 +8311,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C312">
-        <f>B312-$G$1</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D312" s="1">
@@ -8333,7 +8332,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C313">
-        <f>B313-$G$1</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D313" s="1">
@@ -8354,7 +8353,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C314">
-        <f>B314-$G$1</f>
+        <f t="shared" si="4"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D314" s="1">
@@ -8375,7 +8374,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C315">
-        <f>B315-$G$1</f>
+        <f t="shared" si="4"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D315" s="1">
@@ -8396,7 +8395,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C316">
-        <f>B316-$G$1</f>
+        <f t="shared" si="4"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D316" s="1">
@@ -8417,7 +8416,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C317">
-        <f>B317-$G$1</f>
+        <f t="shared" si="4"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D317" s="1">
@@ -8438,7 +8437,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C318">
-        <f>B318-$G$1</f>
+        <f t="shared" si="4"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D318" s="1">
@@ -8459,7 +8458,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C319">
-        <f>B319-$G$1</f>
+        <f t="shared" si="4"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D319" s="1">
@@ -8480,7 +8479,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C320">
-        <f>B320-$G$1</f>
+        <f t="shared" si="4"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D320" s="1">
@@ -8501,7 +8500,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C321">
-        <f>B321-$G$1</f>
+        <f t="shared" si="4"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D321" s="1">
@@ -8522,7 +8521,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C322">
-        <f>B322-$G$1</f>
+        <f t="shared" ref="C322:C385" si="5">B322-$G$1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D322" s="1">
@@ -8543,7 +8542,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C323">
-        <f>B323-$G$1</f>
+        <f t="shared" si="5"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D323" s="1">
@@ -8564,7 +8563,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C324">
-        <f>B324-$G$1</f>
+        <f t="shared" si="5"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D324" s="1">
@@ -8585,7 +8584,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C325">
-        <f>B325-$G$1</f>
+        <f t="shared" si="5"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D325" s="1">
@@ -8606,7 +8605,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C326">
-        <f>B326-$G$1</f>
+        <f t="shared" si="5"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D326" s="1">
@@ -8627,7 +8626,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C327">
-        <f>B327-$G$1</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D327" s="1">
@@ -8648,7 +8647,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C328">
-        <f>B328-$G$1</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D328" s="1">
@@ -8669,7 +8668,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C329">
-        <f>B329-$G$1</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D329" s="1">
@@ -8690,7 +8689,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C330">
-        <f>B330-$G$1</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D330" s="1">
@@ -8711,7 +8710,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C331">
-        <f>B331-$G$1</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D331" s="1">
@@ -8732,7 +8731,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C332">
-        <f>B332-$G$1</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D332" s="1">
@@ -8753,7 +8752,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C333">
-        <f>B333-$G$1</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D333" s="1">
@@ -8774,7 +8773,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C334">
-        <f>B334-$G$1</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D334" s="1">
@@ -8795,7 +8794,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C335">
-        <f>B335-$G$1</f>
+        <f t="shared" si="5"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D335" s="1">
@@ -8816,7 +8815,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C336">
-        <f>B336-$G$1</f>
+        <f t="shared" si="5"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D336" s="1">
@@ -8837,7 +8836,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C337">
-        <f>B337-$G$1</f>
+        <f t="shared" si="5"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D337" s="1">
@@ -8858,7 +8857,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C338">
-        <f>B338-$G$1</f>
+        <f t="shared" si="5"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D338" s="1">
@@ -8879,7 +8878,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C339">
-        <f>B339-$G$1</f>
+        <f t="shared" si="5"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D339" s="1">
@@ -8900,7 +8899,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C340">
-        <f>B340-$G$1</f>
+        <f t="shared" si="5"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D340" s="1">
@@ -8921,7 +8920,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C341">
-        <f>B341-$G$1</f>
+        <f t="shared" si="5"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D341" s="1">
@@ -8942,7 +8941,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C342">
-        <f>B342-$G$1</f>
+        <f t="shared" si="5"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D342" s="1">
@@ -8963,7 +8962,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C343">
-        <f>B343-$G$1</f>
+        <f t="shared" si="5"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D343" s="1">
@@ -8984,7 +8983,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C344">
-        <f>B344-$G$1</f>
+        <f t="shared" si="5"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D344" s="1">
@@ -9005,7 +9004,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C345">
-        <f>B345-$G$1</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D345" s="1">
@@ -9026,7 +9025,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C346">
-        <f>B346-$G$1</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D346" s="1">
@@ -9047,7 +9046,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C347">
-        <f>B347-$G$1</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D347" s="1">
@@ -9068,7 +9067,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C348">
-        <f>B348-$G$1</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D348" s="1">
@@ -9089,7 +9088,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C349">
-        <f>B349-$G$1</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D349" s="1">
@@ -9110,7 +9109,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C350">
-        <f>B350-$G$1</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D350" s="1">
@@ -9131,7 +9130,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C351">
-        <f>B351-$G$1</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D351" s="1">
@@ -9152,7 +9151,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C352">
-        <f>B352-$G$1</f>
+        <f t="shared" si="5"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D352" s="1">
@@ -9173,7 +9172,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C353">
-        <f>B353-$G$1</f>
+        <f t="shared" si="5"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D353" s="1">
@@ -9194,7 +9193,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C354">
-        <f>B354-$G$1</f>
+        <f t="shared" si="5"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D354" s="1">
@@ -9215,7 +9214,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C355">
-        <f>B355-$G$1</f>
+        <f t="shared" si="5"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D355" s="1">
@@ -9236,7 +9235,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C356">
-        <f>B356-$G$1</f>
+        <f t="shared" si="5"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D356" s="1">
@@ -9257,7 +9256,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C357">
-        <f>B357-$G$1</f>
+        <f t="shared" si="5"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D357" s="1">
@@ -9278,7 +9277,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C358">
-        <f>B358-$G$1</f>
+        <f t="shared" si="5"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D358" s="1">
@@ -9299,7 +9298,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C359">
-        <f>B359-$G$1</f>
+        <f t="shared" si="5"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D359" s="1">
@@ -9320,7 +9319,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C360">
-        <f>B360-$G$1</f>
+        <f t="shared" si="5"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D360" s="1">
@@ -9341,7 +9340,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C361">
-        <f>B361-$G$1</f>
+        <f t="shared" si="5"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D361" s="1">
@@ -9362,7 +9361,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C362">
-        <f>B362-$G$1</f>
+        <f t="shared" si="5"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D362" s="1">
@@ -9383,7 +9382,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C363">
-        <f>B363-$G$1</f>
+        <f t="shared" si="5"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D363" s="1">
@@ -9404,7 +9403,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C364">
-        <f>B364-$G$1</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D364" s="1">
@@ -9425,7 +9424,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C365">
-        <f>B365-$G$1</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D365" s="1">
@@ -9446,7 +9445,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C366">
-        <f>B366-$G$1</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D366" s="1">
@@ -9467,7 +9466,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C367">
-        <f>B367-$G$1</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D367" s="1">
@@ -9488,7 +9487,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C368">
-        <f>B368-$G$1</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D368" s="1">
@@ -9509,7 +9508,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C369">
-        <f>B369-$G$1</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D369" s="1">
@@ -9530,7 +9529,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C370">
-        <f>B370-$G$1</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D370" s="1">
@@ -9551,7 +9550,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C371">
-        <f>B371-$G$1</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D371" s="1">
@@ -9572,7 +9571,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C372">
-        <f>B372-$G$1</f>
+        <f t="shared" si="5"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D372" s="1">
@@ -9593,7 +9592,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C373">
-        <f>B373-$G$1</f>
+        <f t="shared" si="5"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D373" s="1">
@@ -9614,7 +9613,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C374">
-        <f>B374-$G$1</f>
+        <f t="shared" si="5"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D374" s="1">
@@ -9635,7 +9634,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C375">
-        <f>B375-$G$1</f>
+        <f t="shared" si="5"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D375" s="1">
@@ -9656,7 +9655,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C376">
-        <f>B376-$G$1</f>
+        <f t="shared" si="5"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D376" s="1">
@@ -9677,7 +9676,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C377">
-        <f>B377-$G$1</f>
+        <f t="shared" si="5"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D377" s="1">
@@ -9698,7 +9697,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C378">
-        <f>B378-$G$1</f>
+        <f t="shared" si="5"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D378" s="1">
@@ -9719,7 +9718,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C379">
-        <f>B379-$G$1</f>
+        <f t="shared" si="5"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D379" s="1">
@@ -9740,7 +9739,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C380">
-        <f>B380-$G$1</f>
+        <f t="shared" si="5"/>
         <v>-9.9999999999997868E-3</v>
       </c>
       <c r="D380" s="1">
@@ -9761,7 +9760,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C381">
-        <f>B381-$G$1</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D381" s="1">
@@ -9782,7 +9781,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C382">
-        <f>B382-$G$1</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D382" s="1">
@@ -9803,7 +9802,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C383">
-        <f>B383-$G$1</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D383" s="1">
@@ -9824,7 +9823,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C384">
-        <f>B384-$G$1</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D384" s="1">
@@ -9845,7 +9844,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C385">
-        <f>B385-$G$1</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D385" s="1">
@@ -9866,7 +9865,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C386">
-        <f>B386-$G$1</f>
+        <f t="shared" ref="C386:C449" si="6">B386-$G$1</f>
         <v>0</v>
       </c>
       <c r="D386" s="1">
@@ -9887,7 +9886,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C387">
-        <f>B387-$G$1</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="D387" s="1">
@@ -9908,7 +9907,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C388">
-        <f>B388-$G$1</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="D388" s="1">
@@ -9929,7 +9928,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C389">
-        <f>B389-$G$1</f>
+        <f t="shared" si="6"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D389" s="1">
@@ -9950,7 +9949,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C390">
-        <f>B390-$G$1</f>
+        <f t="shared" si="6"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D390" s="1">
@@ -9971,7 +9970,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C391">
-        <f>B391-$G$1</f>
+        <f t="shared" si="6"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D391" s="1">
@@ -9992,7 +9991,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C392">
-        <f>B392-$G$1</f>
+        <f t="shared" si="6"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D392" s="1">
@@ -10013,7 +10012,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C393">
-        <f>B393-$G$1</f>
+        <f t="shared" si="6"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D393" s="1">
@@ -10031,7 +10030,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C394">
-        <f>B394-$G$1</f>
+        <f t="shared" si="6"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D394" s="1">
@@ -10050,7 +10049,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C395">
-        <f>B395-$G$1</f>
+        <f t="shared" si="6"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D395" s="1">
@@ -10069,7 +10068,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="C396">
-        <f>B396-$G$1</f>
+        <f t="shared" si="6"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="D396" s="1">

--- a/Legge di Hooke.xlsx
+++ b/Legge di Hooke.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="450" documentId="8_{776634F0-C4C9-4588-BBA4-07B3E3D5FCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77AB726E-B7F6-4945-97E0-76C0DCE162BE}"/>
+  <xr:revisionPtr revIDLastSave="470" documentId="8_{776634F0-C4C9-4588-BBA4-07B3E3D5FCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DCFDAA5-4433-45A6-8E8B-365979AD17E7}"/>
   <bookViews>
-    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{90936311-A4D2-4EF7-9615-E94103A7D1D9}"/>
+    <workbookView xWindow="675" yWindow="1657" windowWidth="16200" windowHeight="9308" xr2:uid="{90936311-A4D2-4EF7-9615-E94103A7D1D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Misure statiche 1" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Molle in serie'!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -48,12 +49,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="26">
   <si>
     <t>m[g]</t>
-  </si>
-  <si>
-    <t>incertezza m [g]</t>
   </si>
   <si>
     <t>posizione</t>
@@ -117,6 +115,18 @@
   </si>
   <si>
     <t>Accelerazione</t>
+  </si>
+  <si>
+    <t>m[kg]</t>
+  </si>
+  <si>
+    <t>incertezza m [kg]</t>
+  </si>
+  <si>
+    <t>posizione[m]</t>
+  </si>
+  <si>
+    <t>allungamento [m]</t>
   </si>
 </sst>
 </file>
@@ -272,7 +282,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -308,6 +318,9 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -649,33 +662,33 @@
   <sheetData>
     <row r="1" spans="1:7" ht="39.75">
       <c r="A1" s="3" t="s">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="1">
-        <v>50</v>
-      </c>
-      <c r="B2" s="1">
-        <v>1</v>
+      <c r="A2" s="21">
+        <v>0.05</v>
+      </c>
+      <c r="B2" s="19">
+        <v>1E-3</v>
       </c>
       <c r="C2" s="1">
         <v>1.24</v>
@@ -694,8 +707,8 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="1">
-        <v>100</v>
+      <c r="A3" s="21">
+        <v>0.1</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="1">
@@ -711,8 +724,8 @@
       <c r="G3" s="2"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="1">
-        <v>200</v>
+      <c r="A4" s="21">
+        <v>0.2</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="1">
@@ -728,8 +741,8 @@
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="1">
-        <v>300</v>
+      <c r="A5" s="21">
+        <v>0.3</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="1">
@@ -745,8 +758,8 @@
       <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="1">
-        <v>400</v>
+      <c r="A6" s="21">
+        <v>0.4</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="20">
@@ -762,8 +775,8 @@
       <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="1">
-        <v>500</v>
+      <c r="A7" s="21">
+        <v>0.5</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="1">
@@ -779,8 +792,8 @@
       <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="1">
-        <v>600</v>
+      <c r="A8" s="21">
+        <v>0.6</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="1">
@@ -796,8 +809,8 @@
       <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="1">
-        <v>700</v>
+      <c r="A9" s="21">
+        <v>0.7</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="1">
@@ -813,8 +826,8 @@
       <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="1">
-        <v>800</v>
+      <c r="A10" s="21">
+        <v>0.8</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="1">
@@ -830,8 +843,8 @@
       <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="1">
-        <v>900</v>
+      <c r="A11" s="21">
+        <v>0.9</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="1">
@@ -861,19 +874,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1004,16 +1017,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="E1" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1060,7 +1073,7 @@
         <v>1.06</v>
       </c>
       <c r="C4" s="2">
-        <f t="shared" ref="C3:C6" si="1">$E$2-B4</f>
+        <f t="shared" ref="C4:C6" si="1">$E$2-B4</f>
         <v>0.10999999999999988</v>
       </c>
       <c r="D4" s="2">
@@ -1145,19 +1158,19 @@
         <v>550</v>
       </c>
       <c r="H1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="K1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="L1" s="13" t="s">
         <v>10</v>
-      </c>
-      <c r="K1" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="13" t="s">
-        <v>11</v>
       </c>
       <c r="M1">
         <v>11.3</v>
@@ -1202,7 +1215,7 @@
         <v>6.7075485130871235E-2</v>
       </c>
       <c r="L2" s="18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1244,7 +1257,7 @@
         <v>0.18601499145723874</v>
       </c>
       <c r="L3" s="18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1286,7 +1299,7 @@
         <v>0.31113123214987526</v>
       </c>
       <c r="L4" s="18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1328,7 +1341,7 @@
         <v>0.42731711305976344</v>
       </c>
       <c r="L5" s="18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="14.65" thickBot="1">
@@ -1370,12 +1383,12 @@
         <v>0.56043505251155346</v>
       </c>
       <c r="L6" s="18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" s="6">
         <f>AVERAGE(B2:B6)</f>
@@ -1418,12 +1431,12 @@
         <v>0.67730949012262742</v>
       </c>
       <c r="L7" s="18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8">
         <f t="shared" ref="B8" si="2">_xlfn.STDEV.S(B2:B6)</f>
@@ -1452,7 +1465,7 @@
     </row>
     <row r="9" spans="1:13" ht="14.65" thickBot="1">
       <c r="A9" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="9">
         <f>B8/SQRT(5)</f>
@@ -1497,16 +1510,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -1641,16 +1654,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="E1" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1774,22 +1787,22 @@
   <sheetData>
     <row r="1" spans="1:7" ht="39">
       <c r="A1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="G1" s="1">
         <v>1.1299999999999999</v>
@@ -9865,7 +9878,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C386">
-        <f t="shared" ref="C386:C449" si="6">B386-$G$1</f>
+        <f t="shared" ref="C386:C396" si="6">B386-$G$1</f>
         <v>0</v>
       </c>
       <c r="D386" s="1">

--- a/Legge di Hooke.xlsx
+++ b/Legge di Hooke.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="470" documentId="8_{776634F0-C4C9-4588-BBA4-07B3E3D5FCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DCFDAA5-4433-45A6-8E8B-365979AD17E7}"/>
+  <xr:revisionPtr revIDLastSave="478" documentId="8_{776634F0-C4C9-4588-BBA4-07B3E3D5FCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7721969C-A558-4808-A139-C6B147DE1BFF}"/>
   <bookViews>
-    <workbookView xWindow="675" yWindow="1657" windowWidth="16200" windowHeight="9308" xr2:uid="{90936311-A4D2-4EF7-9615-E94103A7D1D9}"/>
+    <workbookView xWindow="675" yWindow="1657" windowWidth="16200" windowHeight="9308" firstSheet="1" activeTab="3" xr2:uid="{90936311-A4D2-4EF7-9615-E94103A7D1D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Misure statiche 1" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="27">
   <si>
     <t>m[g]</t>
   </si>
@@ -127,6 +127,9 @@
   </si>
   <si>
     <t>allungamento [m]</t>
+  </si>
+  <si>
+    <t>Masse</t>
   </si>
 </sst>
 </file>
@@ -305,8 +308,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -323,6 +324,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="11" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -684,10 +687,10 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="21">
+      <c r="A2" s="19">
         <v>0.05</v>
       </c>
-      <c r="B2" s="19">
+      <c r="B2" s="17">
         <v>1E-3</v>
       </c>
       <c r="C2" s="1">
@@ -707,7 +710,7 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="21">
+      <c r="A3" s="19">
         <v>0.1</v>
       </c>
       <c r="B3" s="2"/>
@@ -724,7 +727,7 @@
       <c r="G3" s="2"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="21">
+      <c r="A4" s="19">
         <v>0.2</v>
       </c>
       <c r="B4" s="2"/>
@@ -741,7 +744,7 @@
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="21">
+      <c r="A5" s="19">
         <v>0.3</v>
       </c>
       <c r="B5" s="2"/>
@@ -758,11 +761,11 @@
       <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="21">
+      <c r="A6" s="19">
         <v>0.4</v>
       </c>
       <c r="B6" s="2"/>
-      <c r="C6" s="20">
+      <c r="C6" s="18">
         <v>1.1299999999999999</v>
       </c>
       <c r="D6" s="1">
@@ -775,7 +778,7 @@
       <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="21">
+      <c r="A7" s="19">
         <v>0.5</v>
       </c>
       <c r="B7" s="2"/>
@@ -792,7 +795,7 @@
       <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="21">
+      <c r="A8" s="19">
         <v>0.6</v>
       </c>
       <c r="B8" s="2"/>
@@ -809,7 +812,7 @@
       <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="21">
+      <c r="A9" s="19">
         <v>0.7</v>
       </c>
       <c r="B9" s="2"/>
@@ -826,7 +829,7 @@
       <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="21">
+      <c r="A10" s="19">
         <v>0.8</v>
       </c>
       <c r="B10" s="4"/>
@@ -843,7 +846,7 @@
       <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="21">
+      <c r="A11" s="19">
         <v>0.9</v>
       </c>
       <c r="B11" s="2"/>
@@ -1138,24 +1141,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="5"/>
-      <c r="B1" s="14">
-        <v>50</v>
-      </c>
-      <c r="C1" s="14">
-        <v>150</v>
-      </c>
-      <c r="D1" s="14">
-        <v>250</v>
-      </c>
-      <c r="E1" s="14">
-        <v>350</v>
-      </c>
-      <c r="F1" s="14">
-        <v>450</v>
-      </c>
-      <c r="G1" s="15">
-        <v>550</v>
+      <c r="A1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="20">
+        <v>0.05</v>
+      </c>
+      <c r="C1" s="20">
+        <v>0.15</v>
+      </c>
+      <c r="D1" s="20">
+        <v>0.25</v>
+      </c>
+      <c r="E1" s="20">
+        <v>0.35</v>
+      </c>
+      <c r="F1" s="20">
+        <v>0.45</v>
+      </c>
+      <c r="G1" s="21">
+        <v>0.55000000000000004</v>
       </c>
       <c r="H1" t="s">
         <v>8</v>
@@ -1200,7 +1205,7 @@
       </c>
       <c r="H2">
         <f>$B1+$M$1/3</f>
-        <v>53.766666666666666</v>
+        <v>3.8166666666666669</v>
       </c>
       <c r="I2">
         <f>2*PI()/B7</f>
@@ -1214,12 +1219,12 @@
         <f>I2^2</f>
         <v>6.7075485130871235E-2</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="L2" s="16" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="16">
+      <c r="A3" s="14">
         <v>2</v>
       </c>
       <c r="B3">
@@ -1242,7 +1247,7 @@
       </c>
       <c r="H3">
         <f>$C1+$M$1/3</f>
-        <v>153.76666666666668</v>
+        <v>3.916666666666667</v>
       </c>
       <c r="I3">
         <f>2*PI()/C7</f>
@@ -1256,12 +1261,12 @@
         <f t="shared" ref="K3:K7" si="0">I3^2</f>
         <v>0.18601499145723874</v>
       </c>
-      <c r="L3" s="18" t="s">
+      <c r="L3" s="16" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="16">
+      <c r="A4" s="14">
         <v>3</v>
       </c>
       <c r="B4">
@@ -1284,7 +1289,7 @@
       </c>
       <c r="H4">
         <f>$D1+$M$1/3</f>
-        <v>253.76666666666668</v>
+        <v>4.0166666666666675</v>
       </c>
       <c r="I4">
         <f>2*PI()/D7</f>
@@ -1298,12 +1303,12 @@
         <f t="shared" si="0"/>
         <v>0.31113123214987526</v>
       </c>
-      <c r="L4" s="18" t="s">
+      <c r="L4" s="16" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="16">
+      <c r="A5" s="14">
         <v>4</v>
       </c>
       <c r="B5">
@@ -1326,7 +1331,7 @@
       </c>
       <c r="H5">
         <f>$E1+$M$1/3</f>
-        <v>353.76666666666665</v>
+        <v>4.1166666666666671</v>
       </c>
       <c r="I5">
         <f>2*PI()/E$7</f>
@@ -1340,12 +1345,12 @@
         <f t="shared" si="0"/>
         <v>0.42731711305976344</v>
       </c>
-      <c r="L5" s="18" t="s">
+      <c r="L5" s="16" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="14.65" thickBot="1">
-      <c r="A6" s="16">
+      <c r="A6" s="14">
         <v>5</v>
       </c>
       <c r="B6">
@@ -1368,7 +1373,7 @@
       </c>
       <c r="H6">
         <f>$F1+$M$1/3</f>
-        <v>453.76666666666665</v>
+        <v>4.2166666666666668</v>
       </c>
       <c r="I6">
         <f>2*PI()/F$7</f>
@@ -1382,7 +1387,7 @@
         <f t="shared" si="0"/>
         <v>0.56043505251155346</v>
       </c>
-      <c r="L6" s="18" t="s">
+      <c r="L6" s="16" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1416,7 +1421,7 @@
       </c>
       <c r="H7">
         <f>$G1+$M$1/3</f>
-        <v>553.76666666666665</v>
+        <v>4.3166666666666673</v>
       </c>
       <c r="I7">
         <f>2*PI()/G7</f>
@@ -1430,7 +1435,7 @@
         <f t="shared" si="0"/>
         <v>0.67730949012262742</v>
       </c>
-      <c r="L7" s="18" t="s">
+      <c r="L7" s="16" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1616,7 +1621,7 @@
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
-      <c r="G8" s="17"/>
+      <c r="G8" s="15"/>
     </row>
     <row r="9" spans="1:7">
       <c r="D9" s="2"/>
@@ -2369,7 +2374,7 @@
       <c r="E28" s="1">
         <v>-7.0000000000000007E-2</v>
       </c>
-      <c r="F28" s="19">
+      <c r="F28" s="17">
         <v>4.2000000000000002E-4</v>
       </c>
     </row>
@@ -5327,7 +5332,7 @@
       <c r="D169" s="1">
         <v>3.34</v>
       </c>
-      <c r="E169" s="19">
+      <c r="E169" s="17">
         <v>4.66E-4</v>
       </c>
       <c r="F169" s="1">
@@ -5335,7 +5340,7 @@
       </c>
     </row>
     <row r="170" spans="1:6">
-      <c r="A170" s="19">
+      <c r="A170" s="17">
         <v>4.66E-4</v>
       </c>
       <c r="B170" s="1">
@@ -5726,7 +5731,7 @@
       <c r="D188" s="1">
         <v>3.72</v>
       </c>
-      <c r="E188" s="19">
+      <c r="E188" s="17">
         <v>2.9799999999999998E-4</v>
       </c>
       <c r="F188" s="1">
@@ -5734,7 +5739,7 @@
       </c>
     </row>
     <row r="189" spans="1:6">
-      <c r="A189" s="19">
+      <c r="A189" s="17">
         <v>2.9799999999999998E-4</v>
       </c>
       <c r="B189" s="1">
@@ -6296,7 +6301,7 @@
       <c r="E215" s="1">
         <v>-7.0000000000000007E-2</v>
       </c>
-      <c r="F215" s="19">
+      <c r="F215" s="17">
         <v>1.75E-4</v>
       </c>
     </row>
@@ -6902,7 +6907,7 @@
       <c r="D244" s="1">
         <v>4.84</v>
       </c>
-      <c r="E244" s="19">
+      <c r="E244" s="17">
         <v>-1.15E-5</v>
       </c>
       <c r="F244" s="1">
@@ -6910,7 +6915,7 @@
       </c>
     </row>
     <row r="245" spans="1:6">
-      <c r="A245" s="19">
+      <c r="A245" s="17">
         <v>-1.15E-5</v>
       </c>
       <c r="B245" s="1">
@@ -8078,7 +8083,7 @@
       <c r="D300" s="1">
         <v>5.96</v>
       </c>
-      <c r="E300" s="19">
+      <c r="E300" s="17">
         <v>2.9700000000000001E-4</v>
       </c>
       <c r="F300" s="1">
@@ -8086,7 +8091,7 @@
       </c>
     </row>
     <row r="301" spans="1:6">
-      <c r="A301" s="19">
+      <c r="A301" s="17">
         <v>2.9700000000000001E-4</v>
       </c>
       <c r="B301" s="1">
@@ -8249,7 +8254,7 @@
       <c r="E308" s="1">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F308" s="19">
+      <c r="F308" s="17">
         <v>-1.45E-4</v>
       </c>
     </row>
@@ -8477,7 +8482,7 @@
       <c r="D319" s="1">
         <v>6.34</v>
       </c>
-      <c r="E319" s="19">
+      <c r="E319" s="17">
         <v>7.0299999999999996E-4</v>
       </c>
       <c r="F319" s="1">
@@ -8485,7 +8490,7 @@
       </c>
     </row>
     <row r="320" spans="1:6">
-      <c r="A320" s="19">
+      <c r="A320" s="17">
         <v>7.0299999999999996E-4</v>
       </c>
       <c r="B320" s="1">
@@ -8876,7 +8881,7 @@
       <c r="D338" s="1">
         <v>6.72</v>
       </c>
-      <c r="E338" s="19">
+      <c r="E338" s="17">
         <v>9.9500000000000001E-4</v>
       </c>
       <c r="F338" s="1">
@@ -8884,7 +8889,7 @@
       </c>
     </row>
     <row r="339" spans="1:6">
-      <c r="A339" s="19">
+      <c r="A339" s="17">
         <v>9.9500000000000001E-4</v>
       </c>
       <c r="B339" s="1">

--- a/Legge di Hooke.xlsx
+++ b/Legge di Hooke.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="478" documentId="8_{776634F0-C4C9-4588-BBA4-07B3E3D5FCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7721969C-A558-4808-A139-C6B147DE1BFF}"/>
+  <xr:revisionPtr revIDLastSave="479" documentId="8_{776634F0-C4C9-4588-BBA4-07B3E3D5FCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B731EA25-84E0-4526-9ACB-15867CC605B2}"/>
   <bookViews>
     <workbookView xWindow="675" yWindow="1657" windowWidth="16200" windowHeight="9308" firstSheet="1" activeTab="3" xr2:uid="{90936311-A4D2-4EF7-9615-E94103A7D1D9}"/>
   </bookViews>
@@ -285,7 +285,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -326,6 +326,7 @@
     </xf>
     <xf numFmtId="11" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1177,8 +1178,8 @@
       <c r="L1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="M1">
-        <v>11.3</v>
+      <c r="M1" s="22">
+        <v>1.1299999999999999E-2</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -1205,7 +1206,7 @@
       </c>
       <c r="H2">
         <f>$B1+$M$1/3</f>
-        <v>3.8166666666666669</v>
+        <v>5.3766666666666671E-2</v>
       </c>
       <c r="I2">
         <f>2*PI()/B7</f>
@@ -1247,7 +1248,7 @@
       </c>
       <c r="H3">
         <f>$C1+$M$1/3</f>
-        <v>3.916666666666667</v>
+        <v>0.15376666666666666</v>
       </c>
       <c r="I3">
         <f>2*PI()/C7</f>
@@ -1289,7 +1290,7 @@
       </c>
       <c r="H4">
         <f>$D1+$M$1/3</f>
-        <v>4.0166666666666675</v>
+        <v>0.25376666666666664</v>
       </c>
       <c r="I4">
         <f>2*PI()/D7</f>
@@ -1331,7 +1332,7 @@
       </c>
       <c r="H5">
         <f>$E1+$M$1/3</f>
-        <v>4.1166666666666671</v>
+        <v>0.35376666666666662</v>
       </c>
       <c r="I5">
         <f>2*PI()/E$7</f>
@@ -1373,7 +1374,7 @@
       </c>
       <c r="H6">
         <f>$F1+$M$1/3</f>
-        <v>4.2166666666666668</v>
+        <v>0.45376666666666665</v>
       </c>
       <c r="I6">
         <f>2*PI()/F$7</f>
@@ -1421,7 +1422,7 @@
       </c>
       <c r="H7">
         <f>$G1+$M$1/3</f>
-        <v>4.3166666666666673</v>
+        <v>0.55376666666666674</v>
       </c>
       <c r="I7">
         <f>2*PI()/G7</f>

--- a/Legge di Hooke.xlsx
+++ b/Legge di Hooke.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="479" documentId="8_{776634F0-C4C9-4588-BBA4-07B3E3D5FCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B731EA25-84E0-4526-9ACB-15867CC605B2}"/>
+  <xr:revisionPtr revIDLastSave="501" documentId="8_{776634F0-C4C9-4588-BBA4-07B3E3D5FCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB874DA4-D713-419D-AF5A-E008DE7E01A6}"/>
   <bookViews>
-    <workbookView xWindow="675" yWindow="1657" windowWidth="16200" windowHeight="9308" firstSheet="1" activeTab="3" xr2:uid="{90936311-A4D2-4EF7-9615-E94103A7D1D9}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="3" xr2:uid="{90936311-A4D2-4EF7-9615-E94103A7D1D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Misure statiche 1" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="23">
   <si>
     <t>m[g]</t>
   </si>
@@ -69,21 +69,6 @@
     <t>incertezza su d</t>
   </si>
   <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>T^2</t>
-  </si>
-  <si>
-    <t>m(g)</t>
-  </si>
-  <si>
-    <t>σΤ</t>
-  </si>
-  <si>
-    <t>σT^2</t>
-  </si>
-  <si>
     <t>d</t>
   </si>
   <si>
@@ -94,9 +79,6 @@
   </si>
   <si>
     <t>Dev.std.med</t>
-  </si>
-  <si>
-    <t>0.0037153038120194804</t>
   </si>
   <si>
     <t>Position (m) Run #6</t>
@@ -129,7 +111,13 @@
     <t>allungamento [m]</t>
   </si>
   <si>
-    <t>Masse</t>
+    <t>Masse (kg)</t>
+  </si>
+  <si>
+    <t>Masse corrette(Kg)</t>
+  </si>
+  <si>
+    <t>Massa molla (kg)</t>
   </si>
 </sst>
 </file>
@@ -184,7 +172,7 @@
       <name val="Arial Unicode MS"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -203,8 +191,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -281,11 +275,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -299,7 +304,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
@@ -307,7 +311,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -324,9 +327,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -666,16 +675,16 @@
   <sheetData>
     <row r="1" spans="1:7" ht="39.75">
       <c r="A1" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>3</v>
@@ -688,10 +697,10 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="19">
+      <c r="A2" s="17">
         <v>0.05</v>
       </c>
-      <c r="B2" s="17">
+      <c r="B2" s="15">
         <v>1E-3</v>
       </c>
       <c r="C2" s="1">
@@ -711,7 +720,7 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="19">
+      <c r="A3" s="17">
         <v>0.1</v>
       </c>
       <c r="B3" s="2"/>
@@ -728,7 +737,7 @@
       <c r="G3" s="2"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="19">
+      <c r="A4" s="17">
         <v>0.2</v>
       </c>
       <c r="B4" s="2"/>
@@ -745,7 +754,7 @@
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="19">
+      <c r="A5" s="17">
         <v>0.3</v>
       </c>
       <c r="B5" s="2"/>
@@ -762,11 +771,11 @@
       <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="19">
+      <c r="A6" s="17">
         <v>0.4</v>
       </c>
       <c r="B6" s="2"/>
-      <c r="C6" s="18">
+      <c r="C6" s="16">
         <v>1.1299999999999999</v>
       </c>
       <c r="D6" s="1">
@@ -779,7 +788,7 @@
       <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="19">
+      <c r="A7" s="17">
         <v>0.5</v>
       </c>
       <c r="B7" s="2"/>
@@ -796,7 +805,7 @@
       <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="19">
+      <c r="A8" s="17">
         <v>0.6</v>
       </c>
       <c r="B8" s="2"/>
@@ -813,7 +822,7 @@
       <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="19">
+      <c r="A9" s="17">
         <v>0.7</v>
       </c>
       <c r="B9" s="2"/>
@@ -830,7 +839,7 @@
       <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="19">
+      <c r="A10" s="17">
         <v>0.8</v>
       </c>
       <c r="B10" s="4"/>
@@ -847,7 +856,7 @@
       <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="19">
+      <c r="A11" s="17">
         <v>0.9</v>
       </c>
       <c r="B11" s="2"/>
@@ -1030,7 +1039,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1132,369 +1141,283 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEF02A27-EC46-4EB5-A087-5E047C481CB0}">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="5" max="5" width="11.86328125" customWidth="1"/>
     <col min="7" max="7" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.796875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="22.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="20">
+    <row r="1" spans="1:12">
+      <c r="A1" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="18">
         <v>0.05</v>
       </c>
-      <c r="C1" s="20">
+      <c r="C1" s="18">
         <v>0.15</v>
       </c>
-      <c r="D1" s="20">
+      <c r="D1" s="18">
         <v>0.25</v>
       </c>
-      <c r="E1" s="20">
+      <c r="E1" s="18">
         <v>0.35</v>
       </c>
-      <c r="F1" s="20">
+      <c r="F1" s="18">
         <v>0.45</v>
       </c>
-      <c r="G1" s="21">
+      <c r="G1" s="19">
         <v>0.55000000000000004</v>
       </c>
-      <c r="H1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="13" t="s">
+      <c r="H1" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="6">
+        <v>1</v>
+      </c>
+      <c r="B2" s="21">
+        <v>23.844000000000001</v>
+      </c>
+      <c r="C2" s="21">
+        <v>14.49</v>
+      </c>
+      <c r="D2" s="21">
+        <v>11.285</v>
+      </c>
+      <c r="E2" s="21">
+        <v>9.6229999999999993</v>
+      </c>
+      <c r="F2" s="21">
+        <v>8.3829999999999991</v>
+      </c>
+      <c r="G2" s="7">
+        <v>7.6909999999999998</v>
+      </c>
+      <c r="H2" s="6">
+        <f>$B1+$I$2/3</f>
+        <v>5.3766666666666671E-2</v>
+      </c>
+      <c r="I2" s="24">
+        <v>1.1299999999999999E-2</v>
+      </c>
+      <c r="L2" s="14"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="12">
+        <v>2</v>
+      </c>
+      <c r="B3" s="21">
+        <v>24.542999999999999</v>
+      </c>
+      <c r="C3" s="21">
+        <v>14.622</v>
+      </c>
+      <c r="D3" s="21">
+        <v>11.177</v>
+      </c>
+      <c r="E3" s="21">
+        <v>9.5730000000000004</v>
+      </c>
+      <c r="F3" s="21">
+        <v>8.4060000000000006</v>
+      </c>
+      <c r="G3" s="7">
+        <v>7.5910000000000002</v>
+      </c>
+      <c r="H3" s="6">
+        <f>$C1+$I$2/3</f>
+        <v>0.15376666666666666</v>
+      </c>
+      <c r="I3" s="7"/>
+      <c r="L3" s="14"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="12">
+        <v>3</v>
+      </c>
+      <c r="B4" s="21">
+        <v>24.13</v>
+      </c>
+      <c r="C4" s="21">
+        <v>14.653</v>
+      </c>
+      <c r="D4" s="21">
+        <v>11.301</v>
+      </c>
+      <c r="E4" s="21">
+        <v>9.6159999999999997</v>
+      </c>
+      <c r="F4" s="21">
+        <v>8.3879999999999999</v>
+      </c>
+      <c r="G4" s="7">
+        <v>7.6589999999999998</v>
+      </c>
+      <c r="H4" s="6">
+        <f>$D1+$I$2/3</f>
+        <v>0.25376666666666664</v>
+      </c>
+      <c r="I4" s="7"/>
+      <c r="L4" s="14"/>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="12">
+        <v>4</v>
+      </c>
+      <c r="B5" s="21">
+        <v>24.36</v>
+      </c>
+      <c r="C5" s="21">
+        <v>14.534000000000001</v>
+      </c>
+      <c r="D5" s="21">
+        <v>11.298999999999999</v>
+      </c>
+      <c r="E5" s="21">
+        <v>9.6300000000000008</v>
+      </c>
+      <c r="F5" s="21">
+        <v>8.3859999999999992</v>
+      </c>
+      <c r="G5" s="7">
+        <v>7.6</v>
+      </c>
+      <c r="H5" s="6">
+        <f>$E1+$I$2/3</f>
+        <v>0.35376666666666662</v>
+      </c>
+      <c r="I5" s="7"/>
+      <c r="L5" s="14"/>
+    </row>
+    <row r="6" spans="1:12" ht="14.65" thickBot="1">
+      <c r="A6" s="12">
+        <v>5</v>
+      </c>
+      <c r="B6" s="21">
+        <v>24.425000000000001</v>
+      </c>
+      <c r="C6" s="21">
+        <v>14.542</v>
+      </c>
+      <c r="D6" s="21">
+        <v>11.26</v>
+      </c>
+      <c r="E6" s="21">
+        <v>9.6170000000000009</v>
+      </c>
+      <c r="F6" s="21">
+        <v>8.4019999999999992</v>
+      </c>
+      <c r="G6" s="7">
+        <v>7.6319999999999997</v>
+      </c>
+      <c r="H6" s="6">
+        <f>$F1+$I$2/3</f>
+        <v>0.45376666666666665</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="L6" s="14"/>
+    </row>
+    <row r="7" spans="1:12" ht="14.65" thickBot="1">
+      <c r="A7" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="22">
-        <v>1.1299999999999999E-2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="7">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>23.844000000000001</v>
-      </c>
-      <c r="C2">
-        <v>14.49</v>
-      </c>
-      <c r="D2">
-        <v>11.285</v>
-      </c>
-      <c r="E2">
-        <v>9.6229999999999993</v>
-      </c>
-      <c r="F2">
-        <v>8.3829999999999991</v>
-      </c>
-      <c r="G2" s="8">
-        <v>7.6909999999999998</v>
-      </c>
-      <c r="H2">
-        <f>$B1+$M$1/3</f>
-        <v>5.3766666666666671E-2</v>
-      </c>
-      <c r="I2">
-        <f>2*PI()/B7</f>
-        <v>0.25898935331567441</v>
-      </c>
-      <c r="J2">
-        <f>I2*(2*PI()/B7^2)*B9</f>
-        <v>3.4269706290817735E-4</v>
-      </c>
-      <c r="K2">
-        <f>I2^2</f>
-        <v>6.7075485130871235E-2</v>
-      </c>
-      <c r="L2" s="16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="14">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>24.542999999999999</v>
-      </c>
-      <c r="C3">
-        <v>14.622</v>
-      </c>
-      <c r="D3">
-        <v>11.177</v>
-      </c>
-      <c r="E3">
-        <v>9.5730000000000004</v>
-      </c>
-      <c r="F3">
-        <v>8.4060000000000006</v>
-      </c>
-      <c r="G3" s="8">
-        <v>7.5910000000000002</v>
-      </c>
-      <c r="H3">
-        <f>$C1+$M$1/3</f>
-        <v>0.15376666666666666</v>
-      </c>
-      <c r="I3">
-        <f>2*PI()/C7</f>
-        <v>0.43129455301132513</v>
-      </c>
-      <c r="J3">
-        <f>I3*(2*PI()/C7^2)*C9</f>
-        <v>3.8366081728098282E-4</v>
-      </c>
-      <c r="K3">
-        <f t="shared" ref="K3:K7" si="0">I3^2</f>
-        <v>0.18601499145723874</v>
-      </c>
-      <c r="L3" s="16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="14">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>24.13</v>
-      </c>
-      <c r="C4">
-        <v>14.653</v>
-      </c>
-      <c r="D4">
-        <v>11.301</v>
-      </c>
-      <c r="E4">
-        <v>9.6159999999999997</v>
-      </c>
-      <c r="F4">
-        <v>8.3879999999999999</v>
-      </c>
-      <c r="G4" s="8">
-        <v>7.6589999999999998</v>
-      </c>
-      <c r="H4">
-        <f>$D1+$M$1/3</f>
-        <v>0.25376666666666664</v>
-      </c>
-      <c r="I4">
-        <f>2*PI()/D7</f>
-        <v>0.55779138766197822</v>
-      </c>
-      <c r="J4">
-        <f>I4*(2*PI()/D7^2)*D9</f>
-        <v>6.3645316027282251E-4</v>
-      </c>
-      <c r="K4">
-        <f t="shared" si="0"/>
-        <v>0.31113123214987526</v>
-      </c>
-      <c r="L4" s="16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="14">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>24.36</v>
-      </c>
-      <c r="C5">
-        <v>14.534000000000001</v>
-      </c>
-      <c r="D5">
-        <v>11.298999999999999</v>
-      </c>
-      <c r="E5">
-        <v>9.6300000000000008</v>
-      </c>
-      <c r="F5">
-        <v>8.3859999999999992</v>
-      </c>
-      <c r="G5" s="8">
-        <v>7.6</v>
-      </c>
-      <c r="H5">
-        <f>$E1+$M$1/3</f>
-        <v>0.35376666666666662</v>
-      </c>
-      <c r="I5">
-        <f>2*PI()/E$7</f>
-        <v>0.65369496943128103</v>
-      </c>
-      <c r="J5">
-        <f>I5*(2*PI()/E7^2)*E9</f>
-        <v>4.4533067242994513E-4</v>
-      </c>
-      <c r="K5">
-        <f t="shared" si="0"/>
-        <v>0.42731711305976344</v>
-      </c>
-      <c r="L5" s="16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="14.65" thickBot="1">
-      <c r="A6" s="14">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>24.425000000000001</v>
-      </c>
-      <c r="C6">
-        <v>14.542</v>
-      </c>
-      <c r="D6">
-        <v>11.26</v>
-      </c>
-      <c r="E6">
-        <v>9.6170000000000009</v>
-      </c>
-      <c r="F6">
-        <v>8.4019999999999992</v>
-      </c>
-      <c r="G6" s="8">
-        <v>7.6319999999999997</v>
-      </c>
-      <c r="H6">
-        <f>$F1+$M$1/3</f>
-        <v>0.45376666666666665</v>
-      </c>
-      <c r="I6">
-        <f>2*PI()/F$7</f>
-        <v>0.748622102606885</v>
-      </c>
-      <c r="J6">
-        <f>I6*(2*PI()/F7^2)*F9</f>
-        <v>3.0745106222261452E-4</v>
-      </c>
-      <c r="K6">
-        <f t="shared" si="0"/>
-        <v>0.56043505251155346</v>
-      </c>
-      <c r="L6" s="16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <f>AVERAGE(B2:B6)</f>
         <v>24.260399999999997</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <f>AVERAGE(C2:C6)</f>
         <v>14.568199999999999</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <f>AVERAGE(D2:D6)</f>
         <v>11.264399999999998</v>
       </c>
-      <c r="E7" s="6">
-        <f t="shared" ref="E7:G7" si="1">AVERAGE(E2:E6)</f>
+      <c r="E7" s="5">
+        <f t="shared" ref="E7:G7" si="0">AVERAGE(E2:E6)</f>
         <v>9.6117999999999988</v>
       </c>
-      <c r="F7" s="6">
-        <f t="shared" si="1"/>
+      <c r="F7" s="5">
+        <f t="shared" si="0"/>
         <v>8.3930000000000007</v>
       </c>
-      <c r="G7" s="6">
-        <f t="shared" si="1"/>
+      <c r="G7" s="22">
+        <f t="shared" si="0"/>
         <v>7.6345999999999989</v>
       </c>
-      <c r="H7">
-        <f>$G1+$M$1/3</f>
+      <c r="H7" s="25">
+        <f>$G1+$I$2/3</f>
         <v>0.55376666666666674</v>
       </c>
-      <c r="I7">
-        <f>2*PI()/G7</f>
-        <v>0.82298814701223211</v>
-      </c>
-      <c r="J7">
-        <f>I7*(2*PI()/G7^2)*G9</f>
-        <v>1.6455760778816024E-3</v>
-      </c>
-      <c r="K7">
-        <f t="shared" si="0"/>
-        <v>0.67730949012262742</v>
-      </c>
-      <c r="L7" s="16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8">
-        <f t="shared" ref="B8" si="2">_xlfn.STDEV.S(B2:B6)</f>
+      <c r="I7" s="23"/>
+      <c r="L7" s="14"/>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="21">
+        <f t="shared" ref="B8" si="1">_xlfn.STDEV.S(B2:B6)</f>
         <v>0.27715934045238261</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="21">
         <f>_xlfn.STDEV.S(C2:C6)</f>
         <v>6.7187796510973619E-2</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="21">
         <f>_xlfn.STDEV.S(D2:D6)</f>
         <v>5.1524751333703808E-2</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="21">
         <f>_xlfn.STDEV.S(E2:E6)</f>
         <v>2.2398660674245618E-2</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="21">
         <f>_xlfn.STDEV.S(F2:F6)</f>
         <v>1.0295630140987376E-2</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="7">
         <f>_xlfn.STDEV.S(G2:G6)</f>
         <v>4.1476499370125187E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="14.65" thickBot="1">
-      <c r="A9" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="9">
+    <row r="9" spans="1:12" ht="14.65" thickBot="1">
+      <c r="A9" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="8">
         <f>B8/SQRT(5)</f>
         <v>0.12394942517010696</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="8">
         <f>C8/SQRT(5)</f>
         <v>3.0047296051392041E-2</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="8">
         <f>D8/SQRT(5)</f>
         <v>2.3042569301186932E-2</v>
       </c>
-      <c r="E9" s="9">
-        <f t="shared" ref="E9:G9" si="3">E8/SQRT(5)</f>
+      <c r="E9" s="8">
+        <f t="shared" ref="E9:G9" si="2">E8/SQRT(5)</f>
         <v>1.0016985574512895E-2</v>
       </c>
-      <c r="F9" s="9">
-        <f t="shared" si="3"/>
+      <c r="F9" s="8">
+        <f t="shared" si="2"/>
         <v>4.6043457732887032E-3</v>
       </c>
-      <c r="G9" s="9">
-        <f t="shared" si="3"/>
+      <c r="G9" s="23">
+        <f t="shared" si="2"/>
         <v>1.8548854412065423E-2</v>
       </c>
     </row>
@@ -1622,7 +1545,7 @@
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
-      <c r="G8" s="15"/>
+      <c r="G8" s="13"/>
     </row>
     <row r="9" spans="1:7">
       <c r="D9" s="2"/>
@@ -1669,7 +1592,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1793,22 +1716,22 @@
   <sheetData>
     <row r="1" spans="1:7" ht="39">
       <c r="A1" s="2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G1" s="1">
         <v>1.1299999999999999</v>
@@ -2375,7 +2298,7 @@
       <c r="E28" s="1">
         <v>-7.0000000000000007E-2</v>
       </c>
-      <c r="F28" s="17">
+      <c r="F28" s="15">
         <v>4.2000000000000002E-4</v>
       </c>
     </row>
@@ -5333,7 +5256,7 @@
       <c r="D169" s="1">
         <v>3.34</v>
       </c>
-      <c r="E169" s="17">
+      <c r="E169" s="15">
         <v>4.66E-4</v>
       </c>
       <c r="F169" s="1">
@@ -5341,7 +5264,7 @@
       </c>
     </row>
     <row r="170" spans="1:6">
-      <c r="A170" s="17">
+      <c r="A170" s="15">
         <v>4.66E-4</v>
       </c>
       <c r="B170" s="1">
@@ -5732,7 +5655,7 @@
       <c r="D188" s="1">
         <v>3.72</v>
       </c>
-      <c r="E188" s="17">
+      <c r="E188" s="15">
         <v>2.9799999999999998E-4</v>
       </c>
       <c r="F188" s="1">
@@ -5740,7 +5663,7 @@
       </c>
     </row>
     <row r="189" spans="1:6">
-      <c r="A189" s="17">
+      <c r="A189" s="15">
         <v>2.9799999999999998E-4</v>
       </c>
       <c r="B189" s="1">
@@ -6302,7 +6225,7 @@
       <c r="E215" s="1">
         <v>-7.0000000000000007E-2</v>
       </c>
-      <c r="F215" s="17">
+      <c r="F215" s="15">
         <v>1.75E-4</v>
       </c>
     </row>
@@ -6908,7 +6831,7 @@
       <c r="D244" s="1">
         <v>4.84</v>
       </c>
-      <c r="E244" s="17">
+      <c r="E244" s="15">
         <v>-1.15E-5</v>
       </c>
       <c r="F244" s="1">
@@ -6916,7 +6839,7 @@
       </c>
     </row>
     <row r="245" spans="1:6">
-      <c r="A245" s="17">
+      <c r="A245" s="15">
         <v>-1.15E-5</v>
       </c>
       <c r="B245" s="1">
@@ -8084,7 +8007,7 @@
       <c r="D300" s="1">
         <v>5.96</v>
       </c>
-      <c r="E300" s="17">
+      <c r="E300" s="15">
         <v>2.9700000000000001E-4</v>
       </c>
       <c r="F300" s="1">
@@ -8092,7 +8015,7 @@
       </c>
     </row>
     <row r="301" spans="1:6">
-      <c r="A301" s="17">
+      <c r="A301" s="15">
         <v>2.9700000000000001E-4</v>
       </c>
       <c r="B301" s="1">
@@ -8255,7 +8178,7 @@
       <c r="E308" s="1">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F308" s="17">
+      <c r="F308" s="15">
         <v>-1.45E-4</v>
       </c>
     </row>
@@ -8483,7 +8406,7 @@
       <c r="D319" s="1">
         <v>6.34</v>
       </c>
-      <c r="E319" s="17">
+      <c r="E319" s="15">
         <v>7.0299999999999996E-4</v>
       </c>
       <c r="F319" s="1">
@@ -8491,7 +8414,7 @@
       </c>
     </row>
     <row r="320" spans="1:6">
-      <c r="A320" s="17">
+      <c r="A320" s="15">
         <v>7.0299999999999996E-4</v>
       </c>
       <c r="B320" s="1">
@@ -8882,7 +8805,7 @@
       <c r="D338" s="1">
         <v>6.72</v>
       </c>
-      <c r="E338" s="17">
+      <c r="E338" s="15">
         <v>9.9500000000000001E-4</v>
       </c>
       <c r="F338" s="1">
@@ -8890,7 +8813,7 @@
       </c>
     </row>
     <row r="339" spans="1:6">
-      <c r="A339" s="17">
+      <c r="A339" s="15">
         <v>9.9500000000000001E-4</v>
       </c>
       <c r="B339" s="1">

--- a/Legge di Hooke.xlsx
+++ b/Legge di Hooke.xlsx
@@ -8,21 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="501" documentId="8_{776634F0-C4C9-4588-BBA4-07B3E3D5FCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB874DA4-D713-419D-AF5A-E008DE7E01A6}"/>
+  <xr:revisionPtr revIDLastSave="640" documentId="8_{776634F0-C4C9-4588-BBA4-07B3E3D5FCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E980182-08B8-4B7A-80A3-FA25FABC7736}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="3" xr2:uid="{90936311-A4D2-4EF7-9615-E94103A7D1D9}"/>
+    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" firstSheet="5" activeTab="5" xr2:uid="{90936311-A4D2-4EF7-9615-E94103A7D1D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Misure statiche 1" sheetId="1" r:id="rId1"/>
-    <sheet name="Misure statiche 2" sheetId="4" r:id="rId2"/>
-    <sheet name="Misure statiche 3" sheetId="5" r:id="rId3"/>
+    <sheet name="Misure statiche (molla uguale)" sheetId="4" r:id="rId2"/>
+    <sheet name="Misure statiche (molla diversa)" sheetId="5" r:id="rId3"/>
     <sheet name="Misure dinamiche" sheetId="2" r:id="rId4"/>
-    <sheet name="Molle in serie" sheetId="3" r:id="rId5"/>
-    <sheet name="Molle in parallelo" sheetId="6" r:id="rId6"/>
+    <sheet name="Molle in serie (statica)" sheetId="3" r:id="rId5"/>
+    <sheet name="Molle in parallelo (statica)" sheetId="6" r:id="rId6"/>
     <sheet name="Foglio2" sheetId="8" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Molle in serie'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Molle in serie (statica)'!$A$1:$G$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <fileRecoveryPr repairLoad="1"/>
@@ -49,27 +49,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="23">
-  <si>
-    <t>m[g]</t>
-  </si>
-  <si>
-    <t>posizione</t>
-  </si>
-  <si>
-    <t>allungamento</t>
-  </si>
-  <si>
-    <t>incertezza su all.</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="18">
   <si>
     <t>d [m] senza pesi</t>
-  </si>
-  <si>
-    <t>incertezza su d</t>
-  </si>
-  <si>
-    <t>d</t>
   </si>
   <si>
     <t>Media</t>
@@ -102,12 +84,6 @@
     <t>m[kg]</t>
   </si>
   <si>
-    <t>incertezza m [kg]</t>
-  </si>
-  <si>
-    <t>posizione[m]</t>
-  </si>
-  <si>
     <t>allungamento [m]</t>
   </si>
   <si>
@@ -119,12 +95,21 @@
   <si>
     <t>Massa molla (kg)</t>
   </si>
+  <si>
+    <t>posizione [m]</t>
+  </si>
+  <si>
+    <t>incertezza su all. [m]</t>
+  </si>
+  <si>
+    <t>incertezza su d [m]</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -150,13 +135,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -198,7 +176,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -276,6 +254,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="medium">
         <color indexed="64"/>
@@ -286,22 +279,64 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -314,17 +349,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -332,10 +361,80 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -670,207 +769,189 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2118C50C-6C33-4502-AA5F-6A538FA3A440}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="5.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.53125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="39.75">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:5" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A1" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="E1" s="37" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="14.65" thickBot="1">
+      <c r="A2" s="47">
+        <v>0.05</v>
+      </c>
+      <c r="B2" s="39">
+        <v>1.24</v>
+      </c>
+      <c r="C2" s="39">
+        <v>0.02</v>
+      </c>
+      <c r="D2" s="40">
+        <v>1.4142135619999999E-2</v>
+      </c>
+      <c r="E2" s="42">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="14.65" thickBot="1">
+      <c r="A3" s="35">
+        <v>0.1</v>
+      </c>
+      <c r="B3" s="24">
+        <v>1.23</v>
+      </c>
+      <c r="C3" s="24">
+        <v>0.03</v>
+      </c>
+      <c r="D3" s="31">
+        <v>1.4142135619999999E-2</v>
+      </c>
+      <c r="E3" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="17">
-        <v>0.05</v>
-      </c>
-      <c r="B2" s="15">
-        <v>1E-3</v>
-      </c>
-      <c r="C2" s="1">
-        <v>1.24</v>
-      </c>
-      <c r="D2" s="1">
-        <v>0.02</v>
-      </c>
-      <c r="E2" s="1">
+    </row>
+    <row r="4" spans="1:5" ht="14.65" thickBot="1">
+      <c r="A4" s="35">
+        <v>0.2</v>
+      </c>
+      <c r="B4" s="24">
+        <v>1.2</v>
+      </c>
+      <c r="C4" s="24">
+        <v>0.06</v>
+      </c>
+      <c r="D4" s="31">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="F2" s="1">
-        <v>1.26</v>
-      </c>
-      <c r="G2" s="1">
+      <c r="E4" s="42">
         <v>0.01</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="17">
+    <row r="5" spans="1:5">
+      <c r="A5" s="35">
+        <v>0.3</v>
+      </c>
+      <c r="B5" s="24">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="C5" s="24">
         <v>0.1</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="1">
-        <v>1.23</v>
-      </c>
-      <c r="D3" s="1">
-        <v>0.03</v>
-      </c>
-      <c r="E3" s="1">
+      <c r="D5" s="31">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="17">
-        <v>0.2</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="D4" s="1">
-        <v>0.06</v>
-      </c>
-      <c r="E4" s="1">
+      <c r="E5" s="25"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="35">
+        <v>0.4</v>
+      </c>
+      <c r="B6" s="24">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="C6" s="24">
+        <v>0.13</v>
+      </c>
+      <c r="D6" s="31">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="17">
-        <v>0.3</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="1">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="D5" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="E5" s="1">
+      <c r="E6" s="25"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="35">
+        <v>0.5</v>
+      </c>
+      <c r="B7" s="24">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C7" s="24">
+        <v>0.16</v>
+      </c>
+      <c r="D7" s="31">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="17">
-        <v>0.4</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="16">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="D6" s="1">
-        <v>0.13</v>
-      </c>
-      <c r="E6" s="1">
+      <c r="E7" s="25"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="35">
+        <v>0.6</v>
+      </c>
+      <c r="B8" s="24">
+        <v>1.07</v>
+      </c>
+      <c r="C8" s="24">
+        <v>0.19</v>
+      </c>
+      <c r="D8" s="31">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="17">
-        <v>0.5</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="1">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="D7" s="1">
-        <v>0.16</v>
-      </c>
-      <c r="E7" s="1">
+      <c r="E8" s="25"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="35">
+        <v>0.7</v>
+      </c>
+      <c r="B9" s="24">
+        <v>1.04</v>
+      </c>
+      <c r="C9" s="24">
+        <v>0.22</v>
+      </c>
+      <c r="D9" s="31">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="17">
-        <v>0.6</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="1">
-        <v>1.07</v>
-      </c>
-      <c r="D8" s="1">
-        <v>0.19</v>
-      </c>
-      <c r="E8" s="1">
+      <c r="E9" s="25"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="35">
+        <v>0.8</v>
+      </c>
+      <c r="B10" s="24">
+        <v>1.01</v>
+      </c>
+      <c r="C10" s="24">
+        <v>0.25</v>
+      </c>
+      <c r="D10" s="31">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="17">
-        <v>0.7</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="1">
-        <v>1.04</v>
-      </c>
-      <c r="D9" s="1">
-        <v>0.22</v>
-      </c>
-      <c r="E9" s="1">
+      <c r="E10" s="25"/>
+    </row>
+    <row r="11" spans="1:5" ht="14.65" thickBot="1">
+      <c r="A11" s="36">
+        <v>0.9</v>
+      </c>
+      <c r="B11" s="28">
+        <v>0.97</v>
+      </c>
+      <c r="C11" s="28">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="D11" s="45">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="17">
-        <v>0.8</v>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="1">
-        <v>1.01</v>
-      </c>
-      <c r="D10" s="1">
-        <v>0.25</v>
-      </c>
-      <c r="E10" s="1">
-        <v>1.4142135619999999E-2</v>
-      </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="17">
-        <v>0.9</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="1">
-        <v>0.97</v>
-      </c>
-      <c r="D11" s="1">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="E11" s="1">
-        <v>1.4142135619999999E-2</v>
-      </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
+      <c r="E11" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -879,135 +960,134 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC0F6068-CA78-42D8-919F-E852893B0BE9}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="2" max="2" width="12.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.53125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="39.75">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="1">
+    <row r="1" spans="1:5" ht="17.350000000000001" customHeight="1" thickBot="1">
+      <c r="A1" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="37" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="14.65" thickBot="1">
+      <c r="A2" s="38">
         <v>100</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="39">
         <v>1.23</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="39">
         <f>$E$2-B2</f>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="40">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="44">
         <v>1.26</v>
       </c>
-      <c r="F2" s="1">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1">
+    </row>
+    <row r="3" spans="1:5" ht="14.65" thickBot="1">
+      <c r="A3" s="23">
         <v>200</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="24">
         <v>1.19</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="24">
         <f t="shared" ref="C3:C6" si="0">$E$2-B3</f>
         <v>7.0000000000000062E-2</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="31">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1">
+      <c r="E3" s="34" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="14.65" thickBot="1">
+      <c r="A4" s="23">
         <v>300</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="24">
         <v>1.1599999999999999</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="24">
         <f t="shared" si="0"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="31">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1">
+      <c r="E4" s="42">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="23">
         <v>400</v>
       </c>
-      <c r="B5" s="1">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="C5" s="1">
+      <c r="B5" s="24">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="C5" s="24">
         <f t="shared" si="0"/>
         <v>0.13000000000000012</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="31">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="1">
+    </row>
+    <row r="6" spans="1:5" ht="14.65" thickBot="1">
+      <c r="A6" s="27">
         <v>500</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="28">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="28">
         <f t="shared" si="0"/>
         <v>0.15999999999999992</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="45">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:5">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:5">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:5">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:5">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
     </row>
@@ -1022,117 +1102,128 @@
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="4" max="4" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.53125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="26.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="1">
+    <row r="1" spans="1:6" ht="14.65" thickBot="1">
+      <c r="A1" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="37" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="14.65" thickBot="1">
+      <c r="A2" s="38">
         <v>50</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="39">
         <v>1.1100000000000001</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="41">
         <f>$E$2-B2</f>
         <v>5.9999999999999831E-2</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="43">
         <f>0.01*SQRT(2)</f>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="46">
         <v>1.17</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1">
+    <row r="3" spans="1:6" ht="14.65" thickBot="1">
+      <c r="A3" s="23">
         <v>70</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="24">
         <v>1.0900000000000001</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="25">
         <f>$E$2-B3</f>
         <v>7.9999999999999849E-2</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="26">
         <f t="shared" ref="D3:D6" si="0">0.01*SQRT(2)</f>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1">
+      <c r="E3" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="25"/>
+    </row>
+    <row r="4" spans="1:6" ht="14.65" thickBot="1">
+      <c r="A4" s="23">
         <v>100</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="24">
         <v>1.06</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="25">
         <f t="shared" ref="C4:C6" si="1">$E$2-B4</f>
         <v>0.10999999999999988</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="26">
         <f t="shared" si="0"/>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E4" s="2"/>
+      <c r="E4" s="46">
+        <v>0.01</v>
+      </c>
+      <c r="F4" s="25"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="1">
+      <c r="A5" s="23">
         <v>150</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="24">
         <v>1.01</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="25">
         <f t="shared" si="1"/>
         <v>0.15999999999999992</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="26">
         <f t="shared" si="0"/>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="1">
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+    </row>
+    <row r="6" spans="1:6" ht="14.65" thickBot="1">
+      <c r="A6" s="27">
         <v>200</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="28">
         <v>0.95</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="29">
         <f t="shared" si="1"/>
         <v>0.21999999999999997</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="30">
         <f t="shared" si="0"/>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E6" s="2"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
     </row>
     <row r="7" spans="1:6">
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1153,270 +1244,270 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="18">
+      <c r="A1" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="14">
         <v>0.05</v>
       </c>
-      <c r="C1" s="18">
+      <c r="C1" s="14">
         <v>0.15</v>
       </c>
-      <c r="D1" s="18">
+      <c r="D1" s="14">
         <v>0.25</v>
       </c>
-      <c r="E1" s="18">
+      <c r="E1" s="14">
         <v>0.35</v>
       </c>
-      <c r="F1" s="18">
+      <c r="F1" s="14">
         <v>0.45</v>
       </c>
-      <c r="G1" s="19">
+      <c r="G1" s="15">
         <v>0.55000000000000004</v>
       </c>
-      <c r="H1" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="I1" s="26" t="s">
-        <v>22</v>
+      <c r="H1" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="22" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="6">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="21">
+      <c r="B2" s="17">
         <v>23.844000000000001</v>
       </c>
-      <c r="C2" s="21">
+      <c r="C2" s="17">
         <v>14.49</v>
       </c>
-      <c r="D2" s="21">
+      <c r="D2" s="17">
         <v>11.285</v>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="17">
         <v>9.6229999999999993</v>
       </c>
-      <c r="F2" s="21">
+      <c r="F2" s="17">
         <v>8.3829999999999991</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="5">
         <v>7.6909999999999998</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="4">
         <f>$B1+$I$2/3</f>
         <v>5.3766666666666671E-2</v>
       </c>
-      <c r="I2" s="24">
+      <c r="I2" s="20">
         <v>1.1299999999999999E-2</v>
       </c>
-      <c r="L2" s="14"/>
+      <c r="L2" s="12"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="12">
+      <c r="A3" s="10">
         <v>2</v>
       </c>
-      <c r="B3" s="21">
+      <c r="B3" s="17">
         <v>24.542999999999999</v>
       </c>
-      <c r="C3" s="21">
+      <c r="C3" s="17">
         <v>14.622</v>
       </c>
-      <c r="D3" s="21">
+      <c r="D3" s="17">
         <v>11.177</v>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="17">
         <v>9.5730000000000004</v>
       </c>
-      <c r="F3" s="21">
+      <c r="F3" s="17">
         <v>8.4060000000000006</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="5">
         <v>7.5910000000000002</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="4">
         <f>$C1+$I$2/3</f>
         <v>0.15376666666666666</v>
       </c>
-      <c r="I3" s="7"/>
-      <c r="L3" s="14"/>
+      <c r="I3" s="5"/>
+      <c r="L3" s="12"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="12">
+      <c r="A4" s="10">
         <v>3</v>
       </c>
-      <c r="B4" s="21">
+      <c r="B4" s="17">
         <v>24.13</v>
       </c>
-      <c r="C4" s="21">
+      <c r="C4" s="17">
         <v>14.653</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="17">
         <v>11.301</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="17">
         <v>9.6159999999999997</v>
       </c>
-      <c r="F4" s="21">
+      <c r="F4" s="17">
         <v>8.3879999999999999</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="5">
         <v>7.6589999999999998</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="4">
         <f>$D1+$I$2/3</f>
         <v>0.25376666666666664</v>
       </c>
-      <c r="I4" s="7"/>
-      <c r="L4" s="14"/>
+      <c r="I4" s="5"/>
+      <c r="L4" s="12"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="12">
+      <c r="A5" s="10">
         <v>4</v>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="17">
         <v>24.36</v>
       </c>
-      <c r="C5" s="21">
+      <c r="C5" s="17">
         <v>14.534000000000001</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="17">
         <v>11.298999999999999</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="17">
         <v>9.6300000000000008</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="17">
         <v>8.3859999999999992</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="5">
         <v>7.6</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="4">
         <f>$E1+$I$2/3</f>
         <v>0.35376666666666662</v>
       </c>
-      <c r="I5" s="7"/>
-      <c r="L5" s="14"/>
+      <c r="I5" s="5"/>
+      <c r="L5" s="12"/>
     </row>
     <row r="6" spans="1:12" ht="14.65" thickBot="1">
-      <c r="A6" s="12">
+      <c r="A6" s="10">
         <v>5</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="17">
         <v>24.425000000000001</v>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="17">
         <v>14.542</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="17">
         <v>11.26</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="17">
         <v>9.6170000000000009</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="17">
         <v>8.4019999999999992</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="5">
         <v>7.6319999999999997</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="4">
         <f>$F1+$I$2/3</f>
         <v>0.45376666666666665</v>
       </c>
-      <c r="I6" s="7"/>
-      <c r="L6" s="14"/>
+      <c r="I6" s="5"/>
+      <c r="L6" s="12"/>
     </row>
     <row r="7" spans="1:12" ht="14.65" thickBot="1">
-      <c r="A7" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="5">
+      <c r="A7" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="3">
         <f>AVERAGE(B2:B6)</f>
         <v>24.260399999999997</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="3">
         <f>AVERAGE(C2:C6)</f>
         <v>14.568199999999999</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="3">
         <f>AVERAGE(D2:D6)</f>
         <v>11.264399999999998</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="3">
         <f t="shared" ref="E7:G7" si="0">AVERAGE(E2:E6)</f>
         <v>9.6117999999999988</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="3">
         <f t="shared" si="0"/>
         <v>8.3930000000000007</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="18">
         <f t="shared" si="0"/>
         <v>7.6345999999999989</v>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="21">
         <f>$G1+$I$2/3</f>
         <v>0.55376666666666674</v>
       </c>
-      <c r="I7" s="23"/>
-      <c r="L7" s="14"/>
+      <c r="I7" s="19"/>
+      <c r="L7" s="12"/>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="21">
+      <c r="A8" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="17">
         <f t="shared" ref="B8" si="1">_xlfn.STDEV.S(B2:B6)</f>
         <v>0.27715934045238261</v>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="17">
         <f>_xlfn.STDEV.S(C2:C6)</f>
         <v>6.7187796510973619E-2</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="17">
         <f>_xlfn.STDEV.S(D2:D6)</f>
         <v>5.1524751333703808E-2</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="17">
         <f>_xlfn.STDEV.S(E2:E6)</f>
         <v>2.2398660674245618E-2</v>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="17">
         <f>_xlfn.STDEV.S(F2:F6)</f>
         <v>1.0295630140987376E-2</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="5">
         <f>_xlfn.STDEV.S(G2:G6)</f>
         <v>4.1476499370125187E-2</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="14.65" thickBot="1">
-      <c r="A9" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="8">
+      <c r="A9" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6">
         <f>B8/SQRT(5)</f>
         <v>0.12394942517010696</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="6">
         <f>C8/SQRT(5)</f>
         <v>3.0047296051392041E-2</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="6">
         <f>D8/SQRT(5)</f>
         <v>2.3042569301186932E-2</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="6">
         <f t="shared" ref="E9:G9" si="2">E8/SQRT(5)</f>
         <v>1.0016985574512895E-2</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="6">
         <f t="shared" si="2"/>
         <v>4.6043457732887032E-3</v>
       </c>
-      <c r="G9" s="23">
+      <c r="G9" s="19">
         <f t="shared" si="2"/>
         <v>1.8548854412065423E-2</v>
       </c>
@@ -1430,111 +1521,121 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76874985-411F-489E-91EA-3A60FA49533E}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="8.1328125" customWidth="1"/>
+    <col min="2" max="2" width="12.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.53125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="39.75">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="1">
-        <v>70</v>
-      </c>
-      <c r="B2" s="1">
+    <row r="1" spans="1:7" ht="14.65" thickBot="1">
+      <c r="A1" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="37" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="14.65" thickBot="1">
+      <c r="A2" s="38">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="B2" s="39">
         <v>0.99</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="41">
         <f>$E$2-B2</f>
         <v>9.000000000000008E-2</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="43">
         <f>0.01*SQRT(2)</f>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="31">
         <v>1.08</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1">
-        <v>100</v>
-      </c>
-      <c r="B3" s="1">
+    <row r="3" spans="1:7" ht="14.65" thickBot="1">
+      <c r="A3" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="B3" s="24">
         <v>0.94</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="25">
         <f>$E$2-B3</f>
         <v>0.14000000000000012</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="26">
         <f t="shared" ref="D3:D6" si="0">0.01*SQRT(2)</f>
         <v>1.4142135623730952E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1">
-        <v>120</v>
-      </c>
-      <c r="B4" s="1">
+      <c r="E3" s="34" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="14.65" thickBot="1">
+      <c r="A4" s="23">
+        <v>0.12</v>
+      </c>
+      <c r="B4" s="24">
         <v>0.91</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="25">
         <f>$E$2-B4</f>
         <v>0.17000000000000004</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="26">
         <f t="shared" si="0"/>
         <v>1.4142135623730952E-2</v>
       </c>
+      <c r="E4" s="42">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="1">
-        <v>150</v>
-      </c>
-      <c r="B5" s="1">
+      <c r="A5" s="23">
+        <v>0.15</v>
+      </c>
+      <c r="B5" s="24">
         <v>0.87</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="25">
         <f>$E$2-B5</f>
         <v>0.21000000000000008</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="26">
         <f t="shared" si="0"/>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1">
-        <v>200</v>
-      </c>
-      <c r="B6" s="1">
+    </row>
+    <row r="6" spans="1:7" ht="14.65" thickBot="1">
+      <c r="A6" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="B6" s="28">
         <v>0.8</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="29">
         <f>$E$2-B6</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="30">
         <f t="shared" si="0"/>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:7">
       <c r="D7" s="2"/>
@@ -1545,7 +1646,7 @@
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
-      <c r="G8" s="13"/>
+      <c r="G8" s="11"/>
     </row>
     <row r="9" spans="1:7">
       <c r="D9" s="2"/>
@@ -1558,13 +1659,6 @@
       <c r="F10" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1" xr:uid="{76874985-411F-489E-91EA-3A60FA49533E}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="m[g]"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1575,129 +1669,134 @@
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.265625" customWidth="1"/>
+    <col min="1" max="1" width="5.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.53125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="26.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="1">
-        <v>100</v>
-      </c>
-      <c r="B2" s="1">
+    <row r="1" spans="1:6" ht="14.65" thickBot="1">
+      <c r="A1" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="37" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="14.65" thickBot="1">
+      <c r="A2" s="38">
+        <v>0.1</v>
+      </c>
+      <c r="B2" s="39">
         <v>1.25</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="41">
         <f>$E$2-B2</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="43">
         <f>0.01*SQRT(2)</f>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="48">
         <v>1.27</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1">
-        <v>200</v>
-      </c>
-      <c r="B3" s="1">
+    <row r="3" spans="1:6" ht="14.65" thickBot="1">
+      <c r="A3" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="B3" s="24">
         <v>1.23</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="25">
         <f t="shared" ref="C3:C6" si="0">$E$2-B3</f>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="26">
         <f t="shared" ref="D3:D6" si="1">0.01*SQRT(2)</f>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1">
-        <v>500</v>
-      </c>
-      <c r="B4" s="1">
+      <c r="E3" s="37" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="14.65" thickBot="1">
+      <c r="A4" s="23">
+        <v>0.5</v>
+      </c>
+      <c r="B4" s="24">
         <v>1.18</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="25">
         <f t="shared" si="0"/>
         <v>9.000000000000008E-2</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="26">
         <f t="shared" si="1"/>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E4" s="2"/>
+      <c r="E4" s="46">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="1">
-        <v>700</v>
-      </c>
-      <c r="B5" s="1">
+      <c r="A5" s="23">
+        <v>0.7</v>
+      </c>
+      <c r="B5" s="24">
         <v>1.1499999999999999</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="25">
         <f t="shared" si="0"/>
         <v>0.12000000000000011</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="26">
         <f t="shared" si="1"/>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="1">
-        <v>900</v>
-      </c>
-      <c r="B6" s="1">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="C6" s="2">
+      <c r="A6" s="23">
+        <v>0.9</v>
+      </c>
+      <c r="B6" s="24">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="C6" s="25">
         <f t="shared" si="0"/>
         <v>0.14999999999999991</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="26">
         <f t="shared" si="1"/>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1">
-        <v>1000</v>
-      </c>
-      <c r="B7" s="1">
+    </row>
+    <row r="7" spans="1:6" ht="14.65" thickBot="1">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="28">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="29">
         <f>$E$2-B7</f>
         <v>0.16999999999999993</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="30">
         <f>0.01*SQRT(2)</f>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:6">
       <c r="D8" s="2"/>
@@ -1716,22 +1815,22 @@
   <sheetData>
     <row r="1" spans="1:7" ht="39">
       <c r="A1" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G1" s="1">
         <v>1.1299999999999999</v>
@@ -2298,7 +2397,7 @@
       <c r="E28" s="1">
         <v>-7.0000000000000007E-2</v>
       </c>
-      <c r="F28" s="15">
+      <c r="F28" s="13">
         <v>4.2000000000000002E-4</v>
       </c>
     </row>
@@ -5256,7 +5355,7 @@
       <c r="D169" s="1">
         <v>3.34</v>
       </c>
-      <c r="E169" s="15">
+      <c r="E169" s="13">
         <v>4.66E-4</v>
       </c>
       <c r="F169" s="1">
@@ -5264,7 +5363,7 @@
       </c>
     </row>
     <row r="170" spans="1:6">
-      <c r="A170" s="15">
+      <c r="A170" s="13">
         <v>4.66E-4</v>
       </c>
       <c r="B170" s="1">
@@ -5655,7 +5754,7 @@
       <c r="D188" s="1">
         <v>3.72</v>
       </c>
-      <c r="E188" s="15">
+      <c r="E188" s="13">
         <v>2.9799999999999998E-4</v>
       </c>
       <c r="F188" s="1">
@@ -5663,7 +5762,7 @@
       </c>
     </row>
     <row r="189" spans="1:6">
-      <c r="A189" s="15">
+      <c r="A189" s="13">
         <v>2.9799999999999998E-4</v>
       </c>
       <c r="B189" s="1">
@@ -6225,7 +6324,7 @@
       <c r="E215" s="1">
         <v>-7.0000000000000007E-2</v>
       </c>
-      <c r="F215" s="15">
+      <c r="F215" s="13">
         <v>1.75E-4</v>
       </c>
     </row>
@@ -6831,7 +6930,7 @@
       <c r="D244" s="1">
         <v>4.84</v>
       </c>
-      <c r="E244" s="15">
+      <c r="E244" s="13">
         <v>-1.15E-5</v>
       </c>
       <c r="F244" s="1">
@@ -6839,7 +6938,7 @@
       </c>
     </row>
     <row r="245" spans="1:6">
-      <c r="A245" s="15">
+      <c r="A245" s="13">
         <v>-1.15E-5</v>
       </c>
       <c r="B245" s="1">
@@ -8007,7 +8106,7 @@
       <c r="D300" s="1">
         <v>5.96</v>
       </c>
-      <c r="E300" s="15">
+      <c r="E300" s="13">
         <v>2.9700000000000001E-4</v>
       </c>
       <c r="F300" s="1">
@@ -8015,7 +8114,7 @@
       </c>
     </row>
     <row r="301" spans="1:6">
-      <c r="A301" s="15">
+      <c r="A301" s="13">
         <v>2.9700000000000001E-4</v>
       </c>
       <c r="B301" s="1">
@@ -8178,7 +8277,7 @@
       <c r="E308" s="1">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F308" s="15">
+      <c r="F308" s="13">
         <v>-1.45E-4</v>
       </c>
     </row>
@@ -8406,7 +8505,7 @@
       <c r="D319" s="1">
         <v>6.34</v>
       </c>
-      <c r="E319" s="15">
+      <c r="E319" s="13">
         <v>7.0299999999999996E-4</v>
       </c>
       <c r="F319" s="1">
@@ -8414,7 +8513,7 @@
       </c>
     </row>
     <row r="320" spans="1:6">
-      <c r="A320" s="15">
+      <c r="A320" s="13">
         <v>7.0299999999999996E-4</v>
       </c>
       <c r="B320" s="1">
@@ -8805,7 +8904,7 @@
       <c r="D338" s="1">
         <v>6.72</v>
       </c>
-      <c r="E338" s="15">
+      <c r="E338" s="13">
         <v>9.9500000000000001E-4</v>
       </c>
       <c r="F338" s="1">
@@ -8813,7 +8912,7 @@
       </c>
     </row>
     <row r="339" spans="1:6">
-      <c r="A339" s="15">
+      <c r="A339" s="13">
         <v>9.9500000000000001E-4</v>
       </c>
       <c r="B339" s="1">

--- a/Legge di Hooke.xlsx
+++ b/Legge di Hooke.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="640" documentId="8_{776634F0-C4C9-4588-BBA4-07B3E3D5FCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E980182-08B8-4B7A-80A3-FA25FABC7736}"/>
+  <xr:revisionPtr revIDLastSave="650" documentId="8_{776634F0-C4C9-4588-BBA4-07B3E3D5FCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A653FC23-5FFA-4DC2-8BD0-ED732D9B9007}"/>
   <bookViews>
     <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" firstSheet="5" activeTab="5" xr2:uid="{90936311-A4D2-4EF7-9615-E94103A7D1D9}"/>
   </bookViews>
@@ -989,7 +989,7 @@
     </row>
     <row r="2" spans="1:5" ht="14.65" thickBot="1">
       <c r="A2" s="38">
-        <v>100</v>
+        <v>0.1</v>
       </c>
       <c r="B2" s="39">
         <v>1.23</v>
@@ -1007,7 +1007,7 @@
     </row>
     <row r="3" spans="1:5" ht="14.65" thickBot="1">
       <c r="A3" s="23">
-        <v>200</v>
+        <v>0.2</v>
       </c>
       <c r="B3" s="24">
         <v>1.19</v>
@@ -1025,7 +1025,7 @@
     </row>
     <row r="4" spans="1:5" ht="14.65" thickBot="1">
       <c r="A4" s="23">
-        <v>300</v>
+        <v>0.3</v>
       </c>
       <c r="B4" s="24">
         <v>1.1599999999999999</v>
@@ -1043,7 +1043,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="23">
-        <v>400</v>
+        <v>0.4</v>
       </c>
       <c r="B5" s="24">
         <v>1.1299999999999999</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="6" spans="1:5" ht="14.65" thickBot="1">
       <c r="A6" s="27">
-        <v>500</v>
+        <v>0.5</v>
       </c>
       <c r="B6" s="28">
         <v>1.1000000000000001</v>
@@ -1128,7 +1128,7 @@
     </row>
     <row r="2" spans="1:6" ht="14.65" thickBot="1">
       <c r="A2" s="38">
-        <v>50</v>
+        <v>0.05</v>
       </c>
       <c r="B2" s="39">
         <v>1.1100000000000001</v>
@@ -1147,7 +1147,7 @@
     </row>
     <row r="3" spans="1:6" ht="14.65" thickBot="1">
       <c r="A3" s="23">
-        <v>70</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="B3" s="24">
         <v>1.0900000000000001</v>
@@ -1167,7 +1167,7 @@
     </row>
     <row r="4" spans="1:6" ht="14.65" thickBot="1">
       <c r="A4" s="23">
-        <v>100</v>
+        <v>0.1</v>
       </c>
       <c r="B4" s="24">
         <v>1.06</v>
@@ -1187,7 +1187,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="23">
-        <v>150</v>
+        <v>0.15</v>
       </c>
       <c r="B5" s="24">
         <v>1.01</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="6" spans="1:6" ht="14.65" thickBot="1">
       <c r="A6" s="27">
-        <v>200</v>
+        <v>0.2</v>
       </c>
       <c r="B6" s="28">
         <v>0.95</v>

--- a/Legge di Hooke.xlsx
+++ b/Legge di Hooke.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="650" documentId="8_{776634F0-C4C9-4588-BBA4-07B3E3D5FCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A653FC23-5FFA-4DC2-8BD0-ED732D9B9007}"/>
+  <xr:revisionPtr revIDLastSave="652" documentId="8_{776634F0-C4C9-4588-BBA4-07B3E3D5FCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C51EB77-9FB3-46B5-8853-A285E3FC3BF2}"/>
   <bookViews>
-    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" firstSheet="5" activeTab="5" xr2:uid="{90936311-A4D2-4EF7-9615-E94103A7D1D9}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="5" activeTab="6" xr2:uid="{90936311-A4D2-4EF7-9615-E94103A7D1D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Misure statiche 1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Misure dinamiche" sheetId="2" r:id="rId4"/>
     <sheet name="Molle in serie (statica)" sheetId="3" r:id="rId5"/>
     <sheet name="Molle in parallelo (statica)" sheetId="6" r:id="rId6"/>
-    <sheet name="Foglio2" sheetId="8" r:id="rId7"/>
+    <sheet name="Energia " sheetId="8" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Molle in serie (statica)'!$A$1:$G$6</definedName>
@@ -109,7 +109,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -135,6 +135,13 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -331,12 +338,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -349,11 +359,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -781,177 +794,177 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="E1" s="39" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="14.65" thickBot="1">
-      <c r="A2" s="47">
+      <c r="A2" s="49">
         <v>0.05</v>
       </c>
-      <c r="B2" s="39">
+      <c r="B2" s="41">
         <v>1.24</v>
       </c>
-      <c r="C2" s="39">
+      <c r="C2" s="41">
         <v>0.02</v>
       </c>
-      <c r="D2" s="40">
+      <c r="D2" s="42">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E2" s="42">
+      <c r="E2" s="44">
         <v>1.26</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="14.65" thickBot="1">
-      <c r="A3" s="35">
+      <c r="A3" s="37">
         <v>0.1</v>
       </c>
-      <c r="B3" s="24">
+      <c r="B3" s="26">
         <v>1.23</v>
       </c>
-      <c r="C3" s="24">
+      <c r="C3" s="26">
         <v>0.03</v>
       </c>
-      <c r="D3" s="31">
+      <c r="D3" s="33">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E3" s="34" t="s">
+      <c r="E3" s="36" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="14.65" thickBot="1">
-      <c r="A4" s="35">
+      <c r="A4" s="37">
         <v>0.2</v>
       </c>
-      <c r="B4" s="24">
+      <c r="B4" s="26">
         <v>1.2</v>
       </c>
-      <c r="C4" s="24">
+      <c r="C4" s="26">
         <v>0.06</v>
       </c>
-      <c r="D4" s="31">
+      <c r="D4" s="33">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E4" s="42">
+      <c r="E4" s="44">
         <v>0.01</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="35">
+      <c r="A5" s="37">
         <v>0.3</v>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="26">
         <v>1.1599999999999999</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="26">
         <v>0.1</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="33">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E5" s="25"/>
+      <c r="E5" s="27"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="35">
+      <c r="A6" s="37">
         <v>0.4</v>
       </c>
-      <c r="B6" s="24">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="C6" s="24">
+      <c r="B6" s="26">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="C6" s="26">
         <v>0.13</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="33">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E6" s="25"/>
+      <c r="E6" s="27"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="35">
+      <c r="A7" s="37">
         <v>0.5</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="26">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="26">
         <v>0.16</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="33">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E7" s="25"/>
+      <c r="E7" s="27"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="35">
+      <c r="A8" s="37">
         <v>0.6</v>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="26">
         <v>1.07</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="26">
         <v>0.19</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="33">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E8" s="25"/>
+      <c r="E8" s="27"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="35">
+      <c r="A9" s="37">
         <v>0.7</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="26">
         <v>1.04</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="26">
         <v>0.22</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="33">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E9" s="25"/>
+      <c r="E9" s="27"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="35">
+      <c r="A10" s="37">
         <v>0.8</v>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="26">
         <v>1.01</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="26">
         <v>0.25</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="33">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E10" s="25"/>
+      <c r="E10" s="27"/>
     </row>
     <row r="11" spans="1:5" ht="14.65" thickBot="1">
-      <c r="A11" s="36">
+      <c r="A11" s="38">
         <v>0.9</v>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="30">
         <v>0.97</v>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="30">
         <v>0.28999999999999998</v>
       </c>
-      <c r="D11" s="45">
+      <c r="D11" s="47">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E11" s="25"/>
+      <c r="E11" s="27"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -971,103 +984,103 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.350000000000001" customHeight="1" thickBot="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="E1" s="39" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="14.65" thickBot="1">
-      <c r="A2" s="38">
+      <c r="A2" s="40">
         <v>0.1</v>
       </c>
-      <c r="B2" s="39">
+      <c r="B2" s="41">
         <v>1.23</v>
       </c>
-      <c r="C2" s="39">
+      <c r="C2" s="41">
         <f>$E$2-B2</f>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="D2" s="40">
+      <c r="D2" s="42">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E2" s="44">
+      <c r="E2" s="46">
         <v>1.26</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="14.65" thickBot="1">
-      <c r="A3" s="23">
+      <c r="A3" s="25">
         <v>0.2</v>
       </c>
-      <c r="B3" s="24">
+      <c r="B3" s="26">
         <v>1.19</v>
       </c>
-      <c r="C3" s="24">
+      <c r="C3" s="26">
         <f t="shared" ref="C3:C6" si="0">$E$2-B3</f>
         <v>7.0000000000000062E-2</v>
       </c>
-      <c r="D3" s="31">
+      <c r="D3" s="33">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E3" s="34" t="s">
+      <c r="E3" s="36" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="14.65" thickBot="1">
-      <c r="A4" s="23">
+      <c r="A4" s="25">
         <v>0.3</v>
       </c>
-      <c r="B4" s="24">
+      <c r="B4" s="26">
         <v>1.1599999999999999</v>
       </c>
-      <c r="C4" s="24">
+      <c r="C4" s="26">
         <f t="shared" si="0"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="D4" s="31">
+      <c r="D4" s="33">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E4" s="42">
+      <c r="E4" s="44">
         <v>0.01</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="23">
+      <c r="A5" s="25">
         <v>0.4</v>
       </c>
-      <c r="B5" s="24">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="C5" s="24">
+      <c r="B5" s="26">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="C5" s="26">
         <f t="shared" si="0"/>
         <v>0.13000000000000012</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="33">
         <v>1.4142135619999999E-2</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="14.65" thickBot="1">
-      <c r="A6" s="27">
+      <c r="A6" s="29">
         <v>0.5</v>
       </c>
-      <c r="B6" s="28">
+      <c r="B6" s="30">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C6" s="28">
+      <c r="C6" s="30">
         <f t="shared" si="0"/>
         <v>0.15999999999999992</v>
       </c>
-      <c r="D6" s="45">
+      <c r="D6" s="47">
         <v>1.4142135619999999E-2</v>
       </c>
     </row>
@@ -1110,116 +1123,116 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="14.65" thickBot="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="E1" s="39" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.65" thickBot="1">
-      <c r="A2" s="38">
+      <c r="A2" s="40">
         <v>0.05</v>
       </c>
-      <c r="B2" s="39">
+      <c r="B2" s="41">
         <v>1.1100000000000001</v>
       </c>
-      <c r="C2" s="41">
+      <c r="C2" s="43">
         <f>$E$2-B2</f>
         <v>5.9999999999999831E-2</v>
       </c>
-      <c r="D2" s="43">
+      <c r="D2" s="45">
         <f>0.01*SQRT(2)</f>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E2" s="46">
+      <c r="E2" s="48">
         <v>1.17</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="14.65" thickBot="1">
-      <c r="A3" s="23">
+      <c r="A3" s="25">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="B3" s="24">
+      <c r="B3" s="26">
         <v>1.0900000000000001</v>
       </c>
-      <c r="C3" s="25">
+      <c r="C3" s="27">
         <f>$E$2-B3</f>
         <v>7.9999999999999849E-2</v>
       </c>
-      <c r="D3" s="26">
+      <c r="D3" s="28">
         <f t="shared" ref="D3:D6" si="0">0.01*SQRT(2)</f>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E3" s="37" t="s">
+      <c r="E3" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="25"/>
+      <c r="F3" s="27"/>
     </row>
     <row r="4" spans="1:6" ht="14.65" thickBot="1">
-      <c r="A4" s="23">
+      <c r="A4" s="25">
         <v>0.1</v>
       </c>
-      <c r="B4" s="24">
+      <c r="B4" s="26">
         <v>1.06</v>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="27">
         <f t="shared" ref="C4:C6" si="1">$E$2-B4</f>
         <v>0.10999999999999988</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="28">
         <f t="shared" si="0"/>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E4" s="46">
+      <c r="E4" s="48">
         <v>0.01</v>
       </c>
-      <c r="F4" s="25"/>
+      <c r="F4" s="27"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="23">
+      <c r="A5" s="25">
         <v>0.15</v>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="26">
         <v>1.01</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="27">
         <f t="shared" si="1"/>
         <v>0.15999999999999992</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="28">
         <f t="shared" si="0"/>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
     </row>
     <row r="6" spans="1:6" ht="14.65" thickBot="1">
-      <c r="A6" s="27">
+      <c r="A6" s="29">
         <v>0.2</v>
       </c>
-      <c r="B6" s="28">
+      <c r="B6" s="30">
         <v>0.95</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="31">
         <f t="shared" si="1"/>
         <v>0.21999999999999997</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="32">
         <f t="shared" si="0"/>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
     </row>
     <row r="7" spans="1:6">
       <c r="D7" s="2"/>
@@ -1244,270 +1257,270 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="14">
+      <c r="B1" s="16">
         <v>0.05</v>
       </c>
-      <c r="C1" s="14">
+      <c r="C1" s="16">
         <v>0.15</v>
       </c>
-      <c r="D1" s="14">
+      <c r="D1" s="16">
         <v>0.25</v>
       </c>
-      <c r="E1" s="14">
+      <c r="E1" s="16">
         <v>0.35</v>
       </c>
-      <c r="F1" s="14">
+      <c r="F1" s="16">
         <v>0.45</v>
       </c>
-      <c r="G1" s="15">
+      <c r="G1" s="17">
         <v>0.55000000000000004</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="I1" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="4">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="17">
+      <c r="B2" s="19">
         <v>23.844000000000001</v>
       </c>
-      <c r="C2" s="17">
+      <c r="C2" s="19">
         <v>14.49</v>
       </c>
-      <c r="D2" s="17">
+      <c r="D2" s="19">
         <v>11.285</v>
       </c>
-      <c r="E2" s="17">
+      <c r="E2" s="19">
         <v>9.6229999999999993</v>
       </c>
-      <c r="F2" s="17">
+      <c r="F2" s="19">
         <v>8.3829999999999991</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="6">
         <v>7.6909999999999998</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2" s="5">
         <f>$B1+$I$2/3</f>
         <v>5.3766666666666671E-2</v>
       </c>
-      <c r="I2" s="20">
+      <c r="I2" s="22">
         <v>1.1299999999999999E-2</v>
       </c>
-      <c r="L2" s="12"/>
+      <c r="L2" s="13"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="10">
+      <c r="A3" s="11">
         <v>2</v>
       </c>
-      <c r="B3" s="17">
+      <c r="B3" s="19">
         <v>24.542999999999999</v>
       </c>
-      <c r="C3" s="17">
+      <c r="C3" s="19">
         <v>14.622</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="19">
         <v>11.177</v>
       </c>
-      <c r="E3" s="17">
+      <c r="E3" s="19">
         <v>9.5730000000000004</v>
       </c>
-      <c r="F3" s="17">
+      <c r="F3" s="19">
         <v>8.4060000000000006</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="6">
         <v>7.5910000000000002</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="5">
         <f>$C1+$I$2/3</f>
         <v>0.15376666666666666</v>
       </c>
-      <c r="I3" s="5"/>
-      <c r="L3" s="12"/>
+      <c r="I3" s="6"/>
+      <c r="L3" s="13"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="10">
+      <c r="A4" s="11">
         <v>3</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="19">
         <v>24.13</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="19">
         <v>14.653</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="19">
         <v>11.301</v>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="19">
         <v>9.6159999999999997</v>
       </c>
-      <c r="F4" s="17">
+      <c r="F4" s="19">
         <v>8.3879999999999999</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="6">
         <v>7.6589999999999998</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="5">
         <f>$D1+$I$2/3</f>
         <v>0.25376666666666664</v>
       </c>
-      <c r="I4" s="5"/>
-      <c r="L4" s="12"/>
+      <c r="I4" s="6"/>
+      <c r="L4" s="13"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="10">
+      <c r="A5" s="11">
         <v>4</v>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="19">
         <v>24.36</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="19">
         <v>14.534000000000001</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="19">
         <v>11.298999999999999</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="19">
         <v>9.6300000000000008</v>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="19">
         <v>8.3859999999999992</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="6">
         <v>7.6</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="5">
         <f>$E1+$I$2/3</f>
         <v>0.35376666666666662</v>
       </c>
-      <c r="I5" s="5"/>
-      <c r="L5" s="12"/>
+      <c r="I5" s="6"/>
+      <c r="L5" s="13"/>
     </row>
     <row r="6" spans="1:12" ht="14.65" thickBot="1">
-      <c r="A6" s="10">
+      <c r="A6" s="11">
         <v>5</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="19">
         <v>24.425000000000001</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="19">
         <v>14.542</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="19">
         <v>11.26</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="19">
         <v>9.6170000000000009</v>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="19">
         <v>8.4019999999999992</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="6">
         <v>7.6319999999999997</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="5">
         <f>$F1+$I$2/3</f>
         <v>0.45376666666666665</v>
       </c>
-      <c r="I6" s="5"/>
-      <c r="L6" s="12"/>
+      <c r="I6" s="6"/>
+      <c r="L6" s="13"/>
     </row>
     <row r="7" spans="1:12" ht="14.65" thickBot="1">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="4">
         <f>AVERAGE(B2:B6)</f>
         <v>24.260399999999997</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="4">
         <f>AVERAGE(C2:C6)</f>
         <v>14.568199999999999</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="4">
         <f>AVERAGE(D2:D6)</f>
         <v>11.264399999999998</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="4">
         <f t="shared" ref="E7:G7" si="0">AVERAGE(E2:E6)</f>
         <v>9.6117999999999988</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="4">
         <f t="shared" si="0"/>
         <v>8.3930000000000007</v>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="20">
         <f t="shared" si="0"/>
         <v>7.6345999999999989</v>
       </c>
-      <c r="H7" s="21">
+      <c r="H7" s="23">
         <f>$G1+$I$2/3</f>
         <v>0.55376666666666674</v>
       </c>
-      <c r="I7" s="19"/>
-      <c r="L7" s="12"/>
+      <c r="I7" s="21"/>
+      <c r="L7" s="13"/>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="19">
         <f t="shared" ref="B8" si="1">_xlfn.STDEV.S(B2:B6)</f>
         <v>0.27715934045238261</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="19">
         <f>_xlfn.STDEV.S(C2:C6)</f>
         <v>6.7187796510973619E-2</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="19">
         <f>_xlfn.STDEV.S(D2:D6)</f>
         <v>5.1524751333703808E-2</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="19">
         <f>_xlfn.STDEV.S(E2:E6)</f>
         <v>2.2398660674245618E-2</v>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="19">
         <f>_xlfn.STDEV.S(F2:F6)</f>
         <v>1.0295630140987376E-2</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="6">
         <f>_xlfn.STDEV.S(G2:G6)</f>
         <v>4.1476499370125187E-2</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="14.65" thickBot="1">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="7">
         <f>B8/SQRT(5)</f>
         <v>0.12394942517010696</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="7">
         <f>C8/SQRT(5)</f>
         <v>3.0047296051392041E-2</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="7">
         <f>D8/SQRT(5)</f>
         <v>2.3042569301186932E-2</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="7">
         <f t="shared" ref="E9:G9" si="2">E8/SQRT(5)</f>
         <v>1.0016985574512895E-2</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="7">
         <f t="shared" si="2"/>
         <v>4.6043457732887032E-3</v>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="21">
         <f t="shared" si="2"/>
         <v>1.8548854412065423E-2</v>
       </c>
@@ -1532,107 +1545,107 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="E1" s="39" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A2" s="38">
+      <c r="A2" s="40">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="B2" s="39">
+      <c r="B2" s="41">
         <v>0.99</v>
       </c>
-      <c r="C2" s="41">
+      <c r="C2" s="43">
         <f>$E$2-B2</f>
         <v>9.000000000000008E-2</v>
       </c>
-      <c r="D2" s="43">
+      <c r="D2" s="45">
         <f>0.01*SQRT(2)</f>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E2" s="31">
+      <c r="E2" s="33">
         <v>1.08</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A3" s="23">
+      <c r="A3" s="25">
         <v>0.1</v>
       </c>
-      <c r="B3" s="24">
+      <c r="B3" s="26">
         <v>0.94</v>
       </c>
-      <c r="C3" s="25">
+      <c r="C3" s="27">
         <f>$E$2-B3</f>
         <v>0.14000000000000012</v>
       </c>
-      <c r="D3" s="26">
+      <c r="D3" s="28">
         <f t="shared" ref="D3:D6" si="0">0.01*SQRT(2)</f>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E3" s="34" t="s">
+      <c r="E3" s="36" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A4" s="23">
+      <c r="A4" s="25">
         <v>0.12</v>
       </c>
-      <c r="B4" s="24">
+      <c r="B4" s="26">
         <v>0.91</v>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="27">
         <f>$E$2-B4</f>
         <v>0.17000000000000004</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="28">
         <f t="shared" si="0"/>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E4" s="42">
+      <c r="E4" s="44">
         <v>0.01</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="23">
+      <c r="A5" s="25">
         <v>0.15</v>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="26">
         <v>0.87</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="27">
         <f>$E$2-B5</f>
         <v>0.21000000000000008</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="28">
         <f t="shared" si="0"/>
         <v>1.4142135623730952E-2</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A6" s="27">
+      <c r="A6" s="29">
         <v>0.2</v>
       </c>
-      <c r="B6" s="28">
+      <c r="B6" s="30">
         <v>0.8</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="31">
         <f>$E$2-B6</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="32">
         <f t="shared" si="0"/>
         <v>1.4142135623730952E-2</v>
       </c>
@@ -1646,7 +1659,7 @@
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
-      <c r="G8" s="11"/>
+      <c r="G8" s="12"/>
     </row>
     <row r="9" spans="1:7">
       <c r="D9" s="2"/>
@@ -1677,123 +1690,123 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="14.65" thickBot="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="E1" s="39" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.65" thickBot="1">
-      <c r="A2" s="38">
+      <c r="A2" s="40">
         <v>0.1</v>
       </c>
-      <c r="B2" s="39">
+      <c r="B2" s="41">
         <v>1.25</v>
       </c>
-      <c r="C2" s="41">
+      <c r="C2" s="43">
         <f>$E$2-B2</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="D2" s="43">
+      <c r="D2" s="45">
         <f>0.01*SQRT(2)</f>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E2" s="48">
+      <c r="E2" s="50">
         <v>1.27</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="14.65" thickBot="1">
-      <c r="A3" s="23">
+      <c r="A3" s="25">
         <v>0.2</v>
       </c>
-      <c r="B3" s="24">
+      <c r="B3" s="26">
         <v>1.23</v>
       </c>
-      <c r="C3" s="25">
+      <c r="C3" s="27">
         <f t="shared" ref="C3:C6" si="0">$E$2-B3</f>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="D3" s="26">
+      <c r="D3" s="28">
         <f t="shared" ref="D3:D6" si="1">0.01*SQRT(2)</f>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E3" s="37" t="s">
+      <c r="E3" s="39" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="14.65" thickBot="1">
-      <c r="A4" s="23">
+      <c r="A4" s="25">
         <v>0.5</v>
       </c>
-      <c r="B4" s="24">
+      <c r="B4" s="26">
         <v>1.18</v>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="27">
         <f t="shared" si="0"/>
         <v>9.000000000000008E-2</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="28">
         <f t="shared" si="1"/>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E4" s="46">
+      <c r="E4" s="48">
         <v>0.01</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="23">
+      <c r="A5" s="25">
         <v>0.7</v>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="26">
         <v>1.1499999999999999</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="27">
         <f t="shared" si="0"/>
         <v>0.12000000000000011</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="28">
         <f t="shared" si="1"/>
         <v>1.4142135623730952E-2</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="23">
+      <c r="A6" s="25">
         <v>0.9</v>
       </c>
-      <c r="B6" s="24">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="C6" s="25">
+      <c r="B6" s="26">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="C6" s="27">
         <f t="shared" si="0"/>
         <v>0.14999999999999991</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="28">
         <f t="shared" si="1"/>
         <v>1.4142135623730952E-2</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="14.65" thickBot="1">
-      <c r="A7" s="27">
+      <c r="A7" s="29">
         <v>1</v>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="30">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="31">
         <f>$E$2-B7</f>
         <v>0.16999999999999993</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="32">
         <f>0.01*SQRT(2)</f>
         <v>1.4142135623730952E-2</v>
       </c>
@@ -1814,22 +1827,22 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="39">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="G1" s="1">
@@ -1837,504 +1850,504 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="2"/>
-      <c r="B2" s="1">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="C2">
+      <c r="A2" s="3"/>
+      <c r="B2" s="15">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="C2" s="12">
         <f t="shared" ref="C2:C65" si="0">B2-$G$1</f>
         <v>-9.9999999999997868E-3</v>
       </c>
-      <c r="D2" s="1">
-        <v>0</v>
-      </c>
-      <c r="E2" s="1">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1">
+      <c r="D2" s="15">
+        <v>0</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0</v>
+      </c>
+      <c r="F2" s="15">
         <v>0.86</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="1">
-        <v>0</v>
-      </c>
-      <c r="B3" s="1">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="C3">
+      <c r="A3" s="15">
+        <v>0</v>
+      </c>
+      <c r="B3" s="15">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="C3" s="12">
         <f t="shared" si="0"/>
         <v>-9.9999999999997868E-3</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="15">
         <v>0.02</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="15">
         <v>0.03</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="15">
         <v>0.57999999999999996</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="1">
+      <c r="A4" s="15">
         <v>0.03</v>
       </c>
-      <c r="B4" s="1">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="C4">
+      <c r="B4" s="15">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="C4" s="12">
         <f t="shared" si="0"/>
         <v>-9.9999999999997868E-3</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="15">
         <v>0.04</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="15">
         <v>0.04</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="15">
         <v>0.41</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="1">
+      <c r="A5" s="15">
         <v>0.04</v>
       </c>
-      <c r="B5" s="1">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="C5">
+      <c r="B5" s="15">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="C5" s="12">
         <f t="shared" si="0"/>
         <v>-9.9999999999997868E-3</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="15">
         <v>0.06</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="15">
         <v>0.05</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="15">
         <v>0.33</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="1">
+      <c r="A6" s="15">
         <v>0.05</v>
       </c>
-      <c r="B6" s="1">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="C6">
+      <c r="B6" s="15">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="C6" s="12">
         <f t="shared" si="0"/>
         <v>-9.9999999999997868E-3</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="15">
         <v>0.08</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="15">
         <v>0.05</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="15">
         <v>0.3</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="1">
+      <c r="A7" s="15">
         <v>0.05</v>
       </c>
-      <c r="B7" s="1">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="C7">
+      <c r="B7" s="15">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="C7" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="15">
         <v>0.1</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="15">
         <v>0.06</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="15">
         <v>0.24</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="1">
+      <c r="A8" s="15">
         <v>0.06</v>
       </c>
-      <c r="B8" s="1">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="C8">
+      <c r="B8" s="15">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="C8" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="15">
         <v>0.12</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="15">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="15">
         <v>0.15</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="1">
+      <c r="A9" s="15">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="B9" s="1">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="C9">
+      <c r="B9" s="15">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="C9" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="15">
         <v>0.14000000000000001</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="15">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="15">
         <v>0.03</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="1">
+      <c r="A10" s="15">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="B10" s="1">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="C10">
+      <c r="B10" s="15">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="C10" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="15">
         <v>0.16</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="15">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="15">
         <v>-0.08</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="1">
+      <c r="A11" s="15">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="B11" s="1">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="C11">
+      <c r="B11" s="15">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="C11" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="15">
         <v>0.18</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="15">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="15">
         <v>-0.18</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="1">
+      <c r="A12" s="15">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="B12" s="1">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="C12">
+      <c r="B12" s="15">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="C12" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="15">
         <v>0.2</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="15">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="15">
         <v>-0.31</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="1">
+      <c r="A13" s="15">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="B13" s="1">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="C13">
+      <c r="B13" s="15">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="C13" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13" s="15">
         <v>0.22</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="15">
         <v>0.06</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="15">
         <v>-0.46</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="1">
+      <c r="A14" s="15">
         <v>0.06</v>
       </c>
-      <c r="B14" s="1">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="C14">
+      <c r="B14" s="15">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="C14" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="15">
         <v>0.24</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="15">
         <v>0.06</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14" s="15">
         <v>-0.53</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="1">
+      <c r="A15" s="15">
         <v>0.06</v>
       </c>
-      <c r="B15" s="1">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="C15">
+      <c r="B15" s="15">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="C15" s="12">
         <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="15">
         <v>0.26</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="15">
         <v>0.04</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15" s="15">
         <v>-0.51</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="1">
+      <c r="A16" s="15">
         <v>0.04</v>
       </c>
-      <c r="B16" s="1">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="C16">
+      <c r="B16" s="15">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="C16" s="12">
         <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="15">
         <v>0.28000000000000003</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" s="15">
         <v>0.03</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16" s="15">
         <v>-0.5</v>
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="1">
+      <c r="A17" s="15">
         <v>0.03</v>
       </c>
-      <c r="B17" s="1">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="C17">
+      <c r="B17" s="15">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="C17" s="12">
         <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" s="15">
         <v>0.3</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" s="15">
         <v>0.02</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17" s="15">
         <v>-0.56000000000000005</v>
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="1">
+      <c r="A18" s="15">
         <v>0.02</v>
       </c>
-      <c r="B18" s="1">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="C18">
+      <c r="B18" s="15">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="C18" s="12">
         <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="15">
         <v>0.32</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="15">
         <v>0.02</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F18" s="15">
         <v>-0.65</v>
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="1">
+      <c r="A19" s="15">
         <v>0.02</v>
       </c>
-      <c r="B19" s="1">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="C19">
+      <c r="B19" s="15">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="C19" s="12">
         <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19" s="15">
         <v>0.34</v>
       </c>
-      <c r="E19" s="1">
-        <v>0</v>
-      </c>
-      <c r="F19" s="1">
+      <c r="E19" s="15">
+        <v>0</v>
+      </c>
+      <c r="F19" s="15">
         <v>-0.68</v>
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="1">
-        <v>0</v>
-      </c>
-      <c r="B20" s="1">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="C20">
+      <c r="A20" s="15">
+        <v>0</v>
+      </c>
+      <c r="B20" s="15">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="C20" s="12">
         <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20" s="15">
         <v>0.36</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" s="15">
         <v>-0.01</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F20" s="15">
         <v>-0.61</v>
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="1">
+      <c r="A21" s="15">
         <v>-0.01</v>
       </c>
-      <c r="B21" s="1">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="C21">
+      <c r="B21" s="15">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="C21" s="12">
         <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" s="15">
         <v>0.38</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E21" s="15">
         <v>-0.03</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F21" s="15">
         <v>-0.52</v>
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="1">
+      <c r="A22" s="15">
         <v>-0.03</v>
       </c>
-      <c r="B22" s="1">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="C22">
+      <c r="B22" s="15">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="C22" s="12">
         <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22" s="15">
         <v>0.4</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E22" s="15">
         <v>-0.04</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F22" s="15">
         <v>-0.43</v>
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="1">
+      <c r="A23" s="15">
         <v>-0.04</v>
       </c>
-      <c r="B23" s="1">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="C23">
+      <c r="B23" s="15">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="C23" s="12">
         <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D23" s="15">
         <v>0.42</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E23" s="15">
         <v>-0.05</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F23" s="15">
         <v>-0.37</v>
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="1">
+      <c r="A24" s="15">
         <v>-0.05</v>
       </c>
-      <c r="B24" s="1">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="C24">
+      <c r="B24" s="15">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="C24" s="12">
         <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D24" s="15">
         <v>0.44</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E24" s="15">
         <v>-0.05</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F24" s="15">
         <v>-0.3</v>
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="1">
+      <c r="A25" s="15">
         <v>-0.05</v>
       </c>
-      <c r="B25" s="1">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="C25">
+      <c r="B25" s="15">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="C25" s="12">
         <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D25" s="15">
         <v>0.46</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E25" s="15">
         <v>-0.06</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F25" s="15">
         <v>-0.22</v>
       </c>
     </row>
@@ -2397,7 +2410,7 @@
       <c r="E28" s="1">
         <v>-7.0000000000000007E-2</v>
       </c>
-      <c r="F28" s="13">
+      <c r="F28" s="14">
         <v>4.2000000000000002E-4</v>
       </c>
     </row>
@@ -5355,7 +5368,7 @@
       <c r="D169" s="1">
         <v>3.34</v>
       </c>
-      <c r="E169" s="13">
+      <c r="E169" s="14">
         <v>4.66E-4</v>
       </c>
       <c r="F169" s="1">
@@ -5363,7 +5376,7 @@
       </c>
     </row>
     <row r="170" spans="1:6">
-      <c r="A170" s="13">
+      <c r="A170" s="14">
         <v>4.66E-4</v>
       </c>
       <c r="B170" s="1">
@@ -5754,7 +5767,7 @@
       <c r="D188" s="1">
         <v>3.72</v>
       </c>
-      <c r="E188" s="13">
+      <c r="E188" s="14">
         <v>2.9799999999999998E-4</v>
       </c>
       <c r="F188" s="1">
@@ -5762,7 +5775,7 @@
       </c>
     </row>
     <row r="189" spans="1:6">
-      <c r="A189" s="13">
+      <c r="A189" s="14">
         <v>2.9799999999999998E-4</v>
       </c>
       <c r="B189" s="1">
@@ -6324,7 +6337,7 @@
       <c r="E215" s="1">
         <v>-7.0000000000000007E-2</v>
       </c>
-      <c r="F215" s="13">
+      <c r="F215" s="14">
         <v>1.75E-4</v>
       </c>
     </row>
@@ -6930,7 +6943,7 @@
       <c r="D244" s="1">
         <v>4.84</v>
       </c>
-      <c r="E244" s="13">
+      <c r="E244" s="14">
         <v>-1.15E-5</v>
       </c>
       <c r="F244" s="1">
@@ -6938,7 +6951,7 @@
       </c>
     </row>
     <row r="245" spans="1:6">
-      <c r="A245" s="13">
+      <c r="A245" s="14">
         <v>-1.15E-5</v>
       </c>
       <c r="B245" s="1">
@@ -8106,7 +8119,7 @@
       <c r="D300" s="1">
         <v>5.96</v>
       </c>
-      <c r="E300" s="13">
+      <c r="E300" s="14">
         <v>2.9700000000000001E-4</v>
       </c>
       <c r="F300" s="1">
@@ -8114,7 +8127,7 @@
       </c>
     </row>
     <row r="301" spans="1:6">
-      <c r="A301" s="13">
+      <c r="A301" s="14">
         <v>2.9700000000000001E-4</v>
       </c>
       <c r="B301" s="1">
@@ -8277,7 +8290,7 @@
       <c r="E308" s="1">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F308" s="13">
+      <c r="F308" s="14">
         <v>-1.45E-4</v>
       </c>
     </row>
@@ -8505,7 +8518,7 @@
       <c r="D319" s="1">
         <v>6.34</v>
       </c>
-      <c r="E319" s="13">
+      <c r="E319" s="14">
         <v>7.0299999999999996E-4</v>
       </c>
       <c r="F319" s="1">
@@ -8513,7 +8526,7 @@
       </c>
     </row>
     <row r="320" spans="1:6">
-      <c r="A320" s="13">
+      <c r="A320" s="14">
         <v>7.0299999999999996E-4</v>
       </c>
       <c r="B320" s="1">
@@ -8904,7 +8917,7 @@
       <c r="D338" s="1">
         <v>6.72</v>
       </c>
-      <c r="E338" s="13">
+      <c r="E338" s="14">
         <v>9.9500000000000001E-4</v>
       </c>
       <c r="F338" s="1">
@@ -8912,7 +8925,7 @@
       </c>
     </row>
     <row r="339" spans="1:6">
-      <c r="A339" s="13">
+      <c r="A339" s="14">
         <v>9.9500000000000001E-4</v>
       </c>
       <c r="B339" s="1">

--- a/Legge di Hooke.xlsx
+++ b/Legge di Hooke.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="652" documentId="8_{776634F0-C4C9-4588-BBA4-07B3E3D5FCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C51EB77-9FB3-46B5-8853-A285E3FC3BF2}"/>
+  <xr:revisionPtr revIDLastSave="660" documentId="8_{776634F0-C4C9-4588-BBA4-07B3E3D5FCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63CA1B09-5210-4D79-8241-277BA1F64BAC}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="5" activeTab="6" xr2:uid="{90936311-A4D2-4EF7-9615-E94103A7D1D9}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="4" activeTab="7" xr2:uid="{90936311-A4D2-4EF7-9615-E94103A7D1D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Misure statiche 1" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,12 @@
     <sheet name="Molle in serie (statica)" sheetId="3" r:id="rId5"/>
     <sheet name="Molle in parallelo (statica)" sheetId="6" r:id="rId6"/>
     <sheet name="Energia " sheetId="8" r:id="rId7"/>
+    <sheet name="Misure dinamiche 2" sheetId="9" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Molle in serie (statica)'!$A$1:$G$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="19">
   <si>
     <t>d [m] senza pesi</t>
   </si>
@@ -103,6 +103,9 @@
   </si>
   <si>
     <t>incertezza su d [m]</t>
+  </si>
+  <si>
+    <t>Masse (Kg)</t>
   </si>
 </sst>
 </file>
@@ -338,7 +341,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -369,23 +372,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -405,16 +400,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -440,9 +429,6 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -794,177 +780,177 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="E1" s="33" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="14.65" thickBot="1">
-      <c r="A2" s="49">
+      <c r="A2" s="34">
         <v>0.05</v>
       </c>
-      <c r="B2" s="41">
+      <c r="B2" s="35">
         <v>1.24</v>
       </c>
-      <c r="C2" s="41">
+      <c r="C2" s="35">
         <v>0.02</v>
       </c>
-      <c r="D2" s="42">
+      <c r="D2" s="36">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E2" s="44">
+      <c r="E2" s="38">
         <v>1.26</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="14.65" thickBot="1">
-      <c r="A3" s="37">
+      <c r="A3" s="23">
         <v>0.1</v>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="1">
         <v>1.23</v>
       </c>
-      <c r="C3" s="26">
+      <c r="C3" s="1">
         <v>0.03</v>
       </c>
-      <c r="D3" s="33">
+      <c r="D3" s="29">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="32" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="14.65" thickBot="1">
-      <c r="A4" s="37">
+      <c r="A4" s="23">
         <v>0.2</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="1">
         <v>1.2</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="1">
         <v>0.06</v>
       </c>
-      <c r="D4" s="33">
+      <c r="D4" s="29">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E4" s="44">
+      <c r="E4" s="38">
         <v>0.01</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="37">
+      <c r="A5" s="23">
         <v>0.3</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="1">
         <v>1.1599999999999999</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="1">
         <v>0.1</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="29">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E5" s="27"/>
+      <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="37">
+      <c r="A6" s="23">
         <v>0.4</v>
       </c>
-      <c r="B6" s="26">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="C6" s="26">
+      <c r="B6" s="1">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="C6" s="1">
         <v>0.13</v>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="29">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E6" s="27"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="37">
+      <c r="A7" s="23">
         <v>0.5</v>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="1">
         <v>0.16</v>
       </c>
-      <c r="D7" s="33">
+      <c r="D7" s="29">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E7" s="27"/>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="37">
+      <c r="A8" s="23">
         <v>0.6</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="1">
         <v>1.07</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="1">
         <v>0.19</v>
       </c>
-      <c r="D8" s="33">
+      <c r="D8" s="29">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E8" s="27"/>
+      <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="37">
+      <c r="A9" s="23">
         <v>0.7</v>
       </c>
-      <c r="B9" s="26">
+      <c r="B9" s="1">
         <v>1.04</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="1">
         <v>0.22</v>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="29">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E9" s="27"/>
+      <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="37">
+      <c r="A10" s="23">
         <v>0.8</v>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="1">
         <v>1.01</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="1">
         <v>0.25</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="29">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E10" s="27"/>
+      <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5" ht="14.65" thickBot="1">
-      <c r="A11" s="38">
+      <c r="A11" s="25">
         <v>0.9</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="26">
         <v>0.97</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="26">
         <v>0.28999999999999998</v>
       </c>
-      <c r="D11" s="47">
+      <c r="D11" s="41">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E11" s="27"/>
+      <c r="E11" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -984,103 +970,103 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.350000000000001" customHeight="1" thickBot="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="E1" s="33" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="14.65" thickBot="1">
-      <c r="A2" s="40">
+      <c r="A2" s="34">
         <v>0.1</v>
       </c>
-      <c r="B2" s="41">
+      <c r="B2" s="35">
         <v>1.23</v>
       </c>
-      <c r="C2" s="41">
+      <c r="C2" s="35">
         <f>$E$2-B2</f>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="D2" s="42">
+      <c r="D2" s="36">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E2" s="46">
+      <c r="E2" s="40">
         <v>1.26</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="14.65" thickBot="1">
-      <c r="A3" s="25">
+      <c r="A3" s="23">
         <v>0.2</v>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="1">
         <v>1.19</v>
       </c>
-      <c r="C3" s="26">
+      <c r="C3" s="1">
         <f t="shared" ref="C3:C6" si="0">$E$2-B3</f>
         <v>7.0000000000000062E-2</v>
       </c>
-      <c r="D3" s="33">
+      <c r="D3" s="29">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="32" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="14.65" thickBot="1">
-      <c r="A4" s="25">
+      <c r="A4" s="23">
         <v>0.3</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="1">
         <v>1.1599999999999999</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="1">
         <f t="shared" si="0"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="D4" s="33">
+      <c r="D4" s="29">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E4" s="44">
+      <c r="E4" s="38">
         <v>0.01</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="25">
+      <c r="A5" s="23">
         <v>0.4</v>
       </c>
-      <c r="B5" s="26">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="C5" s="26">
+      <c r="B5" s="1">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="C5" s="1">
         <f t="shared" si="0"/>
         <v>0.13000000000000012</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="29">
         <v>1.4142135619999999E-2</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="14.65" thickBot="1">
-      <c r="A6" s="29">
+      <c r="A6" s="25">
         <v>0.5</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="26">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="26">
         <f t="shared" si="0"/>
         <v>0.15999999999999992</v>
       </c>
-      <c r="D6" s="47">
+      <c r="D6" s="41">
         <v>1.4142135619999999E-2</v>
       </c>
     </row>
@@ -1123,116 +1109,116 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="14.65" thickBot="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="E1" s="33" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.65" thickBot="1">
-      <c r="A2" s="40">
+      <c r="A2" s="34">
         <v>0.05</v>
       </c>
-      <c r="B2" s="41">
+      <c r="B2" s="35">
         <v>1.1100000000000001</v>
       </c>
-      <c r="C2" s="43">
+      <c r="C2" s="37">
         <f>$E$2-B2</f>
         <v>5.9999999999999831E-2</v>
       </c>
-      <c r="D2" s="45">
+      <c r="D2" s="39">
         <f>0.01*SQRT(2)</f>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E2" s="48">
+      <c r="E2" s="42">
         <v>1.17</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="14.65" thickBot="1">
-      <c r="A3" s="25">
+      <c r="A3" s="23">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="1">
         <v>1.0900000000000001</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="2">
         <f>$E$2-B3</f>
         <v>7.9999999999999849E-2</v>
       </c>
-      <c r="D3" s="28">
+      <c r="D3" s="24">
         <f t="shared" ref="D3:D6" si="0">0.01*SQRT(2)</f>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E3" s="39" t="s">
+      <c r="E3" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="27"/>
+      <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:6" ht="14.65" thickBot="1">
-      <c r="A4" s="25">
+      <c r="A4" s="23">
         <v>0.1</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="1">
         <v>1.06</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="2">
         <f t="shared" ref="C4:C6" si="1">$E$2-B4</f>
         <v>0.10999999999999988</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="24">
         <f t="shared" si="0"/>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E4" s="48">
+      <c r="E4" s="42">
         <v>0.01</v>
       </c>
-      <c r="F4" s="27"/>
+      <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="25">
+      <c r="A5" s="23">
         <v>0.15</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="1">
         <v>1.01</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="2">
         <f t="shared" si="1"/>
         <v>0.15999999999999992</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="24">
         <f t="shared" si="0"/>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" ht="14.65" thickBot="1">
-      <c r="A6" s="29">
+      <c r="A6" s="25">
         <v>0.2</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="26">
         <v>0.95</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="27">
         <f t="shared" si="1"/>
         <v>0.21999999999999997</v>
       </c>
-      <c r="D6" s="32">
+      <c r="D6" s="28">
         <f t="shared" si="0"/>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="D7" s="2"/>
@@ -1281,7 +1267,7 @@
       <c r="H1" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="24" t="s">
+      <c r="I1" s="22" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1289,19 +1275,19 @@
       <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="19">
+      <c r="B2">
         <v>23.844000000000001</v>
       </c>
-      <c r="C2" s="19">
+      <c r="C2">
         <v>14.49</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2">
         <v>11.285</v>
       </c>
-      <c r="E2" s="19">
+      <c r="E2">
         <v>9.6229999999999993</v>
       </c>
-      <c r="F2" s="19">
+      <c r="F2">
         <v>8.3829999999999991</v>
       </c>
       <c r="G2" s="6">
@@ -1311,7 +1297,7 @@
         <f>$B1+$I$2/3</f>
         <v>5.3766666666666671E-2</v>
       </c>
-      <c r="I2" s="22">
+      <c r="I2" s="6">
         <v>1.1299999999999999E-2</v>
       </c>
       <c r="L2" s="13"/>
@@ -1320,19 +1306,19 @@
       <c r="A3" s="11">
         <v>2</v>
       </c>
-      <c r="B3" s="19">
+      <c r="B3">
         <v>24.542999999999999</v>
       </c>
-      <c r="C3" s="19">
+      <c r="C3">
         <v>14.622</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3">
         <v>11.177</v>
       </c>
-      <c r="E3" s="19">
+      <c r="E3">
         <v>9.5730000000000004</v>
       </c>
-      <c r="F3" s="19">
+      <c r="F3">
         <v>8.4060000000000006</v>
       </c>
       <c r="G3" s="6">
@@ -1349,19 +1335,19 @@
       <c r="A4" s="11">
         <v>3</v>
       </c>
-      <c r="B4" s="19">
+      <c r="B4">
         <v>24.13</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4">
         <v>14.653</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4">
         <v>11.301</v>
       </c>
-      <c r="E4" s="19">
+      <c r="E4">
         <v>9.6159999999999997</v>
       </c>
-      <c r="F4" s="19">
+      <c r="F4">
         <v>8.3879999999999999</v>
       </c>
       <c r="G4" s="6">
@@ -1378,19 +1364,19 @@
       <c r="A5" s="11">
         <v>4</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5">
         <v>24.36</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5">
         <v>14.534000000000001</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5">
         <v>11.298999999999999</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5">
         <v>9.6300000000000008</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5">
         <v>8.3859999999999992</v>
       </c>
       <c r="G5" s="6">
@@ -1407,19 +1393,19 @@
       <c r="A6" s="11">
         <v>5</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6">
         <v>24.425000000000001</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6">
         <v>14.542</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6">
         <v>11.26</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6">
         <v>9.6170000000000009</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6">
         <v>8.4019999999999992</v>
       </c>
       <c r="G6" s="6">
@@ -1456,38 +1442,38 @@
         <f t="shared" si="0"/>
         <v>8.3930000000000007</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="19">
         <f t="shared" si="0"/>
         <v>7.6345999999999989</v>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="21">
         <f>$G1+$I$2/3</f>
         <v>0.55376666666666674</v>
       </c>
-      <c r="I7" s="21"/>
+      <c r="I7" s="20"/>
       <c r="L7" s="13"/>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B8">
         <f t="shared" ref="B8" si="1">_xlfn.STDEV.S(B2:B6)</f>
         <v>0.27715934045238261</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8">
         <f>_xlfn.STDEV.S(C2:C6)</f>
         <v>6.7187796510973619E-2</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8">
         <f>_xlfn.STDEV.S(D2:D6)</f>
         <v>5.1524751333703808E-2</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8">
         <f>_xlfn.STDEV.S(E2:E6)</f>
         <v>2.2398660674245618E-2</v>
       </c>
-      <c r="F8" s="19">
+      <c r="F8">
         <f>_xlfn.STDEV.S(F2:F6)</f>
         <v>1.0295630140987376E-2</v>
       </c>
@@ -1520,7 +1506,7 @@
         <f t="shared" si="2"/>
         <v>4.6043457732887032E-3</v>
       </c>
-      <c r="G9" s="21">
+      <c r="G9" s="20">
         <f t="shared" si="2"/>
         <v>1.8548854412065423E-2</v>
       </c>
@@ -1545,107 +1531,107 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="E1" s="33" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A2" s="40">
+      <c r="A2" s="34">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="B2" s="41">
+      <c r="B2" s="35">
         <v>0.99</v>
       </c>
-      <c r="C2" s="43">
+      <c r="C2" s="37">
         <f>$E$2-B2</f>
         <v>9.000000000000008E-2</v>
       </c>
-      <c r="D2" s="45">
+      <c r="D2" s="39">
         <f>0.01*SQRT(2)</f>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E2" s="33">
+      <c r="E2" s="29">
         <v>1.08</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A3" s="25">
+      <c r="A3" s="23">
         <v>0.1</v>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="1">
         <v>0.94</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="2">
         <f>$E$2-B3</f>
         <v>0.14000000000000012</v>
       </c>
-      <c r="D3" s="28">
+      <c r="D3" s="24">
         <f t="shared" ref="D3:D6" si="0">0.01*SQRT(2)</f>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="32" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A4" s="25">
+      <c r="A4" s="23">
         <v>0.12</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="1">
         <v>0.91</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="2">
         <f>$E$2-B4</f>
         <v>0.17000000000000004</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="24">
         <f t="shared" si="0"/>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E4" s="44">
+      <c r="E4" s="38">
         <v>0.01</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="25">
+      <c r="A5" s="23">
         <v>0.15</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="1">
         <v>0.87</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="2">
         <f>$E$2-B5</f>
         <v>0.21000000000000008</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="24">
         <f t="shared" si="0"/>
         <v>1.4142135623730952E-2</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A6" s="29">
+      <c r="A6" s="25">
         <v>0.2</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="26">
         <v>0.8</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="27">
         <f>$E$2-B6</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="D6" s="32">
+      <c r="D6" s="28">
         <f t="shared" si="0"/>
         <v>1.4142135623730952E-2</v>
       </c>
@@ -1690,123 +1676,123 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="14.65" thickBot="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="E1" s="33" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.65" thickBot="1">
-      <c r="A2" s="40">
+      <c r="A2" s="34">
         <v>0.1</v>
       </c>
-      <c r="B2" s="41">
+      <c r="B2" s="35">
         <v>1.25</v>
       </c>
-      <c r="C2" s="43">
+      <c r="C2" s="37">
         <f>$E$2-B2</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="D2" s="45">
+      <c r="D2" s="39">
         <f>0.01*SQRT(2)</f>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E2" s="50">
+      <c r="E2" s="43">
         <v>1.27</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="14.65" thickBot="1">
-      <c r="A3" s="25">
+      <c r="A3" s="23">
         <v>0.2</v>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="1">
         <v>1.23</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="2">
         <f t="shared" ref="C3:C6" si="0">$E$2-B3</f>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="D3" s="28">
+      <c r="D3" s="24">
         <f t="shared" ref="D3:D6" si="1">0.01*SQRT(2)</f>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E3" s="39" t="s">
+      <c r="E3" s="33" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="14.65" thickBot="1">
-      <c r="A4" s="25">
+      <c r="A4" s="23">
         <v>0.5</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="1">
         <v>1.18</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="2">
         <f t="shared" si="0"/>
         <v>9.000000000000008E-2</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="24">
         <f t="shared" si="1"/>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E4" s="48">
+      <c r="E4" s="42">
         <v>0.01</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="25">
+      <c r="A5" s="23">
         <v>0.7</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="1">
         <v>1.1499999999999999</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="2">
         <f t="shared" si="0"/>
         <v>0.12000000000000011</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="24">
         <f t="shared" si="1"/>
         <v>1.4142135623730952E-2</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="25">
+      <c r="A6" s="23">
         <v>0.9</v>
       </c>
-      <c r="B6" s="26">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="C6" s="27">
+      <c r="B6" s="1">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="C6" s="2">
         <f t="shared" si="0"/>
         <v>0.14999999999999991</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="24">
         <f t="shared" si="1"/>
         <v>1.4142135623730952E-2</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="14.65" thickBot="1">
-      <c r="A7" s="29">
+      <c r="A7" s="25">
         <v>1</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="26">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="27">
         <f>$E$2-B7</f>
         <v>0.16999999999999993</v>
       </c>
-      <c r="D7" s="32">
+      <c r="D7" s="28">
         <f>0.01*SQRT(2)</f>
         <v>1.4142135623730952E-2</v>
       </c>
@@ -10135,4 +10121,269 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4850CE89-F87F-4B70-AE63-B22623A60760}">
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="8" max="8" width="15.3984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="16">
+        <v>0.05</v>
+      </c>
+      <c r="C1" s="16">
+        <v>0.15</v>
+      </c>
+      <c r="D1" s="16">
+        <v>0.25</v>
+      </c>
+      <c r="E1" s="16">
+        <v>0.35</v>
+      </c>
+      <c r="F1" s="16">
+        <v>0.45</v>
+      </c>
+      <c r="G1" s="17">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="5">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>23.844000000000001</v>
+      </c>
+      <c r="C2">
+        <v>14.49</v>
+      </c>
+      <c r="D2">
+        <v>11.285</v>
+      </c>
+      <c r="E2">
+        <v>9.6229999999999993</v>
+      </c>
+      <c r="F2">
+        <v>8.3829999999999991</v>
+      </c>
+      <c r="G2" s="6">
+        <v>7.6909999999999998</v>
+      </c>
+      <c r="H2" s="5">
+        <f>$B1+$I$2/3</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="11">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>24.542999999999999</v>
+      </c>
+      <c r="C3">
+        <v>14.622</v>
+      </c>
+      <c r="D3">
+        <v>11.177</v>
+      </c>
+      <c r="E3">
+        <v>9.5730000000000004</v>
+      </c>
+      <c r="F3">
+        <v>8.4060000000000006</v>
+      </c>
+      <c r="G3" s="6">
+        <v>7.5910000000000002</v>
+      </c>
+      <c r="H3" s="5">
+        <f>$C1+$I$2/3</f>
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="11">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>24.13</v>
+      </c>
+      <c r="C4">
+        <v>14.653</v>
+      </c>
+      <c r="D4">
+        <v>11.301</v>
+      </c>
+      <c r="E4">
+        <v>9.6159999999999997</v>
+      </c>
+      <c r="F4">
+        <v>8.3879999999999999</v>
+      </c>
+      <c r="G4" s="6">
+        <v>7.6589999999999998</v>
+      </c>
+      <c r="H4" s="5">
+        <f>$D1+$I$2/3</f>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="11">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>24.36</v>
+      </c>
+      <c r="C5">
+        <v>14.534000000000001</v>
+      </c>
+      <c r="D5">
+        <v>11.298999999999999</v>
+      </c>
+      <c r="E5">
+        <v>9.6300000000000008</v>
+      </c>
+      <c r="F5">
+        <v>8.3859999999999992</v>
+      </c>
+      <c r="G5" s="6">
+        <v>7.6</v>
+      </c>
+      <c r="H5" s="5">
+        <f>$E1+$I$2/3</f>
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="14.65" thickBot="1">
+      <c r="A6" s="11">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>24.425000000000001</v>
+      </c>
+      <c r="C6">
+        <v>14.542</v>
+      </c>
+      <c r="D6">
+        <v>11.26</v>
+      </c>
+      <c r="E6">
+        <v>9.6170000000000009</v>
+      </c>
+      <c r="F6">
+        <v>8.4019999999999992</v>
+      </c>
+      <c r="G6" s="6">
+        <v>7.6319999999999997</v>
+      </c>
+      <c r="H6" s="5">
+        <f>$F1+$I$2/3</f>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="14.65" thickBot="1">
+      <c r="A7" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="4">
+        <f>AVERAGE(B2:B6)</f>
+        <v>24.260399999999997</v>
+      </c>
+      <c r="C7" s="4">
+        <f>AVERAGE(C2:C6)</f>
+        <v>14.568199999999999</v>
+      </c>
+      <c r="D7" s="4">
+        <f>AVERAGE(D2:D6)</f>
+        <v>11.264399999999998</v>
+      </c>
+      <c r="E7" s="4">
+        <f t="shared" ref="E7:G7" si="0">AVERAGE(E2:E6)</f>
+        <v>9.6117999999999988</v>
+      </c>
+      <c r="F7" s="4">
+        <f t="shared" si="0"/>
+        <v>8.3930000000000007</v>
+      </c>
+      <c r="G7" s="19">
+        <f t="shared" si="0"/>
+        <v>7.6345999999999989</v>
+      </c>
+      <c r="H7" s="21">
+        <f>$G1+$I$2/3</f>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8">
+        <f t="shared" ref="B8" si="1">_xlfn.STDEV.S(B2:B6)</f>
+        <v>0.27715934045238261</v>
+      </c>
+      <c r="C8">
+        <f>_xlfn.STDEV.S(C2:C6)</f>
+        <v>6.7187796510973619E-2</v>
+      </c>
+      <c r="D8">
+        <f>_xlfn.STDEV.S(D2:D6)</f>
+        <v>5.1524751333703808E-2</v>
+      </c>
+      <c r="E8">
+        <f>_xlfn.STDEV.S(E2:E6)</f>
+        <v>2.2398660674245618E-2</v>
+      </c>
+      <c r="F8">
+        <f>_xlfn.STDEV.S(F2:F6)</f>
+        <v>1.0295630140987376E-2</v>
+      </c>
+      <c r="G8" s="6">
+        <f>_xlfn.STDEV.S(G2:G6)</f>
+        <v>4.1476499370125187E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="14.65" thickBot="1">
+      <c r="A9" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="7">
+        <f>B8/SQRT(5)</f>
+        <v>0.12394942517010696</v>
+      </c>
+      <c r="C9" s="7">
+        <f>C8/SQRT(5)</f>
+        <v>3.0047296051392041E-2</v>
+      </c>
+      <c r="D9" s="7">
+        <f>D8/SQRT(5)</f>
+        <v>2.3042569301186932E-2</v>
+      </c>
+      <c r="E9" s="7">
+        <f t="shared" ref="E9:G9" si="2">E8/SQRT(5)</f>
+        <v>1.0016985574512895E-2</v>
+      </c>
+      <c r="F9" s="7">
+        <f t="shared" si="2"/>
+        <v>4.6043457732887032E-3</v>
+      </c>
+      <c r="G9" s="20">
+        <f t="shared" si="2"/>
+        <v>1.8548854412065423E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Legge di Hooke.xlsx
+++ b/Legge di Hooke.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="660" documentId="8_{776634F0-C4C9-4588-BBA4-07B3E3D5FCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63CA1B09-5210-4D79-8241-277BA1F64BAC}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="4" activeTab="7" xr2:uid="{90936311-A4D2-4EF7-9615-E94103A7D1D9}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{90936311-A4D2-4EF7-9615-E94103A7D1D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Misure statiche 1" sheetId="1" r:id="rId1"/>

--- a/Legge di Hooke.xlsx
+++ b/Legge di Hooke.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="660" documentId="8_{776634F0-C4C9-4588-BBA4-07B3E3D5FCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63CA1B09-5210-4D79-8241-277BA1F64BAC}"/>
+  <xr:revisionPtr revIDLastSave="746" documentId="8_{776634F0-C4C9-4588-BBA4-07B3E3D5FCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CC12662-66A8-4D51-A1CA-864B1BD9307C}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{90936311-A4D2-4EF7-9615-E94103A7D1D9}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="4" activeTab="7" xr2:uid="{90936311-A4D2-4EF7-9615-E94103A7D1D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Misure statiche 1" sheetId="1" r:id="rId1"/>
@@ -112,6 +112,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="170" formatCode="0.0000"/>
+  </numFmts>
   <fonts count="7">
     <font>
       <sz val="11"/>
@@ -341,7 +344,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -382,9 +385,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -392,9 +392,6 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -410,22 +407,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -434,6 +422,32 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -780,36 +794,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="31" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="14.65" thickBot="1">
-      <c r="A2" s="34">
+      <c r="A2" s="32">
         <v>0.05</v>
       </c>
-      <c r="B2" s="35">
+      <c r="B2" s="33">
         <v>1.24</v>
       </c>
-      <c r="C2" s="35">
+      <c r="C2" s="33">
         <v>0.02</v>
       </c>
-      <c r="D2" s="36">
+      <c r="D2" s="39">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E2" s="38">
+      <c r="E2" s="35">
         <v>1.26</v>
       </c>
     </row>
@@ -823,10 +837,10 @@
       <c r="C3" s="1">
         <v>0.03</v>
       </c>
-      <c r="D3" s="29">
+      <c r="D3" s="40">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="30" t="s">
         <v>17</v>
       </c>
     </row>
@@ -840,10 +854,10 @@
       <c r="C4" s="1">
         <v>0.06</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="40">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E4" s="38">
+      <c r="E4" s="35">
         <v>0.01</v>
       </c>
     </row>
@@ -857,7 +871,7 @@
       <c r="C5" s="1">
         <v>0.1</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="40">
         <v>1.4142135619999999E-2</v>
       </c>
       <c r="E5" s="2"/>
@@ -872,7 +886,7 @@
       <c r="C6" s="1">
         <v>0.13</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="40">
         <v>1.4142135619999999E-2</v>
       </c>
       <c r="E6" s="2"/>
@@ -887,7 +901,7 @@
       <c r="C7" s="1">
         <v>0.16</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="40">
         <v>1.4142135619999999E-2</v>
       </c>
       <c r="E7" s="2"/>
@@ -902,7 +916,7 @@
       <c r="C8" s="1">
         <v>0.19</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="40">
         <v>1.4142135619999999E-2</v>
       </c>
       <c r="E8" s="2"/>
@@ -917,7 +931,7 @@
       <c r="C9" s="1">
         <v>0.22</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="40">
         <v>1.4142135619999999E-2</v>
       </c>
       <c r="E9" s="2"/>
@@ -932,19 +946,19 @@
       <c r="C10" s="1">
         <v>0.25</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="40">
         <v>1.4142135619999999E-2</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5" ht="14.65" thickBot="1">
-      <c r="A11" s="25">
+      <c r="A11" s="24">
         <v>0.9</v>
       </c>
-      <c r="B11" s="26">
+      <c r="B11" s="25">
         <v>0.97</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="25">
         <v>0.28999999999999998</v>
       </c>
       <c r="D11" s="41">
@@ -970,37 +984,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.350000000000001" customHeight="1" thickBot="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="31" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="14.65" thickBot="1">
-      <c r="A2" s="34">
+      <c r="A2" s="32">
         <v>0.1</v>
       </c>
-      <c r="B2" s="35">
+      <c r="B2" s="33">
         <v>1.23</v>
       </c>
-      <c r="C2" s="35">
+      <c r="C2" s="33">
         <f>$E$2-B2</f>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="D2" s="36">
+      <c r="D2" s="39">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E2" s="40">
+      <c r="E2" s="36">
         <v>1.26</v>
       </c>
     </row>
@@ -1015,10 +1029,10 @@
         <f t="shared" ref="C3:C6" si="0">$E$2-B3</f>
         <v>7.0000000000000062E-2</v>
       </c>
-      <c r="D3" s="29">
+      <c r="D3" s="40">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="30" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1033,10 +1047,10 @@
         <f t="shared" si="0"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="40">
         <v>1.4142135619999999E-2</v>
       </c>
-      <c r="E4" s="38">
+      <c r="E4" s="35">
         <v>0.01</v>
       </c>
     </row>
@@ -1051,18 +1065,18 @@
         <f t="shared" si="0"/>
         <v>0.13000000000000012</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="40">
         <v>1.4142135619999999E-2</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="14.65" thickBot="1">
-      <c r="A6" s="25">
+      <c r="A6" s="24">
         <v>0.5</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="25">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="25">
         <f t="shared" si="0"/>
         <v>0.15999999999999992</v>
       </c>
@@ -1109,38 +1123,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="14.65" thickBot="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="31" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.65" thickBot="1">
-      <c r="A2" s="34">
+      <c r="A2" s="32">
         <v>0.05</v>
       </c>
-      <c r="B2" s="35">
+      <c r="B2" s="33">
         <v>1.1100000000000001</v>
       </c>
-      <c r="C2" s="37">
+      <c r="C2" s="34">
         <f>$E$2-B2</f>
         <v>5.9999999999999831E-2</v>
       </c>
-      <c r="D2" s="39">
+      <c r="D2" s="42">
         <f>0.01*SQRT(2)</f>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E2" s="42">
+      <c r="E2" s="37">
         <v>1.17</v>
       </c>
     </row>
@@ -1155,11 +1169,11 @@
         <f>$E$2-B3</f>
         <v>7.9999999999999849E-2</v>
       </c>
-      <c r="D3" s="24">
+      <c r="D3" s="43">
         <f t="shared" ref="D3:D6" si="0">0.01*SQRT(2)</f>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="E3" s="31" t="s">
         <v>17</v>
       </c>
       <c r="F3" s="2"/>
@@ -1175,11 +1189,11 @@
         <f t="shared" ref="C4:C6" si="1">$E$2-B4</f>
         <v>0.10999999999999988</v>
       </c>
-      <c r="D4" s="24">
+      <c r="D4" s="43">
         <f t="shared" si="0"/>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E4" s="42">
+      <c r="E4" s="37">
         <v>0.01</v>
       </c>
       <c r="F4" s="2"/>
@@ -1195,7 +1209,7 @@
         <f t="shared" si="1"/>
         <v>0.15999999999999992</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="43">
         <f t="shared" si="0"/>
         <v>1.4142135623730952E-2</v>
       </c>
@@ -1203,17 +1217,17 @@
       <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" ht="14.65" thickBot="1">
-      <c r="A6" s="25">
+      <c r="A6" s="24">
         <v>0.2</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="25">
         <v>0.95</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="26">
         <f t="shared" si="1"/>
         <v>0.21999999999999997</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="44">
         <f t="shared" si="0"/>
         <v>1.4142135623730952E-2</v>
       </c>
@@ -1235,8 +1249,9 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="4" width="11.265625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.86328125" customWidth="1"/>
-    <col min="7" max="7" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.265625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.3984375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.796875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="22.3984375" customWidth="1"/>
@@ -1293,7 +1308,7 @@
       <c r="G2" s="6">
         <v>7.6909999999999998</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="51">
         <f>$B1+$I$2/3</f>
         <v>5.3766666666666671E-2</v>
       </c>
@@ -1324,7 +1339,7 @@
       <c r="G3" s="6">
         <v>7.5910000000000002</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="51">
         <f>$C1+$I$2/3</f>
         <v>0.15376666666666666</v>
       </c>
@@ -1353,7 +1368,7 @@
       <c r="G4" s="6">
         <v>7.6589999999999998</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="51">
         <f>$D1+$I$2/3</f>
         <v>0.25376666666666664</v>
       </c>
@@ -1382,7 +1397,7 @@
       <c r="G5" s="6">
         <v>7.6</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="51">
         <f>$E1+$I$2/3</f>
         <v>0.35376666666666662</v>
       </c>
@@ -1411,7 +1426,7 @@
       <c r="G6" s="6">
         <v>7.6319999999999997</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="51">
         <f>$F1+$I$2/3</f>
         <v>0.45376666666666665</v>
       </c>
@@ -1422,31 +1437,31 @@
       <c r="A7" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="45">
         <f>AVERAGE(B2:B6)</f>
         <v>24.260399999999997</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="45">
         <f>AVERAGE(C2:C6)</f>
         <v>14.568199999999999</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="45">
         <f>AVERAGE(D2:D6)</f>
         <v>11.264399999999998</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="45">
         <f t="shared" ref="E7:G7" si="0">AVERAGE(E2:E6)</f>
         <v>9.6117999999999988</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="45">
         <f t="shared" si="0"/>
         <v>8.3930000000000007</v>
       </c>
-      <c r="G7" s="19">
+      <c r="G7" s="46">
         <f t="shared" si="0"/>
         <v>7.6345999999999989</v>
       </c>
-      <c r="H7" s="21">
+      <c r="H7" s="52">
         <f>$G1+$I$2/3</f>
         <v>0.55376666666666674</v>
       </c>
@@ -1457,27 +1472,27 @@
       <c r="A8" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="49">
         <f t="shared" ref="B8" si="1">_xlfn.STDEV.S(B2:B6)</f>
         <v>0.27715934045238261</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="49">
         <f>_xlfn.STDEV.S(C2:C6)</f>
         <v>6.7187796510973619E-2</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="49">
         <f>_xlfn.STDEV.S(D2:D6)</f>
         <v>5.1524751333703808E-2</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="49">
         <f>_xlfn.STDEV.S(E2:E6)</f>
         <v>2.2398660674245618E-2</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="49">
         <f>_xlfn.STDEV.S(F2:F6)</f>
         <v>1.0295630140987376E-2</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="50">
         <f>_xlfn.STDEV.S(G2:G6)</f>
         <v>4.1476499370125187E-2</v>
       </c>
@@ -1486,27 +1501,27 @@
       <c r="A9" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="47">
         <f>B8/SQRT(5)</f>
         <v>0.12394942517010696</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="47">
         <f>C8/SQRT(5)</f>
         <v>3.0047296051392041E-2</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="47">
         <f>D8/SQRT(5)</f>
         <v>2.3042569301186932E-2</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="47">
         <f t="shared" ref="E9:G9" si="2">E8/SQRT(5)</f>
         <v>1.0016985574512895E-2</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="47">
         <f t="shared" si="2"/>
         <v>4.6043457732887032E-3</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="48">
         <f t="shared" si="2"/>
         <v>1.8548854412065423E-2</v>
       </c>
@@ -1531,38 +1546,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="31" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A2" s="34">
+      <c r="A2" s="32">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="B2" s="35">
+      <c r="B2" s="33">
         <v>0.99</v>
       </c>
-      <c r="C2" s="37">
+      <c r="C2" s="34">
         <f>$E$2-B2</f>
         <v>9.000000000000008E-2</v>
       </c>
-      <c r="D2" s="39">
+      <c r="D2" s="42">
         <f>0.01*SQRT(2)</f>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E2" s="29">
+      <c r="E2" s="27">
         <v>1.08</v>
       </c>
     </row>
@@ -1577,11 +1592,11 @@
         <f>$E$2-B3</f>
         <v>0.14000000000000012</v>
       </c>
-      <c r="D3" s="24">
+      <c r="D3" s="43">
         <f t="shared" ref="D3:D6" si="0">0.01*SQRT(2)</f>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="30" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1596,11 +1611,11 @@
         <f>$E$2-B4</f>
         <v>0.17000000000000004</v>
       </c>
-      <c r="D4" s="24">
+      <c r="D4" s="43">
         <f t="shared" si="0"/>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E4" s="38">
+      <c r="E4" s="35">
         <v>0.01</v>
       </c>
     </row>
@@ -1615,23 +1630,23 @@
         <f>$E$2-B5</f>
         <v>0.21000000000000008</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="43">
         <f t="shared" si="0"/>
         <v>1.4142135623730952E-2</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A6" s="25">
+      <c r="A6" s="24">
         <v>0.2</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="25">
         <v>0.8</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="26">
         <f>$E$2-B6</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="44">
         <f t="shared" si="0"/>
         <v>1.4142135623730952E-2</v>
       </c>
@@ -1676,38 +1691,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="14.65" thickBot="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="31" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.65" thickBot="1">
-      <c r="A2" s="34">
+      <c r="A2" s="32">
         <v>0.1</v>
       </c>
-      <c r="B2" s="35">
+      <c r="B2" s="33">
         <v>1.25</v>
       </c>
-      <c r="C2" s="37">
+      <c r="C2" s="34">
         <f>$E$2-B2</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="D2" s="39">
+      <c r="D2" s="42">
         <f>0.01*SQRT(2)</f>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E2" s="43">
+      <c r="E2" s="38">
         <v>1.27</v>
       </c>
     </row>
@@ -1722,11 +1737,11 @@
         <f t="shared" ref="C3:C6" si="0">$E$2-B3</f>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="D3" s="24">
+      <c r="D3" s="43">
         <f t="shared" ref="D3:D6" si="1">0.01*SQRT(2)</f>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="E3" s="31" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1741,11 +1756,11 @@
         <f t="shared" si="0"/>
         <v>9.000000000000008E-2</v>
       </c>
-      <c r="D4" s="24">
+      <c r="D4" s="43">
         <f t="shared" si="1"/>
         <v>1.4142135623730952E-2</v>
       </c>
-      <c r="E4" s="42">
+      <c r="E4" s="37">
         <v>0.01</v>
       </c>
     </row>
@@ -1760,7 +1775,7 @@
         <f t="shared" si="0"/>
         <v>0.12000000000000011</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="43">
         <f t="shared" si="1"/>
         <v>1.4142135623730952E-2</v>
       </c>
@@ -1776,23 +1791,23 @@
         <f t="shared" si="0"/>
         <v>0.14999999999999991</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="43">
         <f t="shared" si="1"/>
         <v>1.4142135623730952E-2</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="14.65" thickBot="1">
-      <c r="A7" s="25">
+      <c r="A7" s="24">
         <v>1</v>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="25">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="26">
         <f>$E$2-B7</f>
         <v>0.16999999999999993</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="44">
         <f>0.01*SQRT(2)</f>
         <v>1.4142135623730952E-2</v>
       </c>

--- a/Legge di Hooke.xlsx
+++ b/Legge di Hooke.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="758" documentId="8_{776634F0-C4C9-4588-BBA4-07B3E3D5FCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4578ED43-53D4-40A0-AA14-F53BC5E451A9}"/>
+  <xr:revisionPtr revIDLastSave="761" documentId="8_{776634F0-C4C9-4588-BBA4-07B3E3D5FCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E542A09-BA63-4AB5-B541-C05832E5A159}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="4" activeTab="6" xr2:uid="{90936311-A4D2-4EF7-9615-E94103A7D1D9}"/>
   </bookViews>
@@ -63,6 +63,12 @@
     <t>Dev.std.med</t>
   </si>
   <si>
+    <t>Position (m) Run #6</t>
+  </si>
+  <si>
+    <t>Velocity (m/s) Run #6</t>
+  </si>
+  <si>
     <t>m[kg]</t>
   </si>
   <si>
@@ -90,13 +96,7 @@
     <t>Masse (Kg)</t>
   </si>
   <si>
-    <t xml:space="preserve">Time (s) </t>
-  </si>
-  <si>
-    <t>Position (m)</t>
-  </si>
-  <si>
-    <t>Velocity (m/s)</t>
+    <t>Time (s) Auto</t>
   </si>
 </sst>
 </file>
@@ -791,16 +791,16 @@
   <sheetData>
     <row r="1" spans="1:5" ht="13.5" customHeight="1" thickBot="1">
       <c r="A1" s="28" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D1" s="29" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E1" s="31" t="s">
         <v>0</v>
@@ -837,7 +837,7 @@
         <v>1.4142135619999999E-2</v>
       </c>
       <c r="E3" s="30" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="14.65" thickBot="1">
@@ -981,16 +981,16 @@
   <sheetData>
     <row r="1" spans="1:5" ht="17.350000000000001" customHeight="1" thickBot="1">
       <c r="A1" s="28" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D1" s="29" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E1" s="31" t="s">
         <v>0</v>
@@ -1029,7 +1029,7 @@
         <v>1.4142135619999999E-2</v>
       </c>
       <c r="E3" s="30" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="14.65" thickBot="1">
@@ -1120,16 +1120,16 @@
   <sheetData>
     <row r="1" spans="1:6" ht="14.65" thickBot="1">
       <c r="A1" s="28" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D1" s="29" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E1" s="31" t="s">
         <v>0</v>
@@ -1170,7 +1170,7 @@
         <v>1.4142135623730952E-2</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3" s="2"/>
     </row>
@@ -1255,7 +1255,7 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="18" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B1" s="16">
         <v>0.05</v>
@@ -1276,10 +1276,10 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="H1" s="18" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I1" s="22" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -1543,16 +1543,16 @@
   <sheetData>
     <row r="1" spans="1:7" ht="14.65" thickBot="1">
       <c r="A1" s="28" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D1" s="29" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E1" s="31" t="s">
         <v>0</v>
@@ -1593,7 +1593,7 @@
         <v>1.4142135623730952E-2</v>
       </c>
       <c r="E3" s="30" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="14.65" thickBot="1">
@@ -1688,16 +1688,16 @@
   <sheetData>
     <row r="1" spans="1:6" ht="14.65" thickBot="1">
       <c r="A1" s="28" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E1" s="31" t="s">
         <v>0</v>
@@ -1738,7 +1738,7 @@
         <v>1.4142135623730952E-2</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="14.65" thickBot="1">
@@ -1828,15 +1828,15 @@
     <col min="3" max="3" width="11.46484375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="26.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="54" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B1" s="54" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C1" s="55" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D1" s="12"/>
       <c r="E1" s="3"/>
@@ -1845,13 +1845,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>0.78</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="B2" s="1">
-        <v>1.1220000000000001</v>
+        <v>1.1224000000000001</v>
       </c>
       <c r="C2" s="53">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
@@ -1859,13 +1859,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1">
-        <v>0.8</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="B3" s="1">
         <v>1.1227</v>
       </c>
       <c r="C3" s="53">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="D3" s="15"/>
       <c r="E3" s="15"/>
@@ -1873,13 +1873,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="1">
-        <v>0.82</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="B4" s="1">
-        <v>1.1234999999999999</v>
+        <v>1.1234</v>
       </c>
       <c r="C4" s="53">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="D4" s="15"/>
       <c r="E4" s="15"/>
@@ -1887,13 +1887,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="1">
-        <v>0.84</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="B5" s="1">
-        <v>1.1247</v>
+        <v>1.1241000000000001</v>
       </c>
       <c r="C5" s="53">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="D5" s="15"/>
       <c r="E5" s="15"/>
@@ -1901,13 +1901,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="1">
-        <v>0.86</v>
+        <v>2.34</v>
       </c>
       <c r="B6" s="1">
-        <v>1.1258999999999999</v>
+        <v>1.1249</v>
       </c>
       <c r="C6" s="53">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
@@ -1915,13 +1915,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="1">
-        <v>0.88</v>
+        <v>2.36</v>
       </c>
       <c r="B7" s="1">
-        <v>1.1272</v>
+        <v>1.1258999999999999</v>
       </c>
       <c r="C7" s="53">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
@@ -1929,13 +1929,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="1">
-        <v>0.9</v>
+        <v>2.38</v>
       </c>
       <c r="B8" s="1">
-        <v>1.1286</v>
+        <v>1.1273</v>
       </c>
       <c r="C8" s="53">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
@@ -1943,13 +1943,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="1">
-        <v>0.92</v>
+        <v>2.4</v>
       </c>
       <c r="B9" s="1">
-        <v>1.1303000000000001</v>
+        <v>1.1284000000000001</v>
       </c>
       <c r="C9" s="53">
-        <v>0.08</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="D9" s="15"/>
       <c r="E9" s="15"/>
@@ -1957,10 +1957,10 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="1">
-        <v>0.94</v>
+        <v>2.42</v>
       </c>
       <c r="B10" s="1">
-        <v>1.1316999999999999</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="C10" s="53">
         <v>7.0000000000000007E-2</v>
@@ -1971,13 +1971,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="1">
-        <v>0.96</v>
+        <v>2.44</v>
       </c>
       <c r="B11" s="1">
-        <v>1.1333</v>
+        <v>1.131</v>
       </c>
       <c r="C11" s="53">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="15"/>
@@ -1985,13 +1985,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="1">
-        <v>0.98</v>
+        <v>2.46</v>
       </c>
       <c r="B12" s="1">
-        <v>1.1346000000000001</v>
+        <v>1.1326000000000001</v>
       </c>
       <c r="C12" s="53">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="D12" s="15"/>
       <c r="E12" s="15"/>
@@ -1999,13 +1999,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="1">
-        <v>1</v>
+        <v>2.48</v>
       </c>
       <c r="B13" s="1">
-        <v>1.1359999999999999</v>
+        <v>1.1335999999999999</v>
       </c>
       <c r="C13" s="53">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="D13" s="15"/>
       <c r="E13" s="15"/>
@@ -2013,13 +2013,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1">
-        <v>1.02</v>
+        <v>2.5</v>
       </c>
       <c r="B14" s="1">
-        <v>1.1375</v>
+        <v>1.1349</v>
       </c>
       <c r="C14" s="53">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="D14" s="15"/>
       <c r="E14" s="15"/>
@@ -2027,13 +2027,13 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="1">
-        <v>1.04</v>
+        <v>2.52</v>
       </c>
       <c r="B15" s="1">
-        <v>1.1384000000000001</v>
+        <v>1.1358999999999999</v>
       </c>
       <c r="C15" s="53">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="15"/>
@@ -2041,13 +2041,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="1">
-        <v>1.06</v>
+        <v>2.54</v>
       </c>
       <c r="B16" s="1">
-        <v>1.139</v>
+        <v>1.1368</v>
       </c>
       <c r="C16" s="53">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="D16" s="15"/>
       <c r="E16" s="15"/>
@@ -2055,10 +2055,10 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="1">
-        <v>1.08</v>
+        <v>2.56</v>
       </c>
       <c r="B17" s="1">
-        <v>1.1397999999999999</v>
+        <v>1.1374</v>
       </c>
       <c r="C17" s="53">
         <v>0.03</v>
@@ -2069,13 +2069,13 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="1">
-        <v>1.1000000000000001</v>
+        <v>2.58</v>
       </c>
       <c r="B18" s="1">
-        <v>1.1402000000000001</v>
+        <v>1.1378999999999999</v>
       </c>
       <c r="C18" s="53">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="D18" s="15"/>
       <c r="E18" s="15"/>
@@ -2083,13 +2083,13 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="1">
-        <v>1.1200000000000001</v>
+        <v>2.6</v>
       </c>
       <c r="B19" s="1">
-        <v>1.1402000000000001</v>
+        <v>1.1380999999999999</v>
       </c>
       <c r="C19" s="53">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
@@ -2097,13 +2097,13 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="1">
-        <v>1.1399999999999999</v>
+        <v>2.62</v>
       </c>
       <c r="B20" s="1">
-        <v>1.1400999999999999</v>
+        <v>1.1382000000000001</v>
       </c>
       <c r="C20" s="53">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
@@ -2111,13 +2111,13 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="1">
-        <v>1.1599999999999999</v>
+        <v>2.64</v>
       </c>
       <c r="B21" s="1">
-        <v>1.1395999999999999</v>
+        <v>1.1377999999999999</v>
       </c>
       <c r="C21" s="53">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
@@ -2125,13 +2125,13 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="1">
-        <v>1.18</v>
+        <v>2.66</v>
       </c>
       <c r="B22" s="1">
-        <v>1.139</v>
+        <v>1.1375</v>
       </c>
       <c r="C22" s="53">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="D22" s="15"/>
       <c r="E22" s="15"/>
@@ -2139,13 +2139,13 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="1">
-        <v>1.2</v>
+        <v>2.68</v>
       </c>
       <c r="B23" s="1">
-        <v>1.1382000000000001</v>
+        <v>1.1368</v>
       </c>
       <c r="C23" s="53">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="15"/>
@@ -2153,13 +2153,13 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="1">
-        <v>1.22</v>
+        <v>2.7</v>
       </c>
       <c r="B24" s="1">
-        <v>1.137</v>
+        <v>1.1365000000000001</v>
       </c>
       <c r="C24" s="53">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="D24" s="15"/>
       <c r="E24" s="15"/>
@@ -2167,13 +2167,13 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="1">
-        <v>1.24</v>
+        <v>2.72</v>
       </c>
       <c r="B25" s="1">
-        <v>1.1355999999999999</v>
+        <v>1.135</v>
       </c>
       <c r="C25" s="53">
-        <v>-7.0000000000000007E-2</v>
+        <v>-0.05</v>
       </c>
       <c r="D25" s="15"/>
       <c r="E25" s="15"/>
@@ -2181,13 +2181,13 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="1">
-        <v>1.26</v>
+        <v>2.74</v>
       </c>
       <c r="B26" s="1">
-        <v>1.1345000000000001</v>
+        <v>1.1339999999999999</v>
       </c>
       <c r="C26" s="53">
-        <v>-7.0000000000000007E-2</v>
+        <v>-0.06</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
@@ -2195,13 +2195,13 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="1">
-        <v>1.28</v>
+        <v>2.76</v>
       </c>
       <c r="B27" s="1">
-        <v>1.1327</v>
+        <v>1.1331</v>
       </c>
       <c r="C27" s="53">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -2209,13 +2209,13 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="1">
-        <v>1.3</v>
+        <v>2.78</v>
       </c>
       <c r="B28" s="1">
         <v>1.1312</v>
       </c>
       <c r="C28" s="53">
-        <v>-0.08</v>
+        <v>-7.0000000000000007E-2</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -2223,13 +2223,13 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="1">
-        <v>1.32</v>
+        <v>2.8</v>
       </c>
       <c r="B29" s="1">
-        <v>1.1296999999999999</v>
+        <v>1.1303000000000001</v>
       </c>
       <c r="C29" s="53">
-        <v>-0.08</v>
+        <v>-7.0000000000000007E-2</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
@@ -2237,13 +2237,13 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="1">
-        <v>1.34</v>
+        <v>2.82</v>
       </c>
       <c r="B30" s="1">
-        <v>1.1276999999999999</v>
+        <v>1.1287</v>
       </c>
       <c r="C30" s="53">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
@@ -2251,13 +2251,13 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="1">
-        <v>1.36</v>
+        <v>2.84</v>
       </c>
       <c r="B31" s="1">
-        <v>1.1264000000000001</v>
+        <v>1.1274999999999999</v>
       </c>
       <c r="C31" s="53">
-        <v>-0.08</v>
+        <v>-7.0000000000000007E-2</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
@@ -2265,13 +2265,13 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="1">
-        <v>1.38</v>
+        <v>2.86</v>
       </c>
       <c r="B32" s="1">
-        <v>1.1244000000000001</v>
+        <v>1.1263000000000001</v>
       </c>
       <c r="C32" s="53">
-        <v>-7.0000000000000007E-2</v>
+        <v>-0.06</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
@@ -2279,13 +2279,13 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="1">
-        <v>1.4</v>
+        <v>2.88</v>
       </c>
       <c r="B33" s="1">
-        <v>1.1232</v>
+        <v>1.1248</v>
       </c>
       <c r="C33" s="53">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
@@ -2293,13 +2293,13 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="1">
-        <v>1.42</v>
+        <v>2.9</v>
       </c>
       <c r="B34" s="1">
-        <v>1.1221000000000001</v>
+        <v>1.1242000000000001</v>
       </c>
       <c r="C34" s="53">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
@@ -2307,13 +2307,13 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="1">
-        <v>1.44</v>
+        <v>2.92</v>
       </c>
       <c r="B35" s="1">
-        <v>1.1214</v>
+        <v>1.1233</v>
       </c>
       <c r="C35" s="53">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
@@ -2321,13 +2321,13 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="1">
-        <v>1.46</v>
+        <v>2.94</v>
       </c>
       <c r="B36" s="1">
-        <v>1.1206</v>
+        <v>1.1225000000000001</v>
       </c>
       <c r="C36" s="53">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
@@ -2335,21 +2335,28 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="1">
-        <v>1.48</v>
+        <v>2.96</v>
       </c>
       <c r="B37" s="1">
-        <v>1.1204000000000001</v>
+        <v>1.1222000000000001</v>
       </c>
       <c r="C37" s="53">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
     </row>
     <row r="38" spans="1:6">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
+      <c r="A38" s="1">
+        <v>2.98</v>
+      </c>
+      <c r="B38" s="1">
+        <v>1.1218999999999999</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
@@ -4875,7 +4882,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="18" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B1" s="16">
         <v>0.05</v>
@@ -4896,7 +4903,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="H1" s="18" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:8">

--- a/Legge di Hooke.xlsx
+++ b/Legge di Hooke.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="761" documentId="8_{776634F0-C4C9-4588-BBA4-07B3E3D5FCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E542A09-BA63-4AB5-B541-C05832E5A159}"/>
+  <xr:revisionPtr revIDLastSave="762" documentId="8_{776634F0-C4C9-4588-BBA4-07B3E3D5FCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADD41B96-8205-43D4-947B-4CB30220CA10}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="4" activeTab="6" xr2:uid="{90936311-A4D2-4EF7-9615-E94103A7D1D9}"/>
   </bookViews>
@@ -63,12 +63,6 @@
     <t>Dev.std.med</t>
   </si>
   <si>
-    <t>Position (m) Run #6</t>
-  </si>
-  <si>
-    <t>Velocity (m/s) Run #6</t>
-  </si>
-  <si>
     <t>m[kg]</t>
   </si>
   <si>
@@ -96,7 +90,13 @@
     <t>Masse (Kg)</t>
   </si>
   <si>
-    <t>Time (s) Auto</t>
+    <t>t1 (s) Set</t>
+  </si>
+  <si>
+    <t>x (m) Set</t>
+  </si>
+  <si>
+    <t>v (m/s) Set</t>
   </si>
 </sst>
 </file>
@@ -335,7 +335,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -439,11 +439,10 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -791,16 +790,16 @@
   <sheetData>
     <row r="1" spans="1:5" ht="13.5" customHeight="1" thickBot="1">
       <c r="A1" s="28" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D1" s="29" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E1" s="31" t="s">
         <v>0</v>
@@ -837,7 +836,7 @@
         <v>1.4142135619999999E-2</v>
       </c>
       <c r="E3" s="30" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="14.65" thickBot="1">
@@ -981,16 +980,16 @@
   <sheetData>
     <row r="1" spans="1:5" ht="17.350000000000001" customHeight="1" thickBot="1">
       <c r="A1" s="28" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D1" s="29" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E1" s="31" t="s">
         <v>0</v>
@@ -1029,7 +1028,7 @@
         <v>1.4142135619999999E-2</v>
       </c>
       <c r="E3" s="30" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="14.65" thickBot="1">
@@ -1120,16 +1119,16 @@
   <sheetData>
     <row r="1" spans="1:6" ht="14.65" thickBot="1">
       <c r="A1" s="28" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D1" s="29" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E1" s="31" t="s">
         <v>0</v>
@@ -1170,7 +1169,7 @@
         <v>1.4142135623730952E-2</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F3" s="2"/>
     </row>
@@ -1255,7 +1254,7 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" s="16">
         <v>0.05</v>
@@ -1276,10 +1275,10 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="H1" s="18" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I1" s="22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -1543,16 +1542,16 @@
   <sheetData>
     <row r="1" spans="1:7" ht="14.65" thickBot="1">
       <c r="A1" s="28" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D1" s="29" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E1" s="31" t="s">
         <v>0</v>
@@ -1593,7 +1592,7 @@
         <v>1.4142135623730952E-2</v>
       </c>
       <c r="E3" s="30" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="14.65" thickBot="1">
@@ -1688,16 +1687,16 @@
   <sheetData>
     <row r="1" spans="1:6" ht="14.65" thickBot="1">
       <c r="A1" s="28" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E1" s="31" t="s">
         <v>0</v>
@@ -1738,7 +1737,7 @@
         <v>1.4142135623730952E-2</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="14.65" thickBot="1">
@@ -1829,14 +1828,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="54" t="s">
         <v>15</v>
-      </c>
-      <c r="B1" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="55" t="s">
-        <v>5</v>
       </c>
       <c r="D1" s="12"/>
       <c r="E1" s="3"/>
@@ -1845,13 +1844,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>2.2599999999999998</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="B2" s="1">
-        <v>1.1224000000000001</v>
-      </c>
-      <c r="C2" s="53">
-        <v>0.01</v>
+        <v>1.1223000000000001</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
@@ -1859,13 +1858,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1">
-        <v>2.2799999999999998</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="B3" s="1">
-        <v>1.1227</v>
-      </c>
-      <c r="C3" s="53">
-        <v>0.02</v>
+        <v>1.1224000000000001</v>
+      </c>
+      <c r="C3">
+        <v>0.01</v>
       </c>
       <c r="D3" s="15"/>
       <c r="E3" s="15"/>
@@ -1873,13 +1872,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="1">
-        <v>2.2999999999999998</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="B4" s="1">
-        <v>1.1234</v>
-      </c>
-      <c r="C4" s="53">
-        <v>0.03</v>
+        <v>1.1227</v>
+      </c>
+      <c r="C4">
+        <v>0.02</v>
       </c>
       <c r="D4" s="15"/>
       <c r="E4" s="15"/>
@@ -1887,13 +1886,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="1">
-        <v>2.3199999999999998</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="B5" s="1">
-        <v>1.1241000000000001</v>
-      </c>
-      <c r="C5" s="53">
-        <v>0.04</v>
+        <v>1.1234</v>
+      </c>
+      <c r="C5">
+        <v>0.03</v>
       </c>
       <c r="D5" s="15"/>
       <c r="E5" s="15"/>
@@ -1901,13 +1900,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="1">
-        <v>2.34</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="B6" s="1">
-        <v>1.1249</v>
-      </c>
-      <c r="C6" s="53">
-        <v>0.05</v>
+        <v>1.1241000000000001</v>
+      </c>
+      <c r="C6">
+        <v>0.04</v>
       </c>
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
@@ -1915,13 +1914,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="1">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="B7" s="1">
-        <v>1.1258999999999999</v>
-      </c>
-      <c r="C7" s="53">
-        <v>0.06</v>
+        <v>1.1249</v>
+      </c>
+      <c r="C7">
+        <v>0.05</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
@@ -1929,12 +1928,12 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="1">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="B8" s="1">
-        <v>1.1273</v>
-      </c>
-      <c r="C8" s="53">
+        <v>1.1258999999999999</v>
+      </c>
+      <c r="C8">
         <v>0.06</v>
       </c>
       <c r="D8" s="15"/>
@@ -1943,13 +1942,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="1">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="B9" s="1">
-        <v>1.1284000000000001</v>
-      </c>
-      <c r="C9" s="53">
-        <v>7.0000000000000007E-2</v>
+        <v>1.1273</v>
+      </c>
+      <c r="C9">
+        <v>0.06</v>
       </c>
       <c r="D9" s="15"/>
       <c r="E9" s="15"/>
@@ -1957,12 +1956,12 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="1">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="B10" s="1">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="C10" s="53">
+        <v>1.1284000000000001</v>
+      </c>
+      <c r="C10">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D10" s="15"/>
@@ -1971,13 +1970,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="1">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="B11" s="1">
-        <v>1.131</v>
-      </c>
-      <c r="C11" s="53">
-        <v>0.06</v>
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="C11">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="15"/>
@@ -1985,12 +1984,12 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="1">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="B12" s="1">
-        <v>1.1326000000000001</v>
-      </c>
-      <c r="C12" s="53">
+        <v>1.131</v>
+      </c>
+      <c r="C12">
         <v>0.06</v>
       </c>
       <c r="D12" s="15"/>
@@ -1999,12 +1998,12 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="1">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="B13" s="1">
-        <v>1.1335999999999999</v>
-      </c>
-      <c r="C13" s="53">
+        <v>1.1326000000000001</v>
+      </c>
+      <c r="C13">
         <v>0.06</v>
       </c>
       <c r="D13" s="15"/>
@@ -2013,13 +2012,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="B14" s="1">
-        <v>1.1349</v>
-      </c>
-      <c r="C14" s="53">
-        <v>0.05</v>
+        <v>1.1335999999999999</v>
+      </c>
+      <c r="C14">
+        <v>0.06</v>
       </c>
       <c r="D14" s="15"/>
       <c r="E14" s="15"/>
@@ -2027,12 +2026,12 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="1">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="B15" s="1">
-        <v>1.1358999999999999</v>
-      </c>
-      <c r="C15" s="53">
+        <v>1.1349</v>
+      </c>
+      <c r="C15">
         <v>0.05</v>
       </c>
       <c r="D15" s="15"/>
@@ -2041,13 +2040,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="1">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="B16" s="1">
-        <v>1.1368</v>
-      </c>
-      <c r="C16" s="53">
-        <v>0.04</v>
+        <v>1.1358999999999999</v>
+      </c>
+      <c r="C16">
+        <v>0.05</v>
       </c>
       <c r="D16" s="15"/>
       <c r="E16" s="15"/>
@@ -2055,13 +2054,13 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="1">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="B17" s="1">
-        <v>1.1374</v>
-      </c>
-      <c r="C17" s="53">
-        <v>0.03</v>
+        <v>1.1368</v>
+      </c>
+      <c r="C17">
+        <v>0.04</v>
       </c>
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
@@ -2069,13 +2068,13 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="1">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="B18" s="1">
-        <v>1.1378999999999999</v>
-      </c>
-      <c r="C18" s="53">
-        <v>0.02</v>
+        <v>1.1374</v>
+      </c>
+      <c r="C18">
+        <v>0.03</v>
       </c>
       <c r="D18" s="15"/>
       <c r="E18" s="15"/>
@@ -2083,13 +2082,13 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="1">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="B19" s="1">
-        <v>1.1380999999999999</v>
-      </c>
-      <c r="C19" s="53">
-        <v>0.01</v>
+        <v>1.1378999999999999</v>
+      </c>
+      <c r="C19">
+        <v>0.02</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
@@ -2097,13 +2096,13 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="1">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="B20" s="1">
-        <v>1.1382000000000001</v>
-      </c>
-      <c r="C20" s="53">
-        <v>-0.01</v>
+        <v>1.1380999999999999</v>
+      </c>
+      <c r="C20">
+        <v>0.01</v>
       </c>
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
@@ -2111,13 +2110,13 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="1">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="B21" s="1">
-        <v>1.1377999999999999</v>
-      </c>
-      <c r="C21" s="53">
-        <v>-0.02</v>
+        <v>1.1382000000000001</v>
+      </c>
+      <c r="C21">
+        <v>-0.01</v>
       </c>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
@@ -2125,12 +2124,12 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="1">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="B22" s="1">
-        <v>1.1375</v>
-      </c>
-      <c r="C22" s="53">
+        <v>1.1377999999999999</v>
+      </c>
+      <c r="C22">
         <v>-0.02</v>
       </c>
       <c r="D22" s="15"/>
@@ -2139,13 +2138,13 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="1">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="B23" s="1">
-        <v>1.1368</v>
-      </c>
-      <c r="C23" s="53">
-        <v>-0.03</v>
+        <v>1.1375</v>
+      </c>
+      <c r="C23">
+        <v>-0.02</v>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="15"/>
@@ -2153,13 +2152,13 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="1">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="B24" s="1">
-        <v>1.1365000000000001</v>
-      </c>
-      <c r="C24" s="53">
-        <v>-0.04</v>
+        <v>1.1368</v>
+      </c>
+      <c r="C24">
+        <v>-0.03</v>
       </c>
       <c r="D24" s="15"/>
       <c r="E24" s="15"/>
@@ -2167,13 +2166,13 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="1">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="B25" s="1">
-        <v>1.135</v>
-      </c>
-      <c r="C25" s="53">
-        <v>-0.05</v>
+        <v>1.1365000000000001</v>
+      </c>
+      <c r="C25">
+        <v>-0.04</v>
       </c>
       <c r="D25" s="15"/>
       <c r="E25" s="15"/>
@@ -2181,13 +2180,13 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="1">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="B26" s="1">
-        <v>1.1339999999999999</v>
-      </c>
-      <c r="C26" s="53">
-        <v>-0.06</v>
+        <v>1.135</v>
+      </c>
+      <c r="C26">
+        <v>-0.05</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
@@ -2195,12 +2194,12 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="1">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="B27" s="1">
-        <v>1.1331</v>
-      </c>
-      <c r="C27" s="53">
+        <v>1.1339999999999999</v>
+      </c>
+      <c r="C27">
         <v>-0.06</v>
       </c>
       <c r="D27" s="1"/>
@@ -2209,13 +2208,13 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="1">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="B28" s="1">
-        <v>1.1312</v>
-      </c>
-      <c r="C28" s="53">
-        <v>-7.0000000000000007E-2</v>
+        <v>1.1331</v>
+      </c>
+      <c r="C28">
+        <v>-0.06</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -2223,12 +2222,12 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="1">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="B29" s="1">
-        <v>1.1303000000000001</v>
-      </c>
-      <c r="C29" s="53">
+        <v>1.1312</v>
+      </c>
+      <c r="C29">
         <v>-7.0000000000000007E-2</v>
       </c>
       <c r="D29" s="1"/>
@@ -2237,13 +2236,13 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="1">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="B30" s="1">
-        <v>1.1287</v>
-      </c>
-      <c r="C30" s="53">
-        <v>-0.06</v>
+        <v>1.1303000000000001</v>
+      </c>
+      <c r="C30">
+        <v>-7.0000000000000007E-2</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
@@ -2251,13 +2250,13 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="1">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="B31" s="1">
-        <v>1.1274999999999999</v>
-      </c>
-      <c r="C31" s="53">
-        <v>-7.0000000000000007E-2</v>
+        <v>1.1287</v>
+      </c>
+      <c r="C31">
+        <v>-0.06</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
@@ -2265,13 +2264,13 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="1">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="B32" s="1">
-        <v>1.1263000000000001</v>
-      </c>
-      <c r="C32" s="53">
-        <v>-0.06</v>
+        <v>1.1274999999999999</v>
+      </c>
+      <c r="C32">
+        <v>-7.0000000000000007E-2</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
@@ -2279,13 +2278,13 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="1">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="B33" s="1">
-        <v>1.1248</v>
-      </c>
-      <c r="C33" s="53">
-        <v>-0.05</v>
+        <v>1.1263000000000001</v>
+      </c>
+      <c r="C33">
+        <v>-0.06</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
@@ -2293,13 +2292,13 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="1">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="B34" s="1">
-        <v>1.1242000000000001</v>
-      </c>
-      <c r="C34" s="53">
-        <v>-0.04</v>
+        <v>1.1248</v>
+      </c>
+      <c r="C34">
+        <v>-0.05</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
@@ -2307,12 +2306,12 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="1">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="B35" s="1">
-        <v>1.1233</v>
-      </c>
-      <c r="C35" s="53">
+        <v>1.1242000000000001</v>
+      </c>
+      <c r="C35">
         <v>-0.04</v>
       </c>
       <c r="D35" s="1"/>
@@ -2321,13 +2320,13 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="1">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="B36" s="1">
-        <v>1.1225000000000001</v>
-      </c>
-      <c r="C36" s="53">
-        <v>-0.03</v>
+        <v>1.1233</v>
+      </c>
+      <c r="C36">
+        <v>-0.04</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
@@ -2335,13 +2334,13 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="1">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="B37" s="1">
-        <v>1.1222000000000001</v>
-      </c>
-      <c r="C37" s="53">
-        <v>-0.02</v>
+        <v>1.1225000000000001</v>
+      </c>
+      <c r="C37">
+        <v>-0.03</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
@@ -2349,13 +2348,13 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="1">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="B38" s="1">
-        <v>1.1218999999999999</v>
+        <v>1.1222000000000001</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
@@ -4882,7 +4881,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" s="16">
         <v>0.05</v>
@@ -4903,7 +4902,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="H1" s="18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:8">

--- a/Legge di Hooke.xlsx
+++ b/Legge di Hooke.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Misure statiche 1" sheetId="1" state="visible" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>m[kg]</t>
   </si>
@@ -64,19 +64,19 @@
     <t xml:space="preserve">Masse (kg)</t>
   </si>
   <si>
-    <t xml:space="preserve">Masse corrette(Kg)</t>
+    <t xml:space="preserve">Masse corrette [kg]</t>
   </si>
   <si>
-    <t xml:space="preserve">Massa molla (kg)</t>
+    <t>ω</t>
   </si>
   <si>
-    <t>Media</t>
+    <t>σω</t>
   </si>
   <si>
-    <t>Dev.std</t>
+    <t xml:space="preserve">Massa molla [kg]</t>
   </si>
   <si>
-    <t>Dev.std.med</t>
+    <t>σω_</t>
   </si>
   <si>
     <t xml:space="preserve">t1 (s) Set</t>
@@ -90,13 +90,23 @@
   <si>
     <t xml:space="preserve">Masse (Kg)</t>
   </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>Dev.std</t>
+  </si>
+  <si>
+    <t>Dev.std.med</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0000"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -135,7 +145,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -155,6 +165,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor indexed="5"/>
       </patternFill>
     </fill>
@@ -164,7 +180,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="26">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -306,6 +322,148 @@
     </border>
     <border>
       <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
         <color auto="1"/>
       </left>
       <right style="medium">
@@ -319,7 +477,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="81">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="1" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -336,7 +494,7 @@
     <xf fontId="1" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="0" borderId="6" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -352,7 +510,7 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="8" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="0" borderId="8" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="9" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -361,13 +519,25 @@
     <xf fontId="1" fillId="0" borderId="10" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="1" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="1" fillId="2" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="1" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="1" fillId="0" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="8" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="9" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
     <xf fontId="2" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="2" fillId="3" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="2" fillId="3" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="1" fillId="0" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="3" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="1" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -386,41 +556,48 @@
     <xf fontId="1" fillId="0" borderId="10" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="13" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="14" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="15" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="13" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="16" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="17" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="18" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="18" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="2" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="4" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="5" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="7" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="5" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="9" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="17" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="19" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="16" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="2" numFmtId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="20" numFmtId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="21" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf fontId="0" fillId="4" borderId="17" numFmtId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="22" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="19" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="23" numFmtId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="24" numFmtId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="19" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="1" fillId="0" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf fontId="2" fillId="3" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="1" fillId="0" borderId="13" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="0" borderId="25" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="1" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
+    <xf fontId="0" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -430,10 +607,22 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="5" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="5" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="6" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="4" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="6" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="6" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1036,7 +1225,7 @@
       <c r="B5" s="9">
         <v>1.1599999999999999</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="12">
         <v>0.10000000000000001</v>
       </c>
       <c r="D5" s="10">
@@ -1146,28 +1335,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="12.796875"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="16.33203125"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="19"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="17.53125"/>
+    <col customWidth="1" min="1" max="2" width="8.125"/>
+    <col customWidth="1" min="3" max="3" width="8.25390625"/>
+    <col customWidth="1" min="4" max="5" width="8.125"/>
     <col bestFit="1" customWidth="1" min="6" max="6" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.350000000000001" customHeight="1">
+    <row r="1" ht="13">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="19" t="s">
-        <v>9</v>
+        <v>2</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="2" ht="14.65">
@@ -1184,12 +1372,12 @@
       <c r="D2" s="6">
         <v>1.4142135619999999e-002</v>
       </c>
-      <c r="E2" s="20">
+      <c r="E2" s="21">
         <v>1.26</v>
       </c>
     </row>
     <row r="3" ht="14.65">
-      <c r="A3" s="8">
+      <c r="A3" s="22">
         <v>0.20000000000000001</v>
       </c>
       <c r="B3" s="9">
@@ -1202,12 +1390,12 @@
       <c r="D3" s="10">
         <v>1.4142135619999999e-002</v>
       </c>
-      <c r="E3" s="21" t="s">
-        <v>10</v>
+      <c r="E3" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="4" ht="14.65">
-      <c r="A4" s="8">
+      <c r="A4" s="22">
         <v>0.29999999999999999</v>
       </c>
       <c r="B4" s="9">
@@ -1225,7 +1413,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8">
+      <c r="A5" s="22">
         <v>0.40000000000000002</v>
       </c>
       <c r="B5" s="9">
@@ -1240,10 +1428,10 @@
       </c>
     </row>
     <row r="6" ht="14.65">
-      <c r="A6" s="14">
+      <c r="A6" s="23">
         <v>0.5</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="24">
         <v>1.1000000000000001</v>
       </c>
       <c r="C6" s="15">
@@ -1294,19 +1482,19 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.65">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="27" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1317,20 +1505,20 @@
       <c r="B2" s="5">
         <v>1.1100000000000001</v>
       </c>
-      <c r="C2" s="22">
+      <c r="C2" s="28">
         <f t="shared" ref="C2:C6" si="1">$E$2-B2</f>
         <v>5.9999999999999831e-002</v>
       </c>
-      <c r="D2" s="23">
+      <c r="D2" s="29">
         <f t="shared" ref="D2:D6" si="2">0.01*SQRT(2)</f>
         <v>1.4142135623730952e-002</v>
       </c>
-      <c r="E2" s="24">
+      <c r="E2" s="30">
         <v>1.1699999999999999</v>
       </c>
     </row>
     <row r="3" ht="14.65">
-      <c r="A3" s="8">
+      <c r="A3" s="22">
         <v>7.0000000000000007e-002</v>
       </c>
       <c r="B3" s="9">
@@ -1340,17 +1528,17 @@
         <f t="shared" si="1"/>
         <v>7.9999999999999849e-002</v>
       </c>
-      <c r="D3" s="25">
+      <c r="D3" s="31">
         <f t="shared" si="2"/>
         <v>1.4142135623730952e-002</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="27" t="s">
         <v>10</v>
       </c>
       <c r="F3" s="13"/>
     </row>
     <row r="4" ht="14.65">
-      <c r="A4" s="8">
+      <c r="A4" s="22">
         <v>0.10000000000000001</v>
       </c>
       <c r="B4" s="9">
@@ -1360,17 +1548,17 @@
         <f t="shared" si="1"/>
         <v>0.10999999999999988</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="31">
         <f t="shared" si="2"/>
         <v>1.4142135623730952e-002</v>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="30">
         <v>1.e-002</v>
       </c>
       <c r="F4" s="13"/>
     </row>
     <row r="5">
-      <c r="A5" s="8">
+      <c r="A5" s="22">
         <v>0.14999999999999999</v>
       </c>
       <c r="B5" s="9">
@@ -1380,7 +1568,7 @@
         <f t="shared" si="1"/>
         <v>0.15999999999999992</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="31">
         <f t="shared" si="2"/>
         <v>1.4142135623730952e-002</v>
       </c>
@@ -1388,17 +1576,17 @@
       <c r="F5" s="13"/>
     </row>
     <row r="6" ht="14.65">
-      <c r="A6" s="14">
+      <c r="A6" s="23">
         <v>0.20000000000000001</v>
       </c>
       <c r="B6" s="15">
         <v>0.94999999999999996</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="32">
         <f t="shared" si="1"/>
         <v>0.21999999999999997</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="33">
         <f t="shared" si="2"/>
         <v>1.4142135623730952e-002</v>
       </c>
@@ -1425,48 +1613,45 @@
     <col bestFit="1" customWidth="1" min="2" max="4" width="11.265625"/>
     <col customWidth="1" min="5" max="5" width="11.86328125"/>
     <col bestFit="1" customWidth="1" min="6" max="7" width="11.265625"/>
-    <col bestFit="1" customWidth="1" min="8" max="8" width="15.3984375"/>
-    <col bestFit="1" customWidth="1" min="9" max="9" width="13.796875"/>
+    <col bestFit="1" customWidth="1" min="8" max="8" width="15.953125"/>
+    <col bestFit="1" customWidth="1" min="9" max="9" width="14.375"/>
     <col customWidth="1" min="12" max="12" width="22.3984375"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="29">
+      <c r="B1" s="35">
         <v>5.0000000000000003e-002</v>
       </c>
-      <c r="C1" s="29">
+      <c r="C1" s="35">
         <v>0.14999999999999999</v>
       </c>
-      <c r="D1" s="29">
+      <c r="D1" s="35">
         <v>0.25</v>
       </c>
-      <c r="E1" s="29">
+      <c r="E1" s="35">
         <v>0.34999999999999998</v>
       </c>
-      <c r="F1" s="29">
+      <c r="F1" s="35">
         <v>0.45000000000000001</v>
       </c>
-      <c r="G1" s="30">
+      <c r="G1" s="36">
         <v>0.55000000000000004</v>
       </c>
-      <c r="H1" s="28" t="s">
+      <c r="H1" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="31" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="32">
+      <c r="A2" s="38">
         <v>1</v>
       </c>
       <c r="B2">
         <v>23.844000000000001</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="39">
         <v>14.49</v>
       </c>
       <c r="D2">
@@ -1478,20 +1663,17 @@
       <c r="F2">
         <v>8.3829999999999991</v>
       </c>
-      <c r="G2" s="33">
+      <c r="G2" s="40">
         <v>7.6909999999999998</v>
       </c>
-      <c r="H2" s="34">
-        <f>$B1+$I$2/3</f>
+      <c r="H2" s="41">
+        <f>$B1+$H$9/3</f>
         <v>5.3766666666666671e-002</v>
       </c>
-      <c r="I2" s="33">
-        <v>1.1299999999999999e-002</v>
-      </c>
-      <c r="L2" s="35"/>
+      <c r="L2" s="42"/>
     </row>
     <row r="3">
-      <c r="A3" s="36">
+      <c r="A3" s="43">
         <v>2</v>
       </c>
       <c r="B3">
@@ -1509,21 +1691,20 @@
       <c r="F3">
         <v>8.4060000000000006</v>
       </c>
-      <c r="G3" s="33">
+      <c r="G3" s="40">
         <v>7.5910000000000002</v>
       </c>
-      <c r="H3" s="34">
-        <f>$C1+$I$2/3</f>
+      <c r="H3" s="41">
+        <f>$C1+$H$9/3</f>
         <v>0.15376666666666666</v>
       </c>
-      <c r="I3" s="33"/>
-      <c r="L3" s="35"/>
+      <c r="L3" s="42"/>
     </row>
     <row r="4">
-      <c r="A4" s="36">
+      <c r="A4" s="43">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="39">
         <v>24.129999999999999</v>
       </c>
       <c r="C4">
@@ -1538,21 +1719,20 @@
       <c r="F4">
         <v>8.3879999999999999</v>
       </c>
-      <c r="G4" s="33">
+      <c r="G4" s="40">
         <v>7.6589999999999998</v>
       </c>
-      <c r="H4" s="34">
-        <f>$D1+$I$2/3</f>
+      <c r="H4" s="41">
+        <f>$D1+$H$9/3</f>
         <v>0.25376666666666664</v>
       </c>
-      <c r="I4" s="33"/>
-      <c r="L4" s="35"/>
+      <c r="L4" s="42"/>
     </row>
     <row r="5">
-      <c r="A5" s="36">
+      <c r="A5" s="43">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="39">
         <v>24.359999999999999</v>
       </c>
       <c r="C5">
@@ -1561,24 +1741,23 @@
       <c r="D5">
         <v>11.298999999999999</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="39">
         <v>9.6300000000000008</v>
       </c>
       <c r="F5">
         <v>8.3859999999999992</v>
       </c>
-      <c r="G5" s="33">
+      <c r="G5" s="44">
         <v>7.5999999999999996</v>
       </c>
-      <c r="H5" s="34">
-        <f>$E1+$I$2/3</f>
+      <c r="H5" s="41">
+        <f>$E1+$H$9/3</f>
         <v>0.35376666666666662</v>
       </c>
-      <c r="I5" s="33"/>
-      <c r="L5" s="35"/>
+      <c r="L5" s="42"/>
     </row>
     <row r="6" ht="14.65">
-      <c r="A6" s="36">
+      <c r="A6" s="45">
         <v>5</v>
       </c>
       <c r="B6">
@@ -1587,7 +1766,7 @@
       <c r="C6">
         <v>14.542</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="39">
         <v>11.26</v>
       </c>
       <c r="E6">
@@ -1596,107 +1775,111 @@
       <c r="F6">
         <v>8.4019999999999992</v>
       </c>
-      <c r="G6" s="33">
+      <c r="G6" s="40">
         <v>7.6319999999999997</v>
       </c>
-      <c r="H6" s="34">
-        <f>$F1+$I$2/3</f>
+      <c r="H6" s="41">
+        <f>$F1+$H$9/3</f>
         <v>0.45376666666666665</v>
       </c>
-      <c r="I6" s="33"/>
-      <c r="L6" s="35"/>
+      <c r="L6" s="42"/>
     </row>
     <row r="7" ht="14.65">
-      <c r="A7" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="38">
+      <c r="A7" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="47">
         <f>AVERAGE(B2:B6)</f>
         <v>24.260399999999997</v>
       </c>
-      <c r="C7" s="38">
+      <c r="C7" s="47">
         <f>AVERAGE(C2:C6)</f>
         <v>14.568199999999999</v>
       </c>
-      <c r="D7" s="38">
+      <c r="D7" s="47">
         <f>AVERAGE(D2:D6)</f>
         <v>11.264399999999998</v>
       </c>
-      <c r="E7" s="38">
+      <c r="E7" s="47">
         <f t="shared" ref="E7:G7" si="3">AVERAGE(E2:E6)</f>
         <v>9.6117999999999988</v>
       </c>
-      <c r="F7" s="38">
+      <c r="F7" s="47">
         <f t="shared" si="3"/>
         <v>8.3930000000000007</v>
       </c>
-      <c r="G7" s="39">
+      <c r="G7" s="48">
         <f t="shared" si="3"/>
         <v>7.6345999999999989</v>
       </c>
-      <c r="H7" s="40">
-        <f>$G1+$I$2/3</f>
+      <c r="H7" s="49">
+        <f>$G1+$H$9/3</f>
         <v>0.55376666666666674</v>
       </c>
-      <c r="I7" s="41"/>
-      <c r="L7" s="35"/>
+      <c r="L7" s="42"/>
     </row>
     <row r="8">
-      <c r="A8" s="42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="43">
+      <c r="A8" s="50" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="51">
         <f>_xlfn.STDEV.S(B2:B6)</f>
         <v>0.27715934045238261</v>
       </c>
-      <c r="C8" s="43">
+      <c r="C8" s="51">
         <f>_xlfn.STDEV.S(C2:C6)</f>
         <v>6.7187796510973619e-002</v>
       </c>
-      <c r="D8" s="43">
+      <c r="D8" s="51">
         <f>_xlfn.STDEV.S(D2:D6)</f>
         <v>5.1524751333703808e-002</v>
       </c>
-      <c r="E8" s="43">
+      <c r="E8" s="51">
         <f>_xlfn.STDEV.S(E2:E6)</f>
         <v>2.2398660674245618e-002</v>
       </c>
-      <c r="F8" s="43">
+      <c r="F8" s="51">
         <f>_xlfn.STDEV.S(F2:F6)</f>
         <v>1.0295630140987376e-002</v>
       </c>
-      <c r="G8" s="44">
+      <c r="G8" s="52">
         <f>_xlfn.STDEV.S(G2:G6)</f>
         <v>4.1476499370125187e-002</v>
       </c>
+      <c r="H8" s="53" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="9" ht="14.65">
-      <c r="A9" s="45" t="s">
+      <c r="A9" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="46">
+      <c r="B9" s="55">
         <f>B8/SQRT(5)</f>
         <v>0.12394942517010696</v>
       </c>
-      <c r="C9" s="46">
+      <c r="C9" s="55">
         <f>C8/SQRT(5)</f>
         <v>3.0047296051392041e-002</v>
       </c>
-      <c r="D9" s="46">
+      <c r="D9" s="55">
         <f>D8/SQRT(5)</f>
         <v>2.3042569301186932e-002</v>
       </c>
-      <c r="E9" s="46">
+      <c r="E9" s="55">
         <f t="shared" ref="E9:G9" si="4">E8/SQRT(5)</f>
         <v>1.0016985574512895e-002</v>
       </c>
-      <c r="F9" s="46">
+      <c r="F9" s="55">
         <f t="shared" si="4"/>
         <v>4.6043457732887032e-003</v>
       </c>
-      <c r="G9" s="47">
+      <c r="G9" s="56">
         <f t="shared" si="4"/>
         <v>1.8548854412065423e-002</v>
+      </c>
+      <c r="H9" s="57">
+        <v>1.1299999999999999e-002</v>
       </c>
     </row>
   </sheetData>
@@ -1719,19 +1902,19 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.65">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="27" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1742,20 +1925,20 @@
       <c r="B2" s="5">
         <v>0.98999999999999999</v>
       </c>
-      <c r="C2" s="22">
+      <c r="C2" s="28">
         <f t="shared" ref="C2:C6" si="5">$E$2-B2</f>
         <v>9.000000000000008e-002</v>
       </c>
-      <c r="D2" s="23">
+      <c r="D2" s="29">
         <f t="shared" ref="D2:D6" si="6">0.01*SQRT(2)</f>
         <v>1.4142135623730952e-002</v>
       </c>
-      <c r="E2" s="48">
+      <c r="E2" s="58">
         <v>1.0800000000000001</v>
       </c>
     </row>
     <row r="3" ht="14.65">
-      <c r="A3" s="8">
+      <c r="A3" s="22">
         <v>0.10000000000000001</v>
       </c>
       <c r="B3" s="9">
@@ -1765,16 +1948,16 @@
         <f t="shared" si="5"/>
         <v>0.14000000000000012</v>
       </c>
-      <c r="D3" s="25">
+      <c r="D3" s="31">
         <f t="shared" si="6"/>
         <v>1.4142135623730952e-002</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="59" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" ht="14.65">
-      <c r="A4" s="8">
+      <c r="A4" s="22">
         <v>0.12</v>
       </c>
       <c r="B4" s="9">
@@ -1784,7 +1967,7 @@
         <f t="shared" si="5"/>
         <v>0.17000000000000004</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="31">
         <f t="shared" si="6"/>
         <v>1.4142135623730952e-002</v>
       </c>
@@ -1793,7 +1976,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8">
+      <c r="A5" s="22">
         <v>0.14999999999999999</v>
       </c>
       <c r="B5" s="9">
@@ -1803,23 +1986,23 @@
         <f t="shared" si="5"/>
         <v>0.21000000000000008</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="31">
         <f t="shared" si="6"/>
         <v>1.4142135623730952e-002</v>
       </c>
     </row>
     <row r="6" ht="14.65">
-      <c r="A6" s="14">
+      <c r="A6" s="23">
         <v>0.20000000000000001</v>
       </c>
       <c r="B6" s="15">
         <v>0.80000000000000004</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="32">
         <f t="shared" si="5"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="33">
         <f t="shared" si="6"/>
         <v>1.4142135623730952e-002</v>
       </c>
@@ -1833,7 +2016,7 @@
       <c r="D8" s="13"/>
       <c r="E8" s="13"/>
       <c r="F8" s="13"/>
-      <c r="G8" s="49"/>
+      <c r="G8" s="60"/>
     </row>
     <row r="9">
       <c r="D9" s="13"/>
@@ -1865,19 +2048,19 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.65">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="27" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1888,20 +2071,20 @@
       <c r="B2" s="5">
         <v>1.25</v>
       </c>
-      <c r="C2" s="22">
+      <c r="C2" s="28">
         <f t="shared" ref="C2:C7" si="7">$E$2-B2</f>
         <v>2.0000000000000018e-002</v>
       </c>
-      <c r="D2" s="23">
+      <c r="D2" s="29">
         <f t="shared" ref="D2:D7" si="8">0.01*SQRT(2)</f>
         <v>1.4142135623730952e-002</v>
       </c>
-      <c r="E2" s="50">
+      <c r="E2" s="61">
         <v>1.27</v>
       </c>
     </row>
     <row r="3" ht="14.65">
-      <c r="A3" s="8">
+      <c r="A3" s="22">
         <v>0.20000000000000001</v>
       </c>
       <c r="B3" s="9">
@@ -1911,16 +2094,16 @@
         <f t="shared" si="7"/>
         <v>4.0000000000000036e-002</v>
       </c>
-      <c r="D3" s="25">
+      <c r="D3" s="31">
         <f t="shared" si="8"/>
         <v>1.4142135623730952e-002</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="27" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" ht="14.65">
-      <c r="A4" s="8">
+      <c r="A4" s="22">
         <v>0.5</v>
       </c>
       <c r="B4" s="9">
@@ -1930,16 +2113,16 @@
         <f t="shared" si="7"/>
         <v>9.000000000000008e-002</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="31">
         <f t="shared" si="8"/>
         <v>1.4142135623730952e-002</v>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="30">
         <v>1.e-002</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8">
+      <c r="A5" s="22">
         <v>0.69999999999999996</v>
       </c>
       <c r="B5" s="9">
@@ -1949,13 +2132,13 @@
         <f t="shared" si="7"/>
         <v>0.12000000000000011</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="31">
         <f t="shared" si="8"/>
         <v>1.4142135623730952e-002</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8">
+      <c r="A6" s="22">
         <v>0.90000000000000002</v>
       </c>
       <c r="B6" s="9">
@@ -1965,23 +2148,23 @@
         <f t="shared" si="7"/>
         <v>0.14999999999999991</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="31">
         <f t="shared" si="8"/>
         <v>1.4142135623730952e-002</v>
       </c>
     </row>
     <row r="7" ht="14.65">
-      <c r="A7" s="14">
+      <c r="A7" s="23">
         <v>1</v>
       </c>
       <c r="B7" s="15">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="32">
         <f t="shared" si="7"/>
         <v>0.16999999999999993</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="33">
         <f t="shared" si="8"/>
         <v>1.4142135623730952e-002</v>
       </c>
@@ -2009,18 +2192,18 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.5">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="52" t="s">
+      <c r="C1" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="49"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
       <c r="G1" s="9"/>
     </row>
     <row r="2">
@@ -2033,9 +2216,9 @@
       <c r="C2">
         <v>0</v>
       </c>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
     </row>
     <row r="3">
       <c r="A3" s="9">
@@ -2047,9 +2230,9 @@
       <c r="C3">
         <v>1.e-002</v>
       </c>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
     </row>
     <row r="4">
       <c r="A4" s="9">
@@ -2061,9 +2244,9 @@
       <c r="C4">
         <v>2.e-002</v>
       </c>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
     </row>
     <row r="5">
       <c r="A5" s="9">
@@ -2075,9 +2258,9 @@
       <c r="C5">
         <v>2.9999999999999999e-002</v>
       </c>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
     </row>
     <row r="6">
       <c r="A6" s="9">
@@ -2089,9 +2272,9 @@
       <c r="C6">
         <v>4.0000000000000001e-002</v>
       </c>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
     </row>
     <row r="7">
       <c r="A7" s="9">
@@ -2103,9 +2286,9 @@
       <c r="C7">
         <v>5.0000000000000003e-002</v>
       </c>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="65"/>
+      <c r="F7" s="65"/>
     </row>
     <row r="8">
       <c r="A8" s="9">
@@ -2117,9 +2300,9 @@
       <c r="C8">
         <v>5.9999999999999998e-002</v>
       </c>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="65"/>
     </row>
     <row r="9">
       <c r="A9" s="9">
@@ -2131,9 +2314,9 @@
       <c r="C9">
         <v>5.9999999999999998e-002</v>
       </c>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
+      <c r="D9" s="65"/>
+      <c r="E9" s="65"/>
+      <c r="F9" s="65"/>
     </row>
     <row r="10">
       <c r="A10" s="9">
@@ -2145,9 +2328,9 @@
       <c r="C10">
         <v>7.0000000000000007e-002</v>
       </c>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
+      <c r="D10" s="65"/>
+      <c r="E10" s="65"/>
+      <c r="F10" s="65"/>
     </row>
     <row r="11">
       <c r="A11" s="9">
@@ -2159,9 +2342,9 @@
       <c r="C11">
         <v>7.0000000000000007e-002</v>
       </c>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
+      <c r="D11" s="65"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="65"/>
     </row>
     <row r="12">
       <c r="A12" s="9">
@@ -2173,9 +2356,9 @@
       <c r="C12">
         <v>5.9999999999999998e-002</v>
       </c>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="65"/>
+      <c r="F12" s="65"/>
     </row>
     <row r="13">
       <c r="A13" s="9">
@@ -2187,9 +2370,9 @@
       <c r="C13">
         <v>5.9999999999999998e-002</v>
       </c>
-      <c r="D13" s="54"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="54"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="65"/>
+      <c r="F13" s="65"/>
     </row>
     <row r="14">
       <c r="A14" s="9">
@@ -2201,9 +2384,9 @@
       <c r="C14">
         <v>5.9999999999999998e-002</v>
       </c>
-      <c r="D14" s="54"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="54"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="65"/>
     </row>
     <row r="15">
       <c r="A15" s="9">
@@ -2215,9 +2398,9 @@
       <c r="C15">
         <v>5.0000000000000003e-002</v>
       </c>
-      <c r="D15" s="54"/>
-      <c r="E15" s="54"/>
-      <c r="F15" s="54"/>
+      <c r="D15" s="65"/>
+      <c r="E15" s="65"/>
+      <c r="F15" s="65"/>
     </row>
     <row r="16">
       <c r="A16" s="9">
@@ -2229,9 +2412,9 @@
       <c r="C16">
         <v>5.0000000000000003e-002</v>
       </c>
-      <c r="D16" s="54"/>
-      <c r="E16" s="54"/>
-      <c r="F16" s="54"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="65"/>
+      <c r="F16" s="65"/>
     </row>
     <row r="17">
       <c r="A17" s="9">
@@ -2243,9 +2426,9 @@
       <c r="C17">
         <v>4.0000000000000001e-002</v>
       </c>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
+      <c r="D17" s="65"/>
+      <c r="E17" s="65"/>
+      <c r="F17" s="65"/>
     </row>
     <row r="18">
       <c r="A18" s="9">
@@ -2257,9 +2440,9 @@
       <c r="C18">
         <v>2.9999999999999999e-002</v>
       </c>
-      <c r="D18" s="54"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="65"/>
+      <c r="F18" s="65"/>
     </row>
     <row r="19">
       <c r="A19" s="9">
@@ -2271,9 +2454,9 @@
       <c r="C19">
         <v>2.e-002</v>
       </c>
-      <c r="D19" s="54"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="65"/>
     </row>
     <row r="20">
       <c r="A20" s="9">
@@ -2285,9 +2468,9 @@
       <c r="C20">
         <v>1.e-002</v>
       </c>
-      <c r="D20" s="54"/>
-      <c r="E20" s="54"/>
-      <c r="F20" s="54"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="65"/>
     </row>
     <row r="21">
       <c r="A21" s="9">
@@ -2299,9 +2482,9 @@
       <c r="C21">
         <v>-1.e-002</v>
       </c>
-      <c r="D21" s="54"/>
-      <c r="E21" s="54"/>
-      <c r="F21" s="54"/>
+      <c r="D21" s="65"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="65"/>
     </row>
     <row r="22">
       <c r="A22" s="9">
@@ -2313,9 +2496,9 @@
       <c r="C22">
         <v>-2.e-002</v>
       </c>
-      <c r="D22" s="54"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="54"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="65"/>
+      <c r="F22" s="65"/>
     </row>
     <row r="23">
       <c r="A23" s="9">
@@ -2327,9 +2510,9 @@
       <c r="C23">
         <v>-2.e-002</v>
       </c>
-      <c r="D23" s="54"/>
-      <c r="E23" s="54"/>
-      <c r="F23" s="54"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="65"/>
     </row>
     <row r="24">
       <c r="A24" s="9">
@@ -2341,9 +2524,9 @@
       <c r="C24">
         <v>-2.9999999999999999e-002</v>
       </c>
-      <c r="D24" s="54"/>
-      <c r="E24" s="54"/>
-      <c r="F24" s="54"/>
+      <c r="D24" s="65"/>
+      <c r="E24" s="65"/>
+      <c r="F24" s="65"/>
     </row>
     <row r="25">
       <c r="A25" s="9">
@@ -2355,9 +2538,9 @@
       <c r="C25">
         <v>-4.0000000000000001e-002</v>
       </c>
-      <c r="D25" s="54"/>
-      <c r="E25" s="54"/>
-      <c r="F25" s="54"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="65"/>
+      <c r="F25" s="65"/>
     </row>
     <row r="26">
       <c r="A26" s="9">
@@ -2399,7 +2582,7 @@
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
-      <c r="F28" s="55"/>
+      <c r="F28" s="66"/>
     </row>
     <row r="29">
       <c r="A29" s="9">
@@ -3455,11 +3638,11 @@
       <c r="A169" s="9"/>
       <c r="B169" s="9"/>
       <c r="D169" s="9"/>
-      <c r="E169" s="55"/>
+      <c r="E169" s="66"/>
       <c r="F169" s="9"/>
     </row>
     <row r="170">
-      <c r="A170" s="55"/>
+      <c r="A170" s="66"/>
       <c r="B170" s="9"/>
       <c r="D170" s="9"/>
       <c r="E170" s="9"/>
@@ -3588,11 +3771,11 @@
       <c r="A188" s="9"/>
       <c r="B188" s="9"/>
       <c r="D188" s="9"/>
-      <c r="E188" s="55"/>
+      <c r="E188" s="66"/>
       <c r="F188" s="9"/>
     </row>
     <row r="189">
-      <c r="A189" s="55"/>
+      <c r="A189" s="66"/>
       <c r="B189" s="9"/>
       <c r="D189" s="9"/>
       <c r="E189" s="9"/>
@@ -3778,7 +3961,7 @@
       <c r="B215" s="9"/>
       <c r="D215" s="9"/>
       <c r="E215" s="9"/>
-      <c r="F215" s="55"/>
+      <c r="F215" s="66"/>
     </row>
     <row r="216">
       <c r="A216" s="9"/>
@@ -3980,11 +4163,11 @@
       <c r="A244" s="9"/>
       <c r="B244" s="9"/>
       <c r="D244" s="9"/>
-      <c r="E244" s="55"/>
+      <c r="E244" s="66"/>
       <c r="F244" s="9"/>
     </row>
     <row r="245">
-      <c r="A245" s="55"/>
+      <c r="A245" s="66"/>
       <c r="B245" s="9"/>
       <c r="D245" s="9"/>
       <c r="E245" s="9"/>
@@ -4372,11 +4555,11 @@
       <c r="A300" s="9"/>
       <c r="B300" s="9"/>
       <c r="D300" s="9"/>
-      <c r="E300" s="55"/>
+      <c r="E300" s="66"/>
       <c r="F300" s="9"/>
     </row>
     <row r="301">
-      <c r="A301" s="55"/>
+      <c r="A301" s="66"/>
       <c r="B301" s="9"/>
       <c r="D301" s="9"/>
       <c r="E301" s="9"/>
@@ -4429,7 +4612,7 @@
       <c r="B308" s="9"/>
       <c r="D308" s="9"/>
       <c r="E308" s="9"/>
-      <c r="F308" s="55"/>
+      <c r="F308" s="66"/>
     </row>
     <row r="309">
       <c r="A309" s="9"/>
@@ -4505,11 +4688,11 @@
       <c r="A319" s="9"/>
       <c r="B319" s="9"/>
       <c r="D319" s="9"/>
-      <c r="E319" s="55"/>
+      <c r="E319" s="66"/>
       <c r="F319" s="9"/>
     </row>
     <row r="320">
-      <c r="A320" s="55"/>
+      <c r="A320" s="66"/>
       <c r="B320" s="9"/>
       <c r="D320" s="9"/>
       <c r="E320" s="9"/>
@@ -4638,11 +4821,11 @@
       <c r="A338" s="9"/>
       <c r="B338" s="9"/>
       <c r="D338" s="9"/>
-      <c r="E338" s="55"/>
+      <c r="E338" s="66"/>
       <c r="F338" s="9"/>
     </row>
     <row r="339">
-      <c r="A339" s="55"/>
+      <c r="A339" s="66"/>
       <c r="B339" s="9"/>
       <c r="D339" s="9"/>
       <c r="E339" s="9"/>
@@ -5063,33 +5246,33 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="29">
+      <c r="B1" s="68">
         <v>5.0000000000000003e-002</v>
       </c>
-      <c r="C1" s="29">
+      <c r="C1" s="68">
         <v>0.14999999999999999</v>
       </c>
-      <c r="D1" s="29">
+      <c r="D1" s="68">
         <v>0.25</v>
       </c>
-      <c r="E1" s="29">
+      <c r="E1" s="68">
         <v>0.34999999999999998</v>
       </c>
-      <c r="F1" s="29">
+      <c r="F1" s="68">
         <v>0.45000000000000001</v>
       </c>
-      <c r="G1" s="30">
+      <c r="G1" s="69">
         <v>0.55000000000000004</v>
       </c>
-      <c r="H1" s="28" t="s">
+      <c r="H1" s="67" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="32">
+      <c r="A2" s="70">
         <v>1</v>
       </c>
       <c r="B2">
@@ -5107,16 +5290,16 @@
       <c r="F2">
         <v>8.3829999999999991</v>
       </c>
-      <c r="G2" s="33">
+      <c r="G2" s="71">
         <v>7.6909999999999998</v>
       </c>
-      <c r="H2" s="32">
+      <c r="H2" s="70">
         <f>$B1+$I$2/3</f>
         <v>5.0000000000000003e-002</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="36">
+      <c r="A3" s="72">
         <v>2</v>
       </c>
       <c r="B3">
@@ -5134,16 +5317,16 @@
       <c r="F3">
         <v>8.4060000000000006</v>
       </c>
-      <c r="G3" s="33">
+      <c r="G3" s="71">
         <v>7.5910000000000002</v>
       </c>
-      <c r="H3" s="32">
+      <c r="H3" s="70">
         <f>$C1+$I$2/3</f>
         <v>0.14999999999999999</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="36">
+      <c r="A4" s="72">
         <v>3</v>
       </c>
       <c r="B4">
@@ -5161,16 +5344,16 @@
       <c r="F4">
         <v>8.3879999999999999</v>
       </c>
-      <c r="G4" s="33">
+      <c r="G4" s="71">
         <v>7.6589999999999998</v>
       </c>
-      <c r="H4" s="32">
+      <c r="H4" s="70">
         <f>$D1+$I$2/3</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="36">
+      <c r="A5" s="72">
         <v>4</v>
       </c>
       <c r="B5">
@@ -5188,16 +5371,16 @@
       <c r="F5">
         <v>8.3859999999999992</v>
       </c>
-      <c r="G5" s="33">
+      <c r="G5" s="71">
         <v>7.5999999999999996</v>
       </c>
-      <c r="H5" s="32">
+      <c r="H5" s="70">
         <f>$E1+$I$2/3</f>
         <v>0.34999999999999998</v>
       </c>
     </row>
     <row r="6" ht="14.65">
-      <c r="A6" s="36">
+      <c r="A6" s="72">
         <v>5</v>
       </c>
       <c r="B6">
@@ -5215,50 +5398,50 @@
       <c r="F6">
         <v>8.4019999999999992</v>
       </c>
-      <c r="G6" s="33">
+      <c r="G6" s="71">
         <v>7.6319999999999997</v>
       </c>
-      <c r="H6" s="32">
+      <c r="H6" s="70">
         <f>$F1+$I$2/3</f>
         <v>0.45000000000000001</v>
       </c>
     </row>
     <row r="7" ht="14.65">
-      <c r="A7" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="56">
+      <c r="A7" s="73" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="74">
         <f>AVERAGE(B2:B6)</f>
         <v>24.260399999999997</v>
       </c>
-      <c r="C7" s="56">
+      <c r="C7" s="74">
         <f>AVERAGE(C2:C6)</f>
         <v>14.568199999999999</v>
       </c>
-      <c r="D7" s="56">
+      <c r="D7" s="74">
         <f>AVERAGE(D2:D6)</f>
         <v>11.264399999999998</v>
       </c>
-      <c r="E7" s="56">
+      <c r="E7" s="74">
         <f t="shared" ref="E7:G7" si="9">AVERAGE(E2:E6)</f>
         <v>9.6117999999999988</v>
       </c>
-      <c r="F7" s="56">
+      <c r="F7" s="74">
         <f t="shared" si="9"/>
         <v>8.3930000000000007</v>
       </c>
-      <c r="G7" s="57">
+      <c r="G7" s="75">
         <f t="shared" si="9"/>
         <v>7.6345999999999989</v>
       </c>
-      <c r="H7" s="58">
+      <c r="H7" s="76">
         <f>$G1+$I$2/3</f>
         <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="42" t="s">
-        <v>15</v>
+      <c r="A8" s="77" t="s">
+        <v>22</v>
       </c>
       <c r="B8">
         <f>_xlfn.STDEV.S(B2:B6)</f>
@@ -5280,36 +5463,36 @@
         <f>_xlfn.STDEV.S(F2:F6)</f>
         <v>1.0295630140987376e-002</v>
       </c>
-      <c r="G8" s="33">
+      <c r="G8" s="71">
         <f>_xlfn.STDEV.S(G2:G6)</f>
         <v>4.1476499370125187e-002</v>
       </c>
     </row>
     <row r="9" ht="14.65">
-      <c r="A9" s="45" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="59">
+      <c r="A9" s="78" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="79">
         <f>B8/SQRT(5)</f>
         <v>0.12394942517010696</v>
       </c>
-      <c r="C9" s="59">
+      <c r="C9" s="79">
         <f>C8/SQRT(5)</f>
         <v>3.0047296051392041e-002</v>
       </c>
-      <c r="D9" s="59">
+      <c r="D9" s="79">
         <f>D8/SQRT(5)</f>
         <v>2.3042569301186932e-002</v>
       </c>
-      <c r="E9" s="59">
+      <c r="E9" s="79">
         <f t="shared" ref="E9:G9" si="10">E8/SQRT(5)</f>
         <v>1.0016985574512895e-002</v>
       </c>
-      <c r="F9" s="59">
+      <c r="F9" s="79">
         <f t="shared" si="10"/>
         <v>4.6043457732887032e-003</v>
       </c>
-      <c r="G9" s="41">
+      <c r="G9" s="80">
         <f t="shared" si="10"/>
         <v>1.8548854412065423e-002</v>
       </c>

--- a/Legge di Hooke.xlsx
+++ b/Legge di Hooke.xlsx
@@ -3,17 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Misure statiche 1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Misure statiche (molla uguale)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Misure statiche (molla diversa)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Misure dinamiche" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Misure dinamiche" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Misure statiche (molla uguale)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Misure statiche (molla diversa)" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Molle in serie (statica)" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Molle in parallelo (statica)" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Energia " sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Misure dinamiche 2" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Molle in serie (statica)'!$A$1:$G$6</definedName>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>m[kg]</t>
   </si>
@@ -44,21 +43,6 @@
   </si>
   <si>
     <t xml:space="preserve">σx0 [m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">posizione [m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">allungamento [m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">incertezza su all. [m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d [m] senza pesi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">incertezza su d [m]</t>
   </si>
   <si>
     <t xml:space="preserve">Masse (kg)</t>
@@ -79,6 +63,21 @@
     <t>σω_</t>
   </si>
   <si>
+    <t xml:space="preserve">posizione [m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">allungamento [m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">incertezza su all. [m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d [m] senza pesi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">incertezza su d [m]</t>
+  </si>
+  <si>
     <t xml:space="preserve">t1 (s) Set</t>
   </si>
   <si>
@@ -86,18 +85,6 @@
   </si>
   <si>
     <t xml:space="preserve">v (m/s) Set</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Masse (Kg)</t>
-  </si>
-  <si>
-    <t>Media</t>
-  </si>
-  <si>
-    <t>Dev.std</t>
-  </si>
-  <si>
-    <t>Dev.std.med</t>
   </si>
 </sst>
 </file>
@@ -121,15 +108,15 @@
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10.000000"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
       <b/>
       <sz val="10.000000"/>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10.000000"/>
-      <color theme="1"/>
-      <name val="Arial Unicode MS"/>
     </font>
     <font>
       <u/>
@@ -145,7 +132,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -161,12 +148,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
-        <bgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
     <fill>
@@ -174,13 +161,8 @@
         <fgColor indexed="5"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="26">
+  <borders count="27">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -289,32 +271,6 @@
         <color auto="1"/>
       </right>
       <top style="none"/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
@@ -464,6 +420,51 @@
     </border>
     <border>
       <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
         <color auto="1"/>
       </left>
       <right style="medium">
@@ -477,7 +478,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="70">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="1" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -519,14 +520,50 @@
     <xf fontId="1" fillId="0" borderId="10" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf fontId="0" fillId="2" borderId="11" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="12" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="13" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="11" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="14" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="15" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="16" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="16" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="15" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="17" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="14" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="2" numFmtId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="18" numFmtId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="19" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="16" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf fontId="0" fillId="3" borderId="15" numFmtId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="20" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="17" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="21" numFmtId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="22" numFmtId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="17" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="1" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="1" fillId="2" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="1" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="1" fillId="0" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="2" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="1" fillId="0" borderId="2" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="23" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="2" borderId="20" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="1" fillId="0" borderId="24" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="8" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -535,17 +572,17 @@
     <xf fontId="1" fillId="0" borderId="9" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="2" fillId="3" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="2" fillId="3" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="1" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="4" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="12" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="0" borderId="25" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="7" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -556,42 +593,15 @@
     <xf fontId="1" fillId="0" borderId="10" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="2" borderId="13" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="14" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="15" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="13" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="16" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="17" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="18" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="18" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="17" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="19" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="2" borderId="16" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="2" numFmtId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="20" numFmtId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="21" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf fontId="0" fillId="4" borderId="17" numFmtId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="22" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="19" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="23" numFmtId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="24" numFmtId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="19" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="3" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="3" fillId="4" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="3" fillId="4" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="1" fillId="0" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="3" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="3" fillId="4" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="1" fillId="0" borderId="25" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="0" borderId="26" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf fontId="1" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -607,22 +617,6 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="5" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="5" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="6" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="4" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="6" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="6" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1142,11 +1136,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="5.796875"/>
-    <col customWidth="1" min="2" max="2" width="11.75390625"/>
-    <col customWidth="1" min="3" max="3" width="11.375"/>
-    <col customWidth="1" min="4" max="4" width="10.625"/>
-    <col customWidth="1" min="5" max="5" width="9.625"/>
+    <col customWidth="1" min="1" max="5" width="8.125"/>
     <col bestFit="1" customWidth="1" min="6" max="6" width="14"/>
   </cols>
   <sheetData>
@@ -1332,280 +1322,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <cols>
-    <col customWidth="1" min="1" max="2" width="8.125"/>
-    <col customWidth="1" min="3" max="3" width="8.25390625"/>
-    <col customWidth="1" min="4" max="5" width="8.125"/>
-    <col bestFit="1" customWidth="1" min="6" max="6" width="14"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="13">
-      <c r="A1" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="20" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" ht="14.65">
-      <c r="A2" s="4">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="B2" s="5">
-        <v>1.23</v>
-      </c>
-      <c r="C2" s="5">
-        <f t="shared" ref="C2:C6" si="0">$E$2-B2</f>
-        <v>3.0000000000000027e-002</v>
-      </c>
-      <c r="D2" s="6">
-        <v>1.4142135619999999e-002</v>
-      </c>
-      <c r="E2" s="21">
-        <v>1.26</v>
-      </c>
-    </row>
-    <row r="3" ht="14.65">
-      <c r="A3" s="22">
-        <v>0.20000000000000001</v>
-      </c>
-      <c r="B3" s="9">
-        <v>1.1899999999999999</v>
-      </c>
-      <c r="C3" s="9">
-        <f t="shared" si="0"/>
-        <v>7.0000000000000062e-002</v>
-      </c>
-      <c r="D3" s="10">
-        <v>1.4142135619999999e-002</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" ht="14.65">
-      <c r="A4" s="22">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="B4" s="9">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="C4" s="9">
-        <f t="shared" si="0"/>
-        <v>0.10000000000000009</v>
-      </c>
-      <c r="D4" s="10">
-        <v>1.4142135619999999e-002</v>
-      </c>
-      <c r="E4" s="7">
-        <v>1.e-002</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="22">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="B5" s="9">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="C5" s="9">
-        <f t="shared" si="0"/>
-        <v>0.13000000000000012</v>
-      </c>
-      <c r="D5" s="10">
-        <v>1.4142135619999999e-002</v>
-      </c>
-    </row>
-    <row r="6" ht="14.65">
-      <c r="A6" s="23">
-        <v>0.5</v>
-      </c>
-      <c r="B6" s="24">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="C6" s="15">
-        <f t="shared" si="0"/>
-        <v>0.15999999999999992</v>
-      </c>
-      <c r="D6" s="16">
-        <v>1.4142135619999999e-002</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="13"/>
-      <c r="B8" s="13"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="13"/>
-      <c r="B10" s="13"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
-    </row>
-  </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <cols>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="12.796875"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="16.33203125"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="19"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="17.53125"/>
-    <col bestFit="1" customWidth="1" min="6" max="6" width="14"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="14.65">
-      <c r="A1" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="27" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" ht="14.65">
-      <c r="A2" s="4">
-        <v>5.0000000000000003e-002</v>
-      </c>
-      <c r="B2" s="5">
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="C2" s="28">
-        <f t="shared" ref="C2:C6" si="1">$E$2-B2</f>
-        <v>5.9999999999999831e-002</v>
-      </c>
-      <c r="D2" s="29">
-        <f t="shared" ref="D2:D6" si="2">0.01*SQRT(2)</f>
-        <v>1.4142135623730952e-002</v>
-      </c>
-      <c r="E2" s="30">
-        <v>1.1699999999999999</v>
-      </c>
-    </row>
-    <row r="3" ht="14.65">
-      <c r="A3" s="22">
-        <v>7.0000000000000007e-002</v>
-      </c>
-      <c r="B3" s="9">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="C3" s="13">
-        <f t="shared" si="1"/>
-        <v>7.9999999999999849e-002</v>
-      </c>
-      <c r="D3" s="31">
-        <f t="shared" si="2"/>
-        <v>1.4142135623730952e-002</v>
-      </c>
-      <c r="E3" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="13"/>
-    </row>
-    <row r="4" ht="14.65">
-      <c r="A4" s="22">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="B4" s="9">
-        <v>1.0600000000000001</v>
-      </c>
-      <c r="C4" s="13">
-        <f t="shared" si="1"/>
-        <v>0.10999999999999988</v>
-      </c>
-      <c r="D4" s="31">
-        <f t="shared" si="2"/>
-        <v>1.4142135623730952e-002</v>
-      </c>
-      <c r="E4" s="30">
-        <v>1.e-002</v>
-      </c>
-      <c r="F4" s="13"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="22">
-        <v>0.14999999999999999</v>
-      </c>
-      <c r="B5" s="9">
-        <v>1.01</v>
-      </c>
-      <c r="C5" s="13">
-        <f t="shared" si="1"/>
-        <v>0.15999999999999992</v>
-      </c>
-      <c r="D5" s="31">
-        <f t="shared" si="2"/>
-        <v>1.4142135623730952e-002</v>
-      </c>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-    </row>
-    <row r="6" ht="14.65">
-      <c r="A6" s="23">
-        <v>0.20000000000000001</v>
-      </c>
-      <c r="B6" s="15">
-        <v>0.94999999999999996</v>
-      </c>
-      <c r="C6" s="32">
-        <f t="shared" si="1"/>
-        <v>0.21999999999999997</v>
-      </c>
-      <c r="D6" s="33">
-        <f t="shared" si="2"/>
-        <v>1.4142135623730952e-002</v>
-      </c>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-    </row>
-    <row r="7">
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-    </row>
-  </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -1619,39 +1335,39 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="35">
+      <c r="A1" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="18">
         <v>5.0000000000000003e-002</v>
       </c>
-      <c r="C1" s="35">
+      <c r="C1" s="18">
         <v>0.14999999999999999</v>
       </c>
-      <c r="D1" s="35">
+      <c r="D1" s="18">
         <v>0.25</v>
       </c>
-      <c r="E1" s="35">
+      <c r="E1" s="18">
         <v>0.34999999999999998</v>
       </c>
-      <c r="F1" s="35">
+      <c r="F1" s="18">
         <v>0.45000000000000001</v>
       </c>
-      <c r="G1" s="36">
+      <c r="G1" s="19">
         <v>0.55000000000000004</v>
       </c>
-      <c r="H1" s="37" t="s">
-        <v>12</v>
+      <c r="H1" s="20" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="38">
+      <c r="A2" s="21">
         <v>1</v>
       </c>
       <c r="B2">
         <v>23.844000000000001</v>
       </c>
-      <c r="C2" s="39">
+      <c r="C2" s="22">
         <v>14.49</v>
       </c>
       <c r="D2">
@@ -1663,17 +1379,17 @@
       <c r="F2">
         <v>8.3829999999999991</v>
       </c>
-      <c r="G2" s="40">
+      <c r="G2" s="23">
         <v>7.6909999999999998</v>
       </c>
-      <c r="H2" s="41">
+      <c r="H2" s="24">
         <f>$B1+$H$9/3</f>
         <v>5.3766666666666671e-002</v>
       </c>
-      <c r="L2" s="42"/>
+      <c r="L2" s="25"/>
     </row>
     <row r="3">
-      <c r="A3" s="43">
+      <c r="A3" s="26">
         <v>2</v>
       </c>
       <c r="B3">
@@ -1691,20 +1407,20 @@
       <c r="F3">
         <v>8.4060000000000006</v>
       </c>
-      <c r="G3" s="40">
+      <c r="G3" s="23">
         <v>7.5910000000000002</v>
       </c>
-      <c r="H3" s="41">
+      <c r="H3" s="24">
         <f>$C1+$H$9/3</f>
         <v>0.15376666666666666</v>
       </c>
-      <c r="L3" s="42"/>
+      <c r="L3" s="25"/>
     </row>
     <row r="4">
-      <c r="A4" s="43">
+      <c r="A4" s="26">
         <v>3</v>
       </c>
-      <c r="B4" s="39">
+      <c r="B4" s="22">
         <v>24.129999999999999</v>
       </c>
       <c r="C4">
@@ -1719,20 +1435,20 @@
       <c r="F4">
         <v>8.3879999999999999</v>
       </c>
-      <c r="G4" s="40">
+      <c r="G4" s="23">
         <v>7.6589999999999998</v>
       </c>
-      <c r="H4" s="41">
+      <c r="H4" s="24">
         <f>$D1+$H$9/3</f>
         <v>0.25376666666666664</v>
       </c>
-      <c r="L4" s="42"/>
+      <c r="L4" s="25"/>
     </row>
     <row r="5">
-      <c r="A5" s="43">
+      <c r="A5" s="26">
         <v>4</v>
       </c>
-      <c r="B5" s="39">
+      <c r="B5" s="22">
         <v>24.359999999999999</v>
       </c>
       <c r="C5">
@@ -1741,23 +1457,23 @@
       <c r="D5">
         <v>11.298999999999999</v>
       </c>
-      <c r="E5" s="39">
+      <c r="E5" s="22">
         <v>9.6300000000000008</v>
       </c>
       <c r="F5">
         <v>8.3859999999999992</v>
       </c>
-      <c r="G5" s="44">
+      <c r="G5" s="27">
         <v>7.5999999999999996</v>
       </c>
-      <c r="H5" s="41">
+      <c r="H5" s="24">
         <f>$E1+$H$9/3</f>
         <v>0.35376666666666662</v>
       </c>
-      <c r="L5" s="42"/>
+      <c r="L5" s="25"/>
     </row>
     <row r="6" ht="14.65">
-      <c r="A6" s="45">
+      <c r="A6" s="28">
         <v>5</v>
       </c>
       <c r="B6">
@@ -1766,7 +1482,7 @@
       <c r="C6">
         <v>14.542</v>
       </c>
-      <c r="D6" s="39">
+      <c r="D6" s="22">
         <v>11.26</v>
       </c>
       <c r="E6">
@@ -1775,110 +1491,110 @@
       <c r="F6">
         <v>8.4019999999999992</v>
       </c>
-      <c r="G6" s="40">
+      <c r="G6" s="23">
         <v>7.6319999999999997</v>
       </c>
-      <c r="H6" s="41">
+      <c r="H6" s="24">
         <f>$F1+$H$9/3</f>
         <v>0.45376666666666665</v>
       </c>
-      <c r="L6" s="42"/>
+      <c r="L6" s="25"/>
     </row>
     <row r="7" ht="14.65">
-      <c r="A7" s="46" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="47">
+      <c r="A7" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="30">
         <f>AVERAGE(B2:B6)</f>
         <v>24.260399999999997</v>
       </c>
-      <c r="C7" s="47">
+      <c r="C7" s="30">
         <f>AVERAGE(C2:C6)</f>
         <v>14.568199999999999</v>
       </c>
-      <c r="D7" s="47">
+      <c r="D7" s="30">
         <f>AVERAGE(D2:D6)</f>
         <v>11.264399999999998</v>
       </c>
-      <c r="E7" s="47">
-        <f t="shared" ref="E7:G7" si="3">AVERAGE(E2:E6)</f>
+      <c r="E7" s="30">
+        <f t="shared" ref="E7:G7" si="0">AVERAGE(E2:E6)</f>
         <v>9.6117999999999988</v>
       </c>
-      <c r="F7" s="47">
-        <f t="shared" si="3"/>
+      <c r="F7" s="30">
+        <f t="shared" si="0"/>
         <v>8.3930000000000007</v>
       </c>
-      <c r="G7" s="48">
-        <f t="shared" si="3"/>
+      <c r="G7" s="31">
+        <f t="shared" si="0"/>
         <v>7.6345999999999989</v>
       </c>
-      <c r="H7" s="49">
+      <c r="H7" s="32">
         <f>$G1+$H$9/3</f>
         <v>0.55376666666666674</v>
       </c>
-      <c r="L7" s="42"/>
+      <c r="L7" s="25"/>
     </row>
     <row r="8">
-      <c r="A8" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="51">
+      <c r="A8" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="34">
         <f>_xlfn.STDEV.S(B2:B6)</f>
         <v>0.27715934045238261</v>
       </c>
-      <c r="C8" s="51">
+      <c r="C8" s="34">
         <f>_xlfn.STDEV.S(C2:C6)</f>
         <v>6.7187796510973619e-002</v>
       </c>
-      <c r="D8" s="51">
+      <c r="D8" s="34">
         <f>_xlfn.STDEV.S(D2:D6)</f>
         <v>5.1524751333703808e-002</v>
       </c>
-      <c r="E8" s="51">
+      <c r="E8" s="34">
         <f>_xlfn.STDEV.S(E2:E6)</f>
         <v>2.2398660674245618e-002</v>
       </c>
-      <c r="F8" s="51">
+      <c r="F8" s="34">
         <f>_xlfn.STDEV.S(F2:F6)</f>
         <v>1.0295630140987376e-002</v>
       </c>
-      <c r="G8" s="52">
+      <c r="G8" s="35">
         <f>_xlfn.STDEV.S(G2:G6)</f>
         <v>4.1476499370125187e-002</v>
       </c>
-      <c r="H8" s="53" t="s">
-        <v>15</v>
+      <c r="H8" s="36" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="9" ht="14.65">
-      <c r="A9" s="54" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="55">
+      <c r="A9" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="38">
         <f>B8/SQRT(5)</f>
         <v>0.12394942517010696</v>
       </c>
-      <c r="C9" s="55">
+      <c r="C9" s="38">
         <f>C8/SQRT(5)</f>
         <v>3.0047296051392041e-002</v>
       </c>
-      <c r="D9" s="55">
+      <c r="D9" s="38">
         <f>D8/SQRT(5)</f>
         <v>2.3042569301186932e-002</v>
       </c>
-      <c r="E9" s="55">
-        <f t="shared" ref="E9:G9" si="4">E8/SQRT(5)</f>
+      <c r="E9" s="38">
+        <f t="shared" ref="E9:G9" si="1">E8/SQRT(5)</f>
         <v>1.0016985574512895e-002</v>
       </c>
-      <c r="F9" s="55">
-        <f t="shared" si="4"/>
+      <c r="F9" s="38">
+        <f t="shared" si="1"/>
         <v>4.6043457732887032e-003</v>
       </c>
-      <c r="G9" s="56">
-        <f t="shared" si="4"/>
+      <c r="G9" s="39">
+        <f t="shared" si="1"/>
         <v>1.8548854412065423e-002</v>
       </c>
-      <c r="H9" s="57">
+      <c r="H9" s="40">
         <v>1.1299999999999999e-002</v>
       </c>
     </row>
@@ -1886,6 +1602,277 @@
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col customWidth="1" min="1" max="2" width="8.125"/>
+    <col customWidth="1" min="3" max="3" width="8.25390625"/>
+    <col customWidth="1" min="4" max="5" width="8.125"/>
+    <col bestFit="1" customWidth="1" min="6" max="6" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="13">
+      <c r="A1" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="43" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" ht="14.65">
+      <c r="A2" s="4">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="B2" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="C2" s="5">
+        <f t="shared" ref="C2:C6" si="2">$E$2-B2</f>
+        <v>3.0000000000000027e-002</v>
+      </c>
+      <c r="D2" s="44">
+        <v>1.4142135619999999e-002</v>
+      </c>
+      <c r="E2" s="45">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="3" ht="14.65">
+      <c r="A3" s="46">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="B3" s="9">
+        <v>1.1899999999999999</v>
+      </c>
+      <c r="C3" s="9">
+        <f t="shared" si="2"/>
+        <v>7.0000000000000062e-002</v>
+      </c>
+      <c r="D3" s="12">
+        <v>1.4142135619999999e-002</v>
+      </c>
+      <c r="E3" s="47" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" ht="14.65">
+      <c r="A4" s="46">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="B4" s="9">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="C4" s="9">
+        <f t="shared" si="2"/>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="D4" s="12">
+        <v>1.4142135619999999e-002</v>
+      </c>
+      <c r="E4" s="48">
+        <v>1.e-002</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="46">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="B5" s="9">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="C5" s="9">
+        <f t="shared" si="2"/>
+        <v>0.13000000000000012</v>
+      </c>
+      <c r="D5" s="10">
+        <v>1.4142135619999999e-002</v>
+      </c>
+    </row>
+    <row r="6" ht="14.65">
+      <c r="A6" s="49">
+        <v>0.5</v>
+      </c>
+      <c r="B6" s="50">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C6" s="15">
+        <f t="shared" si="2"/>
+        <v>0.15999999999999992</v>
+      </c>
+      <c r="D6" s="16">
+        <v>1.4142135619999999e-002</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="13"/>
+      <c r="B9" s="13"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col customWidth="1" min="1" max="5" width="8.125"/>
+    <col bestFit="1" customWidth="1" min="6" max="6" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="14.65">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" ht="14.65">
+      <c r="A2" s="4">
+        <v>5.0000000000000003e-002</v>
+      </c>
+      <c r="B2" s="5">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="C2" s="51">
+        <f t="shared" ref="C2:C6" si="3">$E$2-B2</f>
+        <v>5.9999999999999831e-002</v>
+      </c>
+      <c r="D2" s="52">
+        <f t="shared" ref="D2:D6" si="4">0.01*SQRT(2)</f>
+        <v>1.4142135623730952e-002</v>
+      </c>
+      <c r="E2" s="53">
+        <v>1.1699999999999999</v>
+      </c>
+    </row>
+    <row r="3" ht="14.65">
+      <c r="A3" s="46">
+        <v>7.0000000000000007e-002</v>
+      </c>
+      <c r="B3" s="9">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="C3" s="13">
+        <f t="shared" si="3"/>
+        <v>7.9999999999999849e-002</v>
+      </c>
+      <c r="D3" s="54">
+        <f t="shared" si="4"/>
+        <v>1.4142135623730952e-002</v>
+      </c>
+      <c r="E3" s="47" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="13"/>
+    </row>
+    <row r="4" ht="14.65">
+      <c r="A4" s="46">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="B4" s="9">
+        <v>1.0600000000000001</v>
+      </c>
+      <c r="C4" s="13">
+        <f t="shared" si="3"/>
+        <v>0.10999999999999988</v>
+      </c>
+      <c r="D4" s="55">
+        <f t="shared" si="4"/>
+        <v>1.4142135623730952e-002</v>
+      </c>
+      <c r="E4" s="53">
+        <v>1.e-002</v>
+      </c>
+      <c r="F4" s="13"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="46">
+        <v>0.14999999999999999</v>
+      </c>
+      <c r="B5" s="9">
+        <v>1.01</v>
+      </c>
+      <c r="C5" s="13">
+        <f t="shared" si="3"/>
+        <v>0.15999999999999992</v>
+      </c>
+      <c r="D5" s="55">
+        <f t="shared" si="4"/>
+        <v>1.4142135623730952e-002</v>
+      </c>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+    </row>
+    <row r="6" ht="14.65">
+      <c r="A6" s="49">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="B6" s="15">
+        <v>0.94999999999999996</v>
+      </c>
+      <c r="C6" s="56">
+        <f t="shared" si="3"/>
+        <v>0.21999999999999997</v>
+      </c>
+      <c r="D6" s="57">
+        <f t="shared" si="4"/>
+        <v>1.4142135623730952e-002</v>
+      </c>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+    </row>
+    <row r="7">
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="0" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -1902,20 +1889,20 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.65">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="27" t="s">
-        <v>9</v>
+      <c r="B1" s="59" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="59" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="59" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="60" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="2" ht="14.65">
@@ -1925,20 +1912,20 @@
       <c r="B2" s="5">
         <v>0.98999999999999999</v>
       </c>
-      <c r="C2" s="28">
+      <c r="C2" s="51">
         <f t="shared" ref="C2:C6" si="5">$E$2-B2</f>
         <v>9.000000000000008e-002</v>
       </c>
-      <c r="D2" s="29">
+      <c r="D2" s="52">
         <f t="shared" ref="D2:D6" si="6">0.01*SQRT(2)</f>
         <v>1.4142135623730952e-002</v>
       </c>
-      <c r="E2" s="58">
+      <c r="E2" s="61">
         <v>1.0800000000000001</v>
       </c>
     </row>
     <row r="3" ht="14.65">
-      <c r="A3" s="22">
+      <c r="A3" s="46">
         <v>0.10000000000000001</v>
       </c>
       <c r="B3" s="9">
@@ -1948,16 +1935,16 @@
         <f t="shared" si="5"/>
         <v>0.14000000000000012</v>
       </c>
-      <c r="D3" s="31">
+      <c r="D3" s="55">
         <f t="shared" si="6"/>
         <v>1.4142135623730952e-002</v>
       </c>
-      <c r="E3" s="59" t="s">
-        <v>10</v>
+      <c r="E3" s="62" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4" ht="14.65">
-      <c r="A4" s="22">
+      <c r="A4" s="46">
         <v>0.12</v>
       </c>
       <c r="B4" s="9">
@@ -1967,7 +1954,7 @@
         <f t="shared" si="5"/>
         <v>0.17000000000000004</v>
       </c>
-      <c r="D4" s="31">
+      <c r="D4" s="55">
         <f t="shared" si="6"/>
         <v>1.4142135623730952e-002</v>
       </c>
@@ -1976,7 +1963,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22">
+      <c r="A5" s="46">
         <v>0.14999999999999999</v>
       </c>
       <c r="B5" s="9">
@@ -1986,23 +1973,23 @@
         <f t="shared" si="5"/>
         <v>0.21000000000000008</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="55">
         <f t="shared" si="6"/>
         <v>1.4142135623730952e-002</v>
       </c>
     </row>
     <row r="6" ht="14.65">
-      <c r="A6" s="23">
+      <c r="A6" s="49">
         <v>0.20000000000000001</v>
       </c>
       <c r="B6" s="15">
         <v>0.80000000000000004</v>
       </c>
-      <c r="C6" s="32">
+      <c r="C6" s="56">
         <f t="shared" si="5"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="57">
         <f t="shared" si="6"/>
         <v>1.4142135623730952e-002</v>
       </c>
@@ -2016,7 +2003,7 @@
       <c r="D8" s="13"/>
       <c r="E8" s="13"/>
       <c r="F8" s="13"/>
-      <c r="G8" s="60"/>
+      <c r="G8" s="63"/>
     </row>
     <row r="9">
       <c r="D9" s="13"/>
@@ -2048,20 +2035,20 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.65">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="59" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="27" t="s">
-        <v>9</v>
+      <c r="B1" s="59" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="59" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="62" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="60" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="2" ht="14.65">
@@ -2071,20 +2058,20 @@
       <c r="B2" s="5">
         <v>1.25</v>
       </c>
-      <c r="C2" s="28">
+      <c r="C2" s="51">
         <f t="shared" ref="C2:C7" si="7">$E$2-B2</f>
         <v>2.0000000000000018e-002</v>
       </c>
-      <c r="D2" s="29">
+      <c r="D2" s="52">
         <f t="shared" ref="D2:D7" si="8">0.01*SQRT(2)</f>
         <v>1.4142135623730952e-002</v>
       </c>
-      <c r="E2" s="61">
+      <c r="E2" s="64">
         <v>1.27</v>
       </c>
     </row>
     <row r="3" ht="14.65">
-      <c r="A3" s="22">
+      <c r="A3" s="46">
         <v>0.20000000000000001</v>
       </c>
       <c r="B3" s="9">
@@ -2094,16 +2081,16 @@
         <f t="shared" si="7"/>
         <v>4.0000000000000036e-002</v>
       </c>
-      <c r="D3" s="31">
+      <c r="D3" s="55">
         <f t="shared" si="8"/>
         <v>1.4142135623730952e-002</v>
       </c>
-      <c r="E3" s="27" t="s">
-        <v>10</v>
+      <c r="E3" s="60" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4" ht="14.65">
-      <c r="A4" s="22">
+      <c r="A4" s="46">
         <v>0.5</v>
       </c>
       <c r="B4" s="9">
@@ -2113,16 +2100,16 @@
         <f t="shared" si="7"/>
         <v>9.000000000000008e-002</v>
       </c>
-      <c r="D4" s="31">
+      <c r="D4" s="55">
         <f t="shared" si="8"/>
         <v>1.4142135623730952e-002</v>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="53">
         <v>1.e-002</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22">
+      <c r="A5" s="46">
         <v>0.69999999999999996</v>
       </c>
       <c r="B5" s="9">
@@ -2132,13 +2119,13 @@
         <f t="shared" si="7"/>
         <v>0.12000000000000011</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="55">
         <f t="shared" si="8"/>
         <v>1.4142135623730952e-002</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="22">
+      <c r="A6" s="46">
         <v>0.90000000000000002</v>
       </c>
       <c r="B6" s="9">
@@ -2148,23 +2135,23 @@
         <f t="shared" si="7"/>
         <v>0.14999999999999991</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="55">
         <f t="shared" si="8"/>
         <v>1.4142135623730952e-002</v>
       </c>
     </row>
     <row r="7" ht="14.65">
-      <c r="A7" s="23">
+      <c r="A7" s="49">
         <v>1</v>
       </c>
       <c r="B7" s="15">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="56">
         <f t="shared" si="7"/>
         <v>0.16999999999999993</v>
       </c>
-      <c r="D7" s="33">
+      <c r="D7" s="57">
         <f t="shared" si="8"/>
         <v>1.4142135623730952e-002</v>
       </c>
@@ -2192,18 +2179,18 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.5">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="62" t="s">
+      <c r="B1" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="63" t="s">
+      <c r="C1" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="60"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
       <c r="G1" s="9"/>
     </row>
     <row r="2">
@@ -2216,9 +2203,9 @@
       <c r="C2">
         <v>0</v>
       </c>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
     </row>
     <row r="3">
       <c r="A3" s="9">
@@ -2230,9 +2217,9 @@
       <c r="C3">
         <v>1.e-002</v>
       </c>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
     </row>
     <row r="4">
       <c r="A4" s="9">
@@ -2244,9 +2231,9 @@
       <c r="C4">
         <v>2.e-002</v>
       </c>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
     </row>
     <row r="5">
       <c r="A5" s="9">
@@ -2258,9 +2245,9 @@
       <c r="C5">
         <v>2.9999999999999999e-002</v>
       </c>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
     </row>
     <row r="6">
       <c r="A6" s="9">
@@ -2272,9 +2259,9 @@
       <c r="C6">
         <v>4.0000000000000001e-002</v>
       </c>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
     </row>
     <row r="7">
       <c r="A7" s="9">
@@ -2286,9 +2273,9 @@
       <c r="C7">
         <v>5.0000000000000003e-002</v>
       </c>
-      <c r="D7" s="65"/>
-      <c r="E7" s="65"/>
-      <c r="F7" s="65"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="68"/>
     </row>
     <row r="8">
       <c r="A8" s="9">
@@ -2300,9 +2287,9 @@
       <c r="C8">
         <v>5.9999999999999998e-002</v>
       </c>
-      <c r="D8" s="65"/>
-      <c r="E8" s="65"/>
-      <c r="F8" s="65"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
     </row>
     <row r="9">
       <c r="A9" s="9">
@@ -2314,9 +2301,9 @@
       <c r="C9">
         <v>5.9999999999999998e-002</v>
       </c>
-      <c r="D9" s="65"/>
-      <c r="E9" s="65"/>
-      <c r="F9" s="65"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="68"/>
     </row>
     <row r="10">
       <c r="A10" s="9">
@@ -2328,9 +2315,9 @@
       <c r="C10">
         <v>7.0000000000000007e-002</v>
       </c>
-      <c r="D10" s="65"/>
-      <c r="E10" s="65"/>
-      <c r="F10" s="65"/>
+      <c r="D10" s="68"/>
+      <c r="E10" s="68"/>
+      <c r="F10" s="68"/>
     </row>
     <row r="11">
       <c r="A11" s="9">
@@ -2342,9 +2329,9 @@
       <c r="C11">
         <v>7.0000000000000007e-002</v>
       </c>
-      <c r="D11" s="65"/>
-      <c r="E11" s="65"/>
-      <c r="F11" s="65"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="68"/>
     </row>
     <row r="12">
       <c r="A12" s="9">
@@ -2356,9 +2343,9 @@
       <c r="C12">
         <v>5.9999999999999998e-002</v>
       </c>
-      <c r="D12" s="65"/>
-      <c r="E12" s="65"/>
-      <c r="F12" s="65"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="68"/>
+      <c r="F12" s="68"/>
     </row>
     <row r="13">
       <c r="A13" s="9">
@@ -2370,9 +2357,9 @@
       <c r="C13">
         <v>5.9999999999999998e-002</v>
       </c>
-      <c r="D13" s="65"/>
-      <c r="E13" s="65"/>
-      <c r="F13" s="65"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="68"/>
     </row>
     <row r="14">
       <c r="A14" s="9">
@@ -2384,9 +2371,9 @@
       <c r="C14">
         <v>5.9999999999999998e-002</v>
       </c>
-      <c r="D14" s="65"/>
-      <c r="E14" s="65"/>
-      <c r="F14" s="65"/>
+      <c r="D14" s="68"/>
+      <c r="E14" s="68"/>
+      <c r="F14" s="68"/>
     </row>
     <row r="15">
       <c r="A15" s="9">
@@ -2398,9 +2385,9 @@
       <c r="C15">
         <v>5.0000000000000003e-002</v>
       </c>
-      <c r="D15" s="65"/>
-      <c r="E15" s="65"/>
-      <c r="F15" s="65"/>
+      <c r="D15" s="68"/>
+      <c r="E15" s="68"/>
+      <c r="F15" s="68"/>
     </row>
     <row r="16">
       <c r="A16" s="9">
@@ -2412,9 +2399,9 @@
       <c r="C16">
         <v>5.0000000000000003e-002</v>
       </c>
-      <c r="D16" s="65"/>
-      <c r="E16" s="65"/>
-      <c r="F16" s="65"/>
+      <c r="D16" s="68"/>
+      <c r="E16" s="68"/>
+      <c r="F16" s="68"/>
     </row>
     <row r="17">
       <c r="A17" s="9">
@@ -2426,9 +2413,9 @@
       <c r="C17">
         <v>4.0000000000000001e-002</v>
       </c>
-      <c r="D17" s="65"/>
-      <c r="E17" s="65"/>
-      <c r="F17" s="65"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="68"/>
     </row>
     <row r="18">
       <c r="A18" s="9">
@@ -2440,9 +2427,9 @@
       <c r="C18">
         <v>2.9999999999999999e-002</v>
       </c>
-      <c r="D18" s="65"/>
-      <c r="E18" s="65"/>
-      <c r="F18" s="65"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="68"/>
+      <c r="F18" s="68"/>
     </row>
     <row r="19">
       <c r="A19" s="9">
@@ -2454,9 +2441,9 @@
       <c r="C19">
         <v>2.e-002</v>
       </c>
-      <c r="D19" s="65"/>
-      <c r="E19" s="65"/>
-      <c r="F19" s="65"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="68"/>
+      <c r="F19" s="68"/>
     </row>
     <row r="20">
       <c r="A20" s="9">
@@ -2468,9 +2455,9 @@
       <c r="C20">
         <v>1.e-002</v>
       </c>
-      <c r="D20" s="65"/>
-      <c r="E20" s="65"/>
-      <c r="F20" s="65"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="68"/>
     </row>
     <row r="21">
       <c r="A21" s="9">
@@ -2482,9 +2469,9 @@
       <c r="C21">
         <v>-1.e-002</v>
       </c>
-      <c r="D21" s="65"/>
-      <c r="E21" s="65"/>
-      <c r="F21" s="65"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
     </row>
     <row r="22">
       <c r="A22" s="9">
@@ -2496,9 +2483,9 @@
       <c r="C22">
         <v>-2.e-002</v>
       </c>
-      <c r="D22" s="65"/>
-      <c r="E22" s="65"/>
-      <c r="F22" s="65"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="68"/>
     </row>
     <row r="23">
       <c r="A23" s="9">
@@ -2510,9 +2497,9 @@
       <c r="C23">
         <v>-2.e-002</v>
       </c>
-      <c r="D23" s="65"/>
-      <c r="E23" s="65"/>
-      <c r="F23" s="65"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
     </row>
     <row r="24">
       <c r="A24" s="9">
@@ -2524,9 +2511,9 @@
       <c r="C24">
         <v>-2.9999999999999999e-002</v>
       </c>
-      <c r="D24" s="65"/>
-      <c r="E24" s="65"/>
-      <c r="F24" s="65"/>
+      <c r="D24" s="68"/>
+      <c r="E24" s="68"/>
+      <c r="F24" s="68"/>
     </row>
     <row r="25">
       <c r="A25" s="9">
@@ -2538,9 +2525,9 @@
       <c r="C25">
         <v>-4.0000000000000001e-002</v>
       </c>
-      <c r="D25" s="65"/>
-      <c r="E25" s="65"/>
-      <c r="F25" s="65"/>
+      <c r="D25" s="68"/>
+      <c r="E25" s="68"/>
+      <c r="F25" s="68"/>
     </row>
     <row r="26">
       <c r="A26" s="9">
@@ -2582,7 +2569,7 @@
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
-      <c r="F28" s="66"/>
+      <c r="F28" s="69"/>
     </row>
     <row r="29">
       <c r="A29" s="9">
@@ -3638,11 +3625,11 @@
       <c r="A169" s="9"/>
       <c r="B169" s="9"/>
       <c r="D169" s="9"/>
-      <c r="E169" s="66"/>
+      <c r="E169" s="69"/>
       <c r="F169" s="9"/>
     </row>
     <row r="170">
-      <c r="A170" s="66"/>
+      <c r="A170" s="69"/>
       <c r="B170" s="9"/>
       <c r="D170" s="9"/>
       <c r="E170" s="9"/>
@@ -3771,11 +3758,11 @@
       <c r="A188" s="9"/>
       <c r="B188" s="9"/>
       <c r="D188" s="9"/>
-      <c r="E188" s="66"/>
+      <c r="E188" s="69"/>
       <c r="F188" s="9"/>
     </row>
     <row r="189">
-      <c r="A189" s="66"/>
+      <c r="A189" s="69"/>
       <c r="B189" s="9"/>
       <c r="D189" s="9"/>
       <c r="E189" s="9"/>
@@ -3961,7 +3948,7 @@
       <c r="B215" s="9"/>
       <c r="D215" s="9"/>
       <c r="E215" s="9"/>
-      <c r="F215" s="66"/>
+      <c r="F215" s="69"/>
     </row>
     <row r="216">
       <c r="A216" s="9"/>
@@ -4163,11 +4150,11 @@
       <c r="A244" s="9"/>
       <c r="B244" s="9"/>
       <c r="D244" s="9"/>
-      <c r="E244" s="66"/>
+      <c r="E244" s="69"/>
       <c r="F244" s="9"/>
     </row>
     <row r="245">
-      <c r="A245" s="66"/>
+      <c r="A245" s="69"/>
       <c r="B245" s="9"/>
       <c r="D245" s="9"/>
       <c r="E245" s="9"/>
@@ -4555,11 +4542,11 @@
       <c r="A300" s="9"/>
       <c r="B300" s="9"/>
       <c r="D300" s="9"/>
-      <c r="E300" s="66"/>
+      <c r="E300" s="69"/>
       <c r="F300" s="9"/>
     </row>
     <row r="301">
-      <c r="A301" s="66"/>
+      <c r="A301" s="69"/>
       <c r="B301" s="9"/>
       <c r="D301" s="9"/>
       <c r="E301" s="9"/>
@@ -4612,7 +4599,7 @@
       <c r="B308" s="9"/>
       <c r="D308" s="9"/>
       <c r="E308" s="9"/>
-      <c r="F308" s="66"/>
+      <c r="F308" s="69"/>
     </row>
     <row r="309">
       <c r="A309" s="9"/>
@@ -4688,11 +4675,11 @@
       <c r="A319" s="9"/>
       <c r="B319" s="9"/>
       <c r="D319" s="9"/>
-      <c r="E319" s="66"/>
+      <c r="E319" s="69"/>
       <c r="F319" s="9"/>
     </row>
     <row r="320">
-      <c r="A320" s="66"/>
+      <c r="A320" s="69"/>
       <c r="B320" s="9"/>
       <c r="D320" s="9"/>
       <c r="E320" s="9"/>
@@ -4821,11 +4808,11 @@
       <c r="A338" s="9"/>
       <c r="B338" s="9"/>
       <c r="D338" s="9"/>
-      <c r="E338" s="66"/>
+      <c r="E338" s="69"/>
       <c r="F338" s="9"/>
     </row>
     <row r="339">
-      <c r="A339" s="66"/>
+      <c r="A339" s="69"/>
       <c r="B339" s="9"/>
       <c r="D339" s="9"/>
       <c r="E339" s="9"/>
@@ -5229,273 +5216,6 @@
     </row>
     <row r="397">
       <c r="A397" s="13"/>
-    </row>
-  </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <cols>
-    <col bestFit="1" customWidth="1" min="8" max="8" width="15.3984375"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="67" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="68">
-        <v>5.0000000000000003e-002</v>
-      </c>
-      <c r="C1" s="68">
-        <v>0.14999999999999999</v>
-      </c>
-      <c r="D1" s="68">
-        <v>0.25</v>
-      </c>
-      <c r="E1" s="68">
-        <v>0.34999999999999998</v>
-      </c>
-      <c r="F1" s="68">
-        <v>0.45000000000000001</v>
-      </c>
-      <c r="G1" s="69">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="H1" s="67" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="70">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>23.844000000000001</v>
-      </c>
-      <c r="C2">
-        <v>14.49</v>
-      </c>
-      <c r="D2">
-        <v>11.285</v>
-      </c>
-      <c r="E2">
-        <v>9.6229999999999993</v>
-      </c>
-      <c r="F2">
-        <v>8.3829999999999991</v>
-      </c>
-      <c r="G2" s="71">
-        <v>7.6909999999999998</v>
-      </c>
-      <c r="H2" s="70">
-        <f>$B1+$I$2/3</f>
-        <v>5.0000000000000003e-002</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="72">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>24.542999999999999</v>
-      </c>
-      <c r="C3">
-        <v>14.622</v>
-      </c>
-      <c r="D3">
-        <v>11.177</v>
-      </c>
-      <c r="E3">
-        <v>9.5730000000000004</v>
-      </c>
-      <c r="F3">
-        <v>8.4060000000000006</v>
-      </c>
-      <c r="G3" s="71">
-        <v>7.5910000000000002</v>
-      </c>
-      <c r="H3" s="70">
-        <f>$C1+$I$2/3</f>
-        <v>0.14999999999999999</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="72">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>24.129999999999999</v>
-      </c>
-      <c r="C4">
-        <v>14.653</v>
-      </c>
-      <c r="D4">
-        <v>11.301</v>
-      </c>
-      <c r="E4">
-        <v>9.6159999999999997</v>
-      </c>
-      <c r="F4">
-        <v>8.3879999999999999</v>
-      </c>
-      <c r="G4" s="71">
-        <v>7.6589999999999998</v>
-      </c>
-      <c r="H4" s="70">
-        <f>$D1+$I$2/3</f>
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="72">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>24.359999999999999</v>
-      </c>
-      <c r="C5">
-        <v>14.534000000000001</v>
-      </c>
-      <c r="D5">
-        <v>11.298999999999999</v>
-      </c>
-      <c r="E5">
-        <v>9.6300000000000008</v>
-      </c>
-      <c r="F5">
-        <v>8.3859999999999992</v>
-      </c>
-      <c r="G5" s="71">
-        <v>7.5999999999999996</v>
-      </c>
-      <c r="H5" s="70">
-        <f>$E1+$I$2/3</f>
-        <v>0.34999999999999998</v>
-      </c>
-    </row>
-    <row r="6" ht="14.65">
-      <c r="A6" s="72">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>24.425000000000001</v>
-      </c>
-      <c r="C6">
-        <v>14.542</v>
-      </c>
-      <c r="D6">
-        <v>11.26</v>
-      </c>
-      <c r="E6">
-        <v>9.6170000000000009</v>
-      </c>
-      <c r="F6">
-        <v>8.4019999999999992</v>
-      </c>
-      <c r="G6" s="71">
-        <v>7.6319999999999997</v>
-      </c>
-      <c r="H6" s="70">
-        <f>$F1+$I$2/3</f>
-        <v>0.45000000000000001</v>
-      </c>
-    </row>
-    <row r="7" ht="14.65">
-      <c r="A7" s="73" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="74">
-        <f>AVERAGE(B2:B6)</f>
-        <v>24.260399999999997</v>
-      </c>
-      <c r="C7" s="74">
-        <f>AVERAGE(C2:C6)</f>
-        <v>14.568199999999999</v>
-      </c>
-      <c r="D7" s="74">
-        <f>AVERAGE(D2:D6)</f>
-        <v>11.264399999999998</v>
-      </c>
-      <c r="E7" s="74">
-        <f t="shared" ref="E7:G7" si="9">AVERAGE(E2:E6)</f>
-        <v>9.6117999999999988</v>
-      </c>
-      <c r="F7" s="74">
-        <f t="shared" si="9"/>
-        <v>8.3930000000000007</v>
-      </c>
-      <c r="G7" s="75">
-        <f t="shared" si="9"/>
-        <v>7.6345999999999989</v>
-      </c>
-      <c r="H7" s="76">
-        <f>$G1+$I$2/3</f>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="77" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8">
-        <f>_xlfn.STDEV.S(B2:B6)</f>
-        <v>0.27715934045238261</v>
-      </c>
-      <c r="C8">
-        <f>_xlfn.STDEV.S(C2:C6)</f>
-        <v>6.7187796510973619e-002</v>
-      </c>
-      <c r="D8">
-        <f>_xlfn.STDEV.S(D2:D6)</f>
-        <v>5.1524751333703808e-002</v>
-      </c>
-      <c r="E8">
-        <f>_xlfn.STDEV.S(E2:E6)</f>
-        <v>2.2398660674245618e-002</v>
-      </c>
-      <c r="F8">
-        <f>_xlfn.STDEV.S(F2:F6)</f>
-        <v>1.0295630140987376e-002</v>
-      </c>
-      <c r="G8" s="71">
-        <f>_xlfn.STDEV.S(G2:G6)</f>
-        <v>4.1476499370125187e-002</v>
-      </c>
-    </row>
-    <row r="9" ht="14.65">
-      <c r="A9" s="78" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="79">
-        <f>B8/SQRT(5)</f>
-        <v>0.12394942517010696</v>
-      </c>
-      <c r="C9" s="79">
-        <f>C8/SQRT(5)</f>
-        <v>3.0047296051392041e-002</v>
-      </c>
-      <c r="D9" s="79">
-        <f>D8/SQRT(5)</f>
-        <v>2.3042569301186932e-002</v>
-      </c>
-      <c r="E9" s="79">
-        <f t="shared" ref="E9:G9" si="10">E8/SQRT(5)</f>
-        <v>1.0016985574512895e-002</v>
-      </c>
-      <c r="F9" s="79">
-        <f t="shared" si="10"/>
-        <v>4.6043457732887032e-003</v>
-      </c>
-      <c r="G9" s="80">
-        <f t="shared" si="10"/>
-        <v>1.8548854412065423e-002</v>
-      </c>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>

--- a/Legge di Hooke.xlsx
+++ b/Legge di Hooke.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Misure statiche 1" sheetId="1" state="visible" r:id="rId1"/>
@@ -113,17 +113,17 @@
       <name val="Arial Unicode MS"/>
     </font>
     <font>
-      <b/>
-      <sz val="10.000000"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <u/>
       <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.000000"/>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
     <font>
       <u/>
@@ -162,7 +162,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="32">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -465,6 +465,57 @@
     </border>
     <border>
       <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
         <color auto="1"/>
       </left>
       <right style="medium">
@@ -478,7 +529,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="83">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="1" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -593,15 +644,50 @@
     <xf fontId="1" fillId="0" borderId="10" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="3" fillId="4" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="3" fillId="4" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="1" fillId="2" borderId="25" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="1" fillId="0" borderId="26" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="27" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="27" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="28" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf fontId="1" fillId="0" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="4" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="1" fillId="0" borderId="26" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="0" borderId="29" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="15" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="2" borderId="23" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="1" fillId="0" borderId="30" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="21" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="21" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="22" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="4" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="4" fillId="4" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="4" fillId="4" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="4" fillId="4" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="1" fillId="0" borderId="31" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf fontId="1" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1881,81 +1967,77 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="8.1328125"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="12.796875"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="16.33203125"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="19"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="17.53125"/>
+    <col bestFit="1" customWidth="1" min="1" max="5" width="9.00390625"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.65">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="59" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="59" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="59" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="60" t="s">
-        <v>15</v>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="58" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="2" ht="14.65">
-      <c r="A2" s="4">
+      <c r="A2" s="59">
         <v>7.0000000000000007e-002</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="60">
         <v>0.98999999999999999</v>
       </c>
-      <c r="C2" s="51">
-        <f t="shared" ref="C2:C6" si="5">$E$2-B2</f>
+      <c r="C2" s="61">
+        <f>-B2+$E$2</f>
         <v>9.000000000000008e-002</v>
       </c>
-      <c r="D2" s="52">
-        <f t="shared" ref="D2:D6" si="6">0.01*SQRT(2)</f>
+      <c r="D2" s="62">
+        <f>0.01*SQRT(2)</f>
         <v>1.4142135623730952e-002</v>
       </c>
-      <c r="E2" s="61">
+      <c r="E2" s="63">
         <v>1.0800000000000001</v>
       </c>
     </row>
     <row r="3" ht="14.65">
-      <c r="A3" s="46">
+      <c r="A3" s="64">
         <v>0.10000000000000001</v>
       </c>
       <c r="B3" s="9">
         <v>0.93999999999999995</v>
       </c>
       <c r="C3" s="13">
-        <f t="shared" si="5"/>
+        <f>-B3+$E$2</f>
         <v>0.14000000000000012</v>
       </c>
-      <c r="D3" s="55">
-        <f t="shared" si="6"/>
+      <c r="D3" s="65">
+        <f>0.01*SQRT(2)</f>
         <v>1.4142135623730952e-002</v>
       </c>
-      <c r="E3" s="62" t="s">
-        <v>16</v>
+      <c r="E3" s="66" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="4" ht="14.65">
-      <c r="A4" s="46">
+      <c r="A4" s="64">
         <v>0.12</v>
       </c>
       <c r="B4" s="9">
         <v>0.91000000000000003</v>
       </c>
       <c r="C4" s="13">
-        <f t="shared" si="5"/>
+        <f>-B4+$E$2</f>
         <v>0.17000000000000004</v>
       </c>
-      <c r="D4" s="55">
-        <f t="shared" si="6"/>
+      <c r="D4" s="65">
+        <f>0.01*SQRT(2)</f>
         <v>1.4142135623730952e-002</v>
       </c>
       <c r="E4" s="7">
@@ -1963,47 +2045,47 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="46">
+      <c r="A5" s="64">
         <v>0.14999999999999999</v>
       </c>
       <c r="B5" s="9">
         <v>0.87</v>
       </c>
       <c r="C5" s="13">
-        <f t="shared" si="5"/>
+        <f>-B5+$E$2</f>
         <v>0.21000000000000008</v>
       </c>
-      <c r="D5" s="55">
-        <f t="shared" si="6"/>
+      <c r="D5" s="65">
+        <f>0.01*SQRT(2)</f>
         <v>1.4142135623730952e-002</v>
       </c>
+      <c r="E5" s="13"/>
     </row>
     <row r="6" ht="14.65">
-      <c r="A6" s="49">
+      <c r="A6" s="67">
         <v>0.20000000000000001</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="68">
         <v>0.80000000000000004</v>
       </c>
-      <c r="C6" s="56">
-        <f t="shared" si="5"/>
+      <c r="C6" s="69">
+        <f>-B6+$E$2</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="D6" s="57">
-        <f t="shared" si="6"/>
+      <c r="D6" s="70">
+        <f>0.01*SQRT(2)</f>
         <v>1.4142135623730952e-002</v>
       </c>
+      <c r="E6" s="13"/>
     </row>
     <row r="7">
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
       <c r="F7" s="13"/>
     </row>
     <row r="8">
       <c r="D8" s="13"/>
       <c r="E8" s="13"/>
       <c r="F8" s="13"/>
-      <c r="G8" s="63"/>
+      <c r="G8" s="71"/>
     </row>
     <row r="9">
       <c r="D9" s="13"/>
@@ -2014,6 +2096,13 @@
       <c r="D10" s="13"/>
       <c r="E10" s="13"/>
       <c r="F10" s="13"/>
+    </row>
+    <row r="13" ht="14.25">
+      <c r="J13" s="72"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="72"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -2035,19 +2124,19 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.65">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="59" t="s">
+      <c r="C1" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="62" t="s">
+      <c r="D1" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="60" t="s">
+      <c r="E1" s="76" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2059,14 +2148,14 @@
         <v>1.25</v>
       </c>
       <c r="C2" s="51">
-        <f t="shared" ref="C2:C7" si="7">$E$2-B2</f>
+        <f t="shared" ref="C2:C7" si="5">$E$2-B2</f>
         <v>2.0000000000000018e-002</v>
       </c>
       <c r="D2" s="52">
-        <f t="shared" ref="D2:D7" si="8">0.01*SQRT(2)</f>
+        <f t="shared" ref="D2:D7" si="6">0.01*SQRT(2)</f>
         <v>1.4142135623730952e-002</v>
       </c>
-      <c r="E2" s="64">
+      <c r="E2" s="77">
         <v>1.27</v>
       </c>
     </row>
@@ -2078,14 +2167,14 @@
         <v>1.23</v>
       </c>
       <c r="C3" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>4.0000000000000036e-002</v>
       </c>
       <c r="D3" s="55">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1.4142135623730952e-002</v>
       </c>
-      <c r="E3" s="60" t="s">
+      <c r="E3" s="76" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2097,11 +2186,11 @@
         <v>1.1799999999999999</v>
       </c>
       <c r="C4" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>9.000000000000008e-002</v>
       </c>
       <c r="D4" s="55">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1.4142135623730952e-002</v>
       </c>
       <c r="E4" s="53">
@@ -2116,11 +2205,11 @@
         <v>1.1499999999999999</v>
       </c>
       <c r="C5" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0.12000000000000011</v>
       </c>
       <c r="D5" s="55">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1.4142135623730952e-002</v>
       </c>
     </row>
@@ -2132,11 +2221,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="C6" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="D6" s="55">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1.4142135623730952e-002</v>
       </c>
     </row>
@@ -2148,11 +2237,11 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="C7" s="56">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0.16999999999999993</v>
       </c>
       <c r="D7" s="57">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1.4142135623730952e-002</v>
       </c>
     </row>
@@ -2179,18 +2268,18 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.5">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="66" t="s">
+      <c r="C1" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="63"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
       <c r="G1" s="9"/>
     </row>
     <row r="2">
@@ -2203,9 +2292,9 @@
       <c r="C2">
         <v>0</v>
       </c>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
     </row>
     <row r="3">
       <c r="A3" s="9">
@@ -2217,9 +2306,9 @@
       <c r="C3">
         <v>1.e-002</v>
       </c>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
     </row>
     <row r="4">
       <c r="A4" s="9">
@@ -2231,9 +2320,9 @@
       <c r="C4">
         <v>2.e-002</v>
       </c>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="81"/>
     </row>
     <row r="5">
       <c r="A5" s="9">
@@ -2245,9 +2334,9 @@
       <c r="C5">
         <v>2.9999999999999999e-002</v>
       </c>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
+      <c r="D5" s="81"/>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
     </row>
     <row r="6">
       <c r="A6" s="9">
@@ -2259,9 +2348,9 @@
       <c r="C6">
         <v>4.0000000000000001e-002</v>
       </c>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
+      <c r="D6" s="81"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="81"/>
     </row>
     <row r="7">
       <c r="A7" s="9">
@@ -2273,9 +2362,9 @@
       <c r="C7">
         <v>5.0000000000000003e-002</v>
       </c>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
     </row>
     <row r="8">
       <c r="A8" s="9">
@@ -2287,9 +2376,9 @@
       <c r="C8">
         <v>5.9999999999999998e-002</v>
       </c>
-      <c r="D8" s="68"/>
-      <c r="E8" s="68"/>
-      <c r="F8" s="68"/>
+      <c r="D8" s="81"/>
+      <c r="E8" s="81"/>
+      <c r="F8" s="81"/>
     </row>
     <row r="9">
       <c r="A9" s="9">
@@ -2301,9 +2390,9 @@
       <c r="C9">
         <v>5.9999999999999998e-002</v>
       </c>
-      <c r="D9" s="68"/>
-      <c r="E9" s="68"/>
-      <c r="F9" s="68"/>
+      <c r="D9" s="81"/>
+      <c r="E9" s="81"/>
+      <c r="F9" s="81"/>
     </row>
     <row r="10">
       <c r="A10" s="9">
@@ -2315,9 +2404,9 @@
       <c r="C10">
         <v>7.0000000000000007e-002</v>
       </c>
-      <c r="D10" s="68"/>
-      <c r="E10" s="68"/>
-      <c r="F10" s="68"/>
+      <c r="D10" s="81"/>
+      <c r="E10" s="81"/>
+      <c r="F10" s="81"/>
     </row>
     <row r="11">
       <c r="A11" s="9">
@@ -2329,9 +2418,9 @@
       <c r="C11">
         <v>7.0000000000000007e-002</v>
       </c>
-      <c r="D11" s="68"/>
-      <c r="E11" s="68"/>
-      <c r="F11" s="68"/>
+      <c r="D11" s="81"/>
+      <c r="E11" s="81"/>
+      <c r="F11" s="81"/>
     </row>
     <row r="12">
       <c r="A12" s="9">
@@ -2343,9 +2432,9 @@
       <c r="C12">
         <v>5.9999999999999998e-002</v>
       </c>
-      <c r="D12" s="68"/>
-      <c r="E12" s="68"/>
-      <c r="F12" s="68"/>
+      <c r="D12" s="81"/>
+      <c r="E12" s="81"/>
+      <c r="F12" s="81"/>
     </row>
     <row r="13">
       <c r="A13" s="9">
@@ -2357,9 +2446,9 @@
       <c r="C13">
         <v>5.9999999999999998e-002</v>
       </c>
-      <c r="D13" s="68"/>
-      <c r="E13" s="68"/>
-      <c r="F13" s="68"/>
+      <c r="D13" s="81"/>
+      <c r="E13" s="81"/>
+      <c r="F13" s="81"/>
     </row>
     <row r="14">
       <c r="A14" s="9">
@@ -2371,9 +2460,9 @@
       <c r="C14">
         <v>5.9999999999999998e-002</v>
       </c>
-      <c r="D14" s="68"/>
-      <c r="E14" s="68"/>
-      <c r="F14" s="68"/>
+      <c r="D14" s="81"/>
+      <c r="E14" s="81"/>
+      <c r="F14" s="81"/>
     </row>
     <row r="15">
       <c r="A15" s="9">
@@ -2385,9 +2474,9 @@
       <c r="C15">
         <v>5.0000000000000003e-002</v>
       </c>
-      <c r="D15" s="68"/>
-      <c r="E15" s="68"/>
-      <c r="F15" s="68"/>
+      <c r="D15" s="81"/>
+      <c r="E15" s="81"/>
+      <c r="F15" s="81"/>
     </row>
     <row r="16">
       <c r="A16" s="9">
@@ -2399,9 +2488,9 @@
       <c r="C16">
         <v>5.0000000000000003e-002</v>
       </c>
-      <c r="D16" s="68"/>
-      <c r="E16" s="68"/>
-      <c r="F16" s="68"/>
+      <c r="D16" s="81"/>
+      <c r="E16" s="81"/>
+      <c r="F16" s="81"/>
     </row>
     <row r="17">
       <c r="A17" s="9">
@@ -2413,9 +2502,9 @@
       <c r="C17">
         <v>4.0000000000000001e-002</v>
       </c>
-      <c r="D17" s="68"/>
-      <c r="E17" s="68"/>
-      <c r="F17" s="68"/>
+      <c r="D17" s="81"/>
+      <c r="E17" s="81"/>
+      <c r="F17" s="81"/>
     </row>
     <row r="18">
       <c r="A18" s="9">
@@ -2427,9 +2516,9 @@
       <c r="C18">
         <v>2.9999999999999999e-002</v>
       </c>
-      <c r="D18" s="68"/>
-      <c r="E18" s="68"/>
-      <c r="F18" s="68"/>
+      <c r="D18" s="81"/>
+      <c r="E18" s="81"/>
+      <c r="F18" s="81"/>
     </row>
     <row r="19">
       <c r="A19" s="9">
@@ -2441,9 +2530,9 @@
       <c r="C19">
         <v>2.e-002</v>
       </c>
-      <c r="D19" s="68"/>
-      <c r="E19" s="68"/>
-      <c r="F19" s="68"/>
+      <c r="D19" s="81"/>
+      <c r="E19" s="81"/>
+      <c r="F19" s="81"/>
     </row>
     <row r="20">
       <c r="A20" s="9">
@@ -2455,9 +2544,9 @@
       <c r="C20">
         <v>1.e-002</v>
       </c>
-      <c r="D20" s="68"/>
-      <c r="E20" s="68"/>
-      <c r="F20" s="68"/>
+      <c r="D20" s="81"/>
+      <c r="E20" s="81"/>
+      <c r="F20" s="81"/>
     </row>
     <row r="21">
       <c r="A21" s="9">
@@ -2469,9 +2558,9 @@
       <c r="C21">
         <v>-1.e-002</v>
       </c>
-      <c r="D21" s="68"/>
-      <c r="E21" s="68"/>
-      <c r="F21" s="68"/>
+      <c r="D21" s="81"/>
+      <c r="E21" s="81"/>
+      <c r="F21" s="81"/>
     </row>
     <row r="22">
       <c r="A22" s="9">
@@ -2483,9 +2572,9 @@
       <c r="C22">
         <v>-2.e-002</v>
       </c>
-      <c r="D22" s="68"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="68"/>
+      <c r="D22" s="81"/>
+      <c r="E22" s="81"/>
+      <c r="F22" s="81"/>
     </row>
     <row r="23">
       <c r="A23" s="9">
@@ -2497,9 +2586,9 @@
       <c r="C23">
         <v>-2.e-002</v>
       </c>
-      <c r="D23" s="68"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="68"/>
+      <c r="D23" s="81"/>
+      <c r="E23" s="81"/>
+      <c r="F23" s="81"/>
     </row>
     <row r="24">
       <c r="A24" s="9">
@@ -2511,9 +2600,9 @@
       <c r="C24">
         <v>-2.9999999999999999e-002</v>
       </c>
-      <c r="D24" s="68"/>
-      <c r="E24" s="68"/>
-      <c r="F24" s="68"/>
+      <c r="D24" s="81"/>
+      <c r="E24" s="81"/>
+      <c r="F24" s="81"/>
     </row>
     <row r="25">
       <c r="A25" s="9">
@@ -2525,9 +2614,9 @@
       <c r="C25">
         <v>-4.0000000000000001e-002</v>
       </c>
-      <c r="D25" s="68"/>
-      <c r="E25" s="68"/>
-      <c r="F25" s="68"/>
+      <c r="D25" s="81"/>
+      <c r="E25" s="81"/>
+      <c r="F25" s="81"/>
     </row>
     <row r="26">
       <c r="A26" s="9">
@@ -2569,7 +2658,7 @@
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
-      <c r="F28" s="69"/>
+      <c r="F28" s="82"/>
     </row>
     <row r="29">
       <c r="A29" s="9">
@@ -3625,11 +3714,11 @@
       <c r="A169" s="9"/>
       <c r="B169" s="9"/>
       <c r="D169" s="9"/>
-      <c r="E169" s="69"/>
+      <c r="E169" s="82"/>
       <c r="F169" s="9"/>
     </row>
     <row r="170">
-      <c r="A170" s="69"/>
+      <c r="A170" s="82"/>
       <c r="B170" s="9"/>
       <c r="D170" s="9"/>
       <c r="E170" s="9"/>
@@ -3758,11 +3847,11 @@
       <c r="A188" s="9"/>
       <c r="B188" s="9"/>
       <c r="D188" s="9"/>
-      <c r="E188" s="69"/>
+      <c r="E188" s="82"/>
       <c r="F188" s="9"/>
     </row>
     <row r="189">
-      <c r="A189" s="69"/>
+      <c r="A189" s="82"/>
       <c r="B189" s="9"/>
       <c r="D189" s="9"/>
       <c r="E189" s="9"/>
@@ -3948,7 +4037,7 @@
       <c r="B215" s="9"/>
       <c r="D215" s="9"/>
       <c r="E215" s="9"/>
-      <c r="F215" s="69"/>
+      <c r="F215" s="82"/>
     </row>
     <row r="216">
       <c r="A216" s="9"/>
@@ -4150,11 +4239,11 @@
       <c r="A244" s="9"/>
       <c r="B244" s="9"/>
       <c r="D244" s="9"/>
-      <c r="E244" s="69"/>
+      <c r="E244" s="82"/>
       <c r="F244" s="9"/>
     </row>
     <row r="245">
-      <c r="A245" s="69"/>
+      <c r="A245" s="82"/>
       <c r="B245" s="9"/>
       <c r="D245" s="9"/>
       <c r="E245" s="9"/>
@@ -4542,11 +4631,11 @@
       <c r="A300" s="9"/>
       <c r="B300" s="9"/>
       <c r="D300" s="9"/>
-      <c r="E300" s="69"/>
+      <c r="E300" s="82"/>
       <c r="F300" s="9"/>
     </row>
     <row r="301">
-      <c r="A301" s="69"/>
+      <c r="A301" s="82"/>
       <c r="B301" s="9"/>
       <c r="D301" s="9"/>
       <c r="E301" s="9"/>
@@ -4599,7 +4688,7 @@
       <c r="B308" s="9"/>
       <c r="D308" s="9"/>
       <c r="E308" s="9"/>
-      <c r="F308" s="69"/>
+      <c r="F308" s="82"/>
     </row>
     <row r="309">
       <c r="A309" s="9"/>
@@ -4675,11 +4764,11 @@
       <c r="A319" s="9"/>
       <c r="B319" s="9"/>
       <c r="D319" s="9"/>
-      <c r="E319" s="69"/>
+      <c r="E319" s="82"/>
       <c r="F319" s="9"/>
     </row>
     <row r="320">
-      <c r="A320" s="69"/>
+      <c r="A320" s="82"/>
       <c r="B320" s="9"/>
       <c r="D320" s="9"/>
       <c r="E320" s="9"/>
@@ -4808,11 +4897,11 @@
       <c r="A338" s="9"/>
       <c r="B338" s="9"/>
       <c r="D338" s="9"/>
-      <c r="E338" s="69"/>
+      <c r="E338" s="82"/>
       <c r="F338" s="9"/>
     </row>
     <row r="339">
-      <c r="A339" s="69"/>
+      <c r="A339" s="82"/>
       <c r="B339" s="9"/>
       <c r="D339" s="9"/>
       <c r="E339" s="9"/>

--- a/Legge di Hooke.xlsx
+++ b/Legge di Hooke.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="4"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Misure statiche 1" sheetId="1" state="visible" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>m[kg]</t>
   </si>
@@ -63,21 +63,6 @@
     <t>σω_</t>
   </si>
   <si>
-    <t xml:space="preserve">posizione [m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">allungamento [m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">incertezza su all. [m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d [m] senza pesi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">incertezza su d [m]</t>
-  </si>
-  <si>
     <t xml:space="preserve">t1 (s) Set</t>
   </si>
   <si>
@@ -91,11 +76,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -120,19 +106,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10.000000"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <u/>
       <sz val="10.000000"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -153,16 +133,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor indexed="5"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="33">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -516,20 +491,35 @@
     </border>
     <border>
       <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
         <color auto="1"/>
-      </left>
-      <right style="medium">
+      </top>
+      <bottom style="medium">
         <color auto="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="none"/>
+      </bottom>
       <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="87">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="1" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -683,21 +673,31 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="4" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="4" fillId="4" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="4" fillId="4" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="4" fillId="4" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="1" fillId="0" borderId="31" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="2" borderId="31" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="1" fillId="2" borderId="12" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="1" fillId="2" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="1" fillId="2" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="1" fillId="0" borderId="29" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="1" fillId="2" borderId="32" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="1" fillId="0" borderId="30" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="21" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="21" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="1" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="0" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2116,11 +2116,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="5.796875"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="12.796875"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="16.33203125"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="19"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="17.53125"/>
+    <col bestFit="1" customWidth="1" min="1" max="5" width="9.00390625"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.65">
@@ -2128,120 +2124,122 @@
         <v>0</v>
       </c>
       <c r="B1" s="74" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C1" s="74" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D1" s="75" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E1" s="76" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" ht="14.65">
-      <c r="A2" s="4">
+      <c r="A2" s="77">
         <v>0.10000000000000001</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="9">
         <v>1.25</v>
       </c>
-      <c r="C2" s="51">
-        <f t="shared" ref="C2:C7" si="5">$E$2-B2</f>
+      <c r="C2" s="54">
+        <f>$E$2-B2</f>
         <v>2.0000000000000018e-002</v>
       </c>
-      <c r="D2" s="52">
-        <f t="shared" ref="D2:D7" si="6">0.01*SQRT(2)</f>
+      <c r="D2" s="65">
+        <f>0.01*SQRT(2)</f>
         <v>1.4142135623730952e-002</v>
       </c>
-      <c r="E2" s="77">
+      <c r="E2" s="10">
         <v>1.27</v>
       </c>
     </row>
     <row r="3" ht="14.65">
-      <c r="A3" s="46">
+      <c r="A3" s="77">
         <v>0.20000000000000001</v>
       </c>
       <c r="B3" s="9">
         <v>1.23</v>
       </c>
-      <c r="C3" s="13">
-        <f t="shared" si="5"/>
+      <c r="C3" s="54">
+        <f>$E$2-B3</f>
         <v>4.0000000000000036e-002</v>
       </c>
-      <c r="D3" s="55">
-        <f t="shared" si="6"/>
+      <c r="D3" s="65">
+        <f>0.01*SQRT(2)</f>
         <v>1.4142135623730952e-002</v>
       </c>
-      <c r="E3" s="76" t="s">
-        <v>16</v>
+      <c r="E3" s="78" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="4" ht="14.65">
-      <c r="A4" s="46">
+      <c r="A4" s="77">
         <v>0.5</v>
       </c>
       <c r="B4" s="9">
         <v>1.1799999999999999</v>
       </c>
-      <c r="C4" s="13">
-        <f t="shared" si="5"/>
+      <c r="C4" s="54">
+        <f>$E$2-B4</f>
         <v>9.000000000000008e-002</v>
       </c>
-      <c r="D4" s="55">
-        <f t="shared" si="6"/>
+      <c r="D4" s="65">
+        <f>0.01*SQRT(2)</f>
         <v>1.4142135623730952e-002</v>
       </c>
-      <c r="E4" s="53">
+      <c r="E4" s="7">
         <v>1.e-002</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="46">
+      <c r="A5" s="77">
         <v>0.69999999999999996</v>
       </c>
       <c r="B5" s="9">
         <v>1.1499999999999999</v>
       </c>
-      <c r="C5" s="13">
-        <f t="shared" si="5"/>
+      <c r="C5" s="54">
+        <f>$E$2-B5</f>
         <v>0.12000000000000011</v>
       </c>
-      <c r="D5" s="55">
-        <f t="shared" si="6"/>
+      <c r="D5" s="65">
+        <f>0.01*SQRT(2)</f>
         <v>1.4142135623730952e-002</v>
       </c>
+      <c r="E5" s="13"/>
     </row>
     <row r="6">
-      <c r="A6" s="46">
+      <c r="A6" s="77">
         <v>0.90000000000000002</v>
       </c>
       <c r="B6" s="9">
         <v>1.1200000000000001</v>
       </c>
-      <c r="C6" s="13">
-        <f t="shared" si="5"/>
+      <c r="C6" s="54">
+        <f>$E$2-B6</f>
         <v>0.14999999999999991</v>
       </c>
-      <c r="D6" s="55">
-        <f t="shared" si="6"/>
+      <c r="D6" s="65">
+        <f>0.01*SQRT(2)</f>
         <v>1.4142135623730952e-002</v>
       </c>
+      <c r="E6" s="13"/>
     </row>
     <row r="7" ht="14.65">
-      <c r="A7" s="49">
+      <c r="A7" s="79">
         <v>1</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="80">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C7" s="56">
-        <f t="shared" si="5"/>
+      <c r="C7" s="81">
+        <f>$E$2-B7</f>
         <v>0.16999999999999993</v>
       </c>
-      <c r="D7" s="57">
-        <f t="shared" si="6"/>
+      <c r="D7" s="70">
+        <f>0.01*SQRT(2)</f>
         <v>1.4142135623730952e-002</v>
       </c>
     </row>
@@ -2268,18 +2266,18 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.5">
-      <c r="A1" s="78" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="78" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" s="79" t="s">
-        <v>19</v>
+      <c r="A1" s="82" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="82" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="83" t="s">
+        <v>14</v>
       </c>
       <c r="D1" s="71"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="84"/>
       <c r="G1" s="9"/>
     </row>
     <row r="2">
@@ -2292,9 +2290,9 @@
       <c r="C2">
         <v>0</v>
       </c>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
     </row>
     <row r="3">
       <c r="A3" s="9">
@@ -2306,9 +2304,9 @@
       <c r="C3">
         <v>1.e-002</v>
       </c>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="85"/>
     </row>
     <row r="4">
       <c r="A4" s="9">
@@ -2320,9 +2318,9 @@
       <c r="C4">
         <v>2.e-002</v>
       </c>
-      <c r="D4" s="81"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="81"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="85"/>
     </row>
     <row r="5">
       <c r="A5" s="9">
@@ -2334,9 +2332,9 @@
       <c r="C5">
         <v>2.9999999999999999e-002</v>
       </c>
-      <c r="D5" s="81"/>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
+      <c r="D5" s="85"/>
+      <c r="E5" s="85"/>
+      <c r="F5" s="85"/>
     </row>
     <row r="6">
       <c r="A6" s="9">
@@ -2348,9 +2346,9 @@
       <c r="C6">
         <v>4.0000000000000001e-002</v>
       </c>
-      <c r="D6" s="81"/>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
+      <c r="D6" s="85"/>
+      <c r="E6" s="85"/>
+      <c r="F6" s="85"/>
     </row>
     <row r="7">
       <c r="A7" s="9">
@@ -2362,9 +2360,9 @@
       <c r="C7">
         <v>5.0000000000000003e-002</v>
       </c>
-      <c r="D7" s="81"/>
-      <c r="E7" s="81"/>
-      <c r="F7" s="81"/>
+      <c r="D7" s="85"/>
+      <c r="E7" s="85"/>
+      <c r="F7" s="85"/>
     </row>
     <row r="8">
       <c r="A8" s="9">
@@ -2376,9 +2374,9 @@
       <c r="C8">
         <v>5.9999999999999998e-002</v>
       </c>
-      <c r="D8" s="81"/>
-      <c r="E8" s="81"/>
-      <c r="F8" s="81"/>
+      <c r="D8" s="85"/>
+      <c r="E8" s="85"/>
+      <c r="F8" s="85"/>
     </row>
     <row r="9">
       <c r="A9" s="9">
@@ -2390,9 +2388,9 @@
       <c r="C9">
         <v>5.9999999999999998e-002</v>
       </c>
-      <c r="D9" s="81"/>
-      <c r="E9" s="81"/>
-      <c r="F9" s="81"/>
+      <c r="D9" s="85"/>
+      <c r="E9" s="85"/>
+      <c r="F9" s="85"/>
     </row>
     <row r="10">
       <c r="A10" s="9">
@@ -2404,9 +2402,9 @@
       <c r="C10">
         <v>7.0000000000000007e-002</v>
       </c>
-      <c r="D10" s="81"/>
-      <c r="E10" s="81"/>
-      <c r="F10" s="81"/>
+      <c r="D10" s="85"/>
+      <c r="E10" s="85"/>
+      <c r="F10" s="85"/>
     </row>
     <row r="11">
       <c r="A11" s="9">
@@ -2418,9 +2416,9 @@
       <c r="C11">
         <v>7.0000000000000007e-002</v>
       </c>
-      <c r="D11" s="81"/>
-      <c r="E11" s="81"/>
-      <c r="F11" s="81"/>
+      <c r="D11" s="85"/>
+      <c r="E11" s="85"/>
+      <c r="F11" s="85"/>
     </row>
     <row r="12">
       <c r="A12" s="9">
@@ -2432,9 +2430,9 @@
       <c r="C12">
         <v>5.9999999999999998e-002</v>
       </c>
-      <c r="D12" s="81"/>
-      <c r="E12" s="81"/>
-      <c r="F12" s="81"/>
+      <c r="D12" s="85"/>
+      <c r="E12" s="85"/>
+      <c r="F12" s="85"/>
     </row>
     <row r="13">
       <c r="A13" s="9">
@@ -2446,9 +2444,9 @@
       <c r="C13">
         <v>5.9999999999999998e-002</v>
       </c>
-      <c r="D13" s="81"/>
-      <c r="E13" s="81"/>
-      <c r="F13" s="81"/>
+      <c r="D13" s="85"/>
+      <c r="E13" s="85"/>
+      <c r="F13" s="85"/>
     </row>
     <row r="14">
       <c r="A14" s="9">
@@ -2460,9 +2458,9 @@
       <c r="C14">
         <v>5.9999999999999998e-002</v>
       </c>
-      <c r="D14" s="81"/>
-      <c r="E14" s="81"/>
-      <c r="F14" s="81"/>
+      <c r="D14" s="85"/>
+      <c r="E14" s="85"/>
+      <c r="F14" s="85"/>
     </row>
     <row r="15">
       <c r="A15" s="9">
@@ -2474,9 +2472,9 @@
       <c r="C15">
         <v>5.0000000000000003e-002</v>
       </c>
-      <c r="D15" s="81"/>
-      <c r="E15" s="81"/>
-      <c r="F15" s="81"/>
+      <c r="D15" s="85"/>
+      <c r="E15" s="85"/>
+      <c r="F15" s="85"/>
     </row>
     <row r="16">
       <c r="A16" s="9">
@@ -2488,9 +2486,9 @@
       <c r="C16">
         <v>5.0000000000000003e-002</v>
       </c>
-      <c r="D16" s="81"/>
-      <c r="E16" s="81"/>
-      <c r="F16" s="81"/>
+      <c r="D16" s="85"/>
+      <c r="E16" s="85"/>
+      <c r="F16" s="85"/>
     </row>
     <row r="17">
       <c r="A17" s="9">
@@ -2502,9 +2500,9 @@
       <c r="C17">
         <v>4.0000000000000001e-002</v>
       </c>
-      <c r="D17" s="81"/>
-      <c r="E17" s="81"/>
-      <c r="F17" s="81"/>
+      <c r="D17" s="85"/>
+      <c r="E17" s="85"/>
+      <c r="F17" s="85"/>
     </row>
     <row r="18">
       <c r="A18" s="9">
@@ -2516,9 +2514,9 @@
       <c r="C18">
         <v>2.9999999999999999e-002</v>
       </c>
-      <c r="D18" s="81"/>
-      <c r="E18" s="81"/>
-      <c r="F18" s="81"/>
+      <c r="D18" s="85"/>
+      <c r="E18" s="85"/>
+      <c r="F18" s="85"/>
     </row>
     <row r="19">
       <c r="A19" s="9">
@@ -2530,9 +2528,9 @@
       <c r="C19">
         <v>2.e-002</v>
       </c>
-      <c r="D19" s="81"/>
-      <c r="E19" s="81"/>
-      <c r="F19" s="81"/>
+      <c r="D19" s="85"/>
+      <c r="E19" s="85"/>
+      <c r="F19" s="85"/>
     </row>
     <row r="20">
       <c r="A20" s="9">
@@ -2544,9 +2542,9 @@
       <c r="C20">
         <v>1.e-002</v>
       </c>
-      <c r="D20" s="81"/>
-      <c r="E20" s="81"/>
-      <c r="F20" s="81"/>
+      <c r="D20" s="85"/>
+      <c r="E20" s="85"/>
+      <c r="F20" s="85"/>
     </row>
     <row r="21">
       <c r="A21" s="9">
@@ -2558,9 +2556,9 @@
       <c r="C21">
         <v>-1.e-002</v>
       </c>
-      <c r="D21" s="81"/>
-      <c r="E21" s="81"/>
-      <c r="F21" s="81"/>
+      <c r="D21" s="85"/>
+      <c r="E21" s="85"/>
+      <c r="F21" s="85"/>
     </row>
     <row r="22">
       <c r="A22" s="9">
@@ -2572,9 +2570,9 @@
       <c r="C22">
         <v>-2.e-002</v>
       </c>
-      <c r="D22" s="81"/>
-      <c r="E22" s="81"/>
-      <c r="F22" s="81"/>
+      <c r="D22" s="85"/>
+      <c r="E22" s="85"/>
+      <c r="F22" s="85"/>
     </row>
     <row r="23">
       <c r="A23" s="9">
@@ -2586,9 +2584,9 @@
       <c r="C23">
         <v>-2.e-002</v>
       </c>
-      <c r="D23" s="81"/>
-      <c r="E23" s="81"/>
-      <c r="F23" s="81"/>
+      <c r="D23" s="85"/>
+      <c r="E23" s="85"/>
+      <c r="F23" s="85"/>
     </row>
     <row r="24">
       <c r="A24" s="9">
@@ -2600,9 +2598,9 @@
       <c r="C24">
         <v>-2.9999999999999999e-002</v>
       </c>
-      <c r="D24" s="81"/>
-      <c r="E24" s="81"/>
-      <c r="F24" s="81"/>
+      <c r="D24" s="85"/>
+      <c r="E24" s="85"/>
+      <c r="F24" s="85"/>
     </row>
     <row r="25">
       <c r="A25" s="9">
@@ -2614,9 +2612,9 @@
       <c r="C25">
         <v>-4.0000000000000001e-002</v>
       </c>
-      <c r="D25" s="81"/>
-      <c r="E25" s="81"/>
-      <c r="F25" s="81"/>
+      <c r="D25" s="85"/>
+      <c r="E25" s="85"/>
+      <c r="F25" s="85"/>
     </row>
     <row r="26">
       <c r="A26" s="9">
@@ -2658,7 +2656,7 @@
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
-      <c r="F28" s="82"/>
+      <c r="F28" s="86"/>
     </row>
     <row r="29">
       <c r="A29" s="9">
@@ -3714,11 +3712,11 @@
       <c r="A169" s="9"/>
       <c r="B169" s="9"/>
       <c r="D169" s="9"/>
-      <c r="E169" s="82"/>
+      <c r="E169" s="86"/>
       <c r="F169" s="9"/>
     </row>
     <row r="170">
-      <c r="A170" s="82"/>
+      <c r="A170" s="86"/>
       <c r="B170" s="9"/>
       <c r="D170" s="9"/>
       <c r="E170" s="9"/>
@@ -3847,11 +3845,11 @@
       <c r="A188" s="9"/>
       <c r="B188" s="9"/>
       <c r="D188" s="9"/>
-      <c r="E188" s="82"/>
+      <c r="E188" s="86"/>
       <c r="F188" s="9"/>
     </row>
     <row r="189">
-      <c r="A189" s="82"/>
+      <c r="A189" s="86"/>
       <c r="B189" s="9"/>
       <c r="D189" s="9"/>
       <c r="E189" s="9"/>
@@ -4037,7 +4035,7 @@
       <c r="B215" s="9"/>
       <c r="D215" s="9"/>
       <c r="E215" s="9"/>
-      <c r="F215" s="82"/>
+      <c r="F215" s="86"/>
     </row>
     <row r="216">
       <c r="A216" s="9"/>
@@ -4239,11 +4237,11 @@
       <c r="A244" s="9"/>
       <c r="B244" s="9"/>
       <c r="D244" s="9"/>
-      <c r="E244" s="82"/>
+      <c r="E244" s="86"/>
       <c r="F244" s="9"/>
     </row>
     <row r="245">
-      <c r="A245" s="82"/>
+      <c r="A245" s="86"/>
       <c r="B245" s="9"/>
       <c r="D245" s="9"/>
       <c r="E245" s="9"/>
@@ -4631,11 +4629,11 @@
       <c r="A300" s="9"/>
       <c r="B300" s="9"/>
       <c r="D300" s="9"/>
-      <c r="E300" s="82"/>
+      <c r="E300" s="86"/>
       <c r="F300" s="9"/>
     </row>
     <row r="301">
-      <c r="A301" s="82"/>
+      <c r="A301" s="86"/>
       <c r="B301" s="9"/>
       <c r="D301" s="9"/>
       <c r="E301" s="9"/>
@@ -4688,7 +4686,7 @@
       <c r="B308" s="9"/>
       <c r="D308" s="9"/>
       <c r="E308" s="9"/>
-      <c r="F308" s="82"/>
+      <c r="F308" s="86"/>
     </row>
     <row r="309">
       <c r="A309" s="9"/>
@@ -4764,11 +4762,11 @@
       <c r="A319" s="9"/>
       <c r="B319" s="9"/>
       <c r="D319" s="9"/>
-      <c r="E319" s="82"/>
+      <c r="E319" s="86"/>
       <c r="F319" s="9"/>
     </row>
     <row r="320">
-      <c r="A320" s="82"/>
+      <c r="A320" s="86"/>
       <c r="B320" s="9"/>
       <c r="D320" s="9"/>
       <c r="E320" s="9"/>
@@ -4897,11 +4895,11 @@
       <c r="A338" s="9"/>
       <c r="B338" s="9"/>
       <c r="D338" s="9"/>
-      <c r="E338" s="82"/>
+      <c r="E338" s="86"/>
       <c r="F338" s="9"/>
     </row>
     <row r="339">
-      <c r="A339" s="82"/>
+      <c r="A339" s="86"/>
       <c r="B339" s="9"/>
       <c r="D339" s="9"/>
       <c r="E339" s="9"/>

--- a/Legge di Hooke.xlsx
+++ b/Legge di Hooke.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="5"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Misure statiche 1" sheetId="1" state="visible" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>m[kg]</t>
   </si>
@@ -63,13 +63,10 @@
     <t>σω_</t>
   </si>
   <si>
-    <t xml:space="preserve">t1 (s) Set</t>
+    <t xml:space="preserve">t [s]</t>
   </si>
   <si>
-    <t xml:space="preserve">x (m) Set</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v (m/s) Set</t>
+    <t xml:space="preserve">v [m]</t>
   </si>
 </sst>
 </file>
@@ -112,7 +109,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -129,11 +126,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
         <bgColor rgb="FFFFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="5"/>
       </patternFill>
     </fill>
   </fills>
@@ -519,7 +511,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="90">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="1" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -690,11 +682,17 @@
     <xf fontId="1" fillId="0" borderId="21" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="1" fillId="2" borderId="31" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
+    <xf fontId="1" fillId="2" borderId="12" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="13" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="29" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -703,6 +701,7 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="22" numFmtId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1836,7 +1835,7 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="5" width="8.125"/>
-    <col bestFit="1" customWidth="1" min="6" max="6" width="14"/>
+    <col bestFit="1" customWidth="1" min="6" max="6" width="9.00390625"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.65">
@@ -2260,370 +2259,369 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="7.33203125"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="7.1328125"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="11.46484375"/>
+    <col bestFit="1" customWidth="1" min="1" max="1" width="7.54296875"/>
+    <col customWidth="1" min="2" max="3" width="8.125"/>
   </cols>
   <sheetData>
     <row r="1" ht="25.5">
       <c r="A1" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="82" t="s">
+      <c r="B1" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="84" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="83" t="s">
-        <v>14</v>
-      </c>
       <c r="D1" s="71"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
       <c r="G1" s="9"/>
     </row>
     <row r="2">
-      <c r="A2" s="13">
+      <c r="A2" s="86">
         <v>2.2400000000000002</v>
       </c>
       <c r="B2" s="9">
         <v>1.1223000000000001</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="23">
         <v>0</v>
       </c>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
     </row>
     <row r="3">
-      <c r="A3" s="9">
+      <c r="A3" s="64">
         <v>2.2599999999999998</v>
       </c>
       <c r="B3" s="9">
         <v>1.1224000000000001</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="23">
         <v>1.e-002</v>
       </c>
-      <c r="D3" s="85"/>
-      <c r="E3" s="85"/>
-      <c r="F3" s="85"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
     </row>
     <row r="4">
-      <c r="A4" s="9">
+      <c r="A4" s="64">
         <v>2.2799999999999998</v>
       </c>
       <c r="B4" s="9">
         <v>1.1227</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="23">
         <v>2.e-002</v>
       </c>
-      <c r="D4" s="85"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="85"/>
+      <c r="D4" s="87"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
     </row>
     <row r="5">
-      <c r="A5" s="9">
+      <c r="A5" s="64">
         <v>2.2999999999999998</v>
       </c>
       <c r="B5" s="9">
         <v>1.1234</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="23">
         <v>2.9999999999999999e-002</v>
       </c>
-      <c r="D5" s="85"/>
-      <c r="E5" s="85"/>
-      <c r="F5" s="85"/>
+      <c r="D5" s="87"/>
+      <c r="E5" s="87"/>
+      <c r="F5" s="87"/>
     </row>
     <row r="6">
-      <c r="A6" s="9">
+      <c r="A6" s="64">
         <v>2.3199999999999998</v>
       </c>
       <c r="B6" s="9">
         <v>1.1241000000000001</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="23">
         <v>4.0000000000000001e-002</v>
       </c>
-      <c r="D6" s="85"/>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
+      <c r="D6" s="87"/>
+      <c r="E6" s="87"/>
+      <c r="F6" s="87"/>
     </row>
     <row r="7">
-      <c r="A7" s="9">
+      <c r="A7" s="64">
         <v>2.3399999999999999</v>
       </c>
       <c r="B7" s="9">
         <v>1.1249</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="23">
         <v>5.0000000000000003e-002</v>
       </c>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="85"/>
+      <c r="D7" s="87"/>
+      <c r="E7" s="87"/>
+      <c r="F7" s="87"/>
     </row>
     <row r="8">
-      <c r="A8" s="9">
+      <c r="A8" s="64">
         <v>2.3599999999999999</v>
       </c>
       <c r="B8" s="9">
         <v>1.1258999999999999</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="23">
         <v>5.9999999999999998e-002</v>
       </c>
-      <c r="D8" s="85"/>
-      <c r="E8" s="85"/>
-      <c r="F8" s="85"/>
+      <c r="D8" s="87"/>
+      <c r="E8" s="87"/>
+      <c r="F8" s="87"/>
     </row>
     <row r="9">
-      <c r="A9" s="9">
+      <c r="A9" s="64">
         <v>2.3799999999999999</v>
       </c>
       <c r="B9" s="9">
         <v>1.1273</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="23">
         <v>5.9999999999999998e-002</v>
       </c>
-      <c r="D9" s="85"/>
-      <c r="E9" s="85"/>
-      <c r="F9" s="85"/>
+      <c r="D9" s="87"/>
+      <c r="E9" s="87"/>
+      <c r="F9" s="87"/>
     </row>
     <row r="10">
-      <c r="A10" s="9">
+      <c r="A10" s="64">
         <v>2.3999999999999999</v>
       </c>
       <c r="B10" s="9">
         <v>1.1284000000000001</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="23">
         <v>7.0000000000000007e-002</v>
       </c>
-      <c r="D10" s="85"/>
-      <c r="E10" s="85"/>
-      <c r="F10" s="85"/>
+      <c r="D10" s="87"/>
+      <c r="E10" s="87"/>
+      <c r="F10" s="87"/>
     </row>
     <row r="11">
-      <c r="A11" s="9">
+      <c r="A11" s="64">
         <v>2.4199999999999999</v>
       </c>
       <c r="B11" s="9">
         <v>1.1299999999999999</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="23">
         <v>7.0000000000000007e-002</v>
       </c>
-      <c r="D11" s="85"/>
-      <c r="E11" s="85"/>
-      <c r="F11" s="85"/>
+      <c r="D11" s="87"/>
+      <c r="E11" s="87"/>
+      <c r="F11" s="87"/>
     </row>
     <row r="12">
-      <c r="A12" s="9">
+      <c r="A12" s="64">
         <v>2.4399999999999999</v>
       </c>
       <c r="B12" s="9">
         <v>1.131</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="23">
         <v>5.9999999999999998e-002</v>
       </c>
-      <c r="D12" s="85"/>
-      <c r="E12" s="85"/>
-      <c r="F12" s="85"/>
+      <c r="D12" s="87"/>
+      <c r="E12" s="87"/>
+      <c r="F12" s="87"/>
     </row>
     <row r="13">
-      <c r="A13" s="9">
+      <c r="A13" s="64">
         <v>2.46</v>
       </c>
       <c r="B13" s="9">
         <v>1.1326000000000001</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="23">
         <v>5.9999999999999998e-002</v>
       </c>
-      <c r="D13" s="85"/>
-      <c r="E13" s="85"/>
-      <c r="F13" s="85"/>
+      <c r="D13" s="87"/>
+      <c r="E13" s="87"/>
+      <c r="F13" s="87"/>
     </row>
     <row r="14">
-      <c r="A14" s="9">
+      <c r="A14" s="64">
         <v>2.48</v>
       </c>
       <c r="B14" s="9">
         <v>1.1335999999999999</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="23">
         <v>5.9999999999999998e-002</v>
       </c>
-      <c r="D14" s="85"/>
-      <c r="E14" s="85"/>
-      <c r="F14" s="85"/>
+      <c r="D14" s="87"/>
+      <c r="E14" s="87"/>
+      <c r="F14" s="87"/>
     </row>
     <row r="15">
-      <c r="A15" s="9">
+      <c r="A15" s="64">
         <v>2.5</v>
       </c>
       <c r="B15" s="9">
         <v>1.1349</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="23">
         <v>5.0000000000000003e-002</v>
       </c>
-      <c r="D15" s="85"/>
-      <c r="E15" s="85"/>
-      <c r="F15" s="85"/>
+      <c r="D15" s="87"/>
+      <c r="E15" s="87"/>
+      <c r="F15" s="87"/>
     </row>
     <row r="16">
-      <c r="A16" s="9">
+      <c r="A16" s="64">
         <v>2.52</v>
       </c>
       <c r="B16" s="9">
         <v>1.1358999999999999</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="23">
         <v>5.0000000000000003e-002</v>
       </c>
-      <c r="D16" s="85"/>
-      <c r="E16" s="85"/>
-      <c r="F16" s="85"/>
+      <c r="D16" s="87"/>
+      <c r="E16" s="87"/>
+      <c r="F16" s="87"/>
     </row>
     <row r="17">
-      <c r="A17" s="9">
+      <c r="A17" s="64">
         <v>2.54</v>
       </c>
       <c r="B17" s="9">
         <v>1.1368</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="23">
         <v>4.0000000000000001e-002</v>
       </c>
-      <c r="D17" s="85"/>
-      <c r="E17" s="85"/>
-      <c r="F17" s="85"/>
+      <c r="D17" s="87"/>
+      <c r="E17" s="87"/>
+      <c r="F17" s="87"/>
     </row>
     <row r="18">
-      <c r="A18" s="9">
+      <c r="A18" s="64">
         <v>2.5600000000000001</v>
       </c>
       <c r="B18" s="9">
         <v>1.1374</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="23">
         <v>2.9999999999999999e-002</v>
       </c>
-      <c r="D18" s="85"/>
-      <c r="E18" s="85"/>
-      <c r="F18" s="85"/>
+      <c r="D18" s="87"/>
+      <c r="E18" s="87"/>
+      <c r="F18" s="87"/>
     </row>
     <row r="19">
-      <c r="A19" s="9">
+      <c r="A19" s="64">
         <v>2.5800000000000001</v>
       </c>
       <c r="B19" s="9">
         <v>1.1378999999999999</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="23">
         <v>2.e-002</v>
       </c>
-      <c r="D19" s="85"/>
-      <c r="E19" s="85"/>
-      <c r="F19" s="85"/>
+      <c r="D19" s="87"/>
+      <c r="E19" s="87"/>
+      <c r="F19" s="87"/>
     </row>
     <row r="20">
-      <c r="A20" s="9">
+      <c r="A20" s="64">
         <v>2.6000000000000001</v>
       </c>
       <c r="B20" s="9">
         <v>1.1380999999999999</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="23">
         <v>1.e-002</v>
       </c>
-      <c r="D20" s="85"/>
-      <c r="E20" s="85"/>
-      <c r="F20" s="85"/>
+      <c r="D20" s="87"/>
+      <c r="E20" s="87"/>
+      <c r="F20" s="87"/>
     </row>
     <row r="21">
-      <c r="A21" s="9">
+      <c r="A21" s="64">
         <v>2.6200000000000001</v>
       </c>
       <c r="B21" s="9">
         <v>1.1382000000000001</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="23">
         <v>-1.e-002</v>
       </c>
-      <c r="D21" s="85"/>
-      <c r="E21" s="85"/>
-      <c r="F21" s="85"/>
+      <c r="D21" s="87"/>
+      <c r="E21" s="87"/>
+      <c r="F21" s="87"/>
     </row>
     <row r="22">
-      <c r="A22" s="9">
+      <c r="A22" s="64">
         <v>2.6400000000000001</v>
       </c>
       <c r="B22" s="9">
         <v>1.1377999999999999</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="23">
         <v>-2.e-002</v>
       </c>
-      <c r="D22" s="85"/>
-      <c r="E22" s="85"/>
-      <c r="F22" s="85"/>
+      <c r="D22" s="87"/>
+      <c r="E22" s="87"/>
+      <c r="F22" s="87"/>
     </row>
     <row r="23">
-      <c r="A23" s="9">
+      <c r="A23" s="64">
         <v>2.6600000000000001</v>
       </c>
       <c r="B23" s="9">
         <v>1.1375</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="23">
         <v>-2.e-002</v>
       </c>
-      <c r="D23" s="85"/>
-      <c r="E23" s="85"/>
-      <c r="F23" s="85"/>
+      <c r="D23" s="87"/>
+      <c r="E23" s="87"/>
+      <c r="F23" s="87"/>
     </row>
     <row r="24">
-      <c r="A24" s="9">
+      <c r="A24" s="64">
         <v>2.6800000000000002</v>
       </c>
       <c r="B24" s="9">
         <v>1.1368</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="23">
         <v>-2.9999999999999999e-002</v>
       </c>
-      <c r="D24" s="85"/>
-      <c r="E24" s="85"/>
-      <c r="F24" s="85"/>
+      <c r="D24" s="87"/>
+      <c r="E24" s="87"/>
+      <c r="F24" s="87"/>
     </row>
     <row r="25">
-      <c r="A25" s="9">
+      <c r="A25" s="64">
         <v>2.7000000000000002</v>
       </c>
       <c r="B25" s="9">
         <v>1.1365000000000001</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="23">
         <v>-4.0000000000000001e-002</v>
       </c>
-      <c r="D25" s="85"/>
-      <c r="E25" s="85"/>
-      <c r="F25" s="85"/>
+      <c r="D25" s="87"/>
+      <c r="E25" s="87"/>
+      <c r="F25" s="87"/>
     </row>
     <row r="26">
-      <c r="A26" s="9">
+      <c r="A26" s="64">
         <v>2.7200000000000002</v>
       </c>
       <c r="B26" s="9">
         <v>1.135</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="23">
         <v>-5.0000000000000003e-002</v>
       </c>
       <c r="D26" s="9"/>
@@ -2631,13 +2629,13 @@
       <c r="F26" s="9"/>
     </row>
     <row r="27">
-      <c r="A27" s="9">
+      <c r="A27" s="64">
         <v>2.7400000000000002</v>
       </c>
       <c r="B27" s="9">
         <v>1.1339999999999999</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="23">
         <v>-5.9999999999999998e-002</v>
       </c>
       <c r="D27" s="9"/>
@@ -2645,27 +2643,27 @@
       <c r="F27" s="9"/>
     </row>
     <row r="28">
-      <c r="A28" s="9">
+      <c r="A28" s="64">
         <v>2.7599999999999998</v>
       </c>
       <c r="B28" s="9">
         <v>1.1331</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="23">
         <v>-5.9999999999999998e-002</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
-      <c r="F28" s="86"/>
+      <c r="F28" s="88"/>
     </row>
     <row r="29">
-      <c r="A29" s="9">
+      <c r="A29" s="64">
         <v>2.7799999999999998</v>
       </c>
       <c r="B29" s="9">
         <v>1.1312</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="23">
         <v>-7.0000000000000007e-002</v>
       </c>
       <c r="D29" s="9"/>
@@ -2673,13 +2671,13 @@
       <c r="F29" s="9"/>
     </row>
     <row r="30">
-      <c r="A30" s="9">
+      <c r="A30" s="64">
         <v>2.7999999999999998</v>
       </c>
       <c r="B30" s="9">
         <v>1.1303000000000001</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="23">
         <v>-7.0000000000000007e-002</v>
       </c>
       <c r="D30" s="9"/>
@@ -2687,13 +2685,13 @@
       <c r="F30" s="9"/>
     </row>
     <row r="31">
-      <c r="A31" s="9">
+      <c r="A31" s="64">
         <v>2.8199999999999998</v>
       </c>
       <c r="B31" s="9">
         <v>1.1287</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="23">
         <v>-5.9999999999999998e-002</v>
       </c>
       <c r="D31" s="9"/>
@@ -2701,13 +2699,13 @@
       <c r="F31" s="9"/>
     </row>
     <row r="32">
-      <c r="A32" s="9">
+      <c r="A32" s="64">
         <v>2.8399999999999999</v>
       </c>
       <c r="B32" s="9">
         <v>1.1274999999999999</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="23">
         <v>-7.0000000000000007e-002</v>
       </c>
       <c r="D32" s="9"/>
@@ -2715,13 +2713,13 @@
       <c r="F32" s="9"/>
     </row>
     <row r="33">
-      <c r="A33" s="9">
+      <c r="A33" s="64">
         <v>2.8599999999999999</v>
       </c>
       <c r="B33" s="9">
         <v>1.1263000000000001</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="23">
         <v>-5.9999999999999998e-002</v>
       </c>
       <c r="D33" s="9"/>
@@ -2729,13 +2727,13 @@
       <c r="F33" s="9"/>
     </row>
     <row r="34">
-      <c r="A34" s="9">
+      <c r="A34" s="64">
         <v>2.8799999999999999</v>
       </c>
       <c r="B34" s="9">
         <v>1.1248</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="23">
         <v>-5.0000000000000003e-002</v>
       </c>
       <c r="D34" s="9"/>
@@ -2743,13 +2741,13 @@
       <c r="F34" s="9"/>
     </row>
     <row r="35">
-      <c r="A35" s="9">
+      <c r="A35" s="64">
         <v>2.8999999999999999</v>
       </c>
       <c r="B35" s="9">
         <v>1.1242000000000001</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="23">
         <v>-4.0000000000000001e-002</v>
       </c>
       <c r="D35" s="9"/>
@@ -2757,13 +2755,13 @@
       <c r="F35" s="9"/>
     </row>
     <row r="36">
-      <c r="A36" s="9">
+      <c r="A36" s="64">
         <v>2.9199999999999999</v>
       </c>
       <c r="B36" s="9">
         <v>1.1233</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="23">
         <v>-4.0000000000000001e-002</v>
       </c>
       <c r="D36" s="9"/>
@@ -2771,13 +2769,13 @@
       <c r="F36" s="9"/>
     </row>
     <row r="37">
-      <c r="A37" s="9">
+      <c r="A37" s="64">
         <v>2.9399999999999999</v>
       </c>
       <c r="B37" s="9">
         <v>1.1225000000000001</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="23">
         <v>-2.9999999999999999e-002</v>
       </c>
       <c r="D37" s="9"/>
@@ -2785,13 +2783,13 @@
       <c r="F37" s="9"/>
     </row>
     <row r="38">
-      <c r="A38" s="9">
+      <c r="A38" s="67">
         <v>2.96</v>
       </c>
-      <c r="B38" s="9">
+      <c r="B38" s="68">
         <v>1.1222000000000001</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="89">
         <v>-2.e-002</v>
       </c>
       <c r="D38" s="9"/>
@@ -3712,11 +3710,11 @@
       <c r="A169" s="9"/>
       <c r="B169" s="9"/>
       <c r="D169" s="9"/>
-      <c r="E169" s="86"/>
+      <c r="E169" s="88"/>
       <c r="F169" s="9"/>
     </row>
     <row r="170">
-      <c r="A170" s="86"/>
+      <c r="A170" s="88"/>
       <c r="B170" s="9"/>
       <c r="D170" s="9"/>
       <c r="E170" s="9"/>
@@ -3845,11 +3843,11 @@
       <c r="A188" s="9"/>
       <c r="B188" s="9"/>
       <c r="D188" s="9"/>
-      <c r="E188" s="86"/>
+      <c r="E188" s="88"/>
       <c r="F188" s="9"/>
     </row>
     <row r="189">
-      <c r="A189" s="86"/>
+      <c r="A189" s="88"/>
       <c r="B189" s="9"/>
       <c r="D189" s="9"/>
       <c r="E189" s="9"/>
@@ -4035,7 +4033,7 @@
       <c r="B215" s="9"/>
       <c r="D215" s="9"/>
       <c r="E215" s="9"/>
-      <c r="F215" s="86"/>
+      <c r="F215" s="88"/>
     </row>
     <row r="216">
       <c r="A216" s="9"/>
@@ -4237,11 +4235,11 @@
       <c r="A244" s="9"/>
       <c r="B244" s="9"/>
       <c r="D244" s="9"/>
-      <c r="E244" s="86"/>
+      <c r="E244" s="88"/>
       <c r="F244" s="9"/>
     </row>
     <row r="245">
-      <c r="A245" s="86"/>
+      <c r="A245" s="88"/>
       <c r="B245" s="9"/>
       <c r="D245" s="9"/>
       <c r="E245" s="9"/>
@@ -4629,11 +4627,11 @@
       <c r="A300" s="9"/>
       <c r="B300" s="9"/>
       <c r="D300" s="9"/>
-      <c r="E300" s="86"/>
+      <c r="E300" s="88"/>
       <c r="F300" s="9"/>
     </row>
     <row r="301">
-      <c r="A301" s="86"/>
+      <c r="A301" s="88"/>
       <c r="B301" s="9"/>
       <c r="D301" s="9"/>
       <c r="E301" s="9"/>
@@ -4686,7 +4684,7 @@
       <c r="B308" s="9"/>
       <c r="D308" s="9"/>
       <c r="E308" s="9"/>
-      <c r="F308" s="86"/>
+      <c r="F308" s="88"/>
     </row>
     <row r="309">
       <c r="A309" s="9"/>
@@ -4762,11 +4760,11 @@
       <c r="A319" s="9"/>
       <c r="B319" s="9"/>
       <c r="D319" s="9"/>
-      <c r="E319" s="86"/>
+      <c r="E319" s="88"/>
       <c r="F319" s="9"/>
     </row>
     <row r="320">
-      <c r="A320" s="86"/>
+      <c r="A320" s="88"/>
       <c r="B320" s="9"/>
       <c r="D320" s="9"/>
       <c r="E320" s="9"/>
@@ -4895,11 +4893,11 @@
       <c r="A338" s="9"/>
       <c r="B338" s="9"/>
       <c r="D338" s="9"/>
-      <c r="E338" s="86"/>
+      <c r="E338" s="88"/>
       <c r="F338" s="9"/>
     </row>
     <row r="339">
-      <c r="A339" s="86"/>
+      <c r="A339" s="88"/>
       <c r="B339" s="9"/>
       <c r="D339" s="9"/>
       <c r="E339" s="9"/>
